--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C6B781-4761-468B-BB8E-6DD82E426C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF411D8-99CA-47FB-83CB-2325842B1716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>categoria</t>
   </si>
@@ -40,34 +40,19 @@
     <t>valor da caixa</t>
   </si>
   <si>
-    <t>Doces</t>
-  </si>
-  <si>
-    <t>teste Doces</t>
-  </si>
-  <si>
-    <t>osmar</t>
-  </si>
-  <si>
-    <t>ração</t>
-  </si>
-  <si>
-    <t>teste de ração</t>
-  </si>
-  <si>
-    <t>Danilo</t>
-  </si>
-  <si>
     <t>Erva</t>
   </si>
   <si>
-    <t>teste de erva</t>
-  </si>
-  <si>
-    <t>valter</t>
-  </si>
-  <si>
     <t>Volume</t>
+  </si>
+  <si>
+    <t>0204010001</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Tradicional</t>
+  </si>
+  <si>
+    <t>Prioste</t>
   </si>
 </sst>
 </file>
@@ -551,8 +536,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -908,16 +894,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
@@ -936,76 +923,30 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>10</v>
+      <c r="A2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>15.8</v>
       </c>
       <c r="F2">
-        <v>151.19999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="G2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>25</v>
-      </c>
-      <c r="F3">
-        <v>250</v>
-      </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1000</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>332.55</v>
-      </c>
-      <c r="G4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF411D8-99CA-47FB-83CB-2325842B1716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F30D4AC-3C97-4314-8326-AC8EC9190BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>categoria</t>
   </si>
@@ -53,6 +53,54 @@
   </si>
   <si>
     <t>Prioste</t>
+  </si>
+  <si>
+    <t>0204010002</t>
+  </si>
+  <si>
+    <t>0204010003</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Pura Folha</t>
+  </si>
+  <si>
+    <t>0204010004</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Menta Limã</t>
+  </si>
+  <si>
+    <t>0204010005</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Limão Caipira</t>
+  </si>
+  <si>
+    <t>0204010006</t>
+  </si>
+  <si>
+    <t>0204010007</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Uva Menta</t>
+  </si>
+  <si>
+    <t>0204010008</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Pura Folha com Burrito</t>
+  </si>
+  <si>
+    <t>0204010009</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Cereja Menta</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g Erva Mate Menta Boldo</t>
+  </si>
+  <si>
+    <t>Ver SP270 500g  Erva Mate Ice Cross</t>
   </si>
 </sst>
 </file>
@@ -894,11 +942,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -949,6 +997,190 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>15.8</v>
+      </c>
+      <c r="F3">
+        <v>15.8</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>15.8</v>
+      </c>
+      <c r="F4">
+        <v>15.8</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>15.8</v>
+      </c>
+      <c r="F5">
+        <v>15.8</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>15.8</v>
+      </c>
+      <c r="F6">
+        <v>15.8</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>15.8</v>
+      </c>
+      <c r="F7">
+        <v>15.8</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>15.8</v>
+      </c>
+      <c r="F8">
+        <v>15.8</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>15.8</v>
+      </c>
+      <c r="F9">
+        <v>15.8</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>15.8</v>
+      </c>
+      <c r="F10">
+        <v>15.8</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F30D4AC-3C97-4314-8326-AC8EC9190BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DE793F-188C-4765-9217-25D305DB60F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>categoria</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>Ver SP270 500g  Erva Mate Ice Cross</t>
+  </si>
+  <si>
+    <t>0000000001</t>
+  </si>
+  <si>
+    <t>Aateste</t>
   </si>
 </sst>
 </file>
@@ -942,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1181,6 +1187,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DE793F-188C-4765-9217-25D305DB60F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07289EDB-45D4-4C24-99DB-6CB1053F001D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
   <si>
     <t>categoria</t>
   </si>
@@ -103,17 +103,92 @@
     <t>Ver SP270 500g  Erva Mate Ice Cross</t>
   </si>
   <si>
-    <t>0000000001</t>
-  </si>
-  <si>
-    <t>Aateste</t>
+    <t>0102020001</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 900g ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>0102020002</t>
+  </si>
+  <si>
+    <t>Osmar</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 900g ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 900g ALIM. PREM. ESP. P/CÃES FILHOTE CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 2,1Kg ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 2,1 Kg ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 6Kg ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 6Kg ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL 10,1 Kg ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>Pet PRFUL ALIM. PREM. ESP. P/ GATOS FILHOTE CARNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pet PRFUL ALIM. PREM. ESP. P/ GATOS CASTRADO SALMÃO </t>
+  </si>
+  <si>
+    <t>Pet PRFUL 900g ALIM. PREM. ESP. P/ GATOS ADULTO MIX CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>0102020003</t>
+  </si>
+  <si>
+    <t>0102020004</t>
+  </si>
+  <si>
+    <t>0102020005</t>
+  </si>
+  <si>
+    <t>0102020006</t>
+  </si>
+  <si>
+    <t>0102020007</t>
+  </si>
+  <si>
+    <t>0102020008</t>
+  </si>
+  <si>
+    <t>0102020009</t>
+  </si>
+  <si>
+    <t>0102020010</t>
+  </si>
+  <si>
+    <t>0102020011</t>
+  </si>
+  <si>
+    <t>0102020012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +319,17 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -546,7 +632,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -589,12 +675,18 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="47">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -624,8 +716,13 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Moeda 2" xfId="43" xr:uid="{0C61731C-E737-4A54-9036-17B400FE6FAB}"/>
+    <cellStyle name="Moeda 2 2" xfId="44" xr:uid="{AA48D0B9-D8DC-46BB-B1FE-5B9A19F2820B}"/>
+    <cellStyle name="Moeda 3" xfId="45" xr:uid="{93DB1087-9037-47BC-A973-7F702C06F25D}"/>
+    <cellStyle name="Moeda 4" xfId="42" xr:uid="{1C8828FA-3562-4784-8A96-D5F019290D09}"/>
     <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="46" xr:uid="{C9624187-4D6D-4DA3-8296-B84BDBB8444F}"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
@@ -948,11 +1045,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1194,23 +1291,272 @@
       <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>8.6</v>
+      </c>
+      <c r="F11">
+        <v>103.2</v>
+      </c>
+      <c r="G11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>8.6</v>
+      </c>
+      <c r="F12">
+        <v>103.2</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>9.27</v>
+      </c>
+      <c r="F13">
+        <v>111.2</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F14">
+        <v>103.56</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="2">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F15" s="2">
+        <v>103.56</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>31.65</v>
+      </c>
+      <c r="F16">
+        <v>31.65</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>31.65</v>
+      </c>
+      <c r="F17">
+        <v>31.65</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18">
+        <v>50.74</v>
+      </c>
+      <c r="F18">
+        <v>50.74</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19">
+        <v>50.74</v>
+      </c>
+      <c r="F19">
+        <v>50.74</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20">
+        <v>10.6</v>
+      </c>
+      <c r="F20">
+        <v>127.2</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="F21" s="2">
+        <v>127.2</v>
+      </c>
+      <c r="G21" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="F22" s="2">
+        <v>127.2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07289EDB-45D4-4C24-99DB-6CB1053F001D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2FA01C-1E7C-424E-976B-A617DC68B09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
   <si>
     <t>categoria</t>
   </si>
@@ -1524,6 +1524,9 @@
       <c r="C21" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
       <c r="E21" s="2">
         <v>10.6</v>
       </c>
@@ -1543,6 +1546,9 @@
       </c>
       <c r="C22" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>10.6</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2FA01C-1E7C-424E-976B-A617DC68B09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFEAFA6-A9DD-4562-9C0A-39B8D0367D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -100,9 +100,6 @@
     <t>Erv SP270 500g Erva Mate Menta Boldo</t>
   </si>
   <si>
-    <t>Ver SP270 500g  Erva Mate Ice Cross</t>
-  </si>
-  <si>
     <t>0102020001</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>0102020002</t>
   </si>
   <si>
-    <t>Osmar</t>
-  </si>
-  <si>
     <t>Pet PRFUL 900g ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
   </si>
   <si>
@@ -179,6 +173,12 @@
   </si>
   <si>
     <t>0102020012</t>
+  </si>
+  <si>
+    <t>Prime Full</t>
+  </si>
+  <si>
+    <t>Erv SP270 500g  Erva Mate Ice Cross</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1286,16 +1286,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>8.6</v>
@@ -1309,16 +1309,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E12">
         <v>8.6</v>
@@ -1332,16 +1332,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
         <v>32</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E13">
         <v>9.27</v>
@@ -1355,16 +1355,16 @@
     </row>
     <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E14">
         <v>17.260000000000002</v>
@@ -1378,16 +1378,16 @@
     </row>
     <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2">
         <v>17.260000000000002</v>
@@ -1401,16 +1401,16 @@
     </row>
     <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E16">
         <v>31.65</v>
@@ -1424,16 +1424,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E17">
         <v>31.65</v>
@@ -1447,16 +1447,16 @@
     </row>
     <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E18">
         <v>50.74</v>
@@ -1470,16 +1470,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E19">
         <v>50.74</v>
@@ -1493,16 +1493,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
+        <v>40</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E20">
         <v>10.6</v>
@@ -1516,16 +1516,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
       </c>
       <c r="E21" s="2">
         <v>10.6</v>
@@ -1539,16 +1539,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E22" s="2">
         <v>10.6</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFEAFA6-A9DD-4562-9C0A-39B8D0367D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268B503E-86D9-4D8A-BFB9-1E9E2473A30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
   <sheets>
     <sheet name="base_de_produtos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="144">
   <si>
     <t>categoria</t>
   </si>
@@ -100,85 +100,358 @@
     <t>Erv SP270 500g Erva Mate Menta Boldo</t>
   </si>
   <si>
-    <t>0102020001</t>
-  </si>
-  <si>
     <t>Pet</t>
   </si>
   <si>
-    <t>Pet PRFUL 900g ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>0102020002</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 900g ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 900g ALIM. PREM. ESP. P/CÃES FILHOTE CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 2,1Kg ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 2,1 Kg ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 6Kg ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 6Kg ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL 10,1 Kg ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>Pet PRFUL ALIM. PREM. ESP. P/ GATOS FILHOTE CARNE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pet PRFUL ALIM. PREM. ESP. P/ GATOS CASTRADO SALMÃO </t>
-  </si>
-  <si>
-    <t>Pet PRFUL 900g ALIM. PREM. ESP. P/ GATOS ADULTO MIX CARNE E FRANGO</t>
-  </si>
-  <si>
-    <t>0102020003</t>
-  </si>
-  <si>
-    <t>0102020004</t>
-  </si>
-  <si>
-    <t>0102020005</t>
-  </si>
-  <si>
-    <t>0102020006</t>
-  </si>
-  <si>
-    <t>0102020007</t>
-  </si>
-  <si>
-    <t>0102020008</t>
-  </si>
-  <si>
-    <t>0102020009</t>
-  </si>
-  <si>
-    <t>0102020010</t>
-  </si>
-  <si>
-    <t>0102020011</t>
-  </si>
-  <si>
-    <t>0102020012</t>
-  </si>
-  <si>
     <t>Prime Full</t>
   </si>
   <si>
     <t>Erv SP270 500g  Erva Mate Ice Cross</t>
+  </si>
+  <si>
+    <t>00000</t>
+  </si>
+  <si>
+    <t>Pet Var</t>
+  </si>
+  <si>
+    <t>20663</t>
+  </si>
+  <si>
+    <t>20977</t>
+  </si>
+  <si>
+    <t>20991</t>
+  </si>
+  <si>
+    <t>12529</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Alim.Prem. Esp.P/Cães Ad. Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Alim.Prem. Esp. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Alim. Prem. Esp. P/Cães Filhote Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1Kg Alim.Prem. Esp.P/Cães Ad. Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1 Kg Alim.Prem. Esp. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 6Kg Alim.Prem. Esp.P/Cães Ad. Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 6Kg Alim.Prem. Esp. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 10,1 Kg Alim.Prem. Esp.P/Cães Ad. Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful Alim.Prem. Esp. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Alim. Prem. Esp. P/ Gatos Adulto Mix Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Alim. Prem. Esp. P/ Gatos Filhote Carne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pet Prful 900G Alim. Prem. Esp. P/ Gatos Castrado Salmão </t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Cães Ad.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Cães Filh.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1Kg Honey Pet Alim. Prem. P/Cães Ad.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1Kg Honey Pet Alim. Prem. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1Kg Honey Pet Alim. Prem. P/Cães Filh.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 06Kg Honey Pet Alim. Prem. P/Cães Ad.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 06Kg Honey Pet Alim. Prem. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 06Kg Honey Pet Alim. Prem. P/Cães Filh.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 10,1Kg Honey Pet Alim. Prem. P/Cães Ad.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 10,1Kg Honey Pet Alim. Prem. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 15Kg Honey Pet Alim. Prem. P/Cães Ad.Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 15Kg Honey Pet Alim. Prem. P/Cães Rpm Carne E Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Gatos Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Gatos Peixe</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Gatos Cast.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 900G Honey Pet Alim. Prem. P/Gatos Filh.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1Kg Honey Pet Alim. Prem. P/Gatos Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 2,1Kg Honey Pet Alim. Prem. P/Gatos Cast.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 10,1Kg Honey Pet Alim. Prem. P/Gatos Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 10,1Kg Honey Pet Alim. Prem. P/Gatos Cast.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 05Kg Pitz Pet Alim. Premium. P/Cães Ad.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 06Kg Pitz Pet Alim. Premium. P/Cães Ad.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 10,1Kg Pitz Pet Alim. Premium. P/Cães Ad.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 15Kg Pitz Pet Alim. Premium. P/Cães Ad.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 18Kg Pitz Pet Alim. Premium. P/Cães Ad.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 40G Prime Full Snack P/ Gatos Peixe</t>
+  </si>
+  <si>
+    <t>Pet Prful 40G Prime Full Snack P/ Gatos Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 40G Honey Pet Bifinho  P/ Cães Adulto Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 40G Honey Pet Bifinho  P/ Cães Pq.Porte Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 40G Honey Pet Bifinho  P/ Cães Adulto Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 40G Honey Pet Bifinho  P/ Cães Pq. Porte Frango</t>
+  </si>
+  <si>
+    <t>Pet Prful 180G Honey Pet Bifinho  P/ Cães Adulto Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 180G Honey Pet Bifinho  P/ Cães Pq. Porte  Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 400G Honey Pet Bifinho  P/ Cães Adulto Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 400G Honey Pet Bifinho  P/ Cães Pq. Porte Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful 180G Honey Pet Biscoitos P/ Cães Adulto Integral</t>
+  </si>
+  <si>
+    <t>Pet Prful 180G Honey Pet Biscoitos P/ Cães Mini Integral</t>
+  </si>
+  <si>
+    <t>Pet Prful 50G Prime Full Osso  Palito P/ Caes Nº 6</t>
+  </si>
+  <si>
+    <t>Pet Prful 50G Prime Full Osso  Palito P/ Caes Nº 10</t>
+  </si>
+  <si>
+    <t>Pet Prful 50G Prime Full Osso  Palito P/ Caes Nº 15</t>
+  </si>
+  <si>
+    <t>Pet Prful 110G Prime Full Osso  Palito P/ Caes Nº 6</t>
+  </si>
+  <si>
+    <t>Pet Prful 110G Prime Full Osso  Palito P/ Caes Nº 10</t>
+  </si>
+  <si>
+    <t>Pet Prful 110G Prime Full Osso  Palito P/ Caes Nº 15</t>
+  </si>
+  <si>
+    <t>Pet Prful 400G Prime Full Osso Palito P/ Caes Nº 10</t>
+  </si>
+  <si>
+    <t>Pet Prful 45G Prime Full Osso No P/ Caes N 2/3  C/3</t>
+  </si>
+  <si>
+    <t>Pet Prful 45G Prime Full Osso No P/ Caes N 3/4 C/2</t>
+  </si>
+  <si>
+    <t>Pet Prful 45G Prime Full Osso No P/ Caes N 4/5 C/1</t>
+  </si>
+  <si>
+    <t>Pet Prful 60G Prime Full Osso No P/ Caes N 5/6 C/1</t>
+  </si>
+  <si>
+    <t>Pet Prful 80G Prime Full Osso No P/ Caes N 6/7 C/1</t>
+  </si>
+  <si>
+    <t>Pet Prful 110G Prime Full Osso No P/ Caes N 7/8 C/1</t>
+  </si>
+  <si>
+    <t>Pet Prful 07Unis Honey Pet Tapete Higienico P/ Caes C/7</t>
+  </si>
+  <si>
+    <t>Pet Prful 30Unid Honey Pet Tapete Higienico P/ Caes C/30</t>
+  </si>
+  <si>
+    <t>Pet Prful 04Kg Honey Pet Areia Sanitária P/ Gatos - 4Kg</t>
+  </si>
+  <si>
+    <t>Pet Prful 04Kg Honey Pet  Areia Sanitária Perfumada P/ Gatos - 4Kg</t>
+  </si>
+  <si>
+    <t>Pet Prful 02Lt Prime Full Eliminador De Odores Citronela - 2L</t>
+  </si>
+  <si>
+    <t>Pet Prful 02Lt Prime Full Eliminador De Odores Lavanda - 2L</t>
+  </si>
+  <si>
+    <t>Pet Prful 700Ml Prime Full 5 Em 1 Shampoo -700Ml</t>
+  </si>
+  <si>
+    <t>Pet Prful 700Ml Prime Full Shampoo Neutro-700Ml</t>
+  </si>
+  <si>
+    <t>Pet Prful 700Ml Prime Full Shampoo Bomba De Vitaminas -700Ml</t>
+  </si>
+  <si>
+    <t>Pet Prful 700Ml Prime Full Shampoo Filhotes -700Ml</t>
+  </si>
+  <si>
+    <t>Pet Prful 500Ml Shampoo Condicionador Antipulgas/Carrapatos  -500Ml</t>
+  </si>
+  <si>
+    <t>Pet Prful 500Ml Prime Full Kit Xixi Pode / Xixi Não</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Kit Higiene Pet Suporte C/02 Rolos  P/Caes</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Kit Higiene Refil C/03 Rolos  P/Caes</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Pá Higienica P/ Areia</t>
+  </si>
+  <si>
+    <t>Pet Prful 12 Ui Prime Full Bandeja P/Areia De Gato</t>
+  </si>
+  <si>
+    <t>Pet Prful 06Uni Prime Full Escova Aço P/ Caes E Gatos</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Escova Veterinaria P /Caes E Gatos</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Comedouro De Plástico N°1</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Comedouro De Plástico N°2</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Comedouro De Plástico N°3</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Comedouro De Plástico N°4</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Brinquedo P/ Cães Adestradog M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Brinquedo P/ Cães Adestradog G</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Caes Brinqfull P</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Caes Brinqfull M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Caes Brinqfull G</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Caes Brinqfull Especial M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Brinquedo Cao Galinha Colorida</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Brinquedo Cao Galinha M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Cães Pelucia P</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Cães Pelucia M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Cães Pelucia G</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Gatos M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full  Brinquedo P/ Gatos G</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Coleira P/ Caes Sola Forrada M</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Prime Full Coleira P/ Caes Sola Forrada G</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Guia P/ Caes Com Mosquetao De 60Cm/16Mm - C/8Un+4 C/Amortecedor</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Guia P/ Caes Com Mosquetao 1M/16Mm-C/8Un +4 C/Amortecedor</t>
+  </si>
+  <si>
+    <t>Pet Prful 12Uni Guia P/ Caes Com Mosquetao De 1M/10M</t>
+  </si>
+  <si>
+    <t>Pet Prful 10Uni Peitoral E Guia P/ Caes Neon C/10Un</t>
+  </si>
+  <si>
+    <t>Pet Prful 20Uni Peitoral E Guia P/ Caes Seda C/20Un</t>
+  </si>
+  <si>
+    <t>Pet Prful 20Uni Prime Full Peitoral E Guia P/ Caes Seda Americana  C/20Un</t>
+  </si>
+  <si>
+    <t>Pet Prful Pitz Pet Alim. Stand. P/Cães Ad.Carne</t>
+  </si>
+  <si>
+    <t>Pet Prful Honey Pet Biscoitos P/ Cães Adulto Integral</t>
+  </si>
+  <si>
+    <t>Pet Prful Honey Pet Biscoitos P/ Cães Mini Integral</t>
   </si>
 </sst>
 </file>
@@ -186,7 +459,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -675,16 +948,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1045,11 +1317,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1269,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1285,17 +1557,17 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
+      <c r="A11" s="1">
+        <v>20182</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>8.6</v>
@@ -1308,17 +1580,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>51</v>
+      <c r="A12" s="1">
+        <v>20236</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
       </c>
       <c r="E12">
         <v>8.6</v>
@@ -1331,17 +1603,17 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>51</v>
+      <c r="A13" s="1">
+        <v>20328</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
       </c>
       <c r="E13">
         <v>9.27</v>
@@ -1353,18 +1625,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>51</v>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>20199</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
       </c>
       <c r="E14">
         <v>17.260000000000002</v>
@@ -1376,41 +1648,41 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>20243</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15">
         <v>17.260000000000002</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15">
         <v>103.56</v>
       </c>
       <c r="G15">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>51</v>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>20205</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
       </c>
       <c r="E16">
         <v>31.65</v>
@@ -1423,17 +1695,17 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
+      <c r="A17" s="1">
+        <v>20250</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
       </c>
       <c r="E17">
         <v>31.65</v>
@@ -1445,18 +1717,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>51</v>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>20212</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
       </c>
       <c r="E18">
         <v>50.74</v>
@@ -1469,17 +1741,17 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>51</v>
+      <c r="A19" s="1">
+        <v>20267</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
       </c>
       <c r="E19">
         <v>50.74</v>
@@ -1492,17 +1764,17 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>51</v>
+      <c r="A20" s="1">
+        <v>20366</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
       </c>
       <c r="E20">
         <v>10.6</v>
@@ -1515,49 +1787,3880 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="1">
+        <v>20403</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21">
+        <v>10.6</v>
+      </c>
+      <c r="F21">
+        <v>127.2</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>20410</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22">
+        <v>10.6</v>
+      </c>
+      <c r="F22">
+        <v>127.2</v>
+      </c>
+      <c r="G22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>20441</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23">
+        <v>7.94</v>
+      </c>
+      <c r="F23">
+        <v>95.28</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>20496</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24">
+        <v>7.94</v>
+      </c>
+      <c r="F24">
+        <v>95.28</v>
+      </c>
+      <c r="G24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>20540</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25">
+        <v>8.6</v>
+      </c>
+      <c r="F25">
+        <v>103.2</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>20458</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26">
+        <v>15.26</v>
+      </c>
+      <c r="F26">
+        <v>91.56</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>20502</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="2">
-        <v>10.6</v>
-      </c>
-      <c r="F21" s="2">
-        <v>127.2</v>
-      </c>
-      <c r="G21" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="2">
-        <v>10.6</v>
-      </c>
-      <c r="F22" s="2">
-        <v>127.2</v>
-      </c>
-      <c r="G22" s="2">
-        <v>12</v>
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27">
+        <v>15.26</v>
+      </c>
+      <c r="F27">
+        <v>91.56</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>20557</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F28">
+        <v>103.56</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>20465</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29">
+        <v>27.5</v>
+      </c>
+      <c r="F29">
+        <v>27.5</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>20519</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30">
+        <v>27.5</v>
+      </c>
+      <c r="F30">
+        <v>27.5</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>20564</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31">
+        <v>34.4</v>
+      </c>
+      <c r="F31">
+        <v>34.4</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>20472</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32">
+        <v>43.48</v>
+      </c>
+      <c r="F32">
+        <v>43.48</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>20526</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33">
+        <v>43.48</v>
+      </c>
+      <c r="F33">
+        <v>43.48</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>20489</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34">
+        <v>59.98</v>
+      </c>
+      <c r="F34">
+        <v>59.98</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>20533</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35">
+        <v>59.98</v>
+      </c>
+      <c r="F35">
+        <v>59.98</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>20588</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36">
+        <v>7.94</v>
+      </c>
+      <c r="F36">
+        <v>95.28</v>
+      </c>
+      <c r="G36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>20618</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37">
+        <v>7.94</v>
+      </c>
+      <c r="F37">
+        <v>95.28</v>
+      </c>
+      <c r="G37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>20625</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38">
+        <v>7.94</v>
+      </c>
+      <c r="F38">
+        <v>95.28</v>
+      </c>
+      <c r="G38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>20656</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39">
+        <v>7.94</v>
+      </c>
+      <c r="F39">
+        <v>95.28</v>
+      </c>
+      <c r="G39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>20595</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F40">
+        <v>103.56</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>20632</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F41">
+        <v>103.56</v>
+      </c>
+      <c r="G41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>20601</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42">
+        <v>65.25</v>
+      </c>
+      <c r="F42">
+        <v>65.25</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>20649</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43">
+        <v>65.25</v>
+      </c>
+      <c r="F43">
+        <v>65.25</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>20687</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F44">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>20694</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45">
+        <v>23.93</v>
+      </c>
+      <c r="F45">
+        <v>23393</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>20700</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46">
+        <v>37.5</v>
+      </c>
+      <c r="F46">
+        <v>37.5</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>20717</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47">
+        <v>52.55</v>
+      </c>
+      <c r="F47">
+        <v>52.55</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>20724</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48">
+        <v>63</v>
+      </c>
+      <c r="F48">
+        <v>63</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>22049</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F49">
+        <v>73.5</v>
+      </c>
+      <c r="G49">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>22056</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F50">
+        <v>73.5</v>
+      </c>
+      <c r="G50">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>20809</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51">
+        <v>1.62</v>
+      </c>
+      <c r="F51">
+        <v>58.3</v>
+      </c>
+      <c r="G51">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>20816</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52">
+        <v>1.62</v>
+      </c>
+      <c r="F52">
+        <v>58.3</v>
+      </c>
+      <c r="G52">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>20823</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53">
+        <v>1.62</v>
+      </c>
+      <c r="F53">
+        <v>58.3</v>
+      </c>
+      <c r="G53">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>20830</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54">
+        <v>1.62</v>
+      </c>
+      <c r="F54">
+        <v>58.3</v>
+      </c>
+      <c r="G54">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>20847</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55">
+        <v>6.81</v>
+      </c>
+      <c r="F55">
+        <v>81.72</v>
+      </c>
+      <c r="G55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>20854</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56">
+        <v>6.81</v>
+      </c>
+      <c r="F56">
+        <v>81.72</v>
+      </c>
+      <c r="G56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>20861</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57">
+        <v>13.26</v>
+      </c>
+      <c r="F57">
+        <v>159.12</v>
+      </c>
+      <c r="G57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>20878</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58">
+        <v>13.26</v>
+      </c>
+      <c r="F58">
+        <v>159.12</v>
+      </c>
+      <c r="G58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>20960</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59">
+        <v>3.69</v>
+      </c>
+      <c r="F59">
+        <v>44.28</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>20984</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60">
+        <v>3.69</v>
+      </c>
+      <c r="F60">
+        <v>44.28</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>21059</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61">
+        <v>2.29</v>
+      </c>
+      <c r="F61">
+        <v>45.8</v>
+      </c>
+      <c r="G61">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>21066</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62">
+        <v>2.29</v>
+      </c>
+      <c r="F62">
+        <v>45.8</v>
+      </c>
+      <c r="G62">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>21073</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63">
+        <v>2.29</v>
+      </c>
+      <c r="F63">
+        <v>45.8</v>
+      </c>
+      <c r="G63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>21080</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F64">
+        <v>81.2</v>
+      </c>
+      <c r="G64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>21097</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>89</v>
+      </c>
+      <c r="D65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F65">
+        <v>81.2</v>
+      </c>
+      <c r="G65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>21103</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F66">
+        <v>81.2</v>
+      </c>
+      <c r="G66">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>21141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67">
+        <v>9.35</v>
+      </c>
+      <c r="F67">
+        <v>112.2</v>
+      </c>
+      <c r="G67">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>21158</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F68">
+        <v>55.8</v>
+      </c>
+      <c r="G68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>21165</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F69">
+        <v>55.8</v>
+      </c>
+      <c r="G69">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>21172</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F70">
+        <v>55.8</v>
+      </c>
+      <c r="G70">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>21189</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71">
+        <v>5.82</v>
+      </c>
+      <c r="F71">
+        <v>69.88</v>
+      </c>
+      <c r="G71">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>21196</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72">
+        <v>7.58</v>
+      </c>
+      <c r="F72">
+        <v>90.96</v>
+      </c>
+      <c r="G72">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>21202</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73">
+        <v>9.35</v>
+      </c>
+      <c r="F73">
+        <v>56.1</v>
+      </c>
+      <c r="G73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>21424</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74">
+        <v>9.93</v>
+      </c>
+      <c r="F74">
+        <v>119.16</v>
+      </c>
+      <c r="G74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>21431</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75">
+        <v>39.9</v>
+      </c>
+      <c r="F75">
+        <v>159.6</v>
+      </c>
+      <c r="G75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>21448</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F76">
+        <v>21.8</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>21462</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>101</v>
+      </c>
+      <c r="D77" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77">
+        <v>4.99</v>
+      </c>
+      <c r="F77">
+        <v>24.95</v>
+      </c>
+      <c r="G77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>21479</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78">
+        <v>9.35</v>
+      </c>
+      <c r="F78">
+        <v>56.1</v>
+      </c>
+      <c r="G78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>21486</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>103</v>
+      </c>
+      <c r="D79" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79">
+        <v>9.35</v>
+      </c>
+      <c r="F79">
+        <v>56.1</v>
+      </c>
+      <c r="G79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>21493</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80">
+        <v>9.35</v>
+      </c>
+      <c r="F80">
+        <v>112.2</v>
+      </c>
+      <c r="G80">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>21509</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81">
+        <v>9.35</v>
+      </c>
+      <c r="F81">
+        <v>112.2</v>
+      </c>
+      <c r="G81">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>21516</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82">
+        <v>9.35</v>
+      </c>
+      <c r="F82">
+        <v>112.2</v>
+      </c>
+      <c r="G82">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>21523</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>107</v>
+      </c>
+      <c r="D83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83">
+        <v>9.35</v>
+      </c>
+      <c r="F83">
+        <v>112.2</v>
+      </c>
+      <c r="G83">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>108</v>
+      </c>
+      <c r="D84" t="s">
+        <v>27</v>
+      </c>
+      <c r="E84">
+        <v>9.35</v>
+      </c>
+      <c r="F84">
+        <v>112.2</v>
+      </c>
+      <c r="G84">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>22162</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>109</v>
+      </c>
+      <c r="D85" t="s">
+        <v>27</v>
+      </c>
+      <c r="E85">
+        <v>11.71</v>
+      </c>
+      <c r="F85">
+        <v>140.47</v>
+      </c>
+      <c r="G85">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>21530</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>110</v>
+      </c>
+      <c r="D86" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86">
+        <v>5.5</v>
+      </c>
+      <c r="F86">
+        <v>66</v>
+      </c>
+      <c r="G86">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>22155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87">
+        <v>5.5</v>
+      </c>
+      <c r="F87">
+        <v>66</v>
+      </c>
+      <c r="G87">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>21547</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88">
+        <v>2.17</v>
+      </c>
+      <c r="F88">
+        <v>25.99</v>
+      </c>
+      <c r="G88">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>21554</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>113</v>
+      </c>
+      <c r="D89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89">
+        <v>11.05</v>
+      </c>
+      <c r="F89">
+        <v>132.6</v>
+      </c>
+      <c r="G89">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>22094</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90">
+        <v>7.72</v>
+      </c>
+      <c r="F90">
+        <v>46.33</v>
+      </c>
+      <c r="G90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>21561</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>115</v>
+      </c>
+      <c r="D91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91">
+        <v>5.5</v>
+      </c>
+      <c r="F91">
+        <v>66</v>
+      </c>
+      <c r="G91">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>21578</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" t="s">
+        <v>27</v>
+      </c>
+      <c r="E92">
+        <v>7.72</v>
+      </c>
+      <c r="F92">
+        <v>92.66</v>
+      </c>
+      <c r="G92">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>21585</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>117</v>
+      </c>
+      <c r="D93" t="s">
+        <v>27</v>
+      </c>
+      <c r="E93">
+        <v>8.83</v>
+      </c>
+      <c r="F93">
+        <v>105.99</v>
+      </c>
+      <c r="G93">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>21592</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>118</v>
+      </c>
+      <c r="D94" t="s">
+        <v>27</v>
+      </c>
+      <c r="E94">
+        <v>10.5</v>
+      </c>
+      <c r="F94">
+        <v>126</v>
+      </c>
+      <c r="G94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>21608</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
+        <v>119</v>
+      </c>
+      <c r="D95" t="s">
+        <v>27</v>
+      </c>
+      <c r="E95">
+        <v>11.06</v>
+      </c>
+      <c r="F95">
+        <v>132.66</v>
+      </c>
+      <c r="G95">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>22421</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D96" t="s">
+        <v>27</v>
+      </c>
+      <c r="E96">
+        <v>6.61</v>
+      </c>
+      <c r="F96">
+        <v>79.33</v>
+      </c>
+      <c r="G96">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>22438</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>121</v>
+      </c>
+      <c r="D97" t="s">
+        <v>27</v>
+      </c>
+      <c r="E97">
+        <v>11.06</v>
+      </c>
+      <c r="F97">
+        <v>132.66</v>
+      </c>
+      <c r="G97">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>22353</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>122</v>
+      </c>
+      <c r="D98" t="s">
+        <v>27</v>
+      </c>
+      <c r="E98">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="F98">
+        <v>59.33</v>
+      </c>
+      <c r="G98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>22360</v>
+      </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="s">
+        <v>123</v>
+      </c>
+      <c r="D99" t="s">
+        <v>27</v>
+      </c>
+      <c r="E99">
+        <v>7.16</v>
+      </c>
+      <c r="F99">
+        <v>85.92</v>
+      </c>
+      <c r="G99">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>22377</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" t="s">
+        <v>27</v>
+      </c>
+      <c r="E100">
+        <v>14.38</v>
+      </c>
+      <c r="F100">
+        <v>172.56</v>
+      </c>
+      <c r="G100">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>22414</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>125</v>
+      </c>
+      <c r="D101" t="s">
+        <v>27</v>
+      </c>
+      <c r="E101">
+        <v>8.83</v>
+      </c>
+      <c r="F101">
+        <v>105.99</v>
+      </c>
+      <c r="G101">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>21714</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>126</v>
+      </c>
+      <c r="D102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E102">
+        <v>8.83</v>
+      </c>
+      <c r="F102">
+        <v>105.99</v>
+      </c>
+      <c r="G102">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>22186</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>127</v>
+      </c>
+      <c r="D103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E103">
+        <v>8.83</v>
+      </c>
+      <c r="F103">
+        <v>105.99</v>
+      </c>
+      <c r="G103">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>22339</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>128</v>
+      </c>
+      <c r="D104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104">
+        <v>11.06</v>
+      </c>
+      <c r="F104">
+        <v>132.66</v>
+      </c>
+      <c r="G104">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>22346</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>129</v>
+      </c>
+      <c r="D105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E105">
+        <v>16.61</v>
+      </c>
+      <c r="F105">
+        <v>199.33</v>
+      </c>
+      <c r="G105">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>21721</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>130</v>
+      </c>
+      <c r="D106" t="s">
+        <v>27</v>
+      </c>
+      <c r="E106">
+        <v>22.17</v>
+      </c>
+      <c r="F106">
+        <v>265.99</v>
+      </c>
+      <c r="G106">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>22391</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E107">
+        <v>5.5</v>
+      </c>
+      <c r="F107">
+        <v>66</v>
+      </c>
+      <c r="G107">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>22407</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>132</v>
+      </c>
+      <c r="D108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E108">
+        <v>11.06</v>
+      </c>
+      <c r="F108">
+        <v>132.66</v>
+      </c>
+      <c r="G108">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>21745</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>133</v>
+      </c>
+      <c r="D109" t="s">
+        <v>27</v>
+      </c>
+      <c r="E109">
+        <v>11.05</v>
+      </c>
+      <c r="F109">
+        <v>132.6</v>
+      </c>
+      <c r="G109">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>21752</v>
+      </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" t="s">
+        <v>134</v>
+      </c>
+      <c r="D110" t="s">
+        <v>27</v>
+      </c>
+      <c r="E110">
+        <v>16.61</v>
+      </c>
+      <c r="F110">
+        <v>199.33</v>
+      </c>
+      <c r="G110">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>21776</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" t="s">
+        <v>135</v>
+      </c>
+      <c r="D111" t="s">
+        <v>27</v>
+      </c>
+      <c r="E111">
+        <v>15.5</v>
+      </c>
+      <c r="F111">
+        <v>186</v>
+      </c>
+      <c r="G111">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>21783</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>136</v>
+      </c>
+      <c r="D112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E112">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="F112">
+        <v>192.66</v>
+      </c>
+      <c r="G112">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>21790</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>137</v>
+      </c>
+      <c r="D113" t="s">
+        <v>27</v>
+      </c>
+      <c r="E113">
+        <v>11.06</v>
+      </c>
+      <c r="F113">
+        <v>132.66</v>
+      </c>
+      <c r="G113">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>22315</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>138</v>
+      </c>
+      <c r="D114" t="s">
+        <v>27</v>
+      </c>
+      <c r="E114">
+        <v>22.17</v>
+      </c>
+      <c r="F114">
+        <v>221.66</v>
+      </c>
+      <c r="G114">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>21844</v>
+      </c>
+      <c r="B115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" t="s">
+        <v>139</v>
+      </c>
+      <c r="D115" t="s">
+        <v>27</v>
+      </c>
+      <c r="E115">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="F115">
+        <v>321.11</v>
+      </c>
+      <c r="G115">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>21899</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>140</v>
+      </c>
+      <c r="D116" t="s">
+        <v>27</v>
+      </c>
+      <c r="E116">
+        <v>16.61</v>
+      </c>
+      <c r="F116">
+        <v>332.22</v>
+      </c>
+      <c r="G116">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>20182</v>
+      </c>
+      <c r="B117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" t="s">
+        <v>35</v>
+      </c>
+      <c r="D117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E117">
+        <v>9.64</v>
+      </c>
+      <c r="F117">
+        <v>115.68</v>
+      </c>
+      <c r="G117">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>20236</v>
+      </c>
+      <c r="B118" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" t="s">
+        <v>36</v>
+      </c>
+      <c r="D118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E118">
+        <v>9.64</v>
+      </c>
+      <c r="F118">
+        <v>115.68</v>
+      </c>
+      <c r="G118">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>20328</v>
+      </c>
+      <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" t="s">
+        <v>37</v>
+      </c>
+      <c r="D119" t="s">
+        <v>27</v>
+      </c>
+      <c r="E119">
+        <v>11.02</v>
+      </c>
+      <c r="F119">
+        <v>132.22</v>
+      </c>
+      <c r="G119">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>20205</v>
+      </c>
+      <c r="B120" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" t="s">
+        <v>40</v>
+      </c>
+      <c r="D120" t="s">
+        <v>27</v>
+      </c>
+      <c r="E120">
+        <v>34.29</v>
+      </c>
+      <c r="F120">
+        <v>34.29</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>20250</v>
+      </c>
+      <c r="B121" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" t="s">
+        <v>41</v>
+      </c>
+      <c r="D121" t="s">
+        <v>27</v>
+      </c>
+      <c r="E121">
+        <v>34.29</v>
+      </c>
+      <c r="F121">
+        <v>34.29</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>20212</v>
+      </c>
+      <c r="B122" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" t="s">
+        <v>42</v>
+      </c>
+      <c r="D122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E122">
+        <v>53.18</v>
+      </c>
+      <c r="F122">
+        <v>53.18</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>20267</v>
+      </c>
+      <c r="B123" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" t="s">
+        <v>43</v>
+      </c>
+      <c r="D123" t="s">
+        <v>27</v>
+      </c>
+      <c r="E123">
+        <v>53.18</v>
+      </c>
+      <c r="F123">
+        <v>53.18</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>20366</v>
+      </c>
+      <c r="B124" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124" t="s">
+        <v>44</v>
+      </c>
+      <c r="D124" t="s">
+        <v>27</v>
+      </c>
+      <c r="E124">
+        <v>11.68</v>
+      </c>
+      <c r="F124">
+        <v>140.16</v>
+      </c>
+      <c r="G124">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>20403</v>
+      </c>
+      <c r="B125" t="s">
+        <v>30</v>
+      </c>
+      <c r="C125" t="s">
+        <v>45</v>
+      </c>
+      <c r="D125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E125">
+        <v>11.68</v>
+      </c>
+      <c r="F125">
+        <v>140.16</v>
+      </c>
+      <c r="G125">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>20410</v>
+      </c>
+      <c r="B126" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126" t="s">
+        <v>46</v>
+      </c>
+      <c r="D126" t="s">
+        <v>27</v>
+      </c>
+      <c r="E126">
+        <v>11.68</v>
+      </c>
+      <c r="F126">
+        <v>140.16</v>
+      </c>
+      <c r="G126">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>20441</v>
+      </c>
+      <c r="B127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127" t="s">
+        <v>47</v>
+      </c>
+      <c r="D127" t="s">
+        <v>27</v>
+      </c>
+      <c r="E127">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="F127">
+        <v>107.41</v>
+      </c>
+      <c r="G127">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>20496</v>
+      </c>
+      <c r="B128" t="s">
+        <v>30</v>
+      </c>
+      <c r="C128" t="s">
+        <v>48</v>
+      </c>
+      <c r="D128" t="s">
+        <v>27</v>
+      </c>
+      <c r="E128">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="F128">
+        <v>107.41</v>
+      </c>
+      <c r="G128">
+        <f>F128/E128</f>
+        <v>12.001117318435755</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>20540</v>
+      </c>
+      <c r="B129" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129" t="s">
+        <v>49</v>
+      </c>
+      <c r="D129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E129">
+        <v>9.64</v>
+      </c>
+      <c r="F129">
+        <v>115.68</v>
+      </c>
+      <c r="G129">
+        <f t="shared" ref="G129:G192" si="0">F129/E129</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>20465</v>
+      </c>
+      <c r="B130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130" t="s">
+        <v>53</v>
+      </c>
+      <c r="D130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E130">
+        <v>28.56</v>
+      </c>
+      <c r="F130">
+        <v>28.56</v>
+      </c>
+      <c r="G130">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>20519</v>
+      </c>
+      <c r="B131" t="s">
+        <v>30</v>
+      </c>
+      <c r="C131" t="s">
+        <v>54</v>
+      </c>
+      <c r="D131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E131">
+        <v>28.56</v>
+      </c>
+      <c r="F131">
+        <v>28.56</v>
+      </c>
+      <c r="G131">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>20564</v>
+      </c>
+      <c r="B132" t="s">
+        <v>30</v>
+      </c>
+      <c r="C132" t="s">
+        <v>55</v>
+      </c>
+      <c r="D132" t="s">
+        <v>27</v>
+      </c>
+      <c r="E132">
+        <v>41.92</v>
+      </c>
+      <c r="F132">
+        <v>41.92</v>
+      </c>
+      <c r="G132">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>20472</v>
+      </c>
+      <c r="B133" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133" t="s">
+        <v>56</v>
+      </c>
+      <c r="D133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E133">
+        <v>48.92</v>
+      </c>
+      <c r="F133">
+        <v>48.92</v>
+      </c>
+      <c r="G133">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>20526</v>
+      </c>
+      <c r="B134" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134" t="s">
+        <v>57</v>
+      </c>
+      <c r="D134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E134">
+        <v>48.92</v>
+      </c>
+      <c r="F134">
+        <v>48.92</v>
+      </c>
+      <c r="G134">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>20489</v>
+      </c>
+      <c r="B135" t="s">
+        <v>30</v>
+      </c>
+      <c r="C135" t="s">
+        <v>58</v>
+      </c>
+      <c r="D135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E135">
+        <v>62.92</v>
+      </c>
+      <c r="F135">
+        <v>62.92</v>
+      </c>
+      <c r="G135">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>20533</v>
+      </c>
+      <c r="B136" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136" t="s">
+        <v>59</v>
+      </c>
+      <c r="D136" t="s">
+        <v>27</v>
+      </c>
+      <c r="E136">
+        <v>62.92</v>
+      </c>
+      <c r="F136">
+        <v>62.92</v>
+      </c>
+      <c r="G136">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>20588</v>
+      </c>
+      <c r="B137" t="s">
+        <v>30</v>
+      </c>
+      <c r="C137" t="s">
+        <v>60</v>
+      </c>
+      <c r="D137" t="s">
+        <v>27</v>
+      </c>
+      <c r="E137">
+        <v>10.33</v>
+      </c>
+      <c r="F137">
+        <v>123.95</v>
+      </c>
+      <c r="G137">
+        <f t="shared" si="0"/>
+        <v>11.999031945788964</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>20618</v>
+      </c>
+      <c r="B138" t="s">
+        <v>30</v>
+      </c>
+      <c r="C138" t="s">
+        <v>61</v>
+      </c>
+      <c r="D138" t="s">
+        <v>27</v>
+      </c>
+      <c r="E138">
+        <v>10.33</v>
+      </c>
+      <c r="F138">
+        <v>123.95</v>
+      </c>
+      <c r="G138">
+        <f t="shared" si="0"/>
+        <v>11.999031945788964</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>20625</v>
+      </c>
+      <c r="B139" t="s">
+        <v>30</v>
+      </c>
+      <c r="C139" t="s">
+        <v>62</v>
+      </c>
+      <c r="D139" t="s">
+        <v>27</v>
+      </c>
+      <c r="E139">
+        <v>10.33</v>
+      </c>
+      <c r="F139">
+        <v>123.95</v>
+      </c>
+      <c r="G139">
+        <f t="shared" si="0"/>
+        <v>11.999031945788964</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>20656</v>
+      </c>
+      <c r="B140" t="s">
+        <v>30</v>
+      </c>
+      <c r="C140" t="s">
+        <v>63</v>
+      </c>
+      <c r="D140" t="s">
+        <v>27</v>
+      </c>
+      <c r="E140">
+        <v>10.33</v>
+      </c>
+      <c r="F140">
+        <v>123.95</v>
+      </c>
+      <c r="G140">
+        <f t="shared" si="0"/>
+        <v>11.999031945788964</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>20601</v>
+      </c>
+      <c r="B141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C141" t="s">
+        <v>66</v>
+      </c>
+      <c r="D141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E141">
+        <v>68.84</v>
+      </c>
+      <c r="F141">
+        <v>68.84</v>
+      </c>
+      <c r="G141">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>20649</v>
+      </c>
+      <c r="B142" t="s">
+        <v>30</v>
+      </c>
+      <c r="C142" t="s">
+        <v>67</v>
+      </c>
+      <c r="D142" t="s">
+        <v>27</v>
+      </c>
+      <c r="E142">
+        <v>68.84</v>
+      </c>
+      <c r="F142">
+        <v>68.84</v>
+      </c>
+      <c r="G142">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B143" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143" t="s">
+        <v>141</v>
+      </c>
+      <c r="D143" t="s">
+        <v>27</v>
+      </c>
+      <c r="E143">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F143">
+        <v>98.4</v>
+      </c>
+      <c r="G143">
+        <f t="shared" si="0"/>
+        <v>12.000000000000002</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>20687</v>
+      </c>
+      <c r="B144" t="s">
+        <v>30</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E144">
+        <v>25.19</v>
+      </c>
+      <c r="F144">
+        <v>25.19</v>
+      </c>
+      <c r="G144">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>20694</v>
+      </c>
+      <c r="B145" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145" t="s">
+        <v>69</v>
+      </c>
+      <c r="D145" t="s">
+        <v>27</v>
+      </c>
+      <c r="E145">
+        <v>27.92</v>
+      </c>
+      <c r="F145">
+        <v>27.92</v>
+      </c>
+      <c r="G145">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>20700</v>
+      </c>
+      <c r="B146" t="s">
+        <v>30</v>
+      </c>
+      <c r="C146" t="s">
+        <v>70</v>
+      </c>
+      <c r="D146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E146">
+        <v>41.92</v>
+      </c>
+      <c r="F146">
+        <v>41.92</v>
+      </c>
+      <c r="G146">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>20717</v>
+      </c>
+      <c r="B147" t="s">
+        <v>30</v>
+      </c>
+      <c r="C147" t="s">
+        <v>71</v>
+      </c>
+      <c r="D147" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147">
+        <v>55.92</v>
+      </c>
+      <c r="F147">
+        <v>55.92</v>
+      </c>
+      <c r="G147">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>22049</v>
+      </c>
+      <c r="B148" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" t="s">
+        <v>73</v>
+      </c>
+      <c r="D148" t="s">
+        <v>27</v>
+      </c>
+      <c r="E148">
+        <v>2.99</v>
+      </c>
+      <c r="F148">
+        <v>89.7</v>
+      </c>
+      <c r="G148">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>22056</v>
+      </c>
+      <c r="B149" t="s">
+        <v>30</v>
+      </c>
+      <c r="C149" t="s">
+        <v>74</v>
+      </c>
+      <c r="D149" t="s">
+        <v>27</v>
+      </c>
+      <c r="E149">
+        <v>2.99</v>
+      </c>
+      <c r="F149">
+        <v>89.7</v>
+      </c>
+      <c r="G149">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>20809</v>
+      </c>
+      <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" t="s">
+        <v>75</v>
+      </c>
+      <c r="D150" t="s">
+        <v>27</v>
+      </c>
+      <c r="E150">
+        <v>1.79</v>
+      </c>
+      <c r="F150">
+        <v>64.5</v>
+      </c>
+      <c r="G150">
+        <f t="shared" si="0"/>
+        <v>36.033519553072622</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>20816</v>
+      </c>
+      <c r="B151" t="s">
+        <v>30</v>
+      </c>
+      <c r="C151" t="s">
+        <v>76</v>
+      </c>
+      <c r="D151" t="s">
+        <v>27</v>
+      </c>
+      <c r="E151">
+        <v>1.79</v>
+      </c>
+      <c r="F151">
+        <v>64.5</v>
+      </c>
+      <c r="G151">
+        <f t="shared" si="0"/>
+        <v>36.033519553072622</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>20847</v>
+      </c>
+      <c r="B152" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" t="s">
+        <v>79</v>
+      </c>
+      <c r="D152" t="s">
+        <v>27</v>
+      </c>
+      <c r="E152">
+        <v>7.78</v>
+      </c>
+      <c r="F152">
+        <v>93.4</v>
+      </c>
+      <c r="G152">
+        <f t="shared" si="0"/>
+        <v>12.005141388174808</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>20854</v>
+      </c>
+      <c r="B153" t="s">
+        <v>30</v>
+      </c>
+      <c r="C153" t="s">
+        <v>80</v>
+      </c>
+      <c r="D153" t="s">
+        <v>27</v>
+      </c>
+      <c r="E153">
+        <v>7.78</v>
+      </c>
+      <c r="F153">
+        <v>93.4</v>
+      </c>
+      <c r="G153">
+        <f t="shared" si="0"/>
+        <v>12.005141388174808</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>20861</v>
+      </c>
+      <c r="B154" t="s">
+        <v>30</v>
+      </c>
+      <c r="C154" t="s">
+        <v>81</v>
+      </c>
+      <c r="D154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E154">
+        <v>15.57</v>
+      </c>
+      <c r="F154">
+        <v>186.88</v>
+      </c>
+      <c r="G154">
+        <f t="shared" si="0"/>
+        <v>12.002569043031471</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>20960</v>
+      </c>
+      <c r="B155" t="s">
+        <v>30</v>
+      </c>
+      <c r="C155" t="s">
+        <v>83</v>
+      </c>
+      <c r="D155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E155">
+        <v>5.39</v>
+      </c>
+      <c r="F155">
+        <v>64.64</v>
+      </c>
+      <c r="G155">
+        <f t="shared" si="0"/>
+        <v>11.992578849721708</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>20984</v>
+      </c>
+      <c r="B156" t="s">
+        <v>30</v>
+      </c>
+      <c r="C156" t="s">
+        <v>84</v>
+      </c>
+      <c r="D156" t="s">
+        <v>27</v>
+      </c>
+      <c r="E156">
+        <v>5.39</v>
+      </c>
+      <c r="F156">
+        <v>64.64</v>
+      </c>
+      <c r="G156">
+        <f t="shared" si="0"/>
+        <v>11.992578849721708</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B157" t="s">
+        <v>30</v>
+      </c>
+      <c r="C157" t="s">
+        <v>142</v>
+      </c>
+      <c r="D157" t="s">
+        <v>27</v>
+      </c>
+      <c r="E157">
+        <v>11.38</v>
+      </c>
+      <c r="F157">
+        <v>136.55000000000001</v>
+      </c>
+      <c r="G157">
+        <f t="shared" si="0"/>
+        <v>11.999121265377855</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B158" t="s">
+        <v>30</v>
+      </c>
+      <c r="C158" t="s">
+        <v>143</v>
+      </c>
+      <c r="D158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E158">
+        <v>11.38</v>
+      </c>
+      <c r="F158">
+        <v>136.55000000000001</v>
+      </c>
+      <c r="G158">
+        <f t="shared" si="0"/>
+        <v>11.999121265377855</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>21059</v>
+      </c>
+      <c r="B159" t="s">
+        <v>30</v>
+      </c>
+      <c r="C159" t="s">
+        <v>85</v>
+      </c>
+      <c r="D159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E159">
+        <v>2.99</v>
+      </c>
+      <c r="F159">
+        <v>59.8</v>
+      </c>
+      <c r="G159">
+        <f t="shared" si="0"/>
+        <v>19.999999999999996</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>21097</v>
+      </c>
+      <c r="B160" t="s">
+        <v>30</v>
+      </c>
+      <c r="C160" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" t="s">
+        <v>27</v>
+      </c>
+      <c r="E160">
+        <v>5.39</v>
+      </c>
+      <c r="F160">
+        <v>107.74</v>
+      </c>
+      <c r="G160">
+        <f t="shared" si="0"/>
+        <v>19.988868274582561</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>21103</v>
+      </c>
+      <c r="B161" t="s">
+        <v>30</v>
+      </c>
+      <c r="C161" t="s">
+        <v>90</v>
+      </c>
+      <c r="D161" t="s">
+        <v>27</v>
+      </c>
+      <c r="E161">
+        <v>5.39</v>
+      </c>
+      <c r="F161">
+        <v>107.74</v>
+      </c>
+      <c r="G161">
+        <f t="shared" si="0"/>
+        <v>19.988868274582561</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>21165</v>
+      </c>
+      <c r="B162" t="s">
+        <v>30</v>
+      </c>
+      <c r="C162" t="s">
+        <v>93</v>
+      </c>
+      <c r="D162" t="s">
+        <v>27</v>
+      </c>
+      <c r="E162">
+        <v>5.39</v>
+      </c>
+      <c r="F162">
+        <v>64.64</v>
+      </c>
+      <c r="G162">
+        <f t="shared" si="0"/>
+        <v>11.992578849721708</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>21172</v>
+      </c>
+      <c r="B163" t="s">
+        <v>30</v>
+      </c>
+      <c r="C163" t="s">
+        <v>94</v>
+      </c>
+      <c r="D163" t="s">
+        <v>27</v>
+      </c>
+      <c r="E163">
+        <v>5.39</v>
+      </c>
+      <c r="F163">
+        <v>64.64</v>
+      </c>
+      <c r="G163">
+        <f t="shared" si="0"/>
+        <v>11.992578849721708</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>21189</v>
+      </c>
+      <c r="B164" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164" t="s">
+        <v>95</v>
+      </c>
+      <c r="D164" t="s">
+        <v>27</v>
+      </c>
+      <c r="E164">
+        <v>7.18</v>
+      </c>
+      <c r="F164">
+        <v>86.21</v>
+      </c>
+      <c r="G164">
+        <f t="shared" si="0"/>
+        <v>12.006963788300835</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>21196</v>
+      </c>
+      <c r="B165" t="s">
+        <v>30</v>
+      </c>
+      <c r="C165" t="s">
+        <v>96</v>
+      </c>
+      <c r="D165" t="s">
+        <v>27</v>
+      </c>
+      <c r="E165">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F165">
+        <v>100.59</v>
+      </c>
+      <c r="G165">
+        <f t="shared" si="0"/>
+        <v>12.003579952267302</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>21424</v>
+      </c>
+      <c r="B166" t="s">
+        <v>30</v>
+      </c>
+      <c r="C166" t="s">
+        <v>98</v>
+      </c>
+      <c r="D166" t="s">
+        <v>27</v>
+      </c>
+      <c r="E166">
+        <v>11.92</v>
+      </c>
+      <c r="F166">
+        <v>143.09</v>
+      </c>
+      <c r="G166">
+        <f t="shared" si="0"/>
+        <v>12.004194630872483</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>21431</v>
+      </c>
+      <c r="B167" t="s">
+        <v>30</v>
+      </c>
+      <c r="C167" t="s">
+        <v>99</v>
+      </c>
+      <c r="D167" t="s">
+        <v>27</v>
+      </c>
+      <c r="E167">
+        <v>47.88</v>
+      </c>
+      <c r="F167">
+        <v>191.5</v>
+      </c>
+      <c r="G167">
+        <f t="shared" si="0"/>
+        <v>3.9995822890559731</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>21448</v>
+      </c>
+      <c r="B168" t="s">
+        <v>30</v>
+      </c>
+      <c r="C168" t="s">
+        <v>100</v>
+      </c>
+      <c r="D168" t="s">
+        <v>27</v>
+      </c>
+      <c r="E168">
+        <v>5.93</v>
+      </c>
+      <c r="F168">
+        <v>29.66</v>
+      </c>
+      <c r="G168">
+        <f t="shared" si="0"/>
+        <v>5.0016863406408101</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>21462</v>
+      </c>
+      <c r="B169" t="s">
+        <v>30</v>
+      </c>
+      <c r="C169" t="s">
+        <v>101</v>
+      </c>
+      <c r="D169" t="s">
+        <v>27</v>
+      </c>
+      <c r="G169" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>21479</v>
+      </c>
+      <c r="B170" t="s">
+        <v>30</v>
+      </c>
+      <c r="C170" t="s">
+        <v>102</v>
+      </c>
+      <c r="D170" t="s">
+        <v>27</v>
+      </c>
+      <c r="G170" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>21486</v>
+      </c>
+      <c r="B171" t="s">
+        <v>30</v>
+      </c>
+      <c r="C171" t="s">
+        <v>103</v>
+      </c>
+      <c r="D171" t="s">
+        <v>27</v>
+      </c>
+      <c r="G171" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>21493</v>
+      </c>
+      <c r="B172" t="s">
+        <v>30</v>
+      </c>
+      <c r="C172" t="s">
+        <v>104</v>
+      </c>
+      <c r="D172" t="s">
+        <v>27</v>
+      </c>
+      <c r="G172" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>21509</v>
+      </c>
+      <c r="B173" t="s">
+        <v>30</v>
+      </c>
+      <c r="C173" t="s">
+        <v>105</v>
+      </c>
+      <c r="D173" t="s">
+        <v>27</v>
+      </c>
+      <c r="G173" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>21523</v>
+      </c>
+      <c r="B174" t="s">
+        <v>30</v>
+      </c>
+      <c r="C174" t="s">
+        <v>107</v>
+      </c>
+      <c r="D174" t="s">
+        <v>27</v>
+      </c>
+      <c r="G174" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B175" t="s">
+        <v>30</v>
+      </c>
+      <c r="C175" t="s">
+        <v>108</v>
+      </c>
+      <c r="D175" t="s">
+        <v>27</v>
+      </c>
+      <c r="G175" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>21561</v>
+      </c>
+      <c r="B176" t="s">
+        <v>30</v>
+      </c>
+      <c r="C176" t="s">
+        <v>115</v>
+      </c>
+      <c r="D176" t="s">
+        <v>27</v>
+      </c>
+      <c r="G176" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>21578</v>
+      </c>
+      <c r="B177" t="s">
+        <v>30</v>
+      </c>
+      <c r="C177" t="s">
+        <v>116</v>
+      </c>
+      <c r="D177" t="s">
+        <v>27</v>
+      </c>
+      <c r="G177" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>21585</v>
+      </c>
+      <c r="B178" t="s">
+        <v>30</v>
+      </c>
+      <c r="C178" t="s">
+        <v>117</v>
+      </c>
+      <c r="D178" t="s">
+        <v>27</v>
+      </c>
+      <c r="G178" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>21592</v>
+      </c>
+      <c r="B179" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179" t="s">
+        <v>118</v>
+      </c>
+      <c r="D179" t="s">
+        <v>27</v>
+      </c>
+      <c r="G179" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>21608</v>
+      </c>
+      <c r="B180" t="s">
+        <v>30</v>
+      </c>
+      <c r="C180" t="s">
+        <v>119</v>
+      </c>
+      <c r="D180" t="s">
+        <v>27</v>
+      </c>
+      <c r="G180" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>22421</v>
+      </c>
+      <c r="B181" t="s">
+        <v>30</v>
+      </c>
+      <c r="C181" t="s">
+        <v>120</v>
+      </c>
+      <c r="D181" t="s">
+        <v>27</v>
+      </c>
+      <c r="G181" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>22353</v>
+      </c>
+      <c r="B182" t="s">
+        <v>30</v>
+      </c>
+      <c r="C182" t="s">
+        <v>122</v>
+      </c>
+      <c r="D182" t="s">
+        <v>27</v>
+      </c>
+      <c r="G182" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>22360</v>
+      </c>
+      <c r="B183" t="s">
+        <v>30</v>
+      </c>
+      <c r="C183" t="s">
+        <v>123</v>
+      </c>
+      <c r="D183" t="s">
+        <v>27</v>
+      </c>
+      <c r="G183" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>21714</v>
+      </c>
+      <c r="B184" t="s">
+        <v>30</v>
+      </c>
+      <c r="C184" t="s">
+        <v>126</v>
+      </c>
+      <c r="D184" t="s">
+        <v>27</v>
+      </c>
+      <c r="G184" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>22339</v>
+      </c>
+      <c r="B185" t="s">
+        <v>30</v>
+      </c>
+      <c r="C185" t="s">
+        <v>128</v>
+      </c>
+      <c r="D185" t="s">
+        <v>27</v>
+      </c>
+      <c r="G185" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>22391</v>
+      </c>
+      <c r="B186" t="s">
+        <v>30</v>
+      </c>
+      <c r="C186" t="s">
+        <v>131</v>
+      </c>
+      <c r="D186" t="s">
+        <v>27</v>
+      </c>
+      <c r="G186" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>21745</v>
+      </c>
+      <c r="B187" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187" t="s">
+        <v>133</v>
+      </c>
+      <c r="D187" t="s">
+        <v>27</v>
+      </c>
+      <c r="G187" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>21752</v>
+      </c>
+      <c r="B188" t="s">
+        <v>30</v>
+      </c>
+      <c r="C188" t="s">
+        <v>134</v>
+      </c>
+      <c r="D188" t="s">
+        <v>27</v>
+      </c>
+      <c r="G188" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>21783</v>
+      </c>
+      <c r="B189" t="s">
+        <v>30</v>
+      </c>
+      <c r="C189" t="s">
+        <v>136</v>
+      </c>
+      <c r="D189" t="s">
+        <v>27</v>
+      </c>
+      <c r="G189" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>21790</v>
+      </c>
+      <c r="B190" t="s">
+        <v>30</v>
+      </c>
+      <c r="C190" t="s">
+        <v>137</v>
+      </c>
+      <c r="D190" t="s">
+        <v>27</v>
+      </c>
+      <c r="G190" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>21844</v>
+      </c>
+      <c r="B191" t="s">
+        <v>30</v>
+      </c>
+      <c r="C191" t="s">
+        <v>139</v>
+      </c>
+      <c r="D191" t="s">
+        <v>27</v>
+      </c>
+      <c r="G191" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>21899</v>
+      </c>
+      <c r="B192" t="s">
+        <v>30</v>
+      </c>
+      <c r="C192" t="s">
+        <v>140</v>
+      </c>
+      <c r="D192" t="s">
+        <v>27</v>
+      </c>
+      <c r="G192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268B503E-86D9-4D8A-BFB9-1E9E2473A30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE660974-B745-433E-8F2F-717B83085E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="265">
   <si>
     <t>categoria</t>
   </si>
@@ -452,6 +452,369 @@
   </si>
   <si>
     <t>Pet Prful Honey Pet Biscoitos P/ Cães Mini Integral</t>
+  </si>
+  <si>
+    <t>0105040001</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>Fritop</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Cebola e Salsa</t>
+  </si>
+  <si>
+    <t>0105040002</t>
+  </si>
+  <si>
+    <t>0105040003</t>
+  </si>
+  <si>
+    <t>0105040004</t>
+  </si>
+  <si>
+    <t>0105040005</t>
+  </si>
+  <si>
+    <t>0105040006</t>
+  </si>
+  <si>
+    <t>0105040007</t>
+  </si>
+  <si>
+    <t>0105040008</t>
+  </si>
+  <si>
+    <t>0105040009</t>
+  </si>
+  <si>
+    <t>0105040010</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Requeijão</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Bacon Liso</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Bacon Listrado</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Mix de Queijos</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Churrasco</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Queijo</t>
+  </si>
+  <si>
+    <t>SLG Fritop 200g Polvilho</t>
+  </si>
+  <si>
+    <t>SLG Fritop 50g Batata Chip Original</t>
+  </si>
+  <si>
+    <t>SLG Fritop 50g Batata Chip Cebola e Salsa</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>3106</t>
+  </si>
+  <si>
+    <t>3117</t>
+  </si>
+  <si>
+    <t>3118</t>
+  </si>
+  <si>
+    <t>3119</t>
+  </si>
+  <si>
+    <t>3120</t>
+  </si>
+  <si>
+    <t>3111</t>
+  </si>
+  <si>
+    <t>8108</t>
+  </si>
+  <si>
+    <t>8109</t>
+  </si>
+  <si>
+    <t>8110</t>
+  </si>
+  <si>
+    <t>8111</t>
+  </si>
+  <si>
+    <t>8119</t>
+  </si>
+  <si>
+    <t>8120</t>
+  </si>
+  <si>
+    <t>8121</t>
+  </si>
+  <si>
+    <t>8024</t>
+  </si>
+  <si>
+    <t>8047</t>
+  </si>
+  <si>
+    <t>8074</t>
+  </si>
+  <si>
+    <t>8009</t>
+  </si>
+  <si>
+    <t>8010</t>
+  </si>
+  <si>
+    <t>Doce</t>
+  </si>
+  <si>
+    <t>DOC Gui Cocada 170g em Barra Branca</t>
+  </si>
+  <si>
+    <t>DOC Gui Cocada 170g em Barra Preta</t>
+  </si>
+  <si>
+    <t>DOC Gui Pipoca 100g Milho Caramelizada</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Rolha 512g Pote com 32 Unid</t>
+  </si>
+  <si>
+    <t>DOC Gui Pé de Moça 600g Pote com 20 Unid</t>
+  </si>
+  <si>
+    <t>DOC Gui Creme de Amendoin 200g Negresco</t>
+  </si>
+  <si>
+    <t>DOC Gui Creme de Amendoin 200g Meio Amargo</t>
+  </si>
+  <si>
+    <t>DOC Gui Creme de Amendoin 200g Prestigio</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoca Rolha Pote com 63 Unid 1008g</t>
+  </si>
+  <si>
+    <t>DOC Gui Pé de Moleque Crocante Pote com 56 Unid 1008g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Negresco 91g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Nesquik 91g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Neston 91g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Negresco Display 546g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Nesquik Display 546g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Neston Display 546g</t>
+  </si>
+  <si>
+    <t>DOC Gui Pé de Moça Bestlé Display 600g</t>
+  </si>
+  <si>
+    <t>DOC Gui Pé de Moça 100g</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Retangular Display 1080g</t>
+  </si>
+  <si>
+    <t>DOC Gui Chocolate em Pó 50% 200g com mascavo</t>
+  </si>
+  <si>
+    <t>DOC Gui Chocolate em Pó 70% 200g com mascavo</t>
+  </si>
+  <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>0103050001</t>
+  </si>
+  <si>
+    <t>0103050002</t>
+  </si>
+  <si>
+    <t>0103050003</t>
+  </si>
+  <si>
+    <t>0103050004</t>
+  </si>
+  <si>
+    <t>0103050005</t>
+  </si>
+  <si>
+    <t>0103050006</t>
+  </si>
+  <si>
+    <t>0103050007</t>
+  </si>
+  <si>
+    <t>0103050008</t>
+  </si>
+  <si>
+    <t>0103050009</t>
+  </si>
+  <si>
+    <t>0103050010</t>
+  </si>
+  <si>
+    <t>0103050011</t>
+  </si>
+  <si>
+    <t>0103050012</t>
+  </si>
+  <si>
+    <t>0103050013</t>
+  </si>
+  <si>
+    <t>0103050014</t>
+  </si>
+  <si>
+    <t>0103050015</t>
+  </si>
+  <si>
+    <t>0103050016</t>
+  </si>
+  <si>
+    <t>0103050017</t>
+  </si>
+  <si>
+    <t>0103050018</t>
+  </si>
+  <si>
+    <t>0103050019</t>
+  </si>
+  <si>
+    <t>0103050020</t>
+  </si>
+  <si>
+    <t>0103050021</t>
+  </si>
+  <si>
+    <t>0103050022</t>
+  </si>
+  <si>
+    <t>0103050023</t>
+  </si>
+  <si>
+    <t>0103050024</t>
+  </si>
+  <si>
+    <t>0103050025</t>
+  </si>
+  <si>
+    <t>0103050026</t>
+  </si>
+  <si>
+    <t>0103050027</t>
+  </si>
+  <si>
+    <t>WK</t>
+  </si>
+  <si>
+    <t>Doce WK Abóbora / Coco 50G</t>
+  </si>
+  <si>
+    <t>Doce WK Alfajor 60G</t>
+  </si>
+  <si>
+    <t>Doce WK Brigadeiro 50G</t>
+  </si>
+  <si>
+    <t>Doce WK Beijo De Ninho 50G</t>
+  </si>
+  <si>
+    <t>Doce WK Banana Zero</t>
+  </si>
+  <si>
+    <t>Doce WK Banana</t>
+  </si>
+  <si>
+    <t>Doce WK Cocada Cremosa 48G</t>
+  </si>
+  <si>
+    <t>Doce WK Cocada Amor Br/Pt 60G</t>
+  </si>
+  <si>
+    <t>Doce WK Chocomoça 60G</t>
+  </si>
+  <si>
+    <t>Doce WK Pé De Moça 60G</t>
+  </si>
+  <si>
+    <t>Doce WK Doce L. Chocolate 50G</t>
+  </si>
+  <si>
+    <t>Doce WK Doce L. Goiaba 50G</t>
+  </si>
+  <si>
+    <t>Doce WK Geleia Mocotó 60G</t>
+  </si>
+  <si>
+    <t>Doce WK Geleia Mocotó 350G</t>
+  </si>
+  <si>
+    <t>Doce WK Goiabinha Cx 15 Un 300G</t>
+  </si>
+  <si>
+    <t>Doce WK Paçoca Zélia Cx 65G</t>
+  </si>
+  <si>
+    <t>Doce WK Palha Italiana 48G</t>
+  </si>
+  <si>
+    <t>Doce WK Palha De Ninho 48G</t>
+  </si>
+  <si>
+    <t>Doce WK Pingo De Leite 48G</t>
+  </si>
+  <si>
+    <t>Doce WK Pão De Mel 80G</t>
+  </si>
+  <si>
+    <t>Doce WK Shot Cachaça</t>
+  </si>
+  <si>
+    <t>Doce WK Shot Licores</t>
+  </si>
+  <si>
+    <t>Doce WK Canudos Docelan Doce De Leite 85</t>
+  </si>
+  <si>
+    <t>Doce WK Canudos Wk Doce De Leite Display 60</t>
+  </si>
+  <si>
+    <t>Doce WK Paçocao Caseiro 85G</t>
+  </si>
+  <si>
+    <t>Doce WK Ninho Display 35 Bolinhas</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G</t>
   </si>
 </sst>
 </file>
@@ -954,9 +1317,18 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1317,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -4267,8 +4639,7 @@
         <v>107.41</v>
       </c>
       <c r="G128">
-        <f>F128/E128</f>
-        <v>12.001117318435755</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4291,7 +4662,6 @@
         <v>115.68</v>
       </c>
       <c r="G129">
-        <f t="shared" ref="G129:G192" si="0">F129/E129</f>
         <v>12</v>
       </c>
     </row>
@@ -4315,7 +4685,6 @@
         <v>28.56</v>
       </c>
       <c r="G130">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4339,7 +4708,6 @@
         <v>28.56</v>
       </c>
       <c r="G131">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4363,7 +4731,6 @@
         <v>41.92</v>
       </c>
       <c r="G132">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4387,7 +4754,6 @@
         <v>48.92</v>
       </c>
       <c r="G133">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4411,7 +4777,6 @@
         <v>48.92</v>
       </c>
       <c r="G134">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4435,7 +4800,6 @@
         <v>62.92</v>
       </c>
       <c r="G135">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4459,7 +4823,7 @@
         <v>62.92</v>
       </c>
       <c r="G136">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G129:G192" si="0">F136/E136</f>
         <v>1</v>
       </c>
     </row>
@@ -4483,8 +4847,7 @@
         <v>123.95</v>
       </c>
       <c r="G137">
-        <f t="shared" si="0"/>
-        <v>11.999031945788964</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -4507,8 +4870,7 @@
         <v>123.95</v>
       </c>
       <c r="G138">
-        <f t="shared" si="0"/>
-        <v>11.999031945788964</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -4531,8 +4893,7 @@
         <v>123.95</v>
       </c>
       <c r="G139">
-        <f t="shared" si="0"/>
-        <v>11.999031945788964</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -4555,8 +4916,7 @@
         <v>123.95</v>
       </c>
       <c r="G140">
-        <f t="shared" si="0"/>
-        <v>11.999031945788964</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -4579,7 +4939,6 @@
         <v>68.84</v>
       </c>
       <c r="G141">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4603,7 +4962,6 @@
         <v>68.84</v>
       </c>
       <c r="G142">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4627,8 +4985,7 @@
         <v>98.4</v>
       </c>
       <c r="G143">
-        <f t="shared" si="0"/>
-        <v>12.000000000000002</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -4651,7 +5008,6 @@
         <v>25.19</v>
       </c>
       <c r="G144">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4675,7 +5031,6 @@
         <v>27.92</v>
       </c>
       <c r="G145">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4699,7 +5054,6 @@
         <v>41.92</v>
       </c>
       <c r="G146">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4723,7 +5077,6 @@
         <v>55.92</v>
       </c>
       <c r="G147">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -4747,7 +5100,6 @@
         <v>89.7</v>
       </c>
       <c r="G148">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -4771,7 +5123,6 @@
         <v>89.7</v>
       </c>
       <c r="G149">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -4795,8 +5146,7 @@
         <v>64.5</v>
       </c>
       <c r="G150">
-        <f t="shared" si="0"/>
-        <v>36.033519553072622</v>
+        <v>36</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -4819,8 +5169,7 @@
         <v>64.5</v>
       </c>
       <c r="G151">
-        <f t="shared" si="0"/>
-        <v>36.033519553072622</v>
+        <v>36</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -4843,8 +5192,7 @@
         <v>93.4</v>
       </c>
       <c r="G152">
-        <f t="shared" si="0"/>
-        <v>12.005141388174808</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -4867,8 +5215,7 @@
         <v>93.4</v>
       </c>
       <c r="G153">
-        <f t="shared" si="0"/>
-        <v>12.005141388174808</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -4891,8 +5238,7 @@
         <v>186.88</v>
       </c>
       <c r="G154">
-        <f t="shared" si="0"/>
-        <v>12.002569043031471</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -4915,8 +5261,7 @@
         <v>64.64</v>
       </c>
       <c r="G155">
-        <f t="shared" si="0"/>
-        <v>11.992578849721708</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -4939,8 +5284,7 @@
         <v>64.64</v>
       </c>
       <c r="G156">
-        <f t="shared" si="0"/>
-        <v>11.992578849721708</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -4963,8 +5307,7 @@
         <v>136.55000000000001</v>
       </c>
       <c r="G157">
-        <f t="shared" si="0"/>
-        <v>11.999121265377855</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,8 +5330,7 @@
         <v>136.55000000000001</v>
       </c>
       <c r="G158">
-        <f t="shared" si="0"/>
-        <v>11.999121265377855</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5011,8 +5353,7 @@
         <v>59.8</v>
       </c>
       <c r="G159">
-        <f t="shared" si="0"/>
-        <v>19.999999999999996</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5035,8 +5376,7 @@
         <v>107.74</v>
       </c>
       <c r="G160">
-        <f t="shared" si="0"/>
-        <v>19.988868274582561</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5059,8 +5399,7 @@
         <v>107.74</v>
       </c>
       <c r="G161">
-        <f t="shared" si="0"/>
-        <v>19.988868274582561</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5083,8 +5422,7 @@
         <v>64.64</v>
       </c>
       <c r="G162">
-        <f t="shared" si="0"/>
-        <v>11.992578849721708</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5107,8 +5445,7 @@
         <v>64.64</v>
       </c>
       <c r="G163">
-        <f t="shared" si="0"/>
-        <v>11.992578849721708</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5131,8 +5468,7 @@
         <v>86.21</v>
       </c>
       <c r="G164">
-        <f t="shared" si="0"/>
-        <v>12.006963788300835</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5155,8 +5491,7 @@
         <v>100.59</v>
       </c>
       <c r="G165">
-        <f t="shared" si="0"/>
-        <v>12.003579952267302</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5179,8 +5514,7 @@
         <v>143.09</v>
       </c>
       <c r="G166">
-        <f t="shared" si="0"/>
-        <v>12.004194630872483</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5203,8 +5537,7 @@
         <v>191.5</v>
       </c>
       <c r="G167">
-        <f t="shared" si="0"/>
-        <v>3.9995822890559731</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5227,8 +5560,7 @@
         <v>29.66</v>
       </c>
       <c r="G168">
-        <f t="shared" si="0"/>
-        <v>5.0016863406408101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5244,9 +5576,14 @@
       <c r="D169" t="s">
         <v>27</v>
       </c>
-      <c r="G169" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E169">
+        <v>5.93</v>
+      </c>
+      <c r="F169">
+        <v>29.66</v>
+      </c>
+      <c r="G169">
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5262,9 +5599,14 @@
       <c r="D170" t="s">
         <v>27</v>
       </c>
-      <c r="G170" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E170">
+        <v>9.58</v>
+      </c>
+      <c r="F170">
+        <v>57.49</v>
+      </c>
+      <c r="G170">
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5280,9 +5622,14 @@
       <c r="D171" t="s">
         <v>27</v>
       </c>
-      <c r="G171" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E171">
+        <v>9.58</v>
+      </c>
+      <c r="F171">
+        <v>57.49</v>
+      </c>
+      <c r="G171">
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5298,9 +5645,14 @@
       <c r="D172" t="s">
         <v>27</v>
       </c>
-      <c r="G172" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E172">
+        <v>10.78</v>
+      </c>
+      <c r="F172">
+        <v>129.35</v>
+      </c>
+      <c r="G172">
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5316,9 +5668,14 @@
       <c r="D173" t="s">
         <v>27</v>
       </c>
-      <c r="G173" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E173">
+        <v>10.78</v>
+      </c>
+      <c r="F173">
+        <v>129.35</v>
+      </c>
+      <c r="G173">
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5334,9 +5691,14 @@
       <c r="D174" t="s">
         <v>27</v>
       </c>
-      <c r="G174" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E174">
+        <v>10.78</v>
+      </c>
+      <c r="F174">
+        <v>129.35</v>
+      </c>
+      <c r="G174">
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -5352,9 +5714,14 @@
       <c r="D175" t="s">
         <v>27</v>
       </c>
-      <c r="G175" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E175">
+        <v>11.92</v>
+      </c>
+      <c r="F175">
+        <v>143.09</v>
+      </c>
+      <c r="G175">
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,9 +5737,14 @@
       <c r="D176" t="s">
         <v>27</v>
       </c>
-      <c r="G176" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E176">
+        <v>7.18</v>
+      </c>
+      <c r="F176">
+        <v>86.21</v>
+      </c>
+      <c r="G176">
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -5388,9 +5760,14 @@
       <c r="D177" t="s">
         <v>27</v>
       </c>
-      <c r="G177" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E177">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F177">
+        <v>100.59</v>
+      </c>
+      <c r="G177">
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -5406,9 +5783,14 @@
       <c r="D178" t="s">
         <v>27</v>
       </c>
-      <c r="G178" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E178">
+        <v>9.58</v>
+      </c>
+      <c r="F178">
+        <v>114.97</v>
+      </c>
+      <c r="G178">
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,9 +5806,14 @@
       <c r="D179" t="s">
         <v>27</v>
       </c>
-      <c r="G179" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E179">
+        <v>11.92</v>
+      </c>
+      <c r="F179">
+        <v>143.09</v>
+      </c>
+      <c r="G179">
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -5442,9 +5829,14 @@
       <c r="D180" t="s">
         <v>27</v>
       </c>
-      <c r="G180" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E180">
+        <v>14.37</v>
+      </c>
+      <c r="F180">
+        <v>172.5</v>
+      </c>
+      <c r="G180">
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -5460,9 +5852,14 @@
       <c r="D181" t="s">
         <v>27</v>
       </c>
-      <c r="G181" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E181">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F181">
+        <v>100.59</v>
+      </c>
+      <c r="G181">
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -5478,9 +5875,14 @@
       <c r="D182" t="s">
         <v>27</v>
       </c>
-      <c r="G182" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E182">
+        <v>7.18</v>
+      </c>
+      <c r="F182">
+        <v>86.21</v>
+      </c>
+      <c r="G182">
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -5496,9 +5898,14 @@
       <c r="D183" t="s">
         <v>27</v>
       </c>
-      <c r="G183" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E183">
+        <v>9.58</v>
+      </c>
+      <c r="F183">
+        <v>114.97</v>
+      </c>
+      <c r="G183">
+        <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -5514,9 +5921,14 @@
       <c r="D184" t="s">
         <v>27</v>
       </c>
-      <c r="G184" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E184">
+        <v>11.92</v>
+      </c>
+      <c r="F184">
+        <v>143.09</v>
+      </c>
+      <c r="G184">
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -5532,9 +5944,14 @@
       <c r="D185" t="s">
         <v>27</v>
       </c>
-      <c r="G185" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E185">
+        <v>11.92</v>
+      </c>
+      <c r="F185">
+        <v>143.09</v>
+      </c>
+      <c r="G185">
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -5550,9 +5967,14 @@
       <c r="D186" t="s">
         <v>27</v>
       </c>
-      <c r="G186" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E186">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F186">
+        <v>100.59</v>
+      </c>
+      <c r="G186">
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -5568,9 +5990,14 @@
       <c r="D187" t="s">
         <v>27</v>
       </c>
-      <c r="G187" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E187">
+        <v>11.92</v>
+      </c>
+      <c r="F187">
+        <v>143.09</v>
+      </c>
+      <c r="G187">
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -5586,9 +6013,14 @@
       <c r="D188" t="s">
         <v>27</v>
       </c>
-      <c r="G188" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E188">
+        <v>21.57</v>
+      </c>
+      <c r="F188">
+        <v>258.77999999999997</v>
+      </c>
+      <c r="G188">
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -5604,9 +6036,14 @@
       <c r="D189" t="s">
         <v>27</v>
       </c>
-      <c r="G189" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E189">
+        <v>21.57</v>
+      </c>
+      <c r="F189">
+        <v>258.77999999999997</v>
+      </c>
+      <c r="G189">
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -5622,9 +6059,14 @@
       <c r="D190" t="s">
         <v>27</v>
       </c>
-      <c r="G190" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E190">
+        <v>11.92</v>
+      </c>
+      <c r="F190">
+        <v>143.09</v>
+      </c>
+      <c r="G190">
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -5640,9 +6082,14 @@
       <c r="D191" t="s">
         <v>27</v>
       </c>
-      <c r="G191" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E191">
+        <v>21.57</v>
+      </c>
+      <c r="F191">
+        <v>431.3</v>
+      </c>
+      <c r="G191">
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -5658,9 +6105,1371 @@
       <c r="D192" t="s">
         <v>27</v>
       </c>
-      <c r="G192" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="E192">
+        <v>23.91</v>
+      </c>
+      <c r="F192">
+        <v>478.16</v>
+      </c>
+      <c r="G192">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B193" t="s">
+        <v>145</v>
+      </c>
+      <c r="C193" t="s">
+        <v>147</v>
+      </c>
+      <c r="D193" t="s">
+        <v>146</v>
+      </c>
+      <c r="E193">
+        <v>5.99</v>
+      </c>
+      <c r="F193">
+        <v>5.99</v>
+      </c>
+      <c r="G193">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B194" t="s">
+        <v>145</v>
+      </c>
+      <c r="C194" t="s">
+        <v>157</v>
+      </c>
+      <c r="D194" t="s">
+        <v>146</v>
+      </c>
+      <c r="E194">
+        <v>5.99</v>
+      </c>
+      <c r="F194">
+        <v>5.99</v>
+      </c>
+      <c r="G194">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B195" t="s">
+        <v>145</v>
+      </c>
+      <c r="C195" t="s">
+        <v>158</v>
+      </c>
+      <c r="D195" t="s">
+        <v>146</v>
+      </c>
+      <c r="E195">
+        <v>5.99</v>
+      </c>
+      <c r="F195">
+        <v>5.99</v>
+      </c>
+      <c r="G195">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B196" t="s">
+        <v>145</v>
+      </c>
+      <c r="C196" t="s">
+        <v>159</v>
+      </c>
+      <c r="D196" t="s">
+        <v>146</v>
+      </c>
+      <c r="E196">
+        <v>5.99</v>
+      </c>
+      <c r="F196">
+        <v>5.99</v>
+      </c>
+      <c r="G196">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B197" t="s">
+        <v>145</v>
+      </c>
+      <c r="C197" t="s">
+        <v>160</v>
+      </c>
+      <c r="D197" t="s">
+        <v>146</v>
+      </c>
+      <c r="E197">
+        <v>5.99</v>
+      </c>
+      <c r="F197">
+        <v>5.99</v>
+      </c>
+      <c r="G197">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B198" t="s">
+        <v>145</v>
+      </c>
+      <c r="C198" t="s">
+        <v>161</v>
+      </c>
+      <c r="D198" t="s">
+        <v>146</v>
+      </c>
+      <c r="E198">
+        <v>5.99</v>
+      </c>
+      <c r="F198">
+        <v>5.99</v>
+      </c>
+      <c r="G198">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B199" t="s">
+        <v>145</v>
+      </c>
+      <c r="C199" t="s">
+        <v>162</v>
+      </c>
+      <c r="D199" t="s">
+        <v>146</v>
+      </c>
+      <c r="E199">
+        <v>5.99</v>
+      </c>
+      <c r="F199">
+        <v>5.99</v>
+      </c>
+      <c r="G199">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B200" t="s">
+        <v>145</v>
+      </c>
+      <c r="C200" t="s">
+        <v>163</v>
+      </c>
+      <c r="D200" t="s">
+        <v>146</v>
+      </c>
+      <c r="E200">
+        <v>5.99</v>
+      </c>
+      <c r="F200">
+        <v>5.99</v>
+      </c>
+      <c r="G200">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B201" t="s">
+        <v>145</v>
+      </c>
+      <c r="C201" t="s">
+        <v>164</v>
+      </c>
+      <c r="D201" t="s">
+        <v>146</v>
+      </c>
+      <c r="E201">
+        <v>1.99</v>
+      </c>
+      <c r="F201">
+        <v>1.99</v>
+      </c>
+      <c r="G201">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B202" t="s">
+        <v>145</v>
+      </c>
+      <c r="C202" t="s">
+        <v>165</v>
+      </c>
+      <c r="D202" t="s">
+        <v>146</v>
+      </c>
+      <c r="E202">
+        <v>1.99</v>
+      </c>
+      <c r="F202">
+        <v>1.99</v>
+      </c>
+      <c r="G202">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B203" t="s">
+        <v>187</v>
+      </c>
+      <c r="C203" t="s">
+        <v>188</v>
+      </c>
+      <c r="D203" t="s">
+        <v>209</v>
+      </c>
+      <c r="E203">
+        <v>6.94</v>
+      </c>
+      <c r="F203">
+        <v>83.28</v>
+      </c>
+      <c r="G203">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B204" t="s">
+        <v>187</v>
+      </c>
+      <c r="C204" t="s">
+        <v>189</v>
+      </c>
+      <c r="D204" t="s">
+        <v>209</v>
+      </c>
+      <c r="E204">
+        <v>6.94</v>
+      </c>
+      <c r="F204">
+        <v>83.28</v>
+      </c>
+      <c r="G204">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B205" t="s">
+        <v>187</v>
+      </c>
+      <c r="C205" t="s">
+        <v>190</v>
+      </c>
+      <c r="D205" t="s">
+        <v>209</v>
+      </c>
+      <c r="E205">
+        <v>3.96</v>
+      </c>
+      <c r="F205">
+        <v>118.8</v>
+      </c>
+      <c r="G205">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B206" t="s">
+        <v>187</v>
+      </c>
+      <c r="C206" t="s">
+        <v>191</v>
+      </c>
+      <c r="D206" t="s">
+        <v>209</v>
+      </c>
+      <c r="E206">
+        <v>26.64</v>
+      </c>
+      <c r="F206">
+        <v>213.12</v>
+      </c>
+      <c r="G206">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B207" t="s">
+        <v>187</v>
+      </c>
+      <c r="C207" t="s">
+        <v>192</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+      <c r="E207">
+        <v>29.8</v>
+      </c>
+      <c r="F207">
+        <v>238.4</v>
+      </c>
+      <c r="G207">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B208" t="s">
+        <v>187</v>
+      </c>
+      <c r="C208" t="s">
+        <v>193</v>
+      </c>
+      <c r="D208" t="s">
+        <v>209</v>
+      </c>
+      <c r="E208">
+        <v>12.99</v>
+      </c>
+      <c r="F208">
+        <v>155.88</v>
+      </c>
+      <c r="G208">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B209" t="s">
+        <v>187</v>
+      </c>
+      <c r="C209" t="s">
+        <v>194</v>
+      </c>
+      <c r="D209" t="s">
+        <v>209</v>
+      </c>
+      <c r="E209">
+        <v>12.99</v>
+      </c>
+      <c r="F209">
+        <v>155.88</v>
+      </c>
+      <c r="G209">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B210" t="s">
+        <v>187</v>
+      </c>
+      <c r="C210" t="s">
+        <v>195</v>
+      </c>
+      <c r="D210" t="s">
+        <v>209</v>
+      </c>
+      <c r="E210">
+        <v>12.99</v>
+      </c>
+      <c r="F210">
+        <v>155.88</v>
+      </c>
+      <c r="G210">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B211" t="s">
+        <v>187</v>
+      </c>
+      <c r="C211" t="s">
+        <v>196</v>
+      </c>
+      <c r="D211" t="s">
+        <v>209</v>
+      </c>
+      <c r="E211">
+        <v>25.58</v>
+      </c>
+      <c r="F211">
+        <v>306.95999999999998</v>
+      </c>
+      <c r="G211">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B212" t="s">
+        <v>187</v>
+      </c>
+      <c r="C212" t="s">
+        <v>197</v>
+      </c>
+      <c r="D212" t="s">
+        <v>209</v>
+      </c>
+      <c r="E212">
+        <v>23.85</v>
+      </c>
+      <c r="F212">
+        <v>95.4</v>
+      </c>
+      <c r="G212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B213" t="s">
+        <v>187</v>
+      </c>
+      <c r="C213" t="s">
+        <v>198</v>
+      </c>
+      <c r="D213" t="s">
+        <v>209</v>
+      </c>
+      <c r="E213">
+        <v>3.82</v>
+      </c>
+      <c r="F213">
+        <v>61.12</v>
+      </c>
+      <c r="G213">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B214" t="s">
+        <v>187</v>
+      </c>
+      <c r="C214" t="s">
+        <v>199</v>
+      </c>
+      <c r="D214" t="s">
+        <v>209</v>
+      </c>
+      <c r="E214">
+        <v>3.82</v>
+      </c>
+      <c r="F214">
+        <v>61.12</v>
+      </c>
+      <c r="G214">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B215" t="s">
+        <v>187</v>
+      </c>
+      <c r="C215" t="s">
+        <v>200</v>
+      </c>
+      <c r="D215" t="s">
+        <v>209</v>
+      </c>
+      <c r="E215">
+        <v>3.82</v>
+      </c>
+      <c r="F215">
+        <v>61.12</v>
+      </c>
+      <c r="G215">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B216" t="s">
+        <v>187</v>
+      </c>
+      <c r="C216" t="s">
+        <v>201</v>
+      </c>
+      <c r="D216" t="s">
+        <v>209</v>
+      </c>
+      <c r="E216">
+        <v>25.68</v>
+      </c>
+      <c r="F216">
+        <v>154.08000000000001</v>
+      </c>
+      <c r="G216">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B217" t="s">
+        <v>187</v>
+      </c>
+      <c r="C217" t="s">
+        <v>202</v>
+      </c>
+      <c r="D217" t="s">
+        <v>209</v>
+      </c>
+      <c r="E217">
+        <v>25.68</v>
+      </c>
+      <c r="F217">
+        <v>154.08000000000001</v>
+      </c>
+      <c r="G217">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B218" t="s">
+        <v>187</v>
+      </c>
+      <c r="C218" t="s">
+        <v>203</v>
+      </c>
+      <c r="D218" t="s">
+        <v>209</v>
+      </c>
+      <c r="E218">
+        <v>25.68</v>
+      </c>
+      <c r="F218">
+        <v>154.08000000000001</v>
+      </c>
+      <c r="G218">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B219" t="s">
+        <v>187</v>
+      </c>
+      <c r="C219" t="s">
+        <v>204</v>
+      </c>
+      <c r="D219" t="s">
+        <v>209</v>
+      </c>
+      <c r="E219">
+        <v>38.15</v>
+      </c>
+      <c r="F219">
+        <v>228.9</v>
+      </c>
+      <c r="G219">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B220" t="s">
+        <v>187</v>
+      </c>
+      <c r="C220" t="s">
+        <v>205</v>
+      </c>
+      <c r="D220" t="s">
+        <v>209</v>
+      </c>
+      <c r="E220">
+        <v>6.94</v>
+      </c>
+      <c r="F220">
+        <v>173.5</v>
+      </c>
+      <c r="G220">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B221" t="s">
+        <v>187</v>
+      </c>
+      <c r="C221" t="s">
+        <v>206</v>
+      </c>
+      <c r="D221" t="s">
+        <v>209</v>
+      </c>
+      <c r="E221">
+        <v>35.76</v>
+      </c>
+      <c r="F221">
+        <v>214.56</v>
+      </c>
+      <c r="G221">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B222" t="s">
+        <v>187</v>
+      </c>
+      <c r="C222" t="s">
+        <v>207</v>
+      </c>
+      <c r="D222" t="s">
+        <v>209</v>
+      </c>
+      <c r="E222">
+        <v>13.68</v>
+      </c>
+      <c r="F222">
+        <v>164.16</v>
+      </c>
+      <c r="G222">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B223" t="s">
+        <v>187</v>
+      </c>
+      <c r="C223" t="s">
+        <v>208</v>
+      </c>
+      <c r="D223" t="s">
+        <v>209</v>
+      </c>
+      <c r="E223">
+        <v>15.13</v>
+      </c>
+      <c r="F223">
+        <v>181.56</v>
+      </c>
+      <c r="G223">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B224" t="s">
+        <v>187</v>
+      </c>
+      <c r="C224" t="s">
+        <v>200</v>
+      </c>
+      <c r="D224" t="s">
+        <v>209</v>
+      </c>
+      <c r="E224">
+        <v>16.61</v>
+      </c>
+      <c r="F224">
+        <v>265.76</v>
+      </c>
+      <c r="G224">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B225" t="s">
+        <v>187</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D225" t="s">
+        <v>237</v>
+      </c>
+      <c r="E225" s="3">
+        <v>56</v>
+      </c>
+      <c r="F225" s="3">
+        <v>56</v>
+      </c>
+      <c r="G225" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B226" t="s">
+        <v>187</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D226" t="s">
+        <v>237</v>
+      </c>
+      <c r="E226" s="3">
+        <v>95</v>
+      </c>
+      <c r="F226" s="3">
+        <v>95</v>
+      </c>
+      <c r="G226" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B227" t="s">
+        <v>187</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D227" t="s">
+        <v>237</v>
+      </c>
+      <c r="E227" s="3">
+        <v>44</v>
+      </c>
+      <c r="F227" s="3">
+        <v>44</v>
+      </c>
+      <c r="G227" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B228" t="s">
+        <v>187</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D228" t="s">
+        <v>237</v>
+      </c>
+      <c r="E228" s="3">
+        <v>44</v>
+      </c>
+      <c r="F228" s="3">
+        <v>44</v>
+      </c>
+      <c r="G228" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B229" t="s">
+        <v>187</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D229" t="s">
+        <v>237</v>
+      </c>
+      <c r="E229" s="3">
+        <v>52</v>
+      </c>
+      <c r="F229" s="3">
+        <v>52</v>
+      </c>
+      <c r="G229" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B230" t="s">
+        <v>187</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D230" t="s">
+        <v>237</v>
+      </c>
+      <c r="E230" s="3">
+        <v>56</v>
+      </c>
+      <c r="F230" s="3">
+        <v>56</v>
+      </c>
+      <c r="G230" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B231" t="s">
+        <v>187</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D231" t="s">
+        <v>237</v>
+      </c>
+      <c r="E231" s="3">
+        <v>60</v>
+      </c>
+      <c r="F231" s="3">
+        <v>60</v>
+      </c>
+      <c r="G231" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B232" t="s">
+        <v>187</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D232" t="s">
+        <v>237</v>
+      </c>
+      <c r="E232" s="3">
+        <v>80</v>
+      </c>
+      <c r="F232" s="3">
+        <v>80</v>
+      </c>
+      <c r="G232" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B233" t="s">
+        <v>187</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D233" t="s">
+        <v>237</v>
+      </c>
+      <c r="E233" s="3">
+        <v>56</v>
+      </c>
+      <c r="F233" s="3">
+        <v>56</v>
+      </c>
+      <c r="G233" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B234" t="s">
+        <v>187</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D234" t="s">
+        <v>237</v>
+      </c>
+      <c r="E234" s="3">
+        <v>56</v>
+      </c>
+      <c r="F234" s="3">
+        <v>56</v>
+      </c>
+      <c r="G234" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B235" t="s">
+        <v>187</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+      <c r="E235" s="3">
+        <v>44</v>
+      </c>
+      <c r="F235" s="3">
+        <v>44</v>
+      </c>
+      <c r="G235" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B236" t="s">
+        <v>187</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D236" t="s">
+        <v>237</v>
+      </c>
+      <c r="E236" s="3">
+        <v>44</v>
+      </c>
+      <c r="F236" s="3">
+        <v>44</v>
+      </c>
+      <c r="G236" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B237" t="s">
+        <v>187</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D237" t="s">
+        <v>237</v>
+      </c>
+      <c r="E237" s="3">
+        <v>75</v>
+      </c>
+      <c r="F237" s="3">
+        <v>75</v>
+      </c>
+      <c r="G237" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B238" t="s">
+        <v>187</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D238" t="s">
+        <v>237</v>
+      </c>
+      <c r="E238" s="3">
+        <v>13</v>
+      </c>
+      <c r="F238" s="3">
+        <v>13</v>
+      </c>
+      <c r="G238" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B239" t="s">
+        <v>187</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D239" t="s">
+        <v>237</v>
+      </c>
+      <c r="E239" s="3">
+        <v>205</v>
+      </c>
+      <c r="F239" s="3">
+        <v>205</v>
+      </c>
+      <c r="G239" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B240" t="s">
+        <v>187</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D240" t="s">
+        <v>237</v>
+      </c>
+      <c r="E240" s="3">
+        <v>42</v>
+      </c>
+      <c r="F240" s="3">
+        <v>42</v>
+      </c>
+      <c r="G240" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B241" t="s">
+        <v>187</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D241" t="s">
+        <v>237</v>
+      </c>
+      <c r="E241" s="3">
+        <v>44</v>
+      </c>
+      <c r="F241" s="3">
+        <v>44</v>
+      </c>
+      <c r="G241" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B242" t="s">
+        <v>187</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D242" t="s">
+        <v>237</v>
+      </c>
+      <c r="E242" s="3">
+        <v>44</v>
+      </c>
+      <c r="F242" s="3">
+        <v>44</v>
+      </c>
+      <c r="G242" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B243" t="s">
+        <v>187</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D243" t="s">
+        <v>237</v>
+      </c>
+      <c r="E243" s="3">
+        <v>44</v>
+      </c>
+      <c r="F243" s="3">
+        <v>44</v>
+      </c>
+      <c r="G243" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B244" t="s">
+        <v>187</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D244" t="s">
+        <v>237</v>
+      </c>
+      <c r="E244" s="3">
+        <v>128</v>
+      </c>
+      <c r="F244" s="3">
+        <v>128</v>
+      </c>
+      <c r="G244" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B245" t="s">
+        <v>187</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D245" t="s">
+        <v>237</v>
+      </c>
+      <c r="E245" s="3">
+        <v>55</v>
+      </c>
+      <c r="F245" s="3">
+        <v>55</v>
+      </c>
+      <c r="G245" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B246" t="s">
+        <v>187</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D246" t="s">
+        <v>237</v>
+      </c>
+      <c r="E246" s="3">
+        <v>75</v>
+      </c>
+      <c r="F246" s="3">
+        <v>75</v>
+      </c>
+      <c r="G246" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B247" t="s">
+        <v>187</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D247" t="s">
+        <v>237</v>
+      </c>
+      <c r="E247" s="3">
+        <v>129</v>
+      </c>
+      <c r="F247" s="3">
+        <v>129</v>
+      </c>
+      <c r="G247" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B248" t="s">
+        <v>187</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D248" t="s">
+        <v>237</v>
+      </c>
+      <c r="E248" s="3">
+        <v>44</v>
+      </c>
+      <c r="F248" s="3">
+        <v>44</v>
+      </c>
+      <c r="G248" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B249" t="s">
+        <v>187</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D249" t="s">
+        <v>237</v>
+      </c>
+      <c r="E249" s="3">
+        <v>83</v>
+      </c>
+      <c r="F249" s="3">
+        <v>83</v>
+      </c>
+      <c r="G249" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B250" t="s">
+        <v>187</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D250" t="s">
+        <v>237</v>
+      </c>
+      <c r="E250" s="3">
+        <v>44</v>
+      </c>
+      <c r="F250" s="3">
+        <v>44</v>
+      </c>
+      <c r="G250" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B251" t="s">
+        <v>187</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D251" t="s">
+        <v>237</v>
+      </c>
+      <c r="E251" s="3">
+        <v>77</v>
+      </c>
+      <c r="F251" s="3">
+        <v>77</v>
+      </c>
+      <c r="G251" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE660974-B745-433E-8F2F-717B83085E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4945E1E8-981E-474D-A1CC-552AA5A19434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
   <sheets>
     <sheet name="base_de_produtos" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -4823,7 +4824,7 @@
         <v>62.92</v>
       </c>
       <c r="G136">
-        <f t="shared" ref="G129:G192" si="0">F136/E136</f>
+        <f t="shared" ref="G136" si="0">F136/E136</f>
         <v>1</v>
       </c>
     </row>
@@ -7477,4 +7478,13 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4945E1E8-981E-474D-A1CC-552AA5A19434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF35AC5A-B65B-4A81-AEF5-B5F0A8745424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
   <sheets>
     <sheet name="base_de_produtos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="371">
   <si>
     <t>categoria</t>
   </si>
@@ -110,9 +110,6 @@
     <t>Erv SP270 500g  Erva Mate Ice Cross</t>
   </si>
   <si>
-    <t>00000</t>
-  </si>
-  <si>
     <t>Pet Var</t>
   </si>
   <si>
@@ -816,6 +813,327 @@
   </si>
   <si>
     <t>Doce WK Cone Trufado 60G</t>
+  </si>
+  <si>
+    <t>20182P</t>
+  </si>
+  <si>
+    <t>20236P</t>
+  </si>
+  <si>
+    <t>20328P</t>
+  </si>
+  <si>
+    <t>20199P</t>
+  </si>
+  <si>
+    <t>20243P</t>
+  </si>
+  <si>
+    <t>20205P</t>
+  </si>
+  <si>
+    <t>20250P</t>
+  </si>
+  <si>
+    <t>20212P</t>
+  </si>
+  <si>
+    <t>20267P</t>
+  </si>
+  <si>
+    <t>20366P</t>
+  </si>
+  <si>
+    <t>20403P</t>
+  </si>
+  <si>
+    <t>20410P</t>
+  </si>
+  <si>
+    <t>20441P</t>
+  </si>
+  <si>
+    <t>20496P</t>
+  </si>
+  <si>
+    <t>20540P</t>
+  </si>
+  <si>
+    <t>20458P</t>
+  </si>
+  <si>
+    <t>20502P</t>
+  </si>
+  <si>
+    <t>20557P</t>
+  </si>
+  <si>
+    <t>20465P</t>
+  </si>
+  <si>
+    <t>20519P</t>
+  </si>
+  <si>
+    <t>20564P</t>
+  </si>
+  <si>
+    <t>20472P</t>
+  </si>
+  <si>
+    <t>20526P</t>
+  </si>
+  <si>
+    <t>20489P</t>
+  </si>
+  <si>
+    <t>20533P</t>
+  </si>
+  <si>
+    <t>20588P</t>
+  </si>
+  <si>
+    <t>20618P</t>
+  </si>
+  <si>
+    <t>20625P</t>
+  </si>
+  <si>
+    <t>20656P</t>
+  </si>
+  <si>
+    <t>20595P</t>
+  </si>
+  <si>
+    <t>20632P</t>
+  </si>
+  <si>
+    <t>20601P</t>
+  </si>
+  <si>
+    <t>20649P</t>
+  </si>
+  <si>
+    <t>20687P</t>
+  </si>
+  <si>
+    <t>20694P</t>
+  </si>
+  <si>
+    <t>20700P</t>
+  </si>
+  <si>
+    <t>20717P</t>
+  </si>
+  <si>
+    <t>20724P</t>
+  </si>
+  <si>
+    <t>22049P</t>
+  </si>
+  <si>
+    <t>22056P</t>
+  </si>
+  <si>
+    <t>20809P</t>
+  </si>
+  <si>
+    <t>20816P</t>
+  </si>
+  <si>
+    <t>20823P</t>
+  </si>
+  <si>
+    <t>20830P</t>
+  </si>
+  <si>
+    <t>20847P</t>
+  </si>
+  <si>
+    <t>20854P</t>
+  </si>
+  <si>
+    <t>20861P</t>
+  </si>
+  <si>
+    <t>20878P</t>
+  </si>
+  <si>
+    <t>20960P</t>
+  </si>
+  <si>
+    <t>20984P</t>
+  </si>
+  <si>
+    <t>21059P</t>
+  </si>
+  <si>
+    <t>21066P</t>
+  </si>
+  <si>
+    <t>21073P</t>
+  </si>
+  <si>
+    <t>21080P</t>
+  </si>
+  <si>
+    <t>21097P</t>
+  </si>
+  <si>
+    <t>21103P</t>
+  </si>
+  <si>
+    <t>21141P</t>
+  </si>
+  <si>
+    <t>21158P</t>
+  </si>
+  <si>
+    <t>21165P</t>
+  </si>
+  <si>
+    <t>21172P</t>
+  </si>
+  <si>
+    <t>21189P</t>
+  </si>
+  <si>
+    <t>21196P</t>
+  </si>
+  <si>
+    <t>21202P</t>
+  </si>
+  <si>
+    <t>21424P</t>
+  </si>
+  <si>
+    <t>21431P</t>
+  </si>
+  <si>
+    <t>21448P</t>
+  </si>
+  <si>
+    <t>21462P</t>
+  </si>
+  <si>
+    <t>21479P</t>
+  </si>
+  <si>
+    <t>21486P</t>
+  </si>
+  <si>
+    <t>21493P</t>
+  </si>
+  <si>
+    <t>21509P</t>
+  </si>
+  <si>
+    <t>21516P</t>
+  </si>
+  <si>
+    <t>21523P</t>
+  </si>
+  <si>
+    <t>00000P</t>
+  </si>
+  <si>
+    <t>22162P</t>
+  </si>
+  <si>
+    <t>21530P</t>
+  </si>
+  <si>
+    <t>22155P</t>
+  </si>
+  <si>
+    <t>21547P</t>
+  </si>
+  <si>
+    <t>21554P</t>
+  </si>
+  <si>
+    <t>22094P</t>
+  </si>
+  <si>
+    <t>21561P</t>
+  </si>
+  <si>
+    <t>21578P</t>
+  </si>
+  <si>
+    <t>21585P</t>
+  </si>
+  <si>
+    <t>21592P</t>
+  </si>
+  <si>
+    <t>21608P</t>
+  </si>
+  <si>
+    <t>22421P</t>
+  </si>
+  <si>
+    <t>22438P</t>
+  </si>
+  <si>
+    <t>22353P</t>
+  </si>
+  <si>
+    <t>22360P</t>
+  </si>
+  <si>
+    <t>22377P</t>
+  </si>
+  <si>
+    <t>22414P</t>
+  </si>
+  <si>
+    <t>21714P</t>
+  </si>
+  <si>
+    <t>22186P</t>
+  </si>
+  <si>
+    <t>22339P</t>
+  </si>
+  <si>
+    <t>22346P</t>
+  </si>
+  <si>
+    <t>21721P</t>
+  </si>
+  <si>
+    <t>22391P</t>
+  </si>
+  <si>
+    <t>22407P</t>
+  </si>
+  <si>
+    <t>21745P</t>
+  </si>
+  <si>
+    <t>21752P</t>
+  </si>
+  <si>
+    <t>21776P</t>
+  </si>
+  <si>
+    <t>21783P</t>
+  </si>
+  <si>
+    <t>21790P</t>
+  </si>
+  <si>
+    <t>22315P</t>
+  </si>
+  <si>
+    <t>21844P</t>
+  </si>
+  <si>
+    <t>21899P</t>
+  </si>
+  <si>
+    <t>20182</t>
   </si>
 </sst>
 </file>
@@ -1930,14 +2248,14 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>20182</v>
+      <c r="A11" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -1953,14 +2271,14 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>20236</v>
+      <c r="A12" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
@@ -1976,14 +2294,14 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>20328</v>
+      <c r="A13" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -1999,14 +2317,14 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>20199</v>
+      <c r="A14" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -2022,14 +2340,14 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>20243</v>
+      <c r="A15" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
@@ -2045,14 +2363,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>20205</v>
+      <c r="A16" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -2068,14 +2386,14 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>20250</v>
+      <c r="A17" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
@@ -2091,14 +2409,14 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>20212</v>
+      <c r="A18" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
@@ -2114,14 +2432,14 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>20267</v>
+      <c r="A19" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -2137,14 +2455,14 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>20366</v>
+      <c r="A20" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -2160,14 +2478,14 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>20403</v>
+      <c r="A21" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -2183,14 +2501,14 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>20410</v>
+      <c r="A22" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -2206,14 +2524,14 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>20441</v>
+      <c r="A23" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -2229,14 +2547,14 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>20496</v>
+      <c r="A24" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -2252,14 +2570,14 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>20540</v>
+      <c r="A25" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -2275,14 +2593,14 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>20458</v>
+      <c r="A26" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
@@ -2298,14 +2616,14 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>20502</v>
+      <c r="A27" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
@@ -2321,14 +2639,14 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>20557</v>
+      <c r="A28" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
@@ -2344,14 +2662,14 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>20465</v>
+      <c r="A29" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -2367,14 +2685,14 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>20519</v>
+      <c r="A30" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -2390,14 +2708,14 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>20564</v>
+      <c r="A31" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -2413,14 +2731,14 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>20472</v>
+      <c r="A32" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -2436,14 +2754,14 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>20526</v>
+      <c r="A33" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -2459,14 +2777,14 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>20489</v>
+      <c r="A34" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -2482,14 +2800,14 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>20533</v>
+      <c r="A35" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -2505,14 +2823,14 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>20588</v>
+      <c r="A36" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="B36" t="s">
         <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -2528,14 +2846,14 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>20618</v>
+      <c r="A37" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -2551,14 +2869,14 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>20625</v>
+      <c r="A38" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
@@ -2574,14 +2892,14 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>20656</v>
+      <c r="A39" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -2597,14 +2915,14 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>20595</v>
+      <c r="A40" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -2620,14 +2938,14 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>20632</v>
+      <c r="A41" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -2643,14 +2961,14 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>20601</v>
+      <c r="A42" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -2666,14 +2984,14 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>20649</v>
+      <c r="A43" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -2689,14 +3007,14 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>20687</v>
+      <c r="A44" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -2712,14 +3030,14 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>20694</v>
+      <c r="A45" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -2735,14 +3053,14 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>20700</v>
+      <c r="A46" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -2758,14 +3076,14 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>20717</v>
+      <c r="A47" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -2781,14 +3099,14 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>20724</v>
+      <c r="A48" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="B48" t="s">
         <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -2804,14 +3122,14 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>22049</v>
+      <c r="A49" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -2827,14 +3145,14 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>22056</v>
+      <c r="A50" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -2850,14 +3168,14 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>20809</v>
+      <c r="A51" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -2873,14 +3191,14 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>20816</v>
+      <c r="A52" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -2896,14 +3214,14 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>20823</v>
+      <c r="A53" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -2919,14 +3237,14 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>20830</v>
+      <c r="A54" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="B54" t="s">
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -2942,14 +3260,14 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>20847</v>
+      <c r="A55" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -2965,14 +3283,14 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>20854</v>
+      <c r="A56" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="B56" t="s">
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -2988,14 +3306,14 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>20861</v>
+      <c r="A57" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -3011,14 +3329,14 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>20878</v>
+      <c r="A58" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -3034,14 +3352,14 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>20960</v>
+      <c r="A59" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -3057,14 +3375,14 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>20984</v>
+      <c r="A60" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -3080,14 +3398,14 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>21059</v>
+      <c r="A61" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="B61" t="s">
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -3103,14 +3421,14 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>21066</v>
+      <c r="A62" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="B62" t="s">
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
         <v>27</v>
@@ -3126,14 +3444,14 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>21073</v>
+      <c r="A63" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
         <v>27</v>
@@ -3149,14 +3467,14 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>21080</v>
+      <c r="A64" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
         <v>27</v>
@@ -3172,14 +3490,14 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>21097</v>
+      <c r="A65" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="B65" t="s">
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D65" t="s">
         <v>27</v>
@@ -3195,14 +3513,14 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>21103</v>
+      <c r="A66" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="B66" t="s">
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D66" t="s">
         <v>27</v>
@@ -3218,14 +3536,14 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>21141</v>
+      <c r="A67" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
         <v>27</v>
@@ -3241,14 +3559,14 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>21158</v>
+      <c r="A68" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
         <v>27</v>
@@ -3264,14 +3582,14 @@
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>21165</v>
+      <c r="A69" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="B69" t="s">
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D69" t="s">
         <v>27</v>
@@ -3287,14 +3605,14 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>21172</v>
+      <c r="A70" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="B70" t="s">
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D70" t="s">
         <v>27</v>
@@ -3310,14 +3628,14 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>21189</v>
+      <c r="A71" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="B71" t="s">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D71" t="s">
         <v>27</v>
@@ -3333,14 +3651,14 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>21196</v>
+      <c r="A72" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="B72" t="s">
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D72" t="s">
         <v>27</v>
@@ -3356,14 +3674,14 @@
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>21202</v>
+      <c r="A73" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="B73" t="s">
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
@@ -3379,14 +3697,14 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>21424</v>
+      <c r="A74" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="B74" t="s">
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D74" t="s">
         <v>27</v>
@@ -3402,14 +3720,14 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>21431</v>
+      <c r="A75" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="B75" t="s">
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D75" t="s">
         <v>27</v>
@@ -3425,14 +3743,14 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>21448</v>
+      <c r="A76" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="B76" t="s">
         <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
         <v>27</v>
@@ -3448,14 +3766,14 @@
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>21462</v>
+      <c r="A77" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="B77" t="s">
         <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D77" t="s">
         <v>27</v>
@@ -3471,14 +3789,14 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>21479</v>
+      <c r="A78" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="B78" t="s">
         <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D78" t="s">
         <v>27</v>
@@ -3494,14 +3812,14 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>21486</v>
+      <c r="A79" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="B79" t="s">
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D79" t="s">
         <v>27</v>
@@ -3517,14 +3835,14 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>21493</v>
+      <c r="A80" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="B80" t="s">
         <v>26</v>
       </c>
       <c r="C80" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D80" t="s">
         <v>27</v>
@@ -3540,14 +3858,14 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>21509</v>
+      <c r="A81" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D81" t="s">
         <v>27</v>
@@ -3563,14 +3881,14 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>21516</v>
+      <c r="A82" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="B82" t="s">
         <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
         <v>27</v>
@@ -3586,14 +3904,14 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>21523</v>
+      <c r="A83" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="B83" t="s">
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D83" t="s">
         <v>27</v>
@@ -3610,13 +3928,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>29</v>
+        <v>337</v>
       </c>
       <c r="B84" t="s">
         <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D84" t="s">
         <v>27</v>
@@ -3632,14 +3950,14 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>22162</v>
+      <c r="A85" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="B85" t="s">
         <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D85" t="s">
         <v>27</v>
@@ -3655,14 +3973,14 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>21530</v>
+      <c r="A86" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="B86" t="s">
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D86" t="s">
         <v>27</v>
@@ -3678,14 +3996,14 @@
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>22155</v>
+      <c r="A87" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="B87" t="s">
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D87" t="s">
         <v>27</v>
@@ -3701,14 +4019,14 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>21547</v>
+      <c r="A88" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="B88" t="s">
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D88" t="s">
         <v>27</v>
@@ -3724,14 +4042,14 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>21554</v>
+      <c r="A89" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="B89" t="s">
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
         <v>27</v>
@@ -3747,14 +4065,14 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>22094</v>
+      <c r="A90" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="B90" t="s">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D90" t="s">
         <v>27</v>
@@ -3770,14 +4088,14 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>21561</v>
+      <c r="A91" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="B91" t="s">
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D91" t="s">
         <v>27</v>
@@ -3793,14 +4111,14 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>21578</v>
+      <c r="A92" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="B92" t="s">
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
         <v>27</v>
@@ -3816,14 +4134,14 @@
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>21585</v>
+      <c r="A93" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="B93" t="s">
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D93" t="s">
         <v>27</v>
@@ -3839,14 +4157,14 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>21592</v>
+      <c r="A94" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="B94" t="s">
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D94" t="s">
         <v>27</v>
@@ -3862,14 +4180,14 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>21608</v>
+      <c r="A95" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="B95" t="s">
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D95" t="s">
         <v>27</v>
@@ -3885,14 +4203,14 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>22421</v>
+      <c r="A96" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D96" t="s">
         <v>27</v>
@@ -3908,14 +4226,14 @@
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>22438</v>
+      <c r="A97" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="B97" t="s">
         <v>26</v>
       </c>
       <c r="C97" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D97" t="s">
         <v>27</v>
@@ -3931,14 +4249,14 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>22353</v>
+      <c r="A98" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="B98" t="s">
         <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
         <v>27</v>
@@ -3954,14 +4272,14 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>22360</v>
+      <c r="A99" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="B99" t="s">
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D99" t="s">
         <v>27</v>
@@ -3977,14 +4295,14 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>22377</v>
+      <c r="A100" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="B100" t="s">
         <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D100" t="s">
         <v>27</v>
@@ -4000,14 +4318,14 @@
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>22414</v>
+      <c r="A101" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="B101" t="s">
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
         <v>27</v>
@@ -4023,14 +4341,14 @@
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>21714</v>
+      <c r="A102" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="B102" t="s">
         <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D102" t="s">
         <v>27</v>
@@ -4046,14 +4364,14 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
-        <v>22186</v>
+      <c r="A103" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D103" t="s">
         <v>27</v>
@@ -4069,14 +4387,14 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
-        <v>22339</v>
+      <c r="A104" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="B104" t="s">
         <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D104" t="s">
         <v>27</v>
@@ -4092,14 +4410,14 @@
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
-        <v>22346</v>
+      <c r="A105" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="B105" t="s">
         <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D105" t="s">
         <v>27</v>
@@ -4115,14 +4433,14 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>21721</v>
+      <c r="A106" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="B106" t="s">
         <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D106" t="s">
         <v>27</v>
@@ -4138,14 +4456,14 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
-        <v>22391</v>
+      <c r="A107" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="B107" t="s">
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D107" t="s">
         <v>27</v>
@@ -4161,14 +4479,14 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>22407</v>
+      <c r="A108" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="B108" t="s">
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D108" t="s">
         <v>27</v>
@@ -4184,14 +4502,14 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
-        <v>21745</v>
+      <c r="A109" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="B109" t="s">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D109" t="s">
         <v>27</v>
@@ -4207,14 +4525,14 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>21752</v>
+      <c r="A110" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="B110" t="s">
         <v>26</v>
       </c>
       <c r="C110" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" t="s">
         <v>27</v>
@@ -4230,14 +4548,14 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>21776</v>
+      <c r="A111" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="B111" t="s">
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D111" t="s">
         <v>27</v>
@@ -4253,14 +4571,14 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
-        <v>21783</v>
+      <c r="A112" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="B112" t="s">
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D112" t="s">
         <v>27</v>
@@ -4276,14 +4594,14 @@
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>21790</v>
+      <c r="A113" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="B113" t="s">
         <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D113" t="s">
         <v>27</v>
@@ -4299,14 +4617,14 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>22315</v>
+      <c r="A114" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="B114" t="s">
         <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D114" t="s">
         <v>27</v>
@@ -4322,14 +4640,14 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>21844</v>
+      <c r="A115" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D115" t="s">
         <v>27</v>
@@ -4345,14 +4663,14 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>21899</v>
+      <c r="A116" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="B116" t="s">
         <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D116" t="s">
         <v>27</v>
@@ -4368,14 +4686,14 @@
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>20182</v>
+      <c r="A117" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D117" t="s">
         <v>27</v>
@@ -4395,10 +4713,10 @@
         <v>20236</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D118" t="s">
         <v>27</v>
@@ -4418,10 +4736,10 @@
         <v>20328</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s">
         <v>27</v>
@@ -4441,10 +4759,10 @@
         <v>20205</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D120" t="s">
         <v>27</v>
@@ -4464,10 +4782,10 @@
         <v>20250</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D121" t="s">
         <v>27</v>
@@ -4487,10 +4805,10 @@
         <v>20212</v>
       </c>
       <c r="B122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D122" t="s">
         <v>27</v>
@@ -4510,10 +4828,10 @@
         <v>20267</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C123" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D123" t="s">
         <v>27</v>
@@ -4533,10 +4851,10 @@
         <v>20366</v>
       </c>
       <c r="B124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C124" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D124" t="s">
         <v>27</v>
@@ -4556,10 +4874,10 @@
         <v>20403</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C125" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D125" t="s">
         <v>27</v>
@@ -4579,10 +4897,10 @@
         <v>20410</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D126" t="s">
         <v>27</v>
@@ -4602,10 +4920,10 @@
         <v>20441</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C127" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D127" t="s">
         <v>27</v>
@@ -4625,10 +4943,10 @@
         <v>20496</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D128" t="s">
         <v>27</v>
@@ -4648,10 +4966,10 @@
         <v>20540</v>
       </c>
       <c r="B129" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C129" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
         <v>27</v>
@@ -4671,10 +4989,10 @@
         <v>20465</v>
       </c>
       <c r="B130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C130" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D130" t="s">
         <v>27</v>
@@ -4694,10 +5012,10 @@
         <v>20519</v>
       </c>
       <c r="B131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C131" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D131" t="s">
         <v>27</v>
@@ -4717,10 +5035,10 @@
         <v>20564</v>
       </c>
       <c r="B132" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C132" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D132" t="s">
         <v>27</v>
@@ -4740,10 +5058,10 @@
         <v>20472</v>
       </c>
       <c r="B133" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D133" t="s">
         <v>27</v>
@@ -4763,10 +5081,10 @@
         <v>20526</v>
       </c>
       <c r="B134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D134" t="s">
         <v>27</v>
@@ -4786,10 +5104,10 @@
         <v>20489</v>
       </c>
       <c r="B135" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C135" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D135" t="s">
         <v>27</v>
@@ -4809,10 +5127,10 @@
         <v>20533</v>
       </c>
       <c r="B136" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C136" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D136" t="s">
         <v>27</v>
@@ -4833,10 +5151,10 @@
         <v>20588</v>
       </c>
       <c r="B137" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D137" t="s">
         <v>27</v>
@@ -4856,10 +5174,10 @@
         <v>20618</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C138" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D138" t="s">
         <v>27</v>
@@ -4879,10 +5197,10 @@
         <v>20625</v>
       </c>
       <c r="B139" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C139" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D139" t="s">
         <v>27</v>
@@ -4902,10 +5220,10 @@
         <v>20656</v>
       </c>
       <c r="B140" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C140" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D140" t="s">
         <v>27</v>
@@ -4925,10 +5243,10 @@
         <v>20601</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D141" t="s">
         <v>27</v>
@@ -4948,10 +5266,10 @@
         <v>20649</v>
       </c>
       <c r="B142" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C142" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D142" t="s">
         <v>27</v>
@@ -4968,13 +5286,13 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B143" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D143" t="s">
         <v>27</v>
@@ -4994,10 +5312,10 @@
         <v>20687</v>
       </c>
       <c r="B144" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C144" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D144" t="s">
         <v>27</v>
@@ -5017,10 +5335,10 @@
         <v>20694</v>
       </c>
       <c r="B145" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C145" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D145" t="s">
         <v>27</v>
@@ -5040,10 +5358,10 @@
         <v>20700</v>
       </c>
       <c r="B146" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D146" t="s">
         <v>27</v>
@@ -5063,10 +5381,10 @@
         <v>20717</v>
       </c>
       <c r="B147" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C147" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D147" t="s">
         <v>27</v>
@@ -5086,10 +5404,10 @@
         <v>22049</v>
       </c>
       <c r="B148" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C148" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D148" t="s">
         <v>27</v>
@@ -5109,10 +5427,10 @@
         <v>22056</v>
       </c>
       <c r="B149" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C149" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D149" t="s">
         <v>27</v>
@@ -5132,10 +5450,10 @@
         <v>20809</v>
       </c>
       <c r="B150" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C150" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D150" t="s">
         <v>27</v>
@@ -5155,10 +5473,10 @@
         <v>20816</v>
       </c>
       <c r="B151" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C151" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D151" t="s">
         <v>27</v>
@@ -5178,10 +5496,10 @@
         <v>20847</v>
       </c>
       <c r="B152" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C152" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D152" t="s">
         <v>27</v>
@@ -5201,10 +5519,10 @@
         <v>20854</v>
       </c>
       <c r="B153" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C153" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D153" t="s">
         <v>27</v>
@@ -5224,10 +5542,10 @@
         <v>20861</v>
       </c>
       <c r="B154" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C154" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D154" t="s">
         <v>27</v>
@@ -5247,10 +5565,10 @@
         <v>20960</v>
       </c>
       <c r="B155" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C155" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D155" t="s">
         <v>27</v>
@@ -5270,10 +5588,10 @@
         <v>20984</v>
       </c>
       <c r="B156" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C156" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D156" t="s">
         <v>27</v>
@@ -5290,13 +5608,13 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B157" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D157" t="s">
         <v>27</v>
@@ -5313,13 +5631,13 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B158" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C158" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D158" t="s">
         <v>27</v>
@@ -5339,10 +5657,10 @@
         <v>21059</v>
       </c>
       <c r="B159" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C159" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D159" t="s">
         <v>27</v>
@@ -5362,10 +5680,10 @@
         <v>21097</v>
       </c>
       <c r="B160" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C160" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D160" t="s">
         <v>27</v>
@@ -5385,10 +5703,10 @@
         <v>21103</v>
       </c>
       <c r="B161" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C161" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D161" t="s">
         <v>27</v>
@@ -5408,10 +5726,10 @@
         <v>21165</v>
       </c>
       <c r="B162" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C162" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D162" t="s">
         <v>27</v>
@@ -5431,10 +5749,10 @@
         <v>21172</v>
       </c>
       <c r="B163" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C163" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D163" t="s">
         <v>27</v>
@@ -5454,10 +5772,10 @@
         <v>21189</v>
       </c>
       <c r="B164" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C164" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D164" t="s">
         <v>27</v>
@@ -5477,10 +5795,10 @@
         <v>21196</v>
       </c>
       <c r="B165" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C165" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D165" t="s">
         <v>27</v>
@@ -5500,10 +5818,10 @@
         <v>21424</v>
       </c>
       <c r="B166" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C166" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D166" t="s">
         <v>27</v>
@@ -5523,10 +5841,10 @@
         <v>21431</v>
       </c>
       <c r="B167" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C167" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D167" t="s">
         <v>27</v>
@@ -5546,10 +5864,10 @@
         <v>21448</v>
       </c>
       <c r="B168" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C168" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D168" t="s">
         <v>27</v>
@@ -5569,10 +5887,10 @@
         <v>21462</v>
       </c>
       <c r="B169" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C169" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D169" t="s">
         <v>27</v>
@@ -5592,10 +5910,10 @@
         <v>21479</v>
       </c>
       <c r="B170" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C170" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D170" t="s">
         <v>27</v>
@@ -5615,10 +5933,10 @@
         <v>21486</v>
       </c>
       <c r="B171" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D171" t="s">
         <v>27</v>
@@ -5638,10 +5956,10 @@
         <v>21493</v>
       </c>
       <c r="B172" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C172" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
         <v>27</v>
@@ -5661,10 +5979,10 @@
         <v>21509</v>
       </c>
       <c r="B173" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C173" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D173" t="s">
         <v>27</v>
@@ -5684,10 +6002,10 @@
         <v>21523</v>
       </c>
       <c r="B174" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C174" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D174" t="s">
         <v>27</v>
@@ -5704,13 +6022,13 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B175" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C175" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D175" t="s">
         <v>27</v>
@@ -5730,10 +6048,10 @@
         <v>21561</v>
       </c>
       <c r="B176" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C176" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D176" t="s">
         <v>27</v>
@@ -5753,10 +6071,10 @@
         <v>21578</v>
       </c>
       <c r="B177" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C177" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D177" t="s">
         <v>27</v>
@@ -5776,10 +6094,10 @@
         <v>21585</v>
       </c>
       <c r="B178" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C178" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D178" t="s">
         <v>27</v>
@@ -5799,10 +6117,10 @@
         <v>21592</v>
       </c>
       <c r="B179" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C179" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D179" t="s">
         <v>27</v>
@@ -5822,10 +6140,10 @@
         <v>21608</v>
       </c>
       <c r="B180" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C180" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D180" t="s">
         <v>27</v>
@@ -5845,10 +6163,10 @@
         <v>22421</v>
       </c>
       <c r="B181" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C181" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D181" t="s">
         <v>27</v>
@@ -5868,10 +6186,10 @@
         <v>22353</v>
       </c>
       <c r="B182" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C182" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D182" t="s">
         <v>27</v>
@@ -5891,10 +6209,10 @@
         <v>22360</v>
       </c>
       <c r="B183" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C183" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D183" t="s">
         <v>27</v>
@@ -5914,10 +6232,10 @@
         <v>21714</v>
       </c>
       <c r="B184" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C184" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D184" t="s">
         <v>27</v>
@@ -5937,10 +6255,10 @@
         <v>22339</v>
       </c>
       <c r="B185" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D185" t="s">
         <v>27</v>
@@ -5960,10 +6278,10 @@
         <v>22391</v>
       </c>
       <c r="B186" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C186" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D186" t="s">
         <v>27</v>
@@ -5983,10 +6301,10 @@
         <v>21745</v>
       </c>
       <c r="B187" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C187" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D187" t="s">
         <v>27</v>
@@ -6006,10 +6324,10 @@
         <v>21752</v>
       </c>
       <c r="B188" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C188" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D188" t="s">
         <v>27</v>
@@ -6029,10 +6347,10 @@
         <v>21783</v>
       </c>
       <c r="B189" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C189" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D189" t="s">
         <v>27</v>
@@ -6052,10 +6370,10 @@
         <v>21790</v>
       </c>
       <c r="B190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C190" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D190" t="s">
         <v>27</v>
@@ -6075,10 +6393,10 @@
         <v>21844</v>
       </c>
       <c r="B191" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C191" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D191" t="s">
         <v>27</v>
@@ -6098,10 +6416,10 @@
         <v>21899</v>
       </c>
       <c r="B192" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C192" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D192" t="s">
         <v>27</v>
@@ -6118,16 +6436,16 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B193" t="s">
         <v>144</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
+        <v>146</v>
+      </c>
+      <c r="D193" t="s">
         <v>145</v>
-      </c>
-      <c r="C193" t="s">
-        <v>147</v>
-      </c>
-      <c r="D193" t="s">
-        <v>146</v>
       </c>
       <c r="E193">
         <v>5.99</v>
@@ -6141,16 +6459,16 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B194" t="s">
+        <v>144</v>
+      </c>
+      <c r="C194" t="s">
+        <v>156</v>
+      </c>
+      <c r="D194" t="s">
         <v>145</v>
-      </c>
-      <c r="C194" t="s">
-        <v>157</v>
-      </c>
-      <c r="D194" t="s">
-        <v>146</v>
       </c>
       <c r="E194">
         <v>5.99</v>
@@ -6164,16 +6482,16 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B195" t="s">
+        <v>144</v>
+      </c>
+      <c r="C195" t="s">
+        <v>157</v>
+      </c>
+      <c r="D195" t="s">
         <v>145</v>
-      </c>
-      <c r="C195" t="s">
-        <v>158</v>
-      </c>
-      <c r="D195" t="s">
-        <v>146</v>
       </c>
       <c r="E195">
         <v>5.99</v>
@@ -6187,16 +6505,16 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B196" t="s">
+        <v>144</v>
+      </c>
+      <c r="C196" t="s">
+        <v>158</v>
+      </c>
+      <c r="D196" t="s">
         <v>145</v>
-      </c>
-      <c r="C196" t="s">
-        <v>159</v>
-      </c>
-      <c r="D196" t="s">
-        <v>146</v>
       </c>
       <c r="E196">
         <v>5.99</v>
@@ -6210,16 +6528,16 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B197" t="s">
+        <v>144</v>
+      </c>
+      <c r="C197" t="s">
+        <v>159</v>
+      </c>
+      <c r="D197" t="s">
         <v>145</v>
-      </c>
-      <c r="C197" t="s">
-        <v>160</v>
-      </c>
-      <c r="D197" t="s">
-        <v>146</v>
       </c>
       <c r="E197">
         <v>5.99</v>
@@ -6233,16 +6551,16 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B198" t="s">
+        <v>144</v>
+      </c>
+      <c r="C198" t="s">
+        <v>160</v>
+      </c>
+      <c r="D198" t="s">
         <v>145</v>
-      </c>
-      <c r="C198" t="s">
-        <v>161</v>
-      </c>
-      <c r="D198" t="s">
-        <v>146</v>
       </c>
       <c r="E198">
         <v>5.99</v>
@@ -6256,16 +6574,16 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B199" t="s">
+        <v>144</v>
+      </c>
+      <c r="C199" t="s">
+        <v>161</v>
+      </c>
+      <c r="D199" t="s">
         <v>145</v>
-      </c>
-      <c r="C199" t="s">
-        <v>162</v>
-      </c>
-      <c r="D199" t="s">
-        <v>146</v>
       </c>
       <c r="E199">
         <v>5.99</v>
@@ -6279,16 +6597,16 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B200" t="s">
+        <v>144</v>
+      </c>
+      <c r="C200" t="s">
+        <v>162</v>
+      </c>
+      <c r="D200" t="s">
         <v>145</v>
-      </c>
-      <c r="C200" t="s">
-        <v>163</v>
-      </c>
-      <c r="D200" t="s">
-        <v>146</v>
       </c>
       <c r="E200">
         <v>5.99</v>
@@ -6302,16 +6620,16 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B201" t="s">
+        <v>144</v>
+      </c>
+      <c r="C201" t="s">
+        <v>163</v>
+      </c>
+      <c r="D201" t="s">
         <v>145</v>
-      </c>
-      <c r="C201" t="s">
-        <v>164</v>
-      </c>
-      <c r="D201" t="s">
-        <v>146</v>
       </c>
       <c r="E201">
         <v>1.99</v>
@@ -6325,16 +6643,16 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B202" t="s">
+        <v>144</v>
+      </c>
+      <c r="C202" t="s">
+        <v>164</v>
+      </c>
+      <c r="D202" t="s">
         <v>145</v>
-      </c>
-      <c r="C202" t="s">
-        <v>165</v>
-      </c>
-      <c r="D202" t="s">
-        <v>146</v>
       </c>
       <c r="E202">
         <v>1.99</v>
@@ -6348,16 +6666,16 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B203" t="s">
+        <v>186</v>
+      </c>
+      <c r="C203" t="s">
         <v>187</v>
       </c>
-      <c r="C203" t="s">
-        <v>188</v>
-      </c>
       <c r="D203" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E203">
         <v>6.94</v>
@@ -6371,16 +6689,16 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B204" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C204" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D204" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E204">
         <v>6.94</v>
@@ -6394,16 +6712,16 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B205" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D205" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E205">
         <v>3.96</v>
@@ -6417,16 +6735,16 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C206" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D206" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E206">
         <v>26.64</v>
@@ -6440,16 +6758,16 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B207" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C207" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D207" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E207">
         <v>29.8</v>
@@ -6463,16 +6781,16 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B208" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C208" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D208" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E208">
         <v>12.99</v>
@@ -6486,16 +6804,16 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B209" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C209" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D209" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E209">
         <v>12.99</v>
@@ -6509,16 +6827,16 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B210" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C210" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D210" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E210">
         <v>12.99</v>
@@ -6532,16 +6850,16 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B211" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C211" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D211" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E211">
         <v>25.58</v>
@@ -6555,16 +6873,16 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B212" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C212" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D212" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E212">
         <v>23.85</v>
@@ -6578,16 +6896,16 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B213" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C213" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D213" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E213">
         <v>3.82</v>
@@ -6601,16 +6919,16 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B214" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C214" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D214" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E214">
         <v>3.82</v>
@@ -6624,16 +6942,16 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B215" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C215" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D215" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E215">
         <v>3.82</v>
@@ -6647,16 +6965,16 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B216" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C216" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D216" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E216">
         <v>25.68</v>
@@ -6670,16 +6988,16 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B217" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C217" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D217" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E217">
         <v>25.68</v>
@@ -6693,16 +7011,16 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B218" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C218" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D218" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E218">
         <v>25.68</v>
@@ -6716,16 +7034,16 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B219" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C219" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D219" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E219">
         <v>38.15</v>
@@ -6739,16 +7057,16 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B220" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C220" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D220" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E220">
         <v>6.94</v>
@@ -6762,16 +7080,16 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B221" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C221" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D221" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E221">
         <v>35.76</v>
@@ -6785,16 +7103,16 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B222" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C222" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D222" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E222">
         <v>13.68</v>
@@ -6808,16 +7126,16 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B223" t="s">
         <v>186</v>
       </c>
-      <c r="B223" t="s">
-        <v>187</v>
-      </c>
       <c r="C223" t="s">
+        <v>207</v>
+      </c>
+      <c r="D223" t="s">
         <v>208</v>
-      </c>
-      <c r="D223" t="s">
-        <v>209</v>
       </c>
       <c r="E223">
         <v>15.13</v>
@@ -6831,16 +7149,16 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B224" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C224" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D224" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E224">
         <v>16.61</v>
@@ -6854,16 +7172,16 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B225" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D225" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E225" s="3">
         <v>56</v>
@@ -6877,16 +7195,16 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B226" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D226" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E226" s="3">
         <v>95</v>
@@ -6900,16 +7218,16 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B227" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D227" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E227" s="3">
         <v>44</v>
@@ -6923,16 +7241,16 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B228" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D228" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E228" s="3">
         <v>44</v>
@@ -6946,16 +7264,16 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B229" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D229" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E229" s="3">
         <v>52</v>
@@ -6969,16 +7287,16 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B230" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D230" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E230" s="3">
         <v>56</v>
@@ -6992,16 +7310,16 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B231" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D231" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E231" s="3">
         <v>60</v>
@@ -7015,16 +7333,16 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B232" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D232" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E232" s="3">
         <v>80</v>
@@ -7038,16 +7356,16 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B233" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D233" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E233" s="3">
         <v>56</v>
@@ -7061,16 +7379,16 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B234" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D234" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E234" s="3">
         <v>56</v>
@@ -7084,16 +7402,16 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B235" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D235" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E235" s="3">
         <v>44</v>
@@ -7107,16 +7425,16 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B236" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D236" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E236" s="3">
         <v>44</v>
@@ -7130,16 +7448,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B237" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D237" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E237" s="3">
         <v>75</v>
@@ -7153,16 +7471,16 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B238" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D238" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E238" s="3">
         <v>13</v>
@@ -7176,16 +7494,16 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B239" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D239" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E239" s="3">
         <v>205</v>
@@ -7199,16 +7517,16 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B240" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E240" s="3">
         <v>42</v>
@@ -7222,16 +7540,16 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B241" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D241" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E241" s="3">
         <v>44</v>
@@ -7245,16 +7563,16 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B242" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D242" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E242" s="3">
         <v>44</v>
@@ -7268,16 +7586,16 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B243" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D243" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E243" s="3">
         <v>44</v>
@@ -7291,16 +7609,16 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B244" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D244" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E244" s="3">
         <v>128</v>
@@ -7314,16 +7632,16 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B245" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D245" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E245" s="3">
         <v>55</v>
@@ -7337,16 +7655,16 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B246" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D246" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E246" s="3">
         <v>75</v>
@@ -7360,16 +7678,16 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B247" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D247" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E247" s="3">
         <v>129</v>
@@ -7383,16 +7701,16 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B248" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E248" s="3">
         <v>44</v>
@@ -7406,16 +7724,16 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B249" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E249" s="3">
         <v>83</v>
@@ -7429,16 +7747,16 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B250" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D250" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E250" s="3">
         <v>44</v>
@@ -7452,16 +7770,16 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B251" t="s">
+        <v>186</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D251" t="s">
         <v>236</v>
-      </c>
-      <c r="B251" t="s">
-        <v>187</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D251" t="s">
-        <v>237</v>
       </c>
       <c r="E251" s="3">
         <v>77</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF35AC5A-B65B-4A81-AEF5-B5F0A8745424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE214B0A-4BDF-4D10-A8F9-B03AB1D8009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="373">
   <si>
     <t>categoria</t>
   </si>
@@ -1134,6 +1134,12 @@
   </si>
   <si>
     <t>20182</t>
+  </si>
+  <si>
+    <t>Teste</t>
+  </si>
+  <si>
+    <t>teste</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -7789,6 +7795,29 @@
       </c>
       <c r="G251" s="4">
         <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B252" t="s">
+        <v>371</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D252" t="s">
+        <v>372</v>
+      </c>
+      <c r="E252" s="3">
+        <v>10</v>
+      </c>
+      <c r="F252" s="3">
+        <v>20</v>
+      </c>
+      <c r="G252" s="4">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE214B0A-4BDF-4D10-A8F9-B03AB1D8009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0B305C-9B9A-4682-9AE8-976D3F518B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="375">
   <si>
     <t>categoria</t>
   </si>
@@ -1140,6 +1140,12 @@
   </si>
   <si>
     <t>teste</t>
+  </si>
+  <si>
+    <t>teste x</t>
+  </si>
+  <si>
+    <t>Teste x</t>
   </si>
 </sst>
 </file>
@@ -2014,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -7818,6 +7824,29 @@
       </c>
       <c r="G252" s="4">
         <v>30</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B253" t="s">
+        <v>373</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D253" t="s">
+        <v>374</v>
+      </c>
+      <c r="E253" s="3">
+        <v>40</v>
+      </c>
+      <c r="F253" s="3">
+        <v>50</v>
+      </c>
+      <c r="G253" s="4">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0B305C-9B9A-4682-9AE8-976D3F518B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1108506A-B0B7-4A0E-B99C-99F48F15BCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="391">
   <si>
     <t>categoria</t>
   </si>
@@ -47,54 +47,27 @@
     <t>Volume</t>
   </si>
   <si>
-    <t>0204010001</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Tradicional</t>
   </si>
   <si>
     <t>Prioste</t>
   </si>
   <si>
-    <t>0204010002</t>
-  </si>
-  <si>
-    <t>0204010003</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Pura Folha</t>
   </si>
   <si>
-    <t>0204010004</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Menta Limã</t>
   </si>
   <si>
-    <t>0204010005</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Limão Caipira</t>
   </si>
   <si>
-    <t>0204010006</t>
-  </si>
-  <si>
-    <t>0204010007</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Uva Menta</t>
   </si>
   <si>
-    <t>0204010008</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Pura Folha com Burrito</t>
   </si>
   <si>
-    <t>0204010009</t>
-  </si>
-  <si>
     <t>Erv SP270 500g Erva Mate Cereja Menta</t>
   </si>
   <si>
@@ -452,9 +425,6 @@
     <t>Pet Prful Honey Pet Biscoitos P/ Cães Mini Integral</t>
   </si>
   <si>
-    <t>0105040001</t>
-  </si>
-  <si>
     <t>SLG</t>
   </si>
   <si>
@@ -464,33 +434,6 @@
     <t>SLG Fritop 200g Cebola e Salsa</t>
   </si>
   <si>
-    <t>0105040002</t>
-  </si>
-  <si>
-    <t>0105040003</t>
-  </si>
-  <si>
-    <t>0105040004</t>
-  </si>
-  <si>
-    <t>0105040005</t>
-  </si>
-  <si>
-    <t>0105040006</t>
-  </si>
-  <si>
-    <t>0105040007</t>
-  </si>
-  <si>
-    <t>0105040008</t>
-  </si>
-  <si>
-    <t>0105040009</t>
-  </si>
-  <si>
-    <t>0105040010</t>
-  </si>
-  <si>
     <t>SLG Fritop 200g Requeijão</t>
   </si>
   <si>
@@ -632,9 +575,6 @@
     <t>DOC Gui Paçoquinha Neston Display 546g</t>
   </si>
   <si>
-    <t>DOC Gui Pé de Moça Bestlé Display 600g</t>
-  </si>
-  <si>
     <t>DOC Gui Pé de Moça 100g</t>
   </si>
   <si>
@@ -650,87 +590,6 @@
     <t>Guimarães</t>
   </si>
   <si>
-    <t>0103050001</t>
-  </si>
-  <si>
-    <t>0103050002</t>
-  </si>
-  <si>
-    <t>0103050003</t>
-  </si>
-  <si>
-    <t>0103050004</t>
-  </si>
-  <si>
-    <t>0103050005</t>
-  </si>
-  <si>
-    <t>0103050006</t>
-  </si>
-  <si>
-    <t>0103050007</t>
-  </si>
-  <si>
-    <t>0103050008</t>
-  </si>
-  <si>
-    <t>0103050009</t>
-  </si>
-  <si>
-    <t>0103050010</t>
-  </si>
-  <si>
-    <t>0103050011</t>
-  </si>
-  <si>
-    <t>0103050012</t>
-  </si>
-  <si>
-    <t>0103050013</t>
-  </si>
-  <si>
-    <t>0103050014</t>
-  </si>
-  <si>
-    <t>0103050015</t>
-  </si>
-  <si>
-    <t>0103050016</t>
-  </si>
-  <si>
-    <t>0103050017</t>
-  </si>
-  <si>
-    <t>0103050018</t>
-  </si>
-  <si>
-    <t>0103050019</t>
-  </si>
-  <si>
-    <t>0103050020</t>
-  </si>
-  <si>
-    <t>0103050021</t>
-  </si>
-  <si>
-    <t>0103050022</t>
-  </si>
-  <si>
-    <t>0103050023</t>
-  </si>
-  <si>
-    <t>0103050024</t>
-  </si>
-  <si>
-    <t>0103050025</t>
-  </si>
-  <si>
-    <t>0103050026</t>
-  </si>
-  <si>
-    <t>0103050027</t>
-  </si>
-  <si>
     <t>WK</t>
   </si>
   <si>
@@ -812,9 +671,6 @@
     <t>Doce WK Ninho Display 35 Bolinhas</t>
   </si>
   <si>
-    <t>Doce WK Cone Trufado 60G</t>
-  </si>
-  <si>
     <t>20182P</t>
   </si>
   <si>
@@ -1136,16 +992,208 @@
     <t>20182</t>
   </si>
   <si>
-    <t>Teste</t>
-  </si>
-  <si>
-    <t>teste</t>
-  </si>
-  <si>
-    <t>teste x</t>
-  </si>
-  <si>
-    <t>Teste x</t>
+    <t>DOC Gui Pé de Moça Nestlé Display 600g</t>
+  </si>
+  <si>
+    <t>01030501</t>
+  </si>
+  <si>
+    <t>01030502</t>
+  </si>
+  <si>
+    <t>01030503</t>
+  </si>
+  <si>
+    <t>01030504</t>
+  </si>
+  <si>
+    <t>01030505</t>
+  </si>
+  <si>
+    <t>01030506</t>
+  </si>
+  <si>
+    <t>01030507</t>
+  </si>
+  <si>
+    <t>01030508</t>
+  </si>
+  <si>
+    <t>01030509</t>
+  </si>
+  <si>
+    <t>01030511</t>
+  </si>
+  <si>
+    <t>01030512</t>
+  </si>
+  <si>
+    <t>01030513</t>
+  </si>
+  <si>
+    <t>01030514</t>
+  </si>
+  <si>
+    <t>01030515</t>
+  </si>
+  <si>
+    <t>01030516</t>
+  </si>
+  <si>
+    <t>01030517</t>
+  </si>
+  <si>
+    <t>01030518</t>
+  </si>
+  <si>
+    <t>01030519</t>
+  </si>
+  <si>
+    <t>01030520</t>
+  </si>
+  <si>
+    <t>01030521</t>
+  </si>
+  <si>
+    <t>01030522</t>
+  </si>
+  <si>
+    <t>01030523</t>
+  </si>
+  <si>
+    <t>01030524</t>
+  </si>
+  <si>
+    <t>01030525</t>
+  </si>
+  <si>
+    <t>01030526</t>
+  </si>
+  <si>
+    <t>01030527</t>
+  </si>
+  <si>
+    <t>01030510</t>
+  </si>
+  <si>
+    <t>01030528</t>
+  </si>
+  <si>
+    <t>01030529</t>
+  </si>
+  <si>
+    <t>01030530</t>
+  </si>
+  <si>
+    <t>01030531</t>
+  </si>
+  <si>
+    <t>01030532</t>
+  </si>
+  <si>
+    <t>01030533</t>
+  </si>
+  <si>
+    <t>01030534</t>
+  </si>
+  <si>
+    <t>01030535</t>
+  </si>
+  <si>
+    <t>Doce WK Queijo Nozinho  Espeto com 24 Unid</t>
+  </si>
+  <si>
+    <t>Doce WK Amendoin 70g Espeto com 30 Unid</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Top Tentação Display com 15</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Top Maltine Display com 15</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Tradicional Display com 15</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Leitinho Dispkay com 15</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Coco Display com 15</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Brigadeiro Display com 15</t>
+  </si>
+  <si>
+    <t>Doce WK Cone Trufado 60G Avelã Dipslay com 15</t>
+  </si>
+  <si>
+    <t>01030536</t>
+  </si>
+  <si>
+    <t>Doce WK amendoin 500g sem pele</t>
+  </si>
+  <si>
+    <t>01030537</t>
+  </si>
+  <si>
+    <t>Doce WK Manedouca Espeto com 30</t>
+  </si>
+  <si>
+    <t>01050401</t>
+  </si>
+  <si>
+    <t>01050402</t>
+  </si>
+  <si>
+    <t>01050403</t>
+  </si>
+  <si>
+    <t>01050404</t>
+  </si>
+  <si>
+    <t>01050405</t>
+  </si>
+  <si>
+    <t>01050406</t>
+  </si>
+  <si>
+    <t>01050407</t>
+  </si>
+  <si>
+    <t>01050408</t>
+  </si>
+  <si>
+    <t>01050409</t>
+  </si>
+  <si>
+    <t>01050410</t>
+  </si>
+  <si>
+    <t>02040101</t>
+  </si>
+  <si>
+    <t>02040102</t>
+  </si>
+  <si>
+    <t>02040103</t>
+  </si>
+  <si>
+    <t>02040104</t>
+  </si>
+  <si>
+    <t>02040105</t>
+  </si>
+  <si>
+    <t>02040106</t>
+  </si>
+  <si>
+    <t>02040107</t>
+  </si>
+  <si>
+    <t>02040108</t>
+  </si>
+  <si>
+    <t>02040109</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1350,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1482,6 +1530,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1599,7 +1653,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="47">
+  <cellStyleXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1647,8 +1701,9 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1660,8 +1715,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="47">
+  <cellStyles count="48">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1691,6 +1753,7 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
     <cellStyle name="Moeda 2" xfId="43" xr:uid="{0C61731C-E737-4A54-9036-17B400FE6FAB}"/>
     <cellStyle name="Moeda 2 2" xfId="44" xr:uid="{AA48D0B9-D8DC-46BB-B1FE-5B9A19F2820B}"/>
     <cellStyle name="Moeda 3" xfId="45" xr:uid="{93DB1087-9037-47BC-A973-7F702C06F25D}"/>
@@ -2020,7 +2083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:J261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2054,16 +2117,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>382</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
       <c r="E2">
         <v>15.8</v>
@@ -2077,16 +2140,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>383</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>15.8</v>
@@ -2100,16 +2163,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>15.8</v>
@@ -2123,16 +2186,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>385</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>15.8</v>
@@ -2146,16 +2209,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>15.8</v>
@@ -2169,16 +2232,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>15.8</v>
@@ -2192,16 +2255,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>15.8</v>
@@ -2215,16 +2278,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>15.8</v>
@@ -2238,16 +2301,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>390</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>15.8</v>
@@ -2261,16 +2324,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E11">
         <v>8.6</v>
@@ -2284,16 +2347,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <v>8.6</v>
@@ -2307,16 +2370,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E13">
         <v>9.27</v>
@@ -2330,16 +2393,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E14">
         <v>17.260000000000002</v>
@@ -2353,16 +2416,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E15">
         <v>17.260000000000002</v>
@@ -2376,16 +2439,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>31.65</v>
@@ -2399,16 +2462,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>31.65</v>
@@ -2422,16 +2485,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>50.74</v>
@@ -2445,16 +2508,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>50.74</v>
@@ -2468,16 +2531,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>10.6</v>
@@ -2491,16 +2554,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>10.6</v>
@@ -2514,16 +2577,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>10.6</v>
@@ -2537,16 +2600,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>7.94</v>
@@ -2560,16 +2623,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>7.94</v>
@@ -2583,16 +2646,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>8.6</v>
@@ -2606,16 +2669,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E26">
         <v>15.26</v>
@@ -2629,16 +2692,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E27">
         <v>15.26</v>
@@ -2652,16 +2715,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>17.260000000000002</v>
@@ -2675,16 +2738,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>27.5</v>
@@ -2698,16 +2761,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>27.5</v>
@@ -2721,16 +2784,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>34.4</v>
@@ -2744,16 +2807,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E32">
         <v>43.48</v>
@@ -2767,16 +2830,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>43.48</v>
@@ -2790,16 +2853,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E34">
         <v>59.98</v>
@@ -2813,16 +2876,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E35">
         <v>59.98</v>
@@ -2836,16 +2899,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E36">
         <v>7.94</v>
@@ -2859,16 +2922,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E37">
         <v>7.94</v>
@@ -2882,16 +2945,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E38">
         <v>7.94</v>
@@ -2905,16 +2968,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E39">
         <v>7.94</v>
@@ -2928,16 +2991,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E40">
         <v>17.260000000000002</v>
@@ -2951,16 +3014,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E41">
         <v>17.260000000000002</v>
@@ -2974,16 +3037,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E42">
         <v>65.25</v>
@@ -2997,16 +3060,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E43">
         <v>65.25</v>
@@ -3020,16 +3083,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E44">
         <v>19.899999999999999</v>
@@ -3043,16 +3106,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>298</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E45">
         <v>23.93</v>
@@ -3066,16 +3129,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E46">
         <v>37.5</v>
@@ -3089,16 +3152,16 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>300</v>
+        <v>252</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E47">
         <v>52.55</v>
@@ -3112,16 +3175,16 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E48">
         <v>63</v>
@@ -3135,16 +3198,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>302</v>
+        <v>254</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E49">
         <v>2.4500000000000002</v>
@@ -3158,16 +3221,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>303</v>
+        <v>255</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E50">
         <v>2.4500000000000002</v>
@@ -3181,16 +3244,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>304</v>
+        <v>256</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E51">
         <v>1.62</v>
@@ -3204,16 +3267,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E52">
         <v>1.62</v>
@@ -3227,16 +3290,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E53">
         <v>1.62</v>
@@ -3250,16 +3313,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E54">
         <v>1.62</v>
@@ -3273,16 +3336,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E55">
         <v>6.81</v>
@@ -3296,16 +3359,16 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E56">
         <v>6.81</v>
@@ -3319,16 +3382,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>310</v>
+        <v>262</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E57">
         <v>13.26</v>
@@ -3342,16 +3405,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E58">
         <v>13.26</v>
@@ -3365,16 +3428,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E59">
         <v>3.69</v>
@@ -3388,16 +3451,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E60">
         <v>3.69</v>
@@ -3411,16 +3474,16 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>314</v>
+        <v>266</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E61">
         <v>2.29</v>
@@ -3434,16 +3497,16 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>315</v>
+        <v>267</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E62">
         <v>2.29</v>
@@ -3457,16 +3520,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E63">
         <v>2.29</v>
@@ -3480,16 +3543,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E64">
         <v>4.0599999999999996</v>
@@ -3503,16 +3566,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E65">
         <v>4.0599999999999996</v>
@@ -3526,16 +3589,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E66">
         <v>4.0599999999999996</v>
@@ -3549,16 +3612,16 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E67">
         <v>9.35</v>
@@ -3572,16 +3635,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E68">
         <v>4.6500000000000004</v>
@@ -3595,16 +3658,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E69">
         <v>4.6500000000000004</v>
@@ -3618,16 +3681,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E70">
         <v>4.6500000000000004</v>
@@ -3641,16 +3704,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E71">
         <v>5.82</v>
@@ -3664,16 +3727,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E72">
         <v>7.58</v>
@@ -3687,16 +3750,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E73">
         <v>9.35</v>
@@ -3710,16 +3773,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E74">
         <v>9.93</v>
@@ -3733,16 +3796,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E75">
         <v>39.9</v>
@@ -3756,16 +3819,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E76">
         <v>4.3600000000000003</v>
@@ -3779,16 +3842,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E77">
         <v>4.99</v>
@@ -3802,16 +3865,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>331</v>
+        <v>283</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E78">
         <v>9.35</v>
@@ -3825,16 +3888,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E79">
         <v>9.35</v>
@@ -3848,16 +3911,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E80">
         <v>9.35</v>
@@ -3871,16 +3934,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E81">
         <v>9.35</v>
@@ -3894,16 +3957,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E82">
         <v>9.35</v>
@@ -3917,16 +3980,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="B83" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E83">
         <v>9.35</v>
@@ -3940,16 +4003,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E84">
         <v>9.35</v>
@@ -3963,16 +4026,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E85">
         <v>11.71</v>
@@ -3986,16 +4049,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E86">
         <v>5.5</v>
@@ -4009,16 +4072,16 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="B87" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E87">
         <v>5.5</v>
@@ -4032,16 +4095,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E88">
         <v>2.17</v>
@@ -4055,16 +4118,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E89">
         <v>11.05</v>
@@ -4078,16 +4141,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E90">
         <v>7.72</v>
@@ -4101,16 +4164,16 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E91">
         <v>5.5</v>
@@ -4124,16 +4187,16 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E92">
         <v>7.72</v>
@@ -4147,16 +4210,16 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E93">
         <v>8.83</v>
@@ -4170,16 +4233,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D94" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E94">
         <v>10.5</v>
@@ -4193,16 +4256,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D95" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E95">
         <v>11.06</v>
@@ -4216,16 +4279,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E96">
         <v>6.61</v>
@@ -4239,16 +4302,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E97">
         <v>11.06</v>
@@ -4262,16 +4325,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E98">
         <v>4.9400000000000004</v>
@@ -4285,16 +4348,16 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E99">
         <v>7.16</v>
@@ -4308,16 +4371,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="B100" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E100">
         <v>14.38</v>
@@ -4331,16 +4394,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D101" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E101">
         <v>8.83</v>
@@ -4354,16 +4417,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E102">
         <v>8.83</v>
@@ -4377,16 +4440,16 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E103">
         <v>8.83</v>
@@ -4400,16 +4463,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E104">
         <v>11.06</v>
@@ -4423,16 +4486,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>358</v>
+        <v>310</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D105" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E105">
         <v>16.61</v>
@@ -4446,16 +4509,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E106">
         <v>22.17</v>
@@ -4469,16 +4532,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E107">
         <v>5.5</v>
@@ -4492,16 +4555,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E108">
         <v>11.06</v>
@@ -4515,16 +4578,16 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E109">
         <v>11.05</v>
@@ -4538,16 +4601,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>363</v>
+        <v>315</v>
       </c>
       <c r="B110" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D110" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E110">
         <v>16.61</v>
@@ -4561,16 +4624,16 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="B111" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E111">
         <v>15.5</v>
@@ -4584,16 +4647,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E112">
         <v>16.059999999999999</v>
@@ -4607,16 +4670,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D113" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E113">
         <v>11.06</v>
@@ -4630,16 +4693,16 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>367</v>
+        <v>319</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D114" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E114">
         <v>22.17</v>
@@ -4653,16 +4716,16 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="B115" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E115">
         <v>16.059999999999999</v>
@@ -4676,16 +4739,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="B116" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D116" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E116">
         <v>16.61</v>
@@ -4699,16 +4762,16 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>370</v>
+        <v>322</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C117" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E117">
         <v>9.64</v>
@@ -4725,13 +4788,13 @@
         <v>20236</v>
       </c>
       <c r="B118" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C118" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D118" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E118">
         <v>9.64</v>
@@ -4748,13 +4811,13 @@
         <v>20328</v>
       </c>
       <c r="B119" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C119" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D119" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E119">
         <v>11.02</v>
@@ -4771,13 +4834,13 @@
         <v>20205</v>
       </c>
       <c r="B120" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C120" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D120" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E120">
         <v>34.29</v>
@@ -4794,13 +4857,13 @@
         <v>20250</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C121" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E121">
         <v>34.29</v>
@@ -4817,13 +4880,13 @@
         <v>20212</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D122" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E122">
         <v>53.18</v>
@@ -4840,13 +4903,13 @@
         <v>20267</v>
       </c>
       <c r="B123" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C123" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D123" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E123">
         <v>53.18</v>
@@ -4863,13 +4926,13 @@
         <v>20366</v>
       </c>
       <c r="B124" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C124" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D124" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E124">
         <v>11.68</v>
@@ -4886,13 +4949,13 @@
         <v>20403</v>
       </c>
       <c r="B125" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C125" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D125" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E125">
         <v>11.68</v>
@@ -4909,13 +4972,13 @@
         <v>20410</v>
       </c>
       <c r="B126" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C126" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E126">
         <v>11.68</v>
@@ -4932,13 +4995,13 @@
         <v>20441</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C127" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D127" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E127">
         <v>8.9499999999999993</v>
@@ -4955,13 +5018,13 @@
         <v>20496</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C128" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D128" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E128">
         <v>8.9499999999999993</v>
@@ -4978,13 +5041,13 @@
         <v>20540</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C129" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D129" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E129">
         <v>9.64</v>
@@ -5001,13 +5064,13 @@
         <v>20465</v>
       </c>
       <c r="B130" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C130" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D130" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E130">
         <v>28.56</v>
@@ -5024,13 +5087,13 @@
         <v>20519</v>
       </c>
       <c r="B131" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C131" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D131" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E131">
         <v>28.56</v>
@@ -5047,13 +5110,13 @@
         <v>20564</v>
       </c>
       <c r="B132" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C132" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D132" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E132">
         <v>41.92</v>
@@ -5070,13 +5133,13 @@
         <v>20472</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D133" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E133">
         <v>48.92</v>
@@ -5093,13 +5156,13 @@
         <v>20526</v>
       </c>
       <c r="B134" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C134" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D134" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E134">
         <v>48.92</v>
@@ -5116,13 +5179,13 @@
         <v>20489</v>
       </c>
       <c r="B135" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C135" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D135" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E135">
         <v>62.92</v>
@@ -5139,13 +5202,13 @@
         <v>20533</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C136" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E136">
         <v>62.92</v>
@@ -5163,13 +5226,13 @@
         <v>20588</v>
       </c>
       <c r="B137" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D137" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E137">
         <v>10.33</v>
@@ -5186,13 +5249,13 @@
         <v>20618</v>
       </c>
       <c r="B138" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C138" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D138" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E138">
         <v>10.33</v>
@@ -5209,13 +5272,13 @@
         <v>20625</v>
       </c>
       <c r="B139" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C139" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D139" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E139">
         <v>10.33</v>
@@ -5232,13 +5295,13 @@
         <v>20656</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C140" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D140" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E140">
         <v>10.33</v>
@@ -5255,13 +5318,13 @@
         <v>20601</v>
       </c>
       <c r="B141" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C141" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D141" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E141">
         <v>68.84</v>
@@ -5278,13 +5341,13 @@
         <v>20649</v>
       </c>
       <c r="B142" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C142" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D142" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E142">
         <v>68.84</v>
@@ -5298,16 +5361,16 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C143" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D143" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E143">
         <v>8.1999999999999993</v>
@@ -5324,13 +5387,13 @@
         <v>20687</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C144" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D144" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E144">
         <v>25.19</v>
@@ -5347,13 +5410,13 @@
         <v>20694</v>
       </c>
       <c r="B145" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C145" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D145" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E145">
         <v>27.92</v>
@@ -5370,13 +5433,13 @@
         <v>20700</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C146" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D146" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E146">
         <v>41.92</v>
@@ -5393,13 +5456,13 @@
         <v>20717</v>
       </c>
       <c r="B147" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C147" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D147" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E147">
         <v>55.92</v>
@@ -5416,13 +5479,13 @@
         <v>22049</v>
       </c>
       <c r="B148" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C148" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D148" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E148">
         <v>2.99</v>
@@ -5439,13 +5502,13 @@
         <v>22056</v>
       </c>
       <c r="B149" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C149" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D149" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E149">
         <v>2.99</v>
@@ -5462,13 +5525,13 @@
         <v>20809</v>
       </c>
       <c r="B150" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C150" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D150" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E150">
         <v>1.79</v>
@@ -5485,13 +5548,13 @@
         <v>20816</v>
       </c>
       <c r="B151" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C151" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D151" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E151">
         <v>1.79</v>
@@ -5508,13 +5571,13 @@
         <v>20847</v>
       </c>
       <c r="B152" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C152" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D152" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E152">
         <v>7.78</v>
@@ -5531,13 +5594,13 @@
         <v>20854</v>
       </c>
       <c r="B153" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C153" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D153" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E153">
         <v>7.78</v>
@@ -5554,13 +5617,13 @@
         <v>20861</v>
       </c>
       <c r="B154" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C154" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D154" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E154">
         <v>15.57</v>
@@ -5577,13 +5640,13 @@
         <v>20960</v>
       </c>
       <c r="B155" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C155" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D155" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E155">
         <v>5.39</v>
@@ -5600,13 +5663,13 @@
         <v>20984</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C156" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D156" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E156">
         <v>5.39</v>
@@ -5620,16 +5683,16 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B157" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C157" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D157" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E157">
         <v>11.38</v>
@@ -5643,16 +5706,16 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B158" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C158" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D158" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E158">
         <v>11.38</v>
@@ -5669,13 +5732,13 @@
         <v>21059</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C159" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D159" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E159">
         <v>2.99</v>
@@ -5692,13 +5755,13 @@
         <v>21097</v>
       </c>
       <c r="B160" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C160" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D160" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E160">
         <v>5.39</v>
@@ -5715,13 +5778,13 @@
         <v>21103</v>
       </c>
       <c r="B161" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C161" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D161" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E161">
         <v>5.39</v>
@@ -5738,13 +5801,13 @@
         <v>21165</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C162" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D162" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E162">
         <v>5.39</v>
@@ -5761,13 +5824,13 @@
         <v>21172</v>
       </c>
       <c r="B163" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C163" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D163" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E163">
         <v>5.39</v>
@@ -5784,13 +5847,13 @@
         <v>21189</v>
       </c>
       <c r="B164" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C164" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D164" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E164">
         <v>7.18</v>
@@ -5807,13 +5870,13 @@
         <v>21196</v>
       </c>
       <c r="B165" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C165" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D165" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E165">
         <v>8.3800000000000008</v>
@@ -5830,13 +5893,13 @@
         <v>21424</v>
       </c>
       <c r="B166" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C166" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D166" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E166">
         <v>11.92</v>
@@ -5853,13 +5916,13 @@
         <v>21431</v>
       </c>
       <c r="B167" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C167" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D167" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E167">
         <v>47.88</v>
@@ -5876,13 +5939,13 @@
         <v>21448</v>
       </c>
       <c r="B168" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C168" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D168" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E168">
         <v>5.93</v>
@@ -5899,13 +5962,13 @@
         <v>21462</v>
       </c>
       <c r="B169" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C169" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D169" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E169">
         <v>5.93</v>
@@ -5922,13 +5985,13 @@
         <v>21479</v>
       </c>
       <c r="B170" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C170" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D170" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E170">
         <v>9.58</v>
@@ -5945,13 +6008,13 @@
         <v>21486</v>
       </c>
       <c r="B171" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C171" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D171" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E171">
         <v>9.58</v>
@@ -5968,13 +6031,13 @@
         <v>21493</v>
       </c>
       <c r="B172" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D172" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E172">
         <v>10.78</v>
@@ -5991,13 +6054,13 @@
         <v>21509</v>
       </c>
       <c r="B173" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C173" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D173" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E173">
         <v>10.78</v>
@@ -6014,13 +6077,13 @@
         <v>21523</v>
       </c>
       <c r="B174" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D174" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E174">
         <v>10.78</v>
@@ -6034,16 +6097,16 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B175" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C175" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D175" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E175">
         <v>11.92</v>
@@ -6060,13 +6123,13 @@
         <v>21561</v>
       </c>
       <c r="B176" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C176" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D176" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E176">
         <v>7.18</v>
@@ -6083,13 +6146,13 @@
         <v>21578</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C177" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D177" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E177">
         <v>8.3800000000000008</v>
@@ -6106,13 +6169,13 @@
         <v>21585</v>
       </c>
       <c r="B178" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D178" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E178">
         <v>9.58</v>
@@ -6129,13 +6192,13 @@
         <v>21592</v>
       </c>
       <c r="B179" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C179" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D179" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E179">
         <v>11.92</v>
@@ -6152,13 +6215,13 @@
         <v>21608</v>
       </c>
       <c r="B180" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D180" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E180">
         <v>14.37</v>
@@ -6175,13 +6238,13 @@
         <v>22421</v>
       </c>
       <c r="B181" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C181" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D181" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E181">
         <v>8.3800000000000008</v>
@@ -6198,13 +6261,13 @@
         <v>22353</v>
       </c>
       <c r="B182" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C182" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D182" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E182">
         <v>7.18</v>
@@ -6221,13 +6284,13 @@
         <v>22360</v>
       </c>
       <c r="B183" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C183" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D183" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E183">
         <v>9.58</v>
@@ -6244,13 +6307,13 @@
         <v>21714</v>
       </c>
       <c r="B184" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C184" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D184" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E184">
         <v>11.92</v>
@@ -6267,13 +6330,13 @@
         <v>22339</v>
       </c>
       <c r="B185" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C185" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D185" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E185">
         <v>11.92</v>
@@ -6290,13 +6353,13 @@
         <v>22391</v>
       </c>
       <c r="B186" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C186" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D186" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E186">
         <v>8.3800000000000008</v>
@@ -6313,13 +6376,13 @@
         <v>21745</v>
       </c>
       <c r="B187" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C187" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D187" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E187">
         <v>11.92</v>
@@ -6336,13 +6399,13 @@
         <v>21752</v>
       </c>
       <c r="B188" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C188" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D188" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E188">
         <v>21.57</v>
@@ -6359,13 +6422,13 @@
         <v>21783</v>
       </c>
       <c r="B189" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C189" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D189" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E189">
         <v>21.57</v>
@@ -6382,13 +6445,13 @@
         <v>21790</v>
       </c>
       <c r="B190" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C190" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D190" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E190">
         <v>11.92</v>
@@ -6405,13 +6468,13 @@
         <v>21844</v>
       </c>
       <c r="B191" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D191" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E191">
         <v>21.57</v>
@@ -6428,13 +6491,13 @@
         <v>21899</v>
       </c>
       <c r="B192" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D192" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E192">
         <v>23.91</v>
@@ -6448,16 +6511,16 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>143</v>
+        <v>372</v>
       </c>
       <c r="B193" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C193" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D193" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E193">
         <v>5.99</v>
@@ -6471,16 +6534,16 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>147</v>
+        <v>373</v>
       </c>
       <c r="B194" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C194" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D194" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E194">
         <v>5.99</v>
@@ -6494,16 +6557,16 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>148</v>
+        <v>374</v>
       </c>
       <c r="B195" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C195" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D195" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E195">
         <v>5.99</v>
@@ -6517,16 +6580,16 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>149</v>
+        <v>375</v>
       </c>
       <c r="B196" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C196" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="D196" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E196">
         <v>5.99</v>
@@ -6540,16 +6603,16 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="B197" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C197" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D197" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E197">
         <v>5.99</v>
@@ -6563,16 +6626,16 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>151</v>
+        <v>377</v>
       </c>
       <c r="B198" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C198" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="D198" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E198">
         <v>5.99</v>
@@ -6586,16 +6649,16 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>152</v>
+        <v>378</v>
       </c>
       <c r="B199" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C199" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="D199" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E199">
         <v>5.99</v>
@@ -6609,16 +6672,16 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>153</v>
+        <v>379</v>
       </c>
       <c r="B200" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C200" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D200" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E200">
         <v>5.99</v>
@@ -6632,16 +6695,16 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>154</v>
+        <v>380</v>
       </c>
       <c r="B201" t="s">
+        <v>134</v>
+      </c>
+      <c r="C201" t="s">
         <v>144</v>
       </c>
-      <c r="C201" t="s">
-        <v>163</v>
-      </c>
       <c r="D201" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E201">
         <v>1.99</v>
@@ -6655,16 +6718,16 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>155</v>
+        <v>381</v>
       </c>
       <c r="B202" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C202" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D202" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E202">
         <v>1.99</v>
@@ -6678,16 +6741,16 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="B203" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C203" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D203" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E203">
         <v>6.94</v>
@@ -6701,16 +6764,16 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B204" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C204" t="s">
+        <v>169</v>
+      </c>
+      <c r="D204" t="s">
         <v>188</v>
-      </c>
-      <c r="D204" t="s">
-        <v>208</v>
       </c>
       <c r="E204">
         <v>6.94</v>
@@ -6724,16 +6787,16 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B205" t="s">
         <v>167</v>
       </c>
-      <c r="B205" t="s">
-        <v>186</v>
-      </c>
       <c r="C205" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D205" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E205">
         <v>3.96</v>
@@ -6747,16 +6810,16 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B206" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C206" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D206" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E206">
         <v>26.64</v>
@@ -6770,16 +6833,16 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B207" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C207" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D207" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E207">
         <v>29.8</v>
@@ -6793,16 +6856,16 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B208" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C208" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="D208" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E208">
         <v>12.99</v>
@@ -6814,18 +6877,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="B209" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C209" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D209" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E209">
         <v>12.99</v>
@@ -6837,18 +6900,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="B210" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C210" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D210" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E210">
         <v>12.99</v>
@@ -6860,18 +6923,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B211" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C211" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D211" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E211">
         <v>25.58</v>
@@ -6883,18 +6946,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B212" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C212" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="D212" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E212">
         <v>23.85</v>
@@ -6906,18 +6969,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="B213" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C213" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D213" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E213">
         <v>3.82</v>
@@ -6929,18 +6992,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="B214" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C214" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D214" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E214">
         <v>3.82</v>
@@ -6951,19 +7014,23 @@
       <c r="G214">
         <v>16</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J214">
+        <f>16*3.82</f>
+        <v>61.12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B215" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C215" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D215" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E215">
         <v>3.82</v>
@@ -6975,18 +7042,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B216" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C216" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="D216" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E216">
         <v>25.68</v>
@@ -6998,18 +7065,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B217" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C217" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="D217" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E217">
         <v>25.68</v>
@@ -7021,18 +7088,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B218" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C218" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="D218" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E218">
         <v>25.68</v>
@@ -7044,18 +7111,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="B219" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C219" t="s">
-        <v>203</v>
+        <v>323</v>
       </c>
       <c r="D219" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E219">
         <v>38.15</v>
@@ -7067,18 +7134,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B220" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C220" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D220" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E220">
         <v>6.94</v>
@@ -7090,18 +7157,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B221" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C221" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D221" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E221">
         <v>35.76</v>
@@ -7113,18 +7180,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="B222" t="s">
+        <v>167</v>
+      </c>
+      <c r="C222" t="s">
         <v>186</v>
       </c>
-      <c r="C222" t="s">
-        <v>206</v>
-      </c>
       <c r="D222" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E222">
         <v>13.68</v>
@@ -7136,18 +7203,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B223" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C223" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="D223" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E223">
         <v>15.13</v>
@@ -7159,18 +7226,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B224" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C224" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D224" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E224">
         <v>16.61</v>
@@ -7184,16 +7251,16 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>209</v>
+        <v>324</v>
       </c>
       <c r="B225" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="D225" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E225" s="3">
         <v>56</v>
@@ -7207,16 +7274,16 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="B226" t="s">
-        <v>186</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>238</v>
+        <v>167</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="D226" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E226" s="3">
         <v>95</v>
@@ -7230,16 +7297,16 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>211</v>
+        <v>326</v>
       </c>
       <c r="B227" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D227" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E227" s="3">
         <v>44</v>
@@ -7253,16 +7320,16 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="B228" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="D228" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E228" s="3">
         <v>44</v>
@@ -7276,16 +7343,16 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>213</v>
+        <v>328</v>
       </c>
       <c r="B229" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="D229" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E229" s="3">
         <v>52</v>
@@ -7299,16 +7366,16 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>214</v>
+        <v>329</v>
       </c>
       <c r="B230" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="D230" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E230" s="3">
         <v>56</v>
@@ -7322,16 +7389,16 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>215</v>
+        <v>330</v>
       </c>
       <c r="B231" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="D231" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E231" s="3">
         <v>60</v>
@@ -7345,16 +7412,16 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>216</v>
+        <v>331</v>
       </c>
       <c r="B232" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
       <c r="D232" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E232" s="3">
         <v>80</v>
@@ -7368,16 +7435,16 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="B233" t="s">
-        <v>186</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>245</v>
+        <v>167</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="D233" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E233" s="3">
         <v>56</v>
@@ -7391,16 +7458,16 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>218</v>
+        <v>350</v>
       </c>
       <c r="B234" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="D234" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E234" s="3">
         <v>56</v>
@@ -7414,16 +7481,16 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="B235" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="D235" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E235" s="3">
         <v>44</v>
@@ -7437,16 +7504,16 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>220</v>
+        <v>334</v>
       </c>
       <c r="B236" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="D236" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E236" s="3">
         <v>44</v>
@@ -7460,16 +7527,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="B237" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
       <c r="D237" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E237" s="3">
         <v>75</v>
@@ -7483,16 +7550,16 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>222</v>
+        <v>336</v>
       </c>
       <c r="B238" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="D238" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E238" s="3">
         <v>13</v>
@@ -7506,16 +7573,16 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>223</v>
+        <v>337</v>
       </c>
       <c r="B239" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="D239" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E239" s="3">
         <v>205</v>
@@ -7529,16 +7596,16 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>224</v>
+        <v>338</v>
       </c>
       <c r="B240" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="D240" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E240" s="3">
         <v>42</v>
@@ -7552,16 +7619,16 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>225</v>
+        <v>339</v>
       </c>
       <c r="B241" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="D241" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E241" s="3">
         <v>44</v>
@@ -7575,16 +7642,16 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="B242" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="D242" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E242" s="3">
         <v>44</v>
@@ -7598,16 +7665,16 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>227</v>
+        <v>341</v>
       </c>
       <c r="B243" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
       <c r="D243" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E243" s="3">
         <v>44</v>
@@ -7621,16 +7688,16 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>228</v>
+        <v>342</v>
       </c>
       <c r="B244" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
       <c r="D244" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E244" s="3">
         <v>128</v>
@@ -7644,16 +7711,16 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>229</v>
+        <v>343</v>
       </c>
       <c r="B245" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="D245" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E245" s="3">
         <v>55</v>
@@ -7667,16 +7734,16 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="B246" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="D246" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E246" s="3">
         <v>75</v>
@@ -7690,16 +7757,16 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="B247" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="D247" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E247" s="3">
         <v>129</v>
@@ -7713,16 +7780,16 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>232</v>
+        <v>346</v>
       </c>
       <c r="B248" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="D248" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E248" s="3">
         <v>44</v>
@@ -7736,16 +7803,16 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>233</v>
+        <v>347</v>
       </c>
       <c r="B249" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="D249" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E249" s="3">
         <v>83</v>
@@ -7759,16 +7826,16 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="B250" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="D250" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E250" s="3">
         <v>44</v>
@@ -7782,16 +7849,16 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>235</v>
+        <v>349</v>
       </c>
       <c r="B251" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="D251" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E251" s="3">
         <v>77</v>
@@ -7800,53 +7867,237 @@
         <v>77</v>
       </c>
       <c r="G251" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="B252" t="s">
-        <v>371</v>
+        <v>167</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D252" t="s">
-        <v>372</v>
+        <v>189</v>
       </c>
       <c r="E252" s="3">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="F252" s="3">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="G252" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="B253" t="s">
-        <v>373</v>
+        <v>167</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D253" t="s">
-        <v>374</v>
+        <v>189</v>
       </c>
       <c r="E253" s="3">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="F253" s="3">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G253" s="4">
-        <v>60</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B254" t="s">
+        <v>167</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D254" t="s">
+        <v>189</v>
+      </c>
+      <c r="E254" s="3">
+        <v>77</v>
+      </c>
+      <c r="F254" s="3">
+        <v>77</v>
+      </c>
+      <c r="G254" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B255" t="s">
+        <v>167</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D255" t="s">
+        <v>189</v>
+      </c>
+      <c r="E255" s="3">
+        <v>77</v>
+      </c>
+      <c r="F255" s="3">
+        <v>77</v>
+      </c>
+      <c r="G255" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B256" t="s">
+        <v>167</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D256" t="s">
+        <v>189</v>
+      </c>
+      <c r="E256" s="3">
+        <v>77</v>
+      </c>
+      <c r="F256" s="3">
+        <v>77</v>
+      </c>
+      <c r="G256" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B257" t="s">
+        <v>167</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D257" t="s">
+        <v>189</v>
+      </c>
+      <c r="E257" s="3">
+        <v>77</v>
+      </c>
+      <c r="F257" s="3">
+        <v>77</v>
+      </c>
+      <c r="G257" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B258" t="s">
+        <v>167</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D258" t="s">
+        <v>189</v>
+      </c>
+      <c r="E258" s="3">
+        <v>108</v>
+      </c>
+      <c r="F258" s="3">
+        <v>108</v>
+      </c>
+      <c r="G258" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B259" t="s">
+        <v>167</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D259" t="s">
+        <v>189</v>
+      </c>
+      <c r="E259" s="3">
+        <v>73</v>
+      </c>
+      <c r="F259" s="3">
+        <v>73</v>
+      </c>
+      <c r="G259" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B260" t="s">
+        <v>167</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D260" t="s">
+        <v>189</v>
+      </c>
+      <c r="E260" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="F260" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G260" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B261" t="s">
+        <v>167</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D261" t="s">
+        <v>189</v>
+      </c>
+      <c r="E261" s="3">
+        <v>77</v>
+      </c>
+      <c r="F261" s="3">
+        <v>77</v>
+      </c>
+      <c r="G261" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7858,9 +8109,1299 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>15.8</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>17.260000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>17.260000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>31.65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>31.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>50.74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>50.74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>17.260000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>59.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>59.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>17.260000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>17.260000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>23.93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>52.55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>2.4500000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>2.4500000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>11.05</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>14.38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>22.17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>11.05</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>16.059999999999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>22.17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>16.059999999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>9.64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>9.64</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>11.02</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>34.29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>34.29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>53.18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>53.18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>8.9499999999999993</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>8.9499999999999993</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>9.64</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>28.56</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>28.56</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>41.92</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>48.92</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>48.92</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>62.92</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>62.92</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>68.84</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>68.84</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>25.19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>27.92</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>41.92</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>55.92</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>15.57</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>11.38</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>11.38</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>47.88</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="6">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="6">
+        <v>21.57</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="6">
+        <v>21.57</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="6">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="6">
+        <v>21.57</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="6">
+        <v>23.91</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="6">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="6">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="6">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="6">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="6">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="6">
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="6">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="6">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="6">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="6">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="6">
+        <v>25.58</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="6">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="6">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="6">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="6">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="6">
+        <v>25.68</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="6">
+        <v>25.68</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="6">
+        <v>25.68</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="6">
+        <v>38.15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="6">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="6">
+        <v>35.76</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="6">
+        <v>13.68</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="6">
+        <v>15.13</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="6">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="7">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,20 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1108506A-B0B7-4A0E-B99C-99F48F15BCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171BEE09-1111-4D91-8479-A8331FC8F94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
   <sheets>
     <sheet name="base_de_produtos" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha2" sheetId="3" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha2!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="396">
   <si>
     <t>categoria</t>
   </si>
@@ -1194,6 +1198,21 @@
   </si>
   <si>
     <t>02040109</t>
+  </si>
+  <si>
+    <t>Doce WK Alfajor 60G 20 Unid</t>
+  </si>
+  <si>
+    <t>Este vende um pote só ou tem que ser 8</t>
+  </si>
+  <si>
+    <t>Este vende um pote só ou tem que ser 12</t>
+  </si>
+  <si>
+    <t>Este vende um pote só ou tem que ser 4</t>
+  </si>
+  <si>
+    <t>Este vende um display só ou teque ser 6</t>
   </si>
 </sst>
 </file>
@@ -2083,7 +2102,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EA19E0-0234-448C-AC25-7037E300529C}">
-  <dimension ref="A1:J261"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -6509,7 +6531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>372</v>
       </c>
@@ -6532,7 +6554,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>373</v>
       </c>
@@ -6555,7 +6577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>374</v>
       </c>
@@ -6578,7 +6600,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>375</v>
       </c>
@@ -6601,7 +6623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>376</v>
       </c>
@@ -6624,7 +6646,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>377</v>
       </c>
@@ -6647,7 +6669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>378</v>
       </c>
@@ -6670,7 +6692,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>379</v>
       </c>
@@ -6693,7 +6715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>380</v>
       </c>
@@ -6716,7 +6738,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>381</v>
       </c>
@@ -6739,7 +6761,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>146</v>
       </c>
@@ -6762,7 +6784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>147</v>
       </c>
@@ -6785,7 +6807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>148</v>
       </c>
@@ -6808,7 +6830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>149</v>
       </c>
@@ -6830,8 +6852,11 @@
       <c r="G206">
         <v>8</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I206" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>150</v>
       </c>
@@ -6853,8 +6878,11 @@
       <c r="G207">
         <v>8</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I207" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>151</v>
       </c>
@@ -6876,8 +6904,11 @@
       <c r="G208">
         <v>12</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I208" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>152</v>
       </c>
@@ -6899,8 +6930,11 @@
       <c r="G209">
         <v>12</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I209" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>153</v>
       </c>
@@ -6922,8 +6956,11 @@
       <c r="G210">
         <v>12</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I210" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>154</v>
       </c>
@@ -6945,8 +6982,11 @@
       <c r="G211">
         <v>12</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I211" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>155</v>
       </c>
@@ -6968,8 +7008,11 @@
       <c r="G212">
         <v>4</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I212" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>156</v>
       </c>
@@ -6992,7 +7035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>157</v>
       </c>
@@ -7014,12 +7057,8 @@
       <c r="G214">
         <v>16</v>
       </c>
-      <c r="J214">
-        <f>16*3.82</f>
-        <v>61.12</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>158</v>
       </c>
@@ -7042,7 +7081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>159</v>
       </c>
@@ -7064,8 +7103,11 @@
       <c r="G216">
         <v>6</v>
       </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I216" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>160</v>
       </c>
@@ -7088,7 +7130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>161</v>
       </c>
@@ -7111,7 +7153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>162</v>
       </c>
@@ -7134,7 +7176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>163</v>
       </c>
@@ -7157,7 +7199,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>164</v>
       </c>
@@ -7180,7 +7222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>165</v>
       </c>
@@ -7203,7 +7245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>166</v>
       </c>
@@ -7226,7 +7268,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>158</v>
       </c>
@@ -7249,7 +7291,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>324</v>
       </c>
@@ -7263,7 +7305,7 @@
         <v>189</v>
       </c>
       <c r="E225" s="3">
-        <v>56</v>
+        <v>1.87</v>
       </c>
       <c r="F225" s="3">
         <v>56</v>
@@ -7271,8 +7313,12 @@
       <c r="G225" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I225">
+        <f>F225/G225</f>
+        <v>1.8666666666666667</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>325</v>
       </c>
@@ -7280,13 +7326,13 @@
         <v>167</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>191</v>
+        <v>391</v>
       </c>
       <c r="D226" t="s">
         <v>189</v>
       </c>
       <c r="E226" s="3">
-        <v>95</v>
+        <v>4.75</v>
       </c>
       <c r="F226" s="3">
         <v>95</v>
@@ -7294,8 +7340,12 @@
       <c r="G226" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I226">
+        <f t="shared" ref="I226:I261" si="1">F226/G226</f>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>326</v>
       </c>
@@ -7309,7 +7359,7 @@
         <v>189</v>
       </c>
       <c r="E227" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F227" s="3">
         <v>44</v>
@@ -7317,8 +7367,12 @@
       <c r="G227" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I227">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>327</v>
       </c>
@@ -7332,7 +7386,7 @@
         <v>189</v>
       </c>
       <c r="E228" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F228" s="3">
         <v>44</v>
@@ -7340,8 +7394,12 @@
       <c r="G228" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I228">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>328</v>
       </c>
@@ -7355,7 +7413,7 @@
         <v>189</v>
       </c>
       <c r="E229" s="3">
-        <v>52</v>
+        <v>2.6</v>
       </c>
       <c r="F229" s="3">
         <v>52</v>
@@ -7363,8 +7421,12 @@
       <c r="G229" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I229">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>329</v>
       </c>
@@ -7378,7 +7440,7 @@
         <v>189</v>
       </c>
       <c r="E230" s="3">
-        <v>56</v>
+        <v>2.8</v>
       </c>
       <c r="F230" s="3">
         <v>56</v>
@@ -7386,8 +7448,12 @@
       <c r="G230" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I230">
+        <f t="shared" si="1"/>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>330</v>
       </c>
@@ -7401,7 +7467,7 @@
         <v>189</v>
       </c>
       <c r="E231" s="3">
-        <v>60</v>
+        <v>2.5</v>
       </c>
       <c r="F231" s="3">
         <v>60</v>
@@ -7409,8 +7475,12 @@
       <c r="G231" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I231">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>331</v>
       </c>
@@ -7424,7 +7494,7 @@
         <v>189</v>
       </c>
       <c r="E232" s="3">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F232" s="3">
         <v>80</v>
@@ -7432,8 +7502,12 @@
       <c r="G232" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I232">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>332</v>
       </c>
@@ -7447,7 +7521,7 @@
         <v>189</v>
       </c>
       <c r="E233" s="3">
-        <v>56</v>
+        <v>2.34</v>
       </c>
       <c r="F233" s="3">
         <v>56</v>
@@ -7455,8 +7529,12 @@
       <c r="G233" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I233">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>350</v>
       </c>
@@ -7470,7 +7548,7 @@
         <v>189</v>
       </c>
       <c r="E234" s="3">
-        <v>56</v>
+        <v>2.34</v>
       </c>
       <c r="F234" s="3">
         <v>56</v>
@@ -7478,8 +7556,12 @@
       <c r="G234" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I234">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>333</v>
       </c>
@@ -7493,7 +7575,7 @@
         <v>189</v>
       </c>
       <c r="E235" s="3">
-        <v>44</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F235" s="3">
         <v>44</v>
@@ -7501,8 +7583,12 @@
       <c r="G235" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I235">
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>334</v>
       </c>
@@ -7516,7 +7602,7 @@
         <v>189</v>
       </c>
       <c r="E236" s="3">
-        <v>44</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F236" s="3">
         <v>44</v>
@@ -7524,8 +7610,12 @@
       <c r="G236" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I236">
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>335</v>
       </c>
@@ -7539,7 +7629,7 @@
         <v>189</v>
       </c>
       <c r="E237" s="3">
-        <v>75</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F237" s="3">
         <v>75</v>
@@ -7547,8 +7637,12 @@
       <c r="G237" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I237">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>336</v>
       </c>
@@ -7570,8 +7664,12 @@
       <c r="G238" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I238">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>337</v>
       </c>
@@ -7585,7 +7683,7 @@
         <v>189</v>
       </c>
       <c r="E239" s="3">
-        <v>205</v>
+        <v>13.67</v>
       </c>
       <c r="F239" s="3">
         <v>205</v>
@@ -7593,8 +7691,12 @@
       <c r="G239" s="4">
         <v>15</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I239">
+        <f t="shared" si="1"/>
+        <v>13.666666666666666</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>338</v>
       </c>
@@ -7608,7 +7710,7 @@
         <v>189</v>
       </c>
       <c r="E240" s="3">
-        <v>42</v>
+        <v>1.4</v>
       </c>
       <c r="F240" s="3">
         <v>42</v>
@@ -7616,8 +7718,12 @@
       <c r="G240" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I240">
+        <f t="shared" si="1"/>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>339</v>
       </c>
@@ -7631,7 +7737,7 @@
         <v>189</v>
       </c>
       <c r="E241" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F241" s="3">
         <v>44</v>
@@ -7639,8 +7745,12 @@
       <c r="G241" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I241">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>340</v>
       </c>
@@ -7654,7 +7764,7 @@
         <v>189</v>
       </c>
       <c r="E242" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F242" s="3">
         <v>44</v>
@@ -7662,8 +7772,12 @@
       <c r="G242" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I242">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>341</v>
       </c>
@@ -7677,7 +7791,7 @@
         <v>189</v>
       </c>
       <c r="E243" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F243" s="3">
         <v>44</v>
@@ -7685,8 +7799,12 @@
       <c r="G243" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I243">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>342</v>
       </c>
@@ -7700,7 +7818,7 @@
         <v>189</v>
       </c>
       <c r="E244" s="3">
-        <v>128</v>
+        <v>6.4</v>
       </c>
       <c r="F244" s="3">
         <v>128</v>
@@ -7708,8 +7826,12 @@
       <c r="G244" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I244">
+        <f t="shared" si="1"/>
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>343</v>
       </c>
@@ -7723,7 +7845,7 @@
         <v>189</v>
       </c>
       <c r="E245" s="3">
-        <v>55</v>
+        <v>3.67</v>
       </c>
       <c r="F245" s="3">
         <v>55</v>
@@ -7731,8 +7853,12 @@
       <c r="G245" s="4">
         <v>15</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I245">
+        <f t="shared" si="1"/>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>344</v>
       </c>
@@ -7746,7 +7872,7 @@
         <v>189</v>
       </c>
       <c r="E246" s="3">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F246" s="3">
         <v>75</v>
@@ -7754,8 +7880,12 @@
       <c r="G246" s="4">
         <v>15</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I246">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>345</v>
       </c>
@@ -7769,7 +7899,7 @@
         <v>189</v>
       </c>
       <c r="E247" s="3">
-        <v>129</v>
+        <v>3.08</v>
       </c>
       <c r="F247" s="3">
         <v>129</v>
@@ -7777,8 +7907,12 @@
       <c r="G247" s="4">
         <v>42</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I247">
+        <f t="shared" si="1"/>
+        <v>3.0714285714285716</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>346</v>
       </c>
@@ -7792,7 +7926,7 @@
         <v>189</v>
       </c>
       <c r="E248" s="3">
-        <v>44</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F248" s="3">
         <v>44</v>
@@ -7800,8 +7934,12 @@
       <c r="G248" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I248">
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>347</v>
       </c>
@@ -7815,7 +7953,7 @@
         <v>189</v>
       </c>
       <c r="E249" s="3">
-        <v>83</v>
+        <v>1.98</v>
       </c>
       <c r="F249" s="3">
         <v>83</v>
@@ -7823,8 +7961,12 @@
       <c r="G249" s="4">
         <v>42</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I249">
+        <f t="shared" si="1"/>
+        <v>1.9761904761904763</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>348</v>
       </c>
@@ -7838,7 +7980,7 @@
         <v>189</v>
       </c>
       <c r="E250" s="3">
-        <v>44</v>
+        <v>1.26</v>
       </c>
       <c r="F250" s="3">
         <v>44</v>
@@ -7846,8 +7988,12 @@
       <c r="G250" s="4">
         <v>35</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I250">
+        <f t="shared" si="1"/>
+        <v>1.2571428571428571</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>349</v>
       </c>
@@ -7861,16 +8007,20 @@
         <v>189</v>
       </c>
       <c r="E251" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F251" s="3">
         <v>77</v>
       </c>
       <c r="G251" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I251">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>351</v>
       </c>
@@ -7884,16 +8034,20 @@
         <v>189</v>
       </c>
       <c r="E252" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F252" s="3">
         <v>77</v>
       </c>
       <c r="G252" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I252">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>352</v>
       </c>
@@ -7907,16 +8061,20 @@
         <v>189</v>
       </c>
       <c r="E253" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F253" s="3">
         <v>77</v>
       </c>
       <c r="G253" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I253">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>353</v>
       </c>
@@ -7930,16 +8088,20 @@
         <v>189</v>
       </c>
       <c r="E254" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F254" s="3">
         <v>77</v>
       </c>
       <c r="G254" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I254">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>354</v>
       </c>
@@ -7953,16 +8115,20 @@
         <v>189</v>
       </c>
       <c r="E255" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F255" s="3">
         <v>77</v>
       </c>
       <c r="G255" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I255">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>355</v>
       </c>
@@ -7976,16 +8142,20 @@
         <v>189</v>
       </c>
       <c r="E256" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F256" s="3">
         <v>77</v>
       </c>
       <c r="G256" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I256">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>356</v>
       </c>
@@ -7999,16 +8169,20 @@
         <v>189</v>
       </c>
       <c r="E257" s="3">
-        <v>77</v>
+        <v>5.14</v>
       </c>
       <c r="F257" s="3">
         <v>77</v>
       </c>
       <c r="G257" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I257">
+        <f t="shared" si="1"/>
+        <v>5.1333333333333337</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>357</v>
       </c>
@@ -8028,10 +8202,14 @@
         <v>108</v>
       </c>
       <c r="G258" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="I258">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>358</v>
       </c>
@@ -8051,10 +8229,14 @@
         <v>73</v>
       </c>
       <c r="G259" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="I259">
+        <f t="shared" si="1"/>
+        <v>2.4333333333333331</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>368</v>
       </c>
@@ -8076,8 +8258,12 @@
       <c r="G260" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I260">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>370</v>
       </c>
@@ -8091,23 +8277,6057 @@
         <v>189</v>
       </c>
       <c r="E261" s="3">
-        <v>77</v>
+        <v>2.56</v>
       </c>
       <c r="F261" s="3">
         <v>77</v>
       </c>
       <c r="G261" s="4">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="I261">
+        <f t="shared" si="1"/>
+        <v>2.5666666666666669</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D08511B-311B-490C-99A0-C15D4C5423C8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G261"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>20205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>34.29</v>
+      </c>
+      <c r="F2">
+        <v>34.29</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>20212</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>53.18</v>
+      </c>
+      <c r="F3">
+        <v>53.18</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>20236</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>9.64</v>
+      </c>
+      <c r="F4">
+        <v>115.68</v>
+      </c>
+      <c r="G4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>20250</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>34.29</v>
+      </c>
+      <c r="F5">
+        <v>34.29</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>20267</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>53.18</v>
+      </c>
+      <c r="F6">
+        <v>53.18</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>20328</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>11.02</v>
+      </c>
+      <c r="F7">
+        <v>132.22</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>20366</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>11.68</v>
+      </c>
+      <c r="F8">
+        <v>140.16</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>20403</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>11.68</v>
+      </c>
+      <c r="F9">
+        <v>140.16</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>20410</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>11.68</v>
+      </c>
+      <c r="F10">
+        <v>140.16</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>20441</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="F11">
+        <v>107.41</v>
+      </c>
+      <c r="G11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>20465</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <v>28.56</v>
+      </c>
+      <c r="F12">
+        <v>28.56</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>20472</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>48.92</v>
+      </c>
+      <c r="F13">
+        <v>48.92</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>20489</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>62.92</v>
+      </c>
+      <c r="F14">
+        <v>62.92</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>20496</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="F15">
+        <v>107.41</v>
+      </c>
+      <c r="G15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>20519</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>28.56</v>
+      </c>
+      <c r="F16">
+        <v>28.56</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>20526</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17">
+        <v>48.92</v>
+      </c>
+      <c r="F17">
+        <v>48.92</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>20533</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18">
+        <v>62.92</v>
+      </c>
+      <c r="F18">
+        <v>62.92</v>
+      </c>
+      <c r="G18">
+        <f>F18/E18</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>20540</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <v>9.64</v>
+      </c>
+      <c r="F19">
+        <v>115.68</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>20564</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20">
+        <v>41.92</v>
+      </c>
+      <c r="F20">
+        <v>41.92</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20588</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21">
+        <v>10.33</v>
+      </c>
+      <c r="F21">
+        <v>123.95</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>20601</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22">
+        <v>68.84</v>
+      </c>
+      <c r="F22">
+        <v>68.84</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>20618</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23">
+        <v>10.33</v>
+      </c>
+      <c r="F23">
+        <v>123.95</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>20625</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24">
+        <v>10.33</v>
+      </c>
+      <c r="F24">
+        <v>123.95</v>
+      </c>
+      <c r="G24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>20649</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25">
+        <v>68.84</v>
+      </c>
+      <c r="F25">
+        <v>68.84</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>20656</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26">
+        <v>10.33</v>
+      </c>
+      <c r="F26">
+        <v>123.95</v>
+      </c>
+      <c r="G26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>20687</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27">
+        <v>25.19</v>
+      </c>
+      <c r="F27">
+        <v>25.19</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>20694</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28">
+        <v>27.92</v>
+      </c>
+      <c r="F28">
+        <v>27.92</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>20700</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29">
+        <v>41.92</v>
+      </c>
+      <c r="F29">
+        <v>41.92</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>20717</v>
+      </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30">
+        <v>55.92</v>
+      </c>
+      <c r="F30">
+        <v>55.92</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>20809</v>
+      </c>
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31">
+        <v>1.79</v>
+      </c>
+      <c r="F31">
+        <v>64.5</v>
+      </c>
+      <c r="G31">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>20816</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32">
+        <v>1.79</v>
+      </c>
+      <c r="F32">
+        <v>64.5</v>
+      </c>
+      <c r="G32">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>20847</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33">
+        <v>7.78</v>
+      </c>
+      <c r="F33">
+        <v>93.4</v>
+      </c>
+      <c r="G33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>20854</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>7.78</v>
+      </c>
+      <c r="F34">
+        <v>93.4</v>
+      </c>
+      <c r="G34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>20861</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>15.57</v>
+      </c>
+      <c r="F35">
+        <v>186.88</v>
+      </c>
+      <c r="G35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>20960</v>
+      </c>
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36">
+        <v>5.39</v>
+      </c>
+      <c r="F36">
+        <v>64.64</v>
+      </c>
+      <c r="G36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>20984</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37">
+        <v>5.39</v>
+      </c>
+      <c r="F37">
+        <v>64.64</v>
+      </c>
+      <c r="G37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>21059</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38">
+        <v>2.99</v>
+      </c>
+      <c r="F38">
+        <v>59.8</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>21097</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39">
+        <v>5.39</v>
+      </c>
+      <c r="F39">
+        <v>107.74</v>
+      </c>
+      <c r="G39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>21103</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40">
+        <v>5.39</v>
+      </c>
+      <c r="F40">
+        <v>107.74</v>
+      </c>
+      <c r="G40">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>21165</v>
+      </c>
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41">
+        <v>5.39</v>
+      </c>
+      <c r="F41">
+        <v>64.64</v>
+      </c>
+      <c r="G41">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>21172</v>
+      </c>
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42">
+        <v>5.39</v>
+      </c>
+      <c r="F42">
+        <v>64.64</v>
+      </c>
+      <c r="G42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>21189</v>
+      </c>
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43">
+        <v>7.18</v>
+      </c>
+      <c r="F43">
+        <v>86.21</v>
+      </c>
+      <c r="G43">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>21196</v>
+      </c>
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F44">
+        <v>100.59</v>
+      </c>
+      <c r="G44">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>21424</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45">
+        <v>11.92</v>
+      </c>
+      <c r="F45">
+        <v>143.09</v>
+      </c>
+      <c r="G45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>21431</v>
+      </c>
+      <c r="B46" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46">
+        <v>47.88</v>
+      </c>
+      <c r="F46">
+        <v>191.5</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>21448</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47">
+        <v>5.93</v>
+      </c>
+      <c r="F47">
+        <v>29.66</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>21462</v>
+      </c>
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48">
+        <v>5.93</v>
+      </c>
+      <c r="F48">
+        <v>29.66</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>21479</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49">
+        <v>9.58</v>
+      </c>
+      <c r="F49">
+        <v>57.49</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>21486</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50">
+        <v>9.58</v>
+      </c>
+      <c r="F50">
+        <v>57.49</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>21493</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51">
+        <v>10.78</v>
+      </c>
+      <c r="F51">
+        <v>129.35</v>
+      </c>
+      <c r="G51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>21509</v>
+      </c>
+      <c r="B52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52">
+        <v>10.78</v>
+      </c>
+      <c r="F52">
+        <v>129.35</v>
+      </c>
+      <c r="G52">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>21523</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53">
+        <v>10.78</v>
+      </c>
+      <c r="F53">
+        <v>129.35</v>
+      </c>
+      <c r="G53">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>21561</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54">
+        <v>7.18</v>
+      </c>
+      <c r="F54">
+        <v>86.21</v>
+      </c>
+      <c r="G54">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>21578</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F55">
+        <v>100.59</v>
+      </c>
+      <c r="G55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>21585</v>
+      </c>
+      <c r="B56" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56">
+        <v>9.58</v>
+      </c>
+      <c r="F56">
+        <v>114.97</v>
+      </c>
+      <c r="G56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>21592</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57">
+        <v>11.92</v>
+      </c>
+      <c r="F57">
+        <v>143.09</v>
+      </c>
+      <c r="G57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>21608</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58">
+        <v>14.37</v>
+      </c>
+      <c r="F58">
+        <v>172.5</v>
+      </c>
+      <c r="G58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>21714</v>
+      </c>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59">
+        <v>11.92</v>
+      </c>
+      <c r="F59">
+        <v>143.09</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>21745</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60">
+        <v>11.92</v>
+      </c>
+      <c r="F60">
+        <v>143.09</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>21752</v>
+      </c>
+      <c r="B61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61">
+        <v>21.57</v>
+      </c>
+      <c r="F61">
+        <v>258.77999999999997</v>
+      </c>
+      <c r="G61">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>21783</v>
+      </c>
+      <c r="B62" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" t="s">
+        <v>126</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62">
+        <v>21.57</v>
+      </c>
+      <c r="F62">
+        <v>258.77999999999997</v>
+      </c>
+      <c r="G62">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>21790</v>
+      </c>
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63">
+        <v>11.92</v>
+      </c>
+      <c r="F63">
+        <v>143.09</v>
+      </c>
+      <c r="G63">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>21844</v>
+      </c>
+      <c r="B64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" t="s">
+        <v>129</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64">
+        <v>21.57</v>
+      </c>
+      <c r="F64">
+        <v>431.3</v>
+      </c>
+      <c r="G64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>21899</v>
+      </c>
+      <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65">
+        <v>23.91</v>
+      </c>
+      <c r="F65">
+        <v>478.16</v>
+      </c>
+      <c r="G65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>22049</v>
+      </c>
+      <c r="B66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66">
+        <v>2.99</v>
+      </c>
+      <c r="F66">
+        <v>89.7</v>
+      </c>
+      <c r="G66">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>22056</v>
+      </c>
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67">
+        <v>2.99</v>
+      </c>
+      <c r="F67">
+        <v>89.7</v>
+      </c>
+      <c r="G67">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>22339</v>
+      </c>
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68">
+        <v>11.92</v>
+      </c>
+      <c r="F68">
+        <v>143.09</v>
+      </c>
+      <c r="G68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>22353</v>
+      </c>
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69">
+        <v>7.18</v>
+      </c>
+      <c r="F69">
+        <v>86.21</v>
+      </c>
+      <c r="G69">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>22360</v>
+      </c>
+      <c r="B70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" t="s">
+        <v>113</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70">
+        <v>9.58</v>
+      </c>
+      <c r="F70">
+        <v>114.97</v>
+      </c>
+      <c r="G70">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>22391</v>
+      </c>
+      <c r="B71" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" t="s">
+        <v>121</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F71">
+        <v>100.59</v>
+      </c>
+      <c r="G71">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>22421</v>
+      </c>
+      <c r="B72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F72">
+        <v>100.59</v>
+      </c>
+      <c r="G72">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73">
+        <v>9.35</v>
+      </c>
+      <c r="F73">
+        <v>112.2</v>
+      </c>
+      <c r="G73">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" t="s">
+        <v>189</v>
+      </c>
+      <c r="E74" s="3">
+        <v>56</v>
+      </c>
+      <c r="F74" s="3">
+        <v>56</v>
+      </c>
+      <c r="G74" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B75" t="s">
+        <v>167</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D75" t="s">
+        <v>189</v>
+      </c>
+      <c r="E75" s="3">
+        <v>95</v>
+      </c>
+      <c r="F75" s="3">
+        <v>95</v>
+      </c>
+      <c r="G75" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B76" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D76" t="s">
+        <v>189</v>
+      </c>
+      <c r="E76" s="3">
+        <v>44</v>
+      </c>
+      <c r="F76" s="3">
+        <v>44</v>
+      </c>
+      <c r="G76" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B77" t="s">
+        <v>167</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" t="s">
+        <v>189</v>
+      </c>
+      <c r="E77" s="3">
+        <v>44</v>
+      </c>
+      <c r="F77" s="3">
+        <v>44</v>
+      </c>
+      <c r="G77" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B78" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D78" t="s">
+        <v>189</v>
+      </c>
+      <c r="E78" s="3">
+        <v>52</v>
+      </c>
+      <c r="F78" s="3">
+        <v>52</v>
+      </c>
+      <c r="G78" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B79" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D79" t="s">
+        <v>189</v>
+      </c>
+      <c r="E79" s="3">
+        <v>56</v>
+      </c>
+      <c r="F79" s="3">
+        <v>56</v>
+      </c>
+      <c r="G79" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B80" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" t="s">
+        <v>189</v>
+      </c>
+      <c r="E80" s="3">
+        <v>60</v>
+      </c>
+      <c r="F80" s="3">
+        <v>60</v>
+      </c>
+      <c r="G80" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B81" t="s">
+        <v>167</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D81" t="s">
+        <v>189</v>
+      </c>
+      <c r="E81" s="3">
+        <v>80</v>
+      </c>
+      <c r="F81" s="3">
+        <v>80</v>
+      </c>
+      <c r="G81" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B82" t="s">
+        <v>167</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" t="s">
+        <v>189</v>
+      </c>
+      <c r="E82" s="3">
+        <v>56</v>
+      </c>
+      <c r="F82" s="3">
+        <v>56</v>
+      </c>
+      <c r="G82" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D83" t="s">
+        <v>189</v>
+      </c>
+      <c r="E83" s="3">
+        <v>56</v>
+      </c>
+      <c r="F83" s="3">
+        <v>56</v>
+      </c>
+      <c r="G83" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B84" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D84" t="s">
+        <v>189</v>
+      </c>
+      <c r="E84" s="3">
+        <v>44</v>
+      </c>
+      <c r="F84" s="3">
+        <v>44</v>
+      </c>
+      <c r="G84" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B85" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D85" t="s">
+        <v>189</v>
+      </c>
+      <c r="E85" s="3">
+        <v>44</v>
+      </c>
+      <c r="F85" s="3">
+        <v>44</v>
+      </c>
+      <c r="G85" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B86" t="s">
+        <v>167</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D86" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86" s="3">
+        <v>75</v>
+      </c>
+      <c r="F86" s="3">
+        <v>75</v>
+      </c>
+      <c r="G86" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B87" t="s">
+        <v>167</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D87" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="3">
+        <v>13</v>
+      </c>
+      <c r="F87" s="3">
+        <v>13</v>
+      </c>
+      <c r="G87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B88" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D88" t="s">
+        <v>189</v>
+      </c>
+      <c r="E88" s="3">
+        <v>205</v>
+      </c>
+      <c r="F88" s="3">
+        <v>205</v>
+      </c>
+      <c r="G88" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B89" t="s">
+        <v>167</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D89" t="s">
+        <v>189</v>
+      </c>
+      <c r="E89" s="3">
+        <v>42</v>
+      </c>
+      <c r="F89" s="3">
+        <v>42</v>
+      </c>
+      <c r="G89" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B90" t="s">
+        <v>167</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D90" t="s">
+        <v>189</v>
+      </c>
+      <c r="E90" s="3">
+        <v>44</v>
+      </c>
+      <c r="F90" s="3">
+        <v>44</v>
+      </c>
+      <c r="G90" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B91" t="s">
+        <v>167</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D91" t="s">
+        <v>189</v>
+      </c>
+      <c r="E91" s="3">
+        <v>44</v>
+      </c>
+      <c r="F91" s="3">
+        <v>44</v>
+      </c>
+      <c r="G91" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D92" t="s">
+        <v>189</v>
+      </c>
+      <c r="E92" s="3">
+        <v>44</v>
+      </c>
+      <c r="F92" s="3">
+        <v>44</v>
+      </c>
+      <c r="G92" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B93" t="s">
+        <v>167</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D93" t="s">
+        <v>189</v>
+      </c>
+      <c r="E93" s="3">
+        <v>128</v>
+      </c>
+      <c r="F93" s="3">
+        <v>128</v>
+      </c>
+      <c r="G93" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B94" t="s">
+        <v>167</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D94" t="s">
+        <v>189</v>
+      </c>
+      <c r="E94" s="3">
+        <v>55</v>
+      </c>
+      <c r="F94" s="3">
+        <v>55</v>
+      </c>
+      <c r="G94" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B95" t="s">
+        <v>167</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D95" t="s">
+        <v>189</v>
+      </c>
+      <c r="E95" s="3">
+        <v>75</v>
+      </c>
+      <c r="F95" s="3">
+        <v>75</v>
+      </c>
+      <c r="G95" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B96" t="s">
+        <v>167</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D96" t="s">
+        <v>189</v>
+      </c>
+      <c r="E96" s="3">
+        <v>129</v>
+      </c>
+      <c r="F96" s="3">
+        <v>129</v>
+      </c>
+      <c r="G96" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B97" t="s">
+        <v>167</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D97" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97" s="3">
+        <v>44</v>
+      </c>
+      <c r="F97" s="3">
+        <v>44</v>
+      </c>
+      <c r="G97" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B98" t="s">
+        <v>167</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D98" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98" s="3">
+        <v>83</v>
+      </c>
+      <c r="F98" s="3">
+        <v>83</v>
+      </c>
+      <c r="G98" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B99" t="s">
+        <v>167</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D99" t="s">
+        <v>189</v>
+      </c>
+      <c r="E99" s="3">
+        <v>44</v>
+      </c>
+      <c r="F99" s="3">
+        <v>44</v>
+      </c>
+      <c r="G99" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B100" t="s">
+        <v>167</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D100" t="s">
+        <v>189</v>
+      </c>
+      <c r="E100" s="3">
+        <v>77</v>
+      </c>
+      <c r="F100" s="3">
+        <v>77</v>
+      </c>
+      <c r="G100" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B101" t="s">
+        <v>167</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D101" t="s">
+        <v>189</v>
+      </c>
+      <c r="E101" s="3">
+        <v>77</v>
+      </c>
+      <c r="F101" s="3">
+        <v>77</v>
+      </c>
+      <c r="G101" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B102" t="s">
+        <v>167</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D102" t="s">
+        <v>189</v>
+      </c>
+      <c r="E102" s="3">
+        <v>77</v>
+      </c>
+      <c r="F102" s="3">
+        <v>77</v>
+      </c>
+      <c r="G102" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B103" t="s">
+        <v>167</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D103" t="s">
+        <v>189</v>
+      </c>
+      <c r="E103" s="3">
+        <v>77</v>
+      </c>
+      <c r="F103" s="3">
+        <v>77</v>
+      </c>
+      <c r="G103" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B104" t="s">
+        <v>167</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D104" t="s">
+        <v>189</v>
+      </c>
+      <c r="E104" s="3">
+        <v>77</v>
+      </c>
+      <c r="F104" s="3">
+        <v>77</v>
+      </c>
+      <c r="G104" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B105" t="s">
+        <v>167</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D105" t="s">
+        <v>189</v>
+      </c>
+      <c r="E105" s="3">
+        <v>77</v>
+      </c>
+      <c r="F105" s="3">
+        <v>77</v>
+      </c>
+      <c r="G105" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B106" t="s">
+        <v>167</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D106" t="s">
+        <v>189</v>
+      </c>
+      <c r="E106" s="3">
+        <v>77</v>
+      </c>
+      <c r="F106" s="3">
+        <v>77</v>
+      </c>
+      <c r="G106" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B107" t="s">
+        <v>167</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D107" t="s">
+        <v>189</v>
+      </c>
+      <c r="E107" s="3">
+        <v>108</v>
+      </c>
+      <c r="F107" s="3">
+        <v>108</v>
+      </c>
+      <c r="G107" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B108" t="s">
+        <v>167</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D108" t="s">
+        <v>189</v>
+      </c>
+      <c r="E108" s="3">
+        <v>73</v>
+      </c>
+      <c r="F108" s="3">
+        <v>73</v>
+      </c>
+      <c r="G108" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B109" t="s">
+        <v>167</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D109" t="s">
+        <v>189</v>
+      </c>
+      <c r="E109" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="F109" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G109" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B110" t="s">
+        <v>167</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D110" t="s">
+        <v>189</v>
+      </c>
+      <c r="E110" s="3">
+        <v>77</v>
+      </c>
+      <c r="F110" s="3">
+        <v>77</v>
+      </c>
+      <c r="G110" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B111" t="s">
+        <v>134</v>
+      </c>
+      <c r="C111" t="s">
+        <v>136</v>
+      </c>
+      <c r="D111" t="s">
+        <v>135</v>
+      </c>
+      <c r="E111">
+        <v>5.99</v>
+      </c>
+      <c r="F111">
+        <v>5.99</v>
+      </c>
+      <c r="G111">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B112" t="s">
+        <v>134</v>
+      </c>
+      <c r="C112" t="s">
+        <v>137</v>
+      </c>
+      <c r="D112" t="s">
+        <v>135</v>
+      </c>
+      <c r="E112">
+        <v>5.99</v>
+      </c>
+      <c r="F112">
+        <v>5.99</v>
+      </c>
+      <c r="G112">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B113" t="s">
+        <v>134</v>
+      </c>
+      <c r="C113" t="s">
+        <v>138</v>
+      </c>
+      <c r="D113" t="s">
+        <v>135</v>
+      </c>
+      <c r="E113">
+        <v>5.99</v>
+      </c>
+      <c r="F113">
+        <v>5.99</v>
+      </c>
+      <c r="G113">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B114" t="s">
+        <v>134</v>
+      </c>
+      <c r="C114" t="s">
+        <v>139</v>
+      </c>
+      <c r="D114" t="s">
+        <v>135</v>
+      </c>
+      <c r="E114">
+        <v>5.99</v>
+      </c>
+      <c r="F114">
+        <v>5.99</v>
+      </c>
+      <c r="G114">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B115" t="s">
+        <v>134</v>
+      </c>
+      <c r="C115" t="s">
+        <v>140</v>
+      </c>
+      <c r="D115" t="s">
+        <v>135</v>
+      </c>
+      <c r="E115">
+        <v>5.99</v>
+      </c>
+      <c r="F115">
+        <v>5.99</v>
+      </c>
+      <c r="G115">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B116" t="s">
+        <v>134</v>
+      </c>
+      <c r="C116" t="s">
+        <v>141</v>
+      </c>
+      <c r="D116" t="s">
+        <v>135</v>
+      </c>
+      <c r="E116">
+        <v>5.99</v>
+      </c>
+      <c r="F116">
+        <v>5.99</v>
+      </c>
+      <c r="G116">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B117" t="s">
+        <v>134</v>
+      </c>
+      <c r="C117" t="s">
+        <v>142</v>
+      </c>
+      <c r="D117" t="s">
+        <v>135</v>
+      </c>
+      <c r="E117">
+        <v>5.99</v>
+      </c>
+      <c r="F117">
+        <v>5.99</v>
+      </c>
+      <c r="G117">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B118" t="s">
+        <v>134</v>
+      </c>
+      <c r="C118" t="s">
+        <v>143</v>
+      </c>
+      <c r="D118" t="s">
+        <v>135</v>
+      </c>
+      <c r="E118">
+        <v>5.99</v>
+      </c>
+      <c r="F118">
+        <v>5.99</v>
+      </c>
+      <c r="G118">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B119" t="s">
+        <v>134</v>
+      </c>
+      <c r="C119" t="s">
+        <v>144</v>
+      </c>
+      <c r="D119" t="s">
+        <v>135</v>
+      </c>
+      <c r="E119">
+        <v>1.99</v>
+      </c>
+      <c r="F119">
+        <v>1.99</v>
+      </c>
+      <c r="G119">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B120" t="s">
+        <v>134</v>
+      </c>
+      <c r="C120" t="s">
+        <v>145</v>
+      </c>
+      <c r="D120" t="s">
+        <v>135</v>
+      </c>
+      <c r="E120">
+        <v>1.99</v>
+      </c>
+      <c r="F120">
+        <v>1.99</v>
+      </c>
+      <c r="G120">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121">
+        <v>15.8</v>
+      </c>
+      <c r="F121">
+        <v>15.8</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122">
+        <v>15.8</v>
+      </c>
+      <c r="F122">
+        <v>15.8</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123">
+        <v>15.8</v>
+      </c>
+      <c r="F123">
+        <v>15.8</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124">
+        <v>15.8</v>
+      </c>
+      <c r="F124">
+        <v>15.8</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125">
+        <v>15.8</v>
+      </c>
+      <c r="F125">
+        <v>15.8</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126">
+        <v>15.8</v>
+      </c>
+      <c r="F126">
+        <v>15.8</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127">
+        <v>15.8</v>
+      </c>
+      <c r="F127">
+        <v>15.8</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>16</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128">
+        <v>15.8</v>
+      </c>
+      <c r="F128">
+        <v>15.8</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129">
+        <v>15.8</v>
+      </c>
+      <c r="F129">
+        <v>15.8</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B130" t="s">
+        <v>167</v>
+      </c>
+      <c r="C130" t="s">
+        <v>168</v>
+      </c>
+      <c r="D130" t="s">
+        <v>188</v>
+      </c>
+      <c r="E130">
+        <v>6.94</v>
+      </c>
+      <c r="F130">
+        <v>83.28</v>
+      </c>
+      <c r="G130">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B131" t="s">
+        <v>167</v>
+      </c>
+      <c r="C131" t="s">
+        <v>169</v>
+      </c>
+      <c r="D131" t="s">
+        <v>188</v>
+      </c>
+      <c r="E131">
+        <v>6.94</v>
+      </c>
+      <c r="F131">
+        <v>83.28</v>
+      </c>
+      <c r="G131">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B132" t="s">
+        <v>167</v>
+      </c>
+      <c r="C132" t="s">
+        <v>170</v>
+      </c>
+      <c r="D132" t="s">
+        <v>188</v>
+      </c>
+      <c r="E132">
+        <v>3.96</v>
+      </c>
+      <c r="F132">
+        <v>118.8</v>
+      </c>
+      <c r="G132">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B133" t="s">
+        <v>20</v>
+      </c>
+      <c r="C133" t="s">
+        <v>98</v>
+      </c>
+      <c r="D133" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133">
+        <v>11.92</v>
+      </c>
+      <c r="F133">
+        <v>143.09</v>
+      </c>
+      <c r="G133">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B134" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" t="s">
+        <v>25</v>
+      </c>
+      <c r="D134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134">
+        <v>9.64</v>
+      </c>
+      <c r="F134">
+        <v>115.68</v>
+      </c>
+      <c r="G134">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B135" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" t="s">
+        <v>25</v>
+      </c>
+      <c r="D135" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135">
+        <v>8.6</v>
+      </c>
+      <c r="F135">
+        <v>103.2</v>
+      </c>
+      <c r="G135">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F136">
+        <v>103.56</v>
+      </c>
+      <c r="G136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" t="s">
+        <v>30</v>
+      </c>
+      <c r="D137" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137">
+        <v>31.65</v>
+      </c>
+      <c r="F137">
+        <v>31.65</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B138" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" t="s">
+        <v>32</v>
+      </c>
+      <c r="D138" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138">
+        <v>50.74</v>
+      </c>
+      <c r="F138">
+        <v>50.74</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B139" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" t="s">
+        <v>26</v>
+      </c>
+      <c r="D139" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139">
+        <v>8.6</v>
+      </c>
+      <c r="F139">
+        <v>103.2</v>
+      </c>
+      <c r="G139">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>29</v>
+      </c>
+      <c r="D140" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F140">
+        <v>103.56</v>
+      </c>
+      <c r="G140">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" t="s">
+        <v>31</v>
+      </c>
+      <c r="D141" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141">
+        <v>31.65</v>
+      </c>
+      <c r="F141">
+        <v>31.65</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>33</v>
+      </c>
+      <c r="D142" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142">
+        <v>50.74</v>
+      </c>
+      <c r="F142">
+        <v>50.74</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143">
+        <v>9.27</v>
+      </c>
+      <c r="F143">
+        <v>111.2</v>
+      </c>
+      <c r="G143">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>34</v>
+      </c>
+      <c r="D144" t="s">
+        <v>18</v>
+      </c>
+      <c r="E144">
+        <v>10.6</v>
+      </c>
+      <c r="F144">
+        <v>127.2</v>
+      </c>
+      <c r="G144">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>35</v>
+      </c>
+      <c r="D145" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145">
+        <v>10.6</v>
+      </c>
+      <c r="F145">
+        <v>127.2</v>
+      </c>
+      <c r="G145">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>36</v>
+      </c>
+      <c r="D146" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146">
+        <v>10.6</v>
+      </c>
+      <c r="F146">
+        <v>127.2</v>
+      </c>
+      <c r="G146">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" t="s">
+        <v>37</v>
+      </c>
+      <c r="D147" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147">
+        <v>7.94</v>
+      </c>
+      <c r="F147">
+        <v>95.28</v>
+      </c>
+      <c r="G147">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B148" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" t="s">
+        <v>40</v>
+      </c>
+      <c r="D148" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148">
+        <v>15.26</v>
+      </c>
+      <c r="F148">
+        <v>91.56</v>
+      </c>
+      <c r="G148">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B149" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" t="s">
+        <v>43</v>
+      </c>
+      <c r="D149" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149">
+        <v>27.5</v>
+      </c>
+      <c r="F149">
+        <v>27.5</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B150" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" t="s">
+        <v>46</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150">
+        <v>43.48</v>
+      </c>
+      <c r="F150">
+        <v>43.48</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" t="s">
+        <v>48</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151">
+        <v>59.98</v>
+      </c>
+      <c r="F151">
+        <v>59.98</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" t="s">
+        <v>38</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152">
+        <v>7.94</v>
+      </c>
+      <c r="F152">
+        <v>95.28</v>
+      </c>
+      <c r="G152">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B153" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" t="s">
+        <v>41</v>
+      </c>
+      <c r="D153" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153">
+        <v>15.26</v>
+      </c>
+      <c r="F153">
+        <v>91.56</v>
+      </c>
+      <c r="G153">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B154" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" t="s">
+        <v>44</v>
+      </c>
+      <c r="D154" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154">
+        <v>27.5</v>
+      </c>
+      <c r="F154">
+        <v>27.5</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B155" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" t="s">
+        <v>47</v>
+      </c>
+      <c r="D155" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155">
+        <v>43.48</v>
+      </c>
+      <c r="F155">
+        <v>43.48</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B156" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" t="s">
+        <v>49</v>
+      </c>
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156">
+        <v>59.98</v>
+      </c>
+      <c r="F156">
+        <v>59.98</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B157" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" t="s">
+        <v>39</v>
+      </c>
+      <c r="D157" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157">
+        <v>8.6</v>
+      </c>
+      <c r="F157">
+        <v>103.2</v>
+      </c>
+      <c r="G157">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B158" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" t="s">
+        <v>42</v>
+      </c>
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F158">
+        <v>103.56</v>
+      </c>
+      <c r="G158">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B159" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" t="s">
+        <v>45</v>
+      </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159">
+        <v>34.4</v>
+      </c>
+      <c r="F159">
+        <v>34.4</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B160" t="s">
+        <v>17</v>
+      </c>
+      <c r="C160" t="s">
+        <v>50</v>
+      </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160">
+        <v>7.94</v>
+      </c>
+      <c r="F160">
+        <v>95.28</v>
+      </c>
+      <c r="G160">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B161" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" t="s">
+        <v>54</v>
+      </c>
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F161">
+        <v>103.56</v>
+      </c>
+      <c r="G161">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B162" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" t="s">
+        <v>56</v>
+      </c>
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162">
+        <v>65.25</v>
+      </c>
+      <c r="F162">
+        <v>65.25</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B163" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" t="s">
+        <v>51</v>
+      </c>
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163">
+        <v>7.94</v>
+      </c>
+      <c r="F163">
+        <v>95.28</v>
+      </c>
+      <c r="G163">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B164" t="s">
+        <v>17</v>
+      </c>
+      <c r="C164" t="s">
+        <v>52</v>
+      </c>
+      <c r="D164" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164">
+        <v>7.94</v>
+      </c>
+      <c r="F164">
+        <v>95.28</v>
+      </c>
+      <c r="G164">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B165" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" t="s">
+        <v>55</v>
+      </c>
+      <c r="D165" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F165">
+        <v>103.56</v>
+      </c>
+      <c r="G165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B166" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" t="s">
+        <v>57</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166">
+        <v>65.25</v>
+      </c>
+      <c r="F166">
+        <v>65.25</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B167" t="s">
+        <v>17</v>
+      </c>
+      <c r="C167" t="s">
+        <v>53</v>
+      </c>
+      <c r="D167" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167">
+        <v>7.94</v>
+      </c>
+      <c r="F167">
+        <v>95.28</v>
+      </c>
+      <c r="G167">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B168" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" t="s">
+        <v>131</v>
+      </c>
+      <c r="D168" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F168">
+        <v>98.4</v>
+      </c>
+      <c r="G168">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B169" t="s">
+        <v>17</v>
+      </c>
+      <c r="C169" t="s">
+        <v>58</v>
+      </c>
+      <c r="D169" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F169">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B170" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" t="s">
+        <v>59</v>
+      </c>
+      <c r="D170" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170">
+        <v>23.93</v>
+      </c>
+      <c r="F170">
+        <v>23393</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B171" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" t="s">
+        <v>60</v>
+      </c>
+      <c r="D171" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171">
+        <v>37.5</v>
+      </c>
+      <c r="F171">
+        <v>37.5</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B172" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" t="s">
+        <v>61</v>
+      </c>
+      <c r="D172" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172">
+        <v>52.55</v>
+      </c>
+      <c r="F172">
+        <v>52.55</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B173" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" t="s">
+        <v>62</v>
+      </c>
+      <c r="D173" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173">
+        <v>63</v>
+      </c>
+      <c r="F173">
+        <v>63</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B174" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" t="s">
+        <v>65</v>
+      </c>
+      <c r="D174" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174">
+        <v>1.62</v>
+      </c>
+      <c r="F174">
+        <v>58.3</v>
+      </c>
+      <c r="G174">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B175" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" t="s">
+        <v>66</v>
+      </c>
+      <c r="D175" t="s">
+        <v>18</v>
+      </c>
+      <c r="E175">
+        <v>1.62</v>
+      </c>
+      <c r="F175">
+        <v>58.3</v>
+      </c>
+      <c r="G175">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B176" t="s">
+        <v>17</v>
+      </c>
+      <c r="C176" t="s">
+        <v>67</v>
+      </c>
+      <c r="D176" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176">
+        <v>1.62</v>
+      </c>
+      <c r="F176">
+        <v>58.3</v>
+      </c>
+      <c r="G176">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B177" t="s">
+        <v>17</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>18</v>
+      </c>
+      <c r="E177">
+        <v>1.62</v>
+      </c>
+      <c r="F177">
+        <v>58.3</v>
+      </c>
+      <c r="G177">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B178" t="s">
+        <v>17</v>
+      </c>
+      <c r="C178" t="s">
+        <v>69</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178">
+        <v>6.81</v>
+      </c>
+      <c r="F178">
+        <v>81.72</v>
+      </c>
+      <c r="G178">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B179" t="s">
+        <v>17</v>
+      </c>
+      <c r="C179" t="s">
+        <v>70</v>
+      </c>
+      <c r="D179" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179">
+        <v>6.81</v>
+      </c>
+      <c r="F179">
+        <v>81.72</v>
+      </c>
+      <c r="G179">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B180" t="s">
+        <v>17</v>
+      </c>
+      <c r="C180" t="s">
+        <v>71</v>
+      </c>
+      <c r="D180" t="s">
+        <v>18</v>
+      </c>
+      <c r="E180">
+        <v>13.26</v>
+      </c>
+      <c r="F180">
+        <v>159.12</v>
+      </c>
+      <c r="G180">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B181" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" t="s">
+        <v>72</v>
+      </c>
+      <c r="D181" t="s">
+        <v>18</v>
+      </c>
+      <c r="E181">
+        <v>13.26</v>
+      </c>
+      <c r="F181">
+        <v>159.12</v>
+      </c>
+      <c r="G181">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B182" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" t="s">
+        <v>73</v>
+      </c>
+      <c r="D182" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182">
+        <v>3.69</v>
+      </c>
+      <c r="F182">
+        <v>44.28</v>
+      </c>
+      <c r="G182">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B183" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" t="s">
+        <v>132</v>
+      </c>
+      <c r="D183" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183">
+        <v>11.38</v>
+      </c>
+      <c r="F183">
+        <v>136.55000000000001</v>
+      </c>
+      <c r="G183">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B184" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" t="s">
+        <v>74</v>
+      </c>
+      <c r="D184" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184">
+        <v>3.69</v>
+      </c>
+      <c r="F184">
+        <v>44.28</v>
+      </c>
+      <c r="G184">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B185" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" t="s">
+        <v>133</v>
+      </c>
+      <c r="D185" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185">
+        <v>11.38</v>
+      </c>
+      <c r="F185">
+        <v>136.55000000000001</v>
+      </c>
+      <c r="G185">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B186" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" t="s">
+        <v>75</v>
+      </c>
+      <c r="D186" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186">
+        <v>2.29</v>
+      </c>
+      <c r="F186">
+        <v>45.8</v>
+      </c>
+      <c r="G186">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B187" t="s">
+        <v>17</v>
+      </c>
+      <c r="C187" t="s">
+        <v>76</v>
+      </c>
+      <c r="D187" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187">
+        <v>2.29</v>
+      </c>
+      <c r="F187">
+        <v>45.8</v>
+      </c>
+      <c r="G187">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B188" t="s">
+        <v>17</v>
+      </c>
+      <c r="C188" t="s">
+        <v>77</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188">
+        <v>2.29</v>
+      </c>
+      <c r="F188">
+        <v>45.8</v>
+      </c>
+      <c r="G188">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B189" t="s">
+        <v>17</v>
+      </c>
+      <c r="C189" t="s">
+        <v>78</v>
+      </c>
+      <c r="D189" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F189">
+        <v>81.2</v>
+      </c>
+      <c r="G189">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B190" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" t="s">
+        <v>79</v>
+      </c>
+      <c r="D190" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F190">
+        <v>81.2</v>
+      </c>
+      <c r="G190">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B191" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" t="s">
+        <v>80</v>
+      </c>
+      <c r="D191" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F191">
+        <v>81.2</v>
+      </c>
+      <c r="G191">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B192" t="s">
+        <v>17</v>
+      </c>
+      <c r="C192" t="s">
+        <v>81</v>
+      </c>
+      <c r="D192" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192">
+        <v>9.35</v>
+      </c>
+      <c r="F192">
+        <v>112.2</v>
+      </c>
+      <c r="G192">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B193" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193" t="s">
+        <v>82</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F193">
+        <v>55.8</v>
+      </c>
+      <c r="G193">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B194" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" t="s">
+        <v>83</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F194">
+        <v>55.8</v>
+      </c>
+      <c r="G194">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B195" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" t="s">
+        <v>84</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F195">
+        <v>55.8</v>
+      </c>
+      <c r="G195">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B196" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196" t="s">
+        <v>85</v>
+      </c>
+      <c r="D196" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196">
+        <v>5.82</v>
+      </c>
+      <c r="F196">
+        <v>69.88</v>
+      </c>
+      <c r="G196">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B197" t="s">
+        <v>17</v>
+      </c>
+      <c r="C197" t="s">
+        <v>86</v>
+      </c>
+      <c r="D197" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197">
+        <v>7.58</v>
+      </c>
+      <c r="F197">
+        <v>90.96</v>
+      </c>
+      <c r="G197">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B198" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198" t="s">
+        <v>87</v>
+      </c>
+      <c r="D198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198">
+        <v>9.35</v>
+      </c>
+      <c r="F198">
+        <v>56.1</v>
+      </c>
+      <c r="G198">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B199" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199" t="s">
+        <v>88</v>
+      </c>
+      <c r="D199" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199">
+        <v>9.93</v>
+      </c>
+      <c r="F199">
+        <v>119.16</v>
+      </c>
+      <c r="G199">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B200" t="s">
+        <v>17</v>
+      </c>
+      <c r="C200" t="s">
+        <v>89</v>
+      </c>
+      <c r="D200" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200">
+        <v>39.9</v>
+      </c>
+      <c r="F200">
+        <v>159.6</v>
+      </c>
+      <c r="G200">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B201" t="s">
+        <v>17</v>
+      </c>
+      <c r="C201" t="s">
+        <v>90</v>
+      </c>
+      <c r="D201" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F201">
+        <v>21.8</v>
+      </c>
+      <c r="G201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B202" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202" t="s">
+        <v>91</v>
+      </c>
+      <c r="D202" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202">
+        <v>4.99</v>
+      </c>
+      <c r="F202">
+        <v>24.95</v>
+      </c>
+      <c r="G202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B203" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" t="s">
+        <v>92</v>
+      </c>
+      <c r="D203" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203">
+        <v>9.35</v>
+      </c>
+      <c r="F203">
+        <v>56.1</v>
+      </c>
+      <c r="G203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B204" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" t="s">
+        <v>93</v>
+      </c>
+      <c r="D204" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204">
+        <v>9.35</v>
+      </c>
+      <c r="F204">
+        <v>56.1</v>
+      </c>
+      <c r="G204">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B205" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205" t="s">
+        <v>94</v>
+      </c>
+      <c r="D205" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205">
+        <v>9.35</v>
+      </c>
+      <c r="F205">
+        <v>112.2</v>
+      </c>
+      <c r="G205">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B206" t="s">
+        <v>17</v>
+      </c>
+      <c r="C206" t="s">
+        <v>95</v>
+      </c>
+      <c r="D206" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206">
+        <v>9.35</v>
+      </c>
+      <c r="F206">
+        <v>112.2</v>
+      </c>
+      <c r="G206">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B207" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" t="s">
+        <v>96</v>
+      </c>
+      <c r="D207" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207">
+        <v>9.35</v>
+      </c>
+      <c r="F207">
+        <v>112.2</v>
+      </c>
+      <c r="G207">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B208" t="s">
+        <v>17</v>
+      </c>
+      <c r="C208" t="s">
+        <v>97</v>
+      </c>
+      <c r="D208" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208">
+        <v>9.35</v>
+      </c>
+      <c r="F208">
+        <v>112.2</v>
+      </c>
+      <c r="G208">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B209" t="s">
+        <v>17</v>
+      </c>
+      <c r="C209" t="s">
+        <v>100</v>
+      </c>
+      <c r="D209" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209">
+        <v>5.5</v>
+      </c>
+      <c r="F209">
+        <v>66</v>
+      </c>
+      <c r="G209">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B210" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210" t="s">
+        <v>102</v>
+      </c>
+      <c r="D210" t="s">
+        <v>18</v>
+      </c>
+      <c r="E210">
+        <v>2.17</v>
+      </c>
+      <c r="F210">
+        <v>25.99</v>
+      </c>
+      <c r="G210">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B211" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211" t="s">
+        <v>103</v>
+      </c>
+      <c r="D211" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211">
+        <v>11.05</v>
+      </c>
+      <c r="F211">
+        <v>132.6</v>
+      </c>
+      <c r="G211">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B212" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212" t="s">
+        <v>105</v>
+      </c>
+      <c r="D212" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212">
+        <v>5.5</v>
+      </c>
+      <c r="F212">
+        <v>66</v>
+      </c>
+      <c r="G212">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B213" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213" t="s">
+        <v>106</v>
+      </c>
+      <c r="D213" t="s">
+        <v>18</v>
+      </c>
+      <c r="E213">
+        <v>7.72</v>
+      </c>
+      <c r="F213">
+        <v>92.66</v>
+      </c>
+      <c r="G213">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B214" t="s">
+        <v>17</v>
+      </c>
+      <c r="C214" t="s">
+        <v>107</v>
+      </c>
+      <c r="D214" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214">
+        <v>8.83</v>
+      </c>
+      <c r="F214">
+        <v>105.99</v>
+      </c>
+      <c r="G214">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B215" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" t="s">
+        <v>108</v>
+      </c>
+      <c r="D215" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215">
+        <v>10.5</v>
+      </c>
+      <c r="F215">
+        <v>126</v>
+      </c>
+      <c r="G215">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B216" t="s">
+        <v>17</v>
+      </c>
+      <c r="C216" t="s">
+        <v>109</v>
+      </c>
+      <c r="D216" t="s">
+        <v>18</v>
+      </c>
+      <c r="E216">
+        <v>11.06</v>
+      </c>
+      <c r="F216">
+        <v>132.66</v>
+      </c>
+      <c r="G216">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B217" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217" t="s">
+        <v>116</v>
+      </c>
+      <c r="D217" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217">
+        <v>8.83</v>
+      </c>
+      <c r="F217">
+        <v>105.99</v>
+      </c>
+      <c r="G217">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B218" t="s">
+        <v>17</v>
+      </c>
+      <c r="C218" t="s">
+        <v>120</v>
+      </c>
+      <c r="D218" t="s">
+        <v>18</v>
+      </c>
+      <c r="E218">
+        <v>22.17</v>
+      </c>
+      <c r="F218">
+        <v>265.99</v>
+      </c>
+      <c r="G218">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B219" t="s">
+        <v>17</v>
+      </c>
+      <c r="C219" t="s">
+        <v>123</v>
+      </c>
+      <c r="D219" t="s">
+        <v>18</v>
+      </c>
+      <c r="E219">
+        <v>11.05</v>
+      </c>
+      <c r="F219">
+        <v>132.6</v>
+      </c>
+      <c r="G219">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B220" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220" t="s">
+        <v>124</v>
+      </c>
+      <c r="D220" t="s">
+        <v>18</v>
+      </c>
+      <c r="E220">
+        <v>16.61</v>
+      </c>
+      <c r="F220">
+        <v>199.33</v>
+      </c>
+      <c r="G220">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B221" t="s">
+        <v>17</v>
+      </c>
+      <c r="C221" t="s">
+        <v>125</v>
+      </c>
+      <c r="D221" t="s">
+        <v>18</v>
+      </c>
+      <c r="E221">
+        <v>15.5</v>
+      </c>
+      <c r="F221">
+        <v>186</v>
+      </c>
+      <c r="G221">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B222" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" t="s">
+        <v>126</v>
+      </c>
+      <c r="D222" t="s">
+        <v>18</v>
+      </c>
+      <c r="E222">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="F222">
+        <v>192.66</v>
+      </c>
+      <c r="G222">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B223" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" t="s">
+        <v>127</v>
+      </c>
+      <c r="D223" t="s">
+        <v>18</v>
+      </c>
+      <c r="E223">
+        <v>11.06</v>
+      </c>
+      <c r="F223">
+        <v>132.66</v>
+      </c>
+      <c r="G223">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B224" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224" t="s">
+        <v>129</v>
+      </c>
+      <c r="D224" t="s">
+        <v>18</v>
+      </c>
+      <c r="E224">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="F224">
+        <v>321.11</v>
+      </c>
+      <c r="G224">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B225" t="s">
+        <v>17</v>
+      </c>
+      <c r="C225" t="s">
+        <v>130</v>
+      </c>
+      <c r="D225" t="s">
+        <v>18</v>
+      </c>
+      <c r="E225">
+        <v>16.61</v>
+      </c>
+      <c r="F225">
+        <v>332.22</v>
+      </c>
+      <c r="G225">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B226" t="s">
+        <v>17</v>
+      </c>
+      <c r="C226" t="s">
+        <v>63</v>
+      </c>
+      <c r="D226" t="s">
+        <v>18</v>
+      </c>
+      <c r="E226">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F226">
+        <v>73.5</v>
+      </c>
+      <c r="G226">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B227" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227" t="s">
+        <v>64</v>
+      </c>
+      <c r="D227" t="s">
+        <v>18</v>
+      </c>
+      <c r="E227">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F227">
+        <v>73.5</v>
+      </c>
+      <c r="G227">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B228" t="s">
+        <v>17</v>
+      </c>
+      <c r="C228" t="s">
+        <v>104</v>
+      </c>
+      <c r="D228" t="s">
+        <v>18</v>
+      </c>
+      <c r="E228">
+        <v>7.72</v>
+      </c>
+      <c r="F228">
+        <v>46.33</v>
+      </c>
+      <c r="G228">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B229" t="s">
+        <v>17</v>
+      </c>
+      <c r="C229" t="s">
+        <v>101</v>
+      </c>
+      <c r="D229" t="s">
+        <v>18</v>
+      </c>
+      <c r="E229">
+        <v>5.5</v>
+      </c>
+      <c r="F229">
+        <v>66</v>
+      </c>
+      <c r="G229">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B230" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230" t="s">
+        <v>99</v>
+      </c>
+      <c r="D230" t="s">
+        <v>18</v>
+      </c>
+      <c r="E230">
+        <v>11.71</v>
+      </c>
+      <c r="F230">
+        <v>140.47</v>
+      </c>
+      <c r="G230">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B231" t="s">
+        <v>17</v>
+      </c>
+      <c r="C231" t="s">
+        <v>117</v>
+      </c>
+      <c r="D231" t="s">
+        <v>18</v>
+      </c>
+      <c r="E231">
+        <v>8.83</v>
+      </c>
+      <c r="F231">
+        <v>105.99</v>
+      </c>
+      <c r="G231">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B232" t="s">
+        <v>17</v>
+      </c>
+      <c r="C232" t="s">
+        <v>128</v>
+      </c>
+      <c r="D232" t="s">
+        <v>18</v>
+      </c>
+      <c r="E232">
+        <v>22.17</v>
+      </c>
+      <c r="F232">
+        <v>221.66</v>
+      </c>
+      <c r="G232">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B233" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233" t="s">
+        <v>118</v>
+      </c>
+      <c r="D233" t="s">
+        <v>18</v>
+      </c>
+      <c r="E233">
+        <v>11.06</v>
+      </c>
+      <c r="F233">
+        <v>132.66</v>
+      </c>
+      <c r="G233">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B234" t="s">
+        <v>17</v>
+      </c>
+      <c r="C234" t="s">
+        <v>119</v>
+      </c>
+      <c r="D234" t="s">
+        <v>18</v>
+      </c>
+      <c r="E234">
+        <v>16.61</v>
+      </c>
+      <c r="F234">
+        <v>199.33</v>
+      </c>
+      <c r="G234">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B235" t="s">
+        <v>17</v>
+      </c>
+      <c r="C235" t="s">
+        <v>112</v>
+      </c>
+      <c r="D235" t="s">
+        <v>18</v>
+      </c>
+      <c r="E235">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="F235">
+        <v>59.33</v>
+      </c>
+      <c r="G235">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B236" t="s">
+        <v>17</v>
+      </c>
+      <c r="C236" t="s">
+        <v>113</v>
+      </c>
+      <c r="D236" t="s">
+        <v>18</v>
+      </c>
+      <c r="E236">
+        <v>7.16</v>
+      </c>
+      <c r="F236">
+        <v>85.92</v>
+      </c>
+      <c r="G236">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" t="s">
+        <v>114</v>
+      </c>
+      <c r="D237" t="s">
+        <v>18</v>
+      </c>
+      <c r="E237">
+        <v>14.38</v>
+      </c>
+      <c r="F237">
+        <v>172.56</v>
+      </c>
+      <c r="G237">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B238" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238" t="s">
+        <v>121</v>
+      </c>
+      <c r="D238" t="s">
+        <v>18</v>
+      </c>
+      <c r="E238">
+        <v>5.5</v>
+      </c>
+      <c r="F238">
+        <v>66</v>
+      </c>
+      <c r="G238">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B239" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239" t="s">
+        <v>122</v>
+      </c>
+      <c r="D239" t="s">
+        <v>18</v>
+      </c>
+      <c r="E239">
+        <v>11.06</v>
+      </c>
+      <c r="F239">
+        <v>132.66</v>
+      </c>
+      <c r="G239">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B240" t="s">
+        <v>17</v>
+      </c>
+      <c r="C240" t="s">
+        <v>115</v>
+      </c>
+      <c r="D240" t="s">
+        <v>18</v>
+      </c>
+      <c r="E240">
+        <v>8.83</v>
+      </c>
+      <c r="F240">
+        <v>105.99</v>
+      </c>
+      <c r="G240">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B241" t="s">
+        <v>17</v>
+      </c>
+      <c r="C241" t="s">
+        <v>110</v>
+      </c>
+      <c r="D241" t="s">
+        <v>18</v>
+      </c>
+      <c r="E241">
+        <v>6.61</v>
+      </c>
+      <c r="F241">
+        <v>79.33</v>
+      </c>
+      <c r="G241">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B242" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242" t="s">
+        <v>111</v>
+      </c>
+      <c r="D242" t="s">
+        <v>18</v>
+      </c>
+      <c r="E242">
+        <v>11.06</v>
+      </c>
+      <c r="F242">
+        <v>132.66</v>
+      </c>
+      <c r="G242">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B243" t="s">
+        <v>167</v>
+      </c>
+      <c r="C243" t="s">
+        <v>171</v>
+      </c>
+      <c r="D243" t="s">
+        <v>188</v>
+      </c>
+      <c r="E243">
+        <v>26.64</v>
+      </c>
+      <c r="F243">
+        <v>213.12</v>
+      </c>
+      <c r="G243">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B244" t="s">
+        <v>167</v>
+      </c>
+      <c r="C244" t="s">
+        <v>176</v>
+      </c>
+      <c r="D244" t="s">
+        <v>188</v>
+      </c>
+      <c r="E244">
+        <v>25.58</v>
+      </c>
+      <c r="F244">
+        <v>306.95999999999998</v>
+      </c>
+      <c r="G244">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B245" t="s">
+        <v>167</v>
+      </c>
+      <c r="C245" t="s">
+        <v>172</v>
+      </c>
+      <c r="D245" t="s">
+        <v>188</v>
+      </c>
+      <c r="E245">
+        <v>29.8</v>
+      </c>
+      <c r="F245">
+        <v>238.4</v>
+      </c>
+      <c r="G245">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B246" t="s">
+        <v>167</v>
+      </c>
+      <c r="C246" t="s">
+        <v>173</v>
+      </c>
+      <c r="D246" t="s">
+        <v>188</v>
+      </c>
+      <c r="E246">
+        <v>12.99</v>
+      </c>
+      <c r="F246">
+        <v>155.88</v>
+      </c>
+      <c r="G246">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B247" t="s">
+        <v>167</v>
+      </c>
+      <c r="C247" t="s">
+        <v>174</v>
+      </c>
+      <c r="D247" t="s">
+        <v>188</v>
+      </c>
+      <c r="E247">
+        <v>12.99</v>
+      </c>
+      <c r="F247">
+        <v>155.88</v>
+      </c>
+      <c r="G247">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B248" t="s">
+        <v>167</v>
+      </c>
+      <c r="C248" t="s">
+        <v>175</v>
+      </c>
+      <c r="D248" t="s">
+        <v>188</v>
+      </c>
+      <c r="E248">
+        <v>12.99</v>
+      </c>
+      <c r="F248">
+        <v>155.88</v>
+      </c>
+      <c r="G248">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B249" t="s">
+        <v>167</v>
+      </c>
+      <c r="C249" t="s">
+        <v>186</v>
+      </c>
+      <c r="D249" t="s">
+        <v>188</v>
+      </c>
+      <c r="E249">
+        <v>13.68</v>
+      </c>
+      <c r="F249">
+        <v>164.16</v>
+      </c>
+      <c r="G249">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B250" t="s">
+        <v>167</v>
+      </c>
+      <c r="C250" t="s">
+        <v>187</v>
+      </c>
+      <c r="D250" t="s">
+        <v>188</v>
+      </c>
+      <c r="E250">
+        <v>15.13</v>
+      </c>
+      <c r="F250">
+        <v>181.56</v>
+      </c>
+      <c r="G250">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B251" t="s">
+        <v>167</v>
+      </c>
+      <c r="C251" t="s">
+        <v>323</v>
+      </c>
+      <c r="D251" t="s">
+        <v>188</v>
+      </c>
+      <c r="E251">
+        <v>38.15</v>
+      </c>
+      <c r="F251">
+        <v>228.9</v>
+      </c>
+      <c r="G251">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B252" t="s">
+        <v>167</v>
+      </c>
+      <c r="C252" t="s">
+        <v>184</v>
+      </c>
+      <c r="D252" t="s">
+        <v>188</v>
+      </c>
+      <c r="E252">
+        <v>6.94</v>
+      </c>
+      <c r="F252">
+        <v>173.5</v>
+      </c>
+      <c r="G252">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B253" t="s">
+        <v>167</v>
+      </c>
+      <c r="C253" t="s">
+        <v>185</v>
+      </c>
+      <c r="D253" t="s">
+        <v>188</v>
+      </c>
+      <c r="E253">
+        <v>35.76</v>
+      </c>
+      <c r="F253">
+        <v>214.56</v>
+      </c>
+      <c r="G253">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B254" t="s">
+        <v>167</v>
+      </c>
+      <c r="C254" t="s">
+        <v>177</v>
+      </c>
+      <c r="D254" t="s">
+        <v>188</v>
+      </c>
+      <c r="E254">
+        <v>23.85</v>
+      </c>
+      <c r="F254">
+        <v>95.4</v>
+      </c>
+      <c r="G254">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B255" t="s">
+        <v>167</v>
+      </c>
+      <c r="C255" t="s">
+        <v>178</v>
+      </c>
+      <c r="D255" t="s">
+        <v>188</v>
+      </c>
+      <c r="E255">
+        <v>3.82</v>
+      </c>
+      <c r="F255">
+        <v>61.12</v>
+      </c>
+      <c r="G255">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B256" t="s">
+        <v>167</v>
+      </c>
+      <c r="C256" t="s">
+        <v>179</v>
+      </c>
+      <c r="D256" t="s">
+        <v>188</v>
+      </c>
+      <c r="E256">
+        <v>3.82</v>
+      </c>
+      <c r="F256">
+        <v>61.12</v>
+      </c>
+      <c r="G256">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B257" t="s">
+        <v>167</v>
+      </c>
+      <c r="C257" t="s">
+        <v>180</v>
+      </c>
+      <c r="D257" t="s">
+        <v>188</v>
+      </c>
+      <c r="E257">
+        <v>3.82</v>
+      </c>
+      <c r="F257">
+        <v>61.12</v>
+      </c>
+      <c r="G257">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B258" t="s">
+        <v>167</v>
+      </c>
+      <c r="C258" t="s">
+        <v>180</v>
+      </c>
+      <c r="D258" t="s">
+        <v>188</v>
+      </c>
+      <c r="E258">
+        <v>16.61</v>
+      </c>
+      <c r="F258">
+        <v>265.76</v>
+      </c>
+      <c r="G258">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B259" t="s">
+        <v>167</v>
+      </c>
+      <c r="C259" t="s">
+        <v>181</v>
+      </c>
+      <c r="D259" t="s">
+        <v>188</v>
+      </c>
+      <c r="E259">
+        <v>25.68</v>
+      </c>
+      <c r="F259">
+        <v>154.08000000000001</v>
+      </c>
+      <c r="G259">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B260" t="s">
+        <v>167</v>
+      </c>
+      <c r="C260" t="s">
+        <v>182</v>
+      </c>
+      <c r="D260" t="s">
+        <v>188</v>
+      </c>
+      <c r="E260">
+        <v>25.68</v>
+      </c>
+      <c r="F260">
+        <v>154.08000000000001</v>
+      </c>
+      <c r="G260">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B261" t="s">
+        <v>167</v>
+      </c>
+      <c r="C261" t="s">
+        <v>183</v>
+      </c>
+      <c r="D261" t="s">
+        <v>188</v>
+      </c>
+      <c r="E261">
+        <v>25.68</v>
+      </c>
+      <c r="F261">
+        <v>154.08000000000001</v>
+      </c>
+      <c r="G261">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{1D08511B-311B-490C-99A0-C15D4C5423C8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G261">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
   <dimension ref="A1:D257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529BF322-9168-497F-A600-4AB6788B0CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C794DAF-8E1A-4F48-85EA-47984EFD27A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
   <sheets>
     <sheet name="base_de_produtos" sheetId="1" r:id="rId1"/>
@@ -6577,7 +6577,7 @@
         <v>5.99</v>
       </c>
       <c r="G193">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -6600,7 +6600,7 @@
         <v>5.99</v>
       </c>
       <c r="G194">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -6623,7 +6623,7 @@
         <v>5.99</v>
       </c>
       <c r="G195">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -6646,7 +6646,7 @@
         <v>5.99</v>
       </c>
       <c r="G196">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -6669,7 +6669,7 @@
         <v>5.99</v>
       </c>
       <c r="G197">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -6692,7 +6692,7 @@
         <v>5.99</v>
       </c>
       <c r="G198">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -6715,7 +6715,7 @@
         <v>5.99</v>
       </c>
       <c r="G199">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -6738,7 +6738,7 @@
         <v>5.99</v>
       </c>
       <c r="G200">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -6761,7 +6761,7 @@
         <v>1.99</v>
       </c>
       <c r="G201">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -6784,7 +6784,7 @@
         <v>1.99</v>
       </c>
       <c r="G202">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C794DAF-8E1A-4F48-85EA-47984EFD27A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E2483D-3E4A-47B8-89AF-48BABA541CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -8226,7 +8226,7 @@
         <v>185</v>
       </c>
       <c r="E258" s="3">
-        <v>73</v>
+        <v>2.44</v>
       </c>
       <c r="F258" s="3">
         <v>73</v>
@@ -8235,7 +8235,7 @@
         <v>30</v>
       </c>
       <c r="I258">
-        <f t="shared" si="1"/>
+        <f>F258/G258</f>
         <v>2.4333333333333331</v>
       </c>
     </row>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E2483D-3E4A-47B8-89AF-48BABA541CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFAB3F1-D834-474C-99A1-40A6F884740C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="400">
   <si>
     <t>categoria</t>
   </si>
@@ -1213,6 +1213,18 @@
   </si>
   <si>
     <t>cod do produto</t>
+  </si>
+  <si>
+    <t>B0000001</t>
+  </si>
+  <si>
+    <t>BEB</t>
+  </si>
+  <si>
+    <t>Beb Licor 1985</t>
+  </si>
+  <si>
+    <t>CV7</t>
   </si>
 </sst>
 </file>
@@ -2131,7 +2143,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I260"/>
+  <dimension ref="A1:I261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -6755,13 +6767,13 @@
         <v>135</v>
       </c>
       <c r="E201">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="F201">
-        <v>1.99</v>
+        <v>84</v>
       </c>
       <c r="G201">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -6778,13 +6790,13 @@
         <v>135</v>
       </c>
       <c r="E202">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="F202">
-        <v>1.99</v>
+        <v>84</v>
       </c>
       <c r="G202">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -7344,7 +7356,7 @@
         <v>20</v>
       </c>
       <c r="I225">
-        <f t="shared" ref="I225:I260" si="1">F225/G225</f>
+        <f t="shared" ref="I225:I261" si="1">F225/G225</f>
         <v>4.75</v>
       </c>
     </row>
@@ -8291,6 +8303,33 @@
       <c r="I260">
         <f t="shared" si="1"/>
         <v>2.5666666666666669</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B261" t="s">
+        <v>397</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D261" t="s">
+        <v>399</v>
+      </c>
+      <c r="E261" s="3">
+        <v>40</v>
+      </c>
+      <c r="F261" s="3">
+        <v>50</v>
+      </c>
+      <c r="G261" s="4">
+        <v>6</v>
+      </c>
+      <c r="I261">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333339</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFAB3F1-D834-474C-99A1-40A6F884740C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BE42B6-2C5E-40DC-A753-7DF51145703B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="398">
   <si>
     <t>categoria</t>
   </si>
@@ -1185,15 +1185,6 @@
     <t>Doce WK Alfajor 60G 20 Unid</t>
   </si>
   <si>
-    <t>Este vende um pote só ou tem que ser 8</t>
-  </si>
-  <si>
-    <t>Este vende um pote só ou tem que ser 12</t>
-  </si>
-  <si>
-    <t>Este vende um pote só ou tem que ser 4</t>
-  </si>
-  <si>
     <t>Este vende um display só ou teque ser 6</t>
   </si>
   <si>
@@ -1225,6 +1216,9 @@
   </si>
   <si>
     <t>CV7</t>
+  </si>
+  <si>
+    <t>DOC Gui Paçoquinha Rolha Pote com 32 Unid de 16g</t>
   </si>
 </sst>
 </file>
@@ -6876,13 +6870,13 @@
         <v>167</v>
       </c>
       <c r="C206" t="s">
-        <v>171</v>
+        <v>397</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
       </c>
       <c r="E206">
-        <v>26.64</v>
+        <v>0.84</v>
       </c>
       <c r="F206">
         <v>26.64</v>
@@ -6890,8 +6884,9 @@
       <c r="G206">
         <v>32</v>
       </c>
-      <c r="I206" t="s">
-        <v>386</v>
+      <c r="I206">
+        <f>26.64/32</f>
+        <v>0.83250000000000002</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -6908,7 +6903,7 @@
         <v>184</v>
       </c>
       <c r="E207">
-        <v>29.8</v>
+        <v>0.93</v>
       </c>
       <c r="F207">
         <v>29.8</v>
@@ -6916,8 +6911,9 @@
       <c r="G207">
         <v>32</v>
       </c>
-      <c r="I207" t="s">
-        <v>386</v>
+      <c r="I207">
+        <f>29.8/32</f>
+        <v>0.93125000000000002</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -6942,9 +6938,6 @@
       <c r="G208">
         <v>1</v>
       </c>
-      <c r="I208" t="s">
-        <v>387</v>
-      </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
@@ -6968,9 +6961,6 @@
       <c r="G209">
         <v>1</v>
       </c>
-      <c r="I209" t="s">
-        <v>387</v>
-      </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
@@ -6994,9 +6984,6 @@
       <c r="G210">
         <v>1</v>
       </c>
-      <c r="I210" t="s">
-        <v>387</v>
-      </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
@@ -7020,9 +7007,6 @@
       <c r="G211">
         <v>63</v>
       </c>
-      <c r="I211" t="s">
-        <v>387</v>
-      </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
@@ -7046,9 +7030,6 @@
       <c r="G212">
         <v>56</v>
       </c>
-      <c r="I212" t="s">
-        <v>388</v>
-      </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
@@ -7127,7 +7108,7 @@
         <v>167</v>
       </c>
       <c r="C216" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
@@ -7142,7 +7123,7 @@
         <v>42</v>
       </c>
       <c r="I216" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -7153,7 +7134,7 @@
         <v>167</v>
       </c>
       <c r="C217" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
@@ -7176,7 +7157,7 @@
         <v>167</v>
       </c>
       <c r="C218" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
@@ -7199,7 +7180,7 @@
         <v>167</v>
       </c>
       <c r="C219" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
@@ -7245,7 +7226,7 @@
         <v>167</v>
       </c>
       <c r="C221" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
@@ -8307,19 +8288,19 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B261" t="s">
+        <v>394</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D261" t="s">
         <v>396</v>
       </c>
-      <c r="B261" t="s">
-        <v>397</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D261" t="s">
-        <v>399</v>
-      </c>
       <c r="E261" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F261" s="3">
         <v>50</v>
@@ -8356,7 +8337,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -14113,7 +14094,7 @@
         <v>167</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>184</v>
@@ -14159,7 +14140,7 @@
         <v>167</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>184</v>
@@ -14274,7 +14255,7 @@
         <v>167</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D258" s="8" t="s">
         <v>184</v>
@@ -14297,7 +14278,7 @@
         <v>167</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>184</v>
@@ -14320,7 +14301,7 @@
         <v>167</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>184</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BE42B6-2C5E-40DC-A753-7DF51145703B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3337DE-FF8E-461E-BA70-A8615FA67388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="397">
   <si>
     <t>categoria</t>
   </si>
@@ -1183,9 +1183,6 @@
   </si>
   <si>
     <t>Doce WK Alfajor 60G 20 Unid</t>
-  </si>
-  <si>
-    <t>Este vende um display só ou teque ser 6</t>
   </si>
   <si>
     <t>DOC Gui Paçoquinha Negresco Display 546g Uni 13g 42 Uni</t>
@@ -2143,7 +2140,8 @@
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="68" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2159,7 +2157,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -2182,7 +2180,7 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>15.8</v>
       </c>
       <c r="F2">
@@ -2205,7 +2203,7 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>15.8</v>
       </c>
       <c r="F3">
@@ -2228,7 +2226,7 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>15.8</v>
       </c>
       <c r="F4">
@@ -2251,7 +2249,7 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>15.8</v>
       </c>
       <c r="F5">
@@ -2274,7 +2272,7 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>15.8</v>
       </c>
       <c r="F6">
@@ -2297,7 +2295,7 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>15.8</v>
       </c>
       <c r="F7">
@@ -2320,7 +2318,7 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>15.8</v>
       </c>
       <c r="F8">
@@ -2343,7 +2341,7 @@
       <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>15.8</v>
       </c>
       <c r="F9">
@@ -2366,7 +2364,7 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>15.8</v>
       </c>
       <c r="F10">
@@ -2389,7 +2387,7 @@
       <c r="D11" t="s">
         <v>18</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>8.6</v>
       </c>
       <c r="F11">
@@ -2412,7 +2410,7 @@
       <c r="D12" t="s">
         <v>18</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="4">
         <v>8.6</v>
       </c>
       <c r="F12">
@@ -2435,7 +2433,7 @@
       <c r="D13" t="s">
         <v>18</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>9.27</v>
       </c>
       <c r="F13">
@@ -2458,7 +2456,7 @@
       <c r="D14" t="s">
         <v>18</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>17.260000000000002</v>
       </c>
       <c r="F14">
@@ -2481,7 +2479,7 @@
       <c r="D15" t="s">
         <v>18</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>17.260000000000002</v>
       </c>
       <c r="F15">
@@ -2504,7 +2502,7 @@
       <c r="D16" t="s">
         <v>18</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>31.65</v>
       </c>
       <c r="F16">
@@ -2527,7 +2525,7 @@
       <c r="D17" t="s">
         <v>18</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>31.65</v>
       </c>
       <c r="F17">
@@ -2550,7 +2548,7 @@
       <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>50.74</v>
       </c>
       <c r="F18">
@@ -2573,7 +2571,7 @@
       <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>50.74</v>
       </c>
       <c r="F19">
@@ -2596,7 +2594,7 @@
       <c r="D20" t="s">
         <v>18</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="4">
         <v>10.6</v>
       </c>
       <c r="F20">
@@ -2619,7 +2617,7 @@
       <c r="D21" t="s">
         <v>18</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="4">
         <v>10.6</v>
       </c>
       <c r="F21">
@@ -2642,7 +2640,7 @@
       <c r="D22" t="s">
         <v>18</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="4">
         <v>10.6</v>
       </c>
       <c r="F22">
@@ -2665,7 +2663,7 @@
       <c r="D23" t="s">
         <v>18</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>7.94</v>
       </c>
       <c r="F23">
@@ -2688,7 +2686,7 @@
       <c r="D24" t="s">
         <v>18</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>7.94</v>
       </c>
       <c r="F24">
@@ -2711,7 +2709,7 @@
       <c r="D25" t="s">
         <v>18</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="4">
         <v>8.6</v>
       </c>
       <c r="F25">
@@ -2734,7 +2732,7 @@
       <c r="D26" t="s">
         <v>18</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="4">
         <v>15.26</v>
       </c>
       <c r="F26">
@@ -2757,7 +2755,7 @@
       <c r="D27" t="s">
         <v>18</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="4">
         <v>15.26</v>
       </c>
       <c r="F27">
@@ -2780,7 +2778,7 @@
       <c r="D28" t="s">
         <v>18</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="4">
         <v>17.260000000000002</v>
       </c>
       <c r="F28">
@@ -2803,7 +2801,7 @@
       <c r="D29" t="s">
         <v>18</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="4">
         <v>27.5</v>
       </c>
       <c r="F29">
@@ -2826,7 +2824,7 @@
       <c r="D30" t="s">
         <v>18</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="4">
         <v>27.5</v>
       </c>
       <c r="F30">
@@ -2849,7 +2847,7 @@
       <c r="D31" t="s">
         <v>18</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="4">
         <v>34.4</v>
       </c>
       <c r="F31">
@@ -2872,7 +2870,7 @@
       <c r="D32" t="s">
         <v>18</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="4">
         <v>43.48</v>
       </c>
       <c r="F32">
@@ -2895,7 +2893,7 @@
       <c r="D33" t="s">
         <v>18</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="4">
         <v>43.48</v>
       </c>
       <c r="F33">
@@ -2918,7 +2916,7 @@
       <c r="D34" t="s">
         <v>18</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="4">
         <v>59.98</v>
       </c>
       <c r="F34">
@@ -2941,7 +2939,7 @@
       <c r="D35" t="s">
         <v>18</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="4">
         <v>59.98</v>
       </c>
       <c r="F35">
@@ -2964,7 +2962,7 @@
       <c r="D36" t="s">
         <v>18</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="4">
         <v>7.94</v>
       </c>
       <c r="F36">
@@ -2987,7 +2985,7 @@
       <c r="D37" t="s">
         <v>18</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="4">
         <v>7.94</v>
       </c>
       <c r="F37">
@@ -3010,7 +3008,7 @@
       <c r="D38" t="s">
         <v>18</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="4">
         <v>7.94</v>
       </c>
       <c r="F38">
@@ -3033,7 +3031,7 @@
       <c r="D39" t="s">
         <v>18</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="4">
         <v>7.94</v>
       </c>
       <c r="F39">
@@ -3056,7 +3054,7 @@
       <c r="D40" t="s">
         <v>18</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="4">
         <v>17.260000000000002</v>
       </c>
       <c r="F40">
@@ -3079,7 +3077,7 @@
       <c r="D41" t="s">
         <v>18</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="4">
         <v>17.260000000000002</v>
       </c>
       <c r="F41">
@@ -3102,7 +3100,7 @@
       <c r="D42" t="s">
         <v>18</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="4">
         <v>65.25</v>
       </c>
       <c r="F42">
@@ -3125,7 +3123,7 @@
       <c r="D43" t="s">
         <v>18</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>65.25</v>
       </c>
       <c r="F43">
@@ -3148,7 +3146,7 @@
       <c r="D44" t="s">
         <v>18</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="4">
         <v>19.899999999999999</v>
       </c>
       <c r="F44">
@@ -3171,7 +3169,7 @@
       <c r="D45" t="s">
         <v>18</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="4">
         <v>23.93</v>
       </c>
       <c r="F45">
@@ -3194,7 +3192,7 @@
       <c r="D46" t="s">
         <v>18</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="4">
         <v>37.5</v>
       </c>
       <c r="F46">
@@ -3217,7 +3215,7 @@
       <c r="D47" t="s">
         <v>18</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="4">
         <v>52.55</v>
       </c>
       <c r="F47">
@@ -3240,7 +3238,7 @@
       <c r="D48" t="s">
         <v>18</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="4">
         <v>63</v>
       </c>
       <c r="F48">
@@ -3263,7 +3261,7 @@
       <c r="D49" t="s">
         <v>18</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="4">
         <v>2.4500000000000002</v>
       </c>
       <c r="F49">
@@ -3286,7 +3284,7 @@
       <c r="D50" t="s">
         <v>18</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="4">
         <v>2.4500000000000002</v>
       </c>
       <c r="F50">
@@ -3309,7 +3307,7 @@
       <c r="D51" t="s">
         <v>18</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="4">
         <v>1.62</v>
       </c>
       <c r="F51">
@@ -3332,7 +3330,7 @@
       <c r="D52" t="s">
         <v>18</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="4">
         <v>1.62</v>
       </c>
       <c r="F52">
@@ -3355,7 +3353,7 @@
       <c r="D53" t="s">
         <v>18</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="4">
         <v>1.62</v>
       </c>
       <c r="F53">
@@ -3378,7 +3376,7 @@
       <c r="D54" t="s">
         <v>18</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="4">
         <v>1.62</v>
       </c>
       <c r="F54">
@@ -3401,7 +3399,7 @@
       <c r="D55" t="s">
         <v>18</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="4">
         <v>6.81</v>
       </c>
       <c r="F55">
@@ -3424,7 +3422,7 @@
       <c r="D56" t="s">
         <v>18</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="4">
         <v>6.81</v>
       </c>
       <c r="F56">
@@ -3447,7 +3445,7 @@
       <c r="D57" t="s">
         <v>18</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="4">
         <v>13.26</v>
       </c>
       <c r="F57">
@@ -3470,7 +3468,7 @@
       <c r="D58" t="s">
         <v>18</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="4">
         <v>13.26</v>
       </c>
       <c r="F58">
@@ -3493,7 +3491,7 @@
       <c r="D59" t="s">
         <v>18</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="4">
         <v>3.69</v>
       </c>
       <c r="F59">
@@ -3516,7 +3514,7 @@
       <c r="D60" t="s">
         <v>18</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="4">
         <v>3.69</v>
       </c>
       <c r="F60">
@@ -3539,7 +3537,7 @@
       <c r="D61" t="s">
         <v>18</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="4">
         <v>2.29</v>
       </c>
       <c r="F61">
@@ -3562,7 +3560,7 @@
       <c r="D62" t="s">
         <v>18</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="4">
         <v>2.29</v>
       </c>
       <c r="F62">
@@ -3585,7 +3583,7 @@
       <c r="D63" t="s">
         <v>18</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="4">
         <v>2.29</v>
       </c>
       <c r="F63">
@@ -3608,7 +3606,7 @@
       <c r="D64" t="s">
         <v>18</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="4">
         <v>4.0599999999999996</v>
       </c>
       <c r="F64">
@@ -3631,7 +3629,7 @@
       <c r="D65" t="s">
         <v>18</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="4">
         <v>4.0599999999999996</v>
       </c>
       <c r="F65">
@@ -3654,7 +3652,7 @@
       <c r="D66" t="s">
         <v>18</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="4">
         <v>4.0599999999999996</v>
       </c>
       <c r="F66">
@@ -3677,7 +3675,7 @@
       <c r="D67" t="s">
         <v>18</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="4">
         <v>9.35</v>
       </c>
       <c r="F67">
@@ -3700,7 +3698,7 @@
       <c r="D68" t="s">
         <v>18</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="4">
         <v>4.6500000000000004</v>
       </c>
       <c r="F68">
@@ -3723,7 +3721,7 @@
       <c r="D69" t="s">
         <v>18</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="4">
         <v>4.6500000000000004</v>
       </c>
       <c r="F69">
@@ -3746,7 +3744,7 @@
       <c r="D70" t="s">
         <v>18</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="4">
         <v>4.6500000000000004</v>
       </c>
       <c r="F70">
@@ -3769,7 +3767,7 @@
       <c r="D71" t="s">
         <v>18</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="4">
         <v>5.82</v>
       </c>
       <c r="F71">
@@ -3792,7 +3790,7 @@
       <c r="D72" t="s">
         <v>18</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="4">
         <v>7.58</v>
       </c>
       <c r="F72">
@@ -3815,7 +3813,7 @@
       <c r="D73" t="s">
         <v>18</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="4">
         <v>9.35</v>
       </c>
       <c r="F73">
@@ -3838,7 +3836,7 @@
       <c r="D74" t="s">
         <v>18</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="4">
         <v>9.93</v>
       </c>
       <c r="F74">
@@ -3861,7 +3859,7 @@
       <c r="D75" t="s">
         <v>18</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="4">
         <v>39.9</v>
       </c>
       <c r="F75">
@@ -3884,7 +3882,7 @@
       <c r="D76" t="s">
         <v>18</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="4">
         <v>4.3600000000000003</v>
       </c>
       <c r="F76">
@@ -3907,7 +3905,7 @@
       <c r="D77" t="s">
         <v>18</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="4">
         <v>4.99</v>
       </c>
       <c r="F77">
@@ -3930,7 +3928,7 @@
       <c r="D78" t="s">
         <v>18</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="4">
         <v>9.35</v>
       </c>
       <c r="F78">
@@ -3953,7 +3951,7 @@
       <c r="D79" t="s">
         <v>18</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="4">
         <v>9.35</v>
       </c>
       <c r="F79">
@@ -3976,7 +3974,7 @@
       <c r="D80" t="s">
         <v>18</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="4">
         <v>9.35</v>
       </c>
       <c r="F80">
@@ -3999,7 +3997,7 @@
       <c r="D81" t="s">
         <v>18</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="4">
         <v>9.35</v>
       </c>
       <c r="F81">
@@ -4022,7 +4020,7 @@
       <c r="D82" t="s">
         <v>18</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="4">
         <v>9.35</v>
       </c>
       <c r="F82">
@@ -4045,7 +4043,7 @@
       <c r="D83" t="s">
         <v>18</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="4">
         <v>9.35</v>
       </c>
       <c r="F83">
@@ -4068,7 +4066,7 @@
       <c r="D84" t="s">
         <v>18</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="4">
         <v>9.35</v>
       </c>
       <c r="F84">
@@ -4091,7 +4089,7 @@
       <c r="D85" t="s">
         <v>18</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="4">
         <v>11.71</v>
       </c>
       <c r="F85">
@@ -4114,7 +4112,7 @@
       <c r="D86" t="s">
         <v>18</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="4">
         <v>5.5</v>
       </c>
       <c r="F86">
@@ -4137,7 +4135,7 @@
       <c r="D87" t="s">
         <v>18</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="4">
         <v>5.5</v>
       </c>
       <c r="F87">
@@ -4160,7 +4158,7 @@
       <c r="D88" t="s">
         <v>18</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="4">
         <v>2.17</v>
       </c>
       <c r="F88">
@@ -4183,7 +4181,7 @@
       <c r="D89" t="s">
         <v>18</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="4">
         <v>11.05</v>
       </c>
       <c r="F89">
@@ -4206,7 +4204,7 @@
       <c r="D90" t="s">
         <v>18</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="4">
         <v>7.72</v>
       </c>
       <c r="F90">
@@ -4229,7 +4227,7 @@
       <c r="D91" t="s">
         <v>18</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="4">
         <v>5.5</v>
       </c>
       <c r="F91">
@@ -4252,7 +4250,7 @@
       <c r="D92" t="s">
         <v>18</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="4">
         <v>7.72</v>
       </c>
       <c r="F92">
@@ -4275,7 +4273,7 @@
       <c r="D93" t="s">
         <v>18</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="4">
         <v>8.83</v>
       </c>
       <c r="F93">
@@ -4298,7 +4296,7 @@
       <c r="D94" t="s">
         <v>18</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="4">
         <v>10.5</v>
       </c>
       <c r="F94">
@@ -4321,7 +4319,7 @@
       <c r="D95" t="s">
         <v>18</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="4">
         <v>11.06</v>
       </c>
       <c r="F95">
@@ -4344,7 +4342,7 @@
       <c r="D96" t="s">
         <v>18</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="4">
         <v>6.61</v>
       </c>
       <c r="F96">
@@ -4367,7 +4365,7 @@
       <c r="D97" t="s">
         <v>18</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="4">
         <v>11.06</v>
       </c>
       <c r="F97">
@@ -4390,7 +4388,7 @@
       <c r="D98" t="s">
         <v>18</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="4">
         <v>4.9400000000000004</v>
       </c>
       <c r="F98">
@@ -4413,7 +4411,7 @@
       <c r="D99" t="s">
         <v>18</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="4">
         <v>7.16</v>
       </c>
       <c r="F99">
@@ -4436,7 +4434,7 @@
       <c r="D100" t="s">
         <v>18</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="4">
         <v>14.38</v>
       </c>
       <c r="F100">
@@ -4459,7 +4457,7 @@
       <c r="D101" t="s">
         <v>18</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="4">
         <v>8.83</v>
       </c>
       <c r="F101">
@@ -4482,7 +4480,7 @@
       <c r="D102" t="s">
         <v>18</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="4">
         <v>8.83</v>
       </c>
       <c r="F102">
@@ -4505,7 +4503,7 @@
       <c r="D103" t="s">
         <v>18</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="4">
         <v>8.83</v>
       </c>
       <c r="F103">
@@ -4528,7 +4526,7 @@
       <c r="D104" t="s">
         <v>18</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="4">
         <v>11.06</v>
       </c>
       <c r="F104">
@@ -4551,7 +4549,7 @@
       <c r="D105" t="s">
         <v>18</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="4">
         <v>16.61</v>
       </c>
       <c r="F105">
@@ -4574,7 +4572,7 @@
       <c r="D106" t="s">
         <v>18</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="4">
         <v>22.17</v>
       </c>
       <c r="F106">
@@ -4597,7 +4595,7 @@
       <c r="D107" t="s">
         <v>18</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="4">
         <v>5.5</v>
       </c>
       <c r="F107">
@@ -4620,7 +4618,7 @@
       <c r="D108" t="s">
         <v>18</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="4">
         <v>11.06</v>
       </c>
       <c r="F108">
@@ -4643,7 +4641,7 @@
       <c r="D109" t="s">
         <v>18</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="4">
         <v>11.05</v>
       </c>
       <c r="F109">
@@ -4666,7 +4664,7 @@
       <c r="D110" t="s">
         <v>18</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="4">
         <v>16.61</v>
       </c>
       <c r="F110">
@@ -4689,7 +4687,7 @@
       <c r="D111" t="s">
         <v>18</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="4">
         <v>15.5</v>
       </c>
       <c r="F111">
@@ -4712,7 +4710,7 @@
       <c r="D112" t="s">
         <v>18</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="4">
         <v>16.059999999999999</v>
       </c>
       <c r="F112">
@@ -4735,7 +4733,7 @@
       <c r="D113" t="s">
         <v>18</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="4">
         <v>11.06</v>
       </c>
       <c r="F113">
@@ -4758,7 +4756,7 @@
       <c r="D114" t="s">
         <v>18</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="4">
         <v>22.17</v>
       </c>
       <c r="F114">
@@ -4781,7 +4779,7 @@
       <c r="D115" t="s">
         <v>18</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="4">
         <v>16.059999999999999</v>
       </c>
       <c r="F115">
@@ -4804,7 +4802,7 @@
       <c r="D116" t="s">
         <v>18</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="4">
         <v>16.61</v>
       </c>
       <c r="F116">
@@ -4827,7 +4825,7 @@
       <c r="D117" t="s">
         <v>18</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="4">
         <v>9.64</v>
       </c>
       <c r="F117">
@@ -4850,7 +4848,7 @@
       <c r="D118" t="s">
         <v>18</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="4">
         <v>9.64</v>
       </c>
       <c r="F118">
@@ -4873,7 +4871,7 @@
       <c r="D119" t="s">
         <v>18</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="4">
         <v>11.02</v>
       </c>
       <c r="F119">
@@ -4896,7 +4894,7 @@
       <c r="D120" t="s">
         <v>18</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="4">
         <v>34.29</v>
       </c>
       <c r="F120">
@@ -4919,7 +4917,7 @@
       <c r="D121" t="s">
         <v>18</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="4">
         <v>34.29</v>
       </c>
       <c r="F121">
@@ -4942,7 +4940,7 @@
       <c r="D122" t="s">
         <v>18</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="4">
         <v>53.18</v>
       </c>
       <c r="F122">
@@ -4965,7 +4963,7 @@
       <c r="D123" t="s">
         <v>18</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="4">
         <v>53.18</v>
       </c>
       <c r="F123">
@@ -4988,7 +4986,7 @@
       <c r="D124" t="s">
         <v>18</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="4">
         <v>11.68</v>
       </c>
       <c r="F124">
@@ -5011,7 +5009,7 @@
       <c r="D125" t="s">
         <v>18</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="4">
         <v>11.68</v>
       </c>
       <c r="F125">
@@ -5034,7 +5032,7 @@
       <c r="D126" t="s">
         <v>18</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="4">
         <v>11.68</v>
       </c>
       <c r="F126">
@@ -5057,7 +5055,7 @@
       <c r="D127" t="s">
         <v>18</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="4">
         <v>8.9499999999999993</v>
       </c>
       <c r="F127">
@@ -5080,7 +5078,7 @@
       <c r="D128" t="s">
         <v>18</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="4">
         <v>8.9499999999999993</v>
       </c>
       <c r="F128">
@@ -5103,7 +5101,7 @@
       <c r="D129" t="s">
         <v>18</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="4">
         <v>9.64</v>
       </c>
       <c r="F129">
@@ -5126,7 +5124,7 @@
       <c r="D130" t="s">
         <v>18</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="4">
         <v>28.56</v>
       </c>
       <c r="F130">
@@ -5149,7 +5147,7 @@
       <c r="D131" t="s">
         <v>18</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="4">
         <v>28.56</v>
       </c>
       <c r="F131">
@@ -5172,7 +5170,7 @@
       <c r="D132" t="s">
         <v>18</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="4">
         <v>41.92</v>
       </c>
       <c r="F132">
@@ -5195,7 +5193,7 @@
       <c r="D133" t="s">
         <v>18</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="4">
         <v>48.92</v>
       </c>
       <c r="F133">
@@ -5218,7 +5216,7 @@
       <c r="D134" t="s">
         <v>18</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="4">
         <v>48.92</v>
       </c>
       <c r="F134">
@@ -5241,7 +5239,7 @@
       <c r="D135" t="s">
         <v>18</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="4">
         <v>62.92</v>
       </c>
       <c r="F135">
@@ -5264,7 +5262,7 @@
       <c r="D136" t="s">
         <v>18</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="4">
         <v>62.92</v>
       </c>
       <c r="F136">
@@ -5288,7 +5286,7 @@
       <c r="D137" t="s">
         <v>18</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="4">
         <v>10.33</v>
       </c>
       <c r="F137">
@@ -5311,7 +5309,7 @@
       <c r="D138" t="s">
         <v>18</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="4">
         <v>10.33</v>
       </c>
       <c r="F138">
@@ -5334,7 +5332,7 @@
       <c r="D139" t="s">
         <v>18</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="4">
         <v>10.33</v>
       </c>
       <c r="F139">
@@ -5357,7 +5355,7 @@
       <c r="D140" t="s">
         <v>18</v>
       </c>
-      <c r="E140">
+      <c r="E140" s="4">
         <v>10.33</v>
       </c>
       <c r="F140">
@@ -5380,7 +5378,7 @@
       <c r="D141" t="s">
         <v>18</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="4">
         <v>68.84</v>
       </c>
       <c r="F141">
@@ -5403,7 +5401,7 @@
       <c r="D142" t="s">
         <v>18</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="4">
         <v>68.84</v>
       </c>
       <c r="F142">
@@ -5426,7 +5424,7 @@
       <c r="D143" t="s">
         <v>18</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="4">
         <v>8.1999999999999993</v>
       </c>
       <c r="F143">
@@ -5449,7 +5447,7 @@
       <c r="D144" t="s">
         <v>18</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="4">
         <v>25.19</v>
       </c>
       <c r="F144">
@@ -5472,7 +5470,7 @@
       <c r="D145" t="s">
         <v>18</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="4">
         <v>27.92</v>
       </c>
       <c r="F145">
@@ -5495,7 +5493,7 @@
       <c r="D146" t="s">
         <v>18</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="4">
         <v>41.92</v>
       </c>
       <c r="F146">
@@ -5518,7 +5516,7 @@
       <c r="D147" t="s">
         <v>18</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="4">
         <v>55.92</v>
       </c>
       <c r="F147">
@@ -5541,7 +5539,7 @@
       <c r="D148" t="s">
         <v>18</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="4">
         <v>2.99</v>
       </c>
       <c r="F148">
@@ -5564,7 +5562,7 @@
       <c r="D149" t="s">
         <v>18</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="4">
         <v>2.99</v>
       </c>
       <c r="F149">
@@ -5587,7 +5585,7 @@
       <c r="D150" t="s">
         <v>18</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="4">
         <v>1.79</v>
       </c>
       <c r="F150">
@@ -5610,7 +5608,7 @@
       <c r="D151" t="s">
         <v>18</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="4">
         <v>1.79</v>
       </c>
       <c r="F151">
@@ -5633,7 +5631,7 @@
       <c r="D152" t="s">
         <v>18</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="4">
         <v>7.78</v>
       </c>
       <c r="F152">
@@ -5656,7 +5654,7 @@
       <c r="D153" t="s">
         <v>18</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="4">
         <v>7.78</v>
       </c>
       <c r="F153">
@@ -5679,7 +5677,7 @@
       <c r="D154" t="s">
         <v>18</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="4">
         <v>15.57</v>
       </c>
       <c r="F154">
@@ -5702,7 +5700,7 @@
       <c r="D155" t="s">
         <v>18</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="4">
         <v>5.39</v>
       </c>
       <c r="F155">
@@ -5725,7 +5723,7 @@
       <c r="D156" t="s">
         <v>18</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="4">
         <v>5.39</v>
       </c>
       <c r="F156">
@@ -5748,7 +5746,7 @@
       <c r="D157" t="s">
         <v>18</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="4">
         <v>11.38</v>
       </c>
       <c r="F157">
@@ -5771,7 +5769,7 @@
       <c r="D158" t="s">
         <v>18</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="4">
         <v>11.38</v>
       </c>
       <c r="F158">
@@ -5794,7 +5792,7 @@
       <c r="D159" t="s">
         <v>18</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="4">
         <v>2.99</v>
       </c>
       <c r="F159">
@@ -5817,7 +5815,7 @@
       <c r="D160" t="s">
         <v>18</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="4">
         <v>5.39</v>
       </c>
       <c r="F160">
@@ -5840,7 +5838,7 @@
       <c r="D161" t="s">
         <v>18</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="4">
         <v>5.39</v>
       </c>
       <c r="F161">
@@ -5863,7 +5861,7 @@
       <c r="D162" t="s">
         <v>18</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="4">
         <v>5.39</v>
       </c>
       <c r="F162">
@@ -5886,7 +5884,7 @@
       <c r="D163" t="s">
         <v>18</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="4">
         <v>5.39</v>
       </c>
       <c r="F163">
@@ -5909,7 +5907,7 @@
       <c r="D164" t="s">
         <v>18</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="4">
         <v>7.18</v>
       </c>
       <c r="F164">
@@ -5932,7 +5930,7 @@
       <c r="D165" t="s">
         <v>18</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="4">
         <v>8.3800000000000008</v>
       </c>
       <c r="F165">
@@ -5955,7 +5953,7 @@
       <c r="D166" t="s">
         <v>18</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="4">
         <v>11.92</v>
       </c>
       <c r="F166">
@@ -5978,7 +5976,7 @@
       <c r="D167" t="s">
         <v>18</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="4">
         <v>47.88</v>
       </c>
       <c r="F167">
@@ -6001,7 +5999,7 @@
       <c r="D168" t="s">
         <v>18</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="4">
         <v>5.93</v>
       </c>
       <c r="F168">
@@ -6024,7 +6022,7 @@
       <c r="D169" t="s">
         <v>18</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="4">
         <v>5.93</v>
       </c>
       <c r="F169">
@@ -6047,7 +6045,7 @@
       <c r="D170" t="s">
         <v>18</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="4">
         <v>9.58</v>
       </c>
       <c r="F170">
@@ -6070,7 +6068,7 @@
       <c r="D171" t="s">
         <v>18</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="4">
         <v>9.58</v>
       </c>
       <c r="F171">
@@ -6093,7 +6091,7 @@
       <c r="D172" t="s">
         <v>18</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="4">
         <v>10.78</v>
       </c>
       <c r="F172">
@@ -6116,7 +6114,7 @@
       <c r="D173" t="s">
         <v>18</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="4">
         <v>10.78</v>
       </c>
       <c r="F173">
@@ -6139,7 +6137,7 @@
       <c r="D174" t="s">
         <v>18</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="4">
         <v>10.78</v>
       </c>
       <c r="F174">
@@ -6162,7 +6160,7 @@
       <c r="D175" t="s">
         <v>18</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="4">
         <v>11.92</v>
       </c>
       <c r="F175">
@@ -6185,7 +6183,7 @@
       <c r="D176" t="s">
         <v>18</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="4">
         <v>7.18</v>
       </c>
       <c r="F176">
@@ -6208,7 +6206,7 @@
       <c r="D177" t="s">
         <v>18</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="4">
         <v>8.3800000000000008</v>
       </c>
       <c r="F177">
@@ -6231,7 +6229,7 @@
       <c r="D178" t="s">
         <v>18</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="4">
         <v>9.58</v>
       </c>
       <c r="F178">
@@ -6254,7 +6252,7 @@
       <c r="D179" t="s">
         <v>18</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="4">
         <v>11.92</v>
       </c>
       <c r="F179">
@@ -6277,7 +6275,7 @@
       <c r="D180" t="s">
         <v>18</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="4">
         <v>14.37</v>
       </c>
       <c r="F180">
@@ -6300,7 +6298,7 @@
       <c r="D181" t="s">
         <v>18</v>
       </c>
-      <c r="E181">
+      <c r="E181" s="4">
         <v>8.3800000000000008</v>
       </c>
       <c r="F181">
@@ -6323,7 +6321,7 @@
       <c r="D182" t="s">
         <v>18</v>
       </c>
-      <c r="E182">
+      <c r="E182" s="4">
         <v>7.18</v>
       </c>
       <c r="F182">
@@ -6346,7 +6344,7 @@
       <c r="D183" t="s">
         <v>18</v>
       </c>
-      <c r="E183">
+      <c r="E183" s="4">
         <v>9.58</v>
       </c>
       <c r="F183">
@@ -6369,7 +6367,7 @@
       <c r="D184" t="s">
         <v>18</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="4">
         <v>11.92</v>
       </c>
       <c r="F184">
@@ -6392,7 +6390,7 @@
       <c r="D185" t="s">
         <v>18</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="4">
         <v>11.92</v>
       </c>
       <c r="F185">
@@ -6415,7 +6413,7 @@
       <c r="D186" t="s">
         <v>18</v>
       </c>
-      <c r="E186">
+      <c r="E186" s="4">
         <v>8.3800000000000008</v>
       </c>
       <c r="F186">
@@ -6438,7 +6436,7 @@
       <c r="D187" t="s">
         <v>18</v>
       </c>
-      <c r="E187">
+      <c r="E187" s="4">
         <v>11.92</v>
       </c>
       <c r="F187">
@@ -6461,7 +6459,7 @@
       <c r="D188" t="s">
         <v>18</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="4">
         <v>21.57</v>
       </c>
       <c r="F188">
@@ -6484,7 +6482,7 @@
       <c r="D189" t="s">
         <v>18</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="4">
         <v>21.57</v>
       </c>
       <c r="F189">
@@ -6507,7 +6505,7 @@
       <c r="D190" t="s">
         <v>18</v>
       </c>
-      <c r="E190">
+      <c r="E190" s="4">
         <v>11.92</v>
       </c>
       <c r="F190">
@@ -6530,7 +6528,7 @@
       <c r="D191" t="s">
         <v>18</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="4">
         <v>21.57</v>
       </c>
       <c r="F191">
@@ -6553,7 +6551,7 @@
       <c r="D192" t="s">
         <v>18</v>
       </c>
-      <c r="E192">
+      <c r="E192" s="4">
         <v>23.91</v>
       </c>
       <c r="F192">
@@ -6576,7 +6574,7 @@
       <c r="D193" t="s">
         <v>135</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="4">
         <v>5.99</v>
       </c>
       <c r="F193">
@@ -6599,7 +6597,7 @@
       <c r="D194" t="s">
         <v>135</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="4">
         <v>5.99</v>
       </c>
       <c r="F194">
@@ -6622,7 +6620,7 @@
       <c r="D195" t="s">
         <v>135</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="4">
         <v>5.99</v>
       </c>
       <c r="F195">
@@ -6645,7 +6643,7 @@
       <c r="D196" t="s">
         <v>135</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="4">
         <v>5.99</v>
       </c>
       <c r="F196">
@@ -6668,7 +6666,7 @@
       <c r="D197" t="s">
         <v>135</v>
       </c>
-      <c r="E197">
+      <c r="E197" s="4">
         <v>5.99</v>
       </c>
       <c r="F197">
@@ -6691,7 +6689,7 @@
       <c r="D198" t="s">
         <v>135</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="4">
         <v>5.99</v>
       </c>
       <c r="F198">
@@ -6714,7 +6712,7 @@
       <c r="D199" t="s">
         <v>135</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="4">
         <v>5.99</v>
       </c>
       <c r="F199">
@@ -6737,7 +6735,7 @@
       <c r="D200" t="s">
         <v>135</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="4">
         <v>5.99</v>
       </c>
       <c r="F200">
@@ -6760,7 +6758,7 @@
       <c r="D201" t="s">
         <v>135</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="4">
         <v>3.5</v>
       </c>
       <c r="F201">
@@ -6783,7 +6781,7 @@
       <c r="D202" t="s">
         <v>135</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="4">
         <v>3.5</v>
       </c>
       <c r="F202">
@@ -6806,7 +6804,7 @@
       <c r="D203" t="s">
         <v>184</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="4">
         <v>6.94</v>
       </c>
       <c r="F203">
@@ -6829,7 +6827,7 @@
       <c r="D204" t="s">
         <v>184</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="4">
         <v>6.94</v>
       </c>
       <c r="F204">
@@ -6852,7 +6850,7 @@
       <c r="D205" t="s">
         <v>184</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="4">
         <v>3.96</v>
       </c>
       <c r="F205">
@@ -6870,12 +6868,12 @@
         <v>167</v>
       </c>
       <c r="C206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D206" t="s">
         <v>184</v>
       </c>
-      <c r="E206">
+      <c r="E206" s="4">
         <v>0.84</v>
       </c>
       <c r="F206">
@@ -6902,7 +6900,7 @@
       <c r="D207" t="s">
         <v>184</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="4">
         <v>0.93</v>
       </c>
       <c r="F207">
@@ -6929,7 +6927,7 @@
       <c r="D208" t="s">
         <v>184</v>
       </c>
-      <c r="E208">
+      <c r="E208" s="4">
         <v>12.99</v>
       </c>
       <c r="F208">
@@ -6952,7 +6950,7 @@
       <c r="D209" t="s">
         <v>184</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="4">
         <v>12.99</v>
       </c>
       <c r="F209">
@@ -6975,7 +6973,7 @@
       <c r="D210" t="s">
         <v>184</v>
       </c>
-      <c r="E210">
+      <c r="E210" s="4">
         <v>12.99</v>
       </c>
       <c r="F210">
@@ -6998,14 +6996,18 @@
       <c r="D211" t="s">
         <v>184</v>
       </c>
-      <c r="E211">
-        <v>25.58</v>
+      <c r="E211" s="4">
+        <v>0.41</v>
       </c>
       <c r="F211">
         <v>25.58</v>
       </c>
       <c r="G211">
         <v>63</v>
+      </c>
+      <c r="I211">
+        <f>F211/G211</f>
+        <v>0.40603174603174602</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -7021,14 +7023,18 @@
       <c r="D212" t="s">
         <v>184</v>
       </c>
-      <c r="E212">
-        <v>23.85</v>
+      <c r="E212" s="4">
+        <v>0.43</v>
       </c>
       <c r="F212">
         <v>23.85</v>
       </c>
       <c r="G212">
         <v>56</v>
+      </c>
+      <c r="I212">
+        <f>F212/G212</f>
+        <v>0.42589285714285718</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -7044,7 +7050,7 @@
       <c r="D213" t="s">
         <v>184</v>
       </c>
-      <c r="E213">
+      <c r="E213" s="4">
         <v>3.82</v>
       </c>
       <c r="F213">
@@ -7067,7 +7073,7 @@
       <c r="D214" t="s">
         <v>184</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="4">
         <v>3.82</v>
       </c>
       <c r="F214">
@@ -7090,7 +7096,7 @@
       <c r="D215" t="s">
         <v>184</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="4">
         <v>3.82</v>
       </c>
       <c r="F215">
@@ -7108,13 +7114,13 @@
         <v>167</v>
       </c>
       <c r="C216" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
       </c>
-      <c r="E216">
-        <v>25.68</v>
+      <c r="E216" s="4">
+        <v>0.61</v>
       </c>
       <c r="F216">
         <v>25.68</v>
@@ -7122,8 +7128,9 @@
       <c r="G216">
         <v>42</v>
       </c>
-      <c r="I216" t="s">
-        <v>386</v>
+      <c r="I216">
+        <f>F216/G216</f>
+        <v>0.61142857142857143</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -7134,19 +7141,23 @@
         <v>167</v>
       </c>
       <c r="C217" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
       </c>
-      <c r="E217">
-        <v>25.68</v>
+      <c r="E217" s="4">
+        <v>0.61</v>
       </c>
       <c r="F217">
         <v>25.68</v>
       </c>
       <c r="G217">
         <v>42</v>
+      </c>
+      <c r="I217">
+        <f t="shared" ref="I217:I219" si="1">F217/G217</f>
+        <v>0.61142857142857143</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -7157,19 +7168,23 @@
         <v>167</v>
       </c>
       <c r="C218" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
       </c>
-      <c r="E218">
-        <v>25.68</v>
+      <c r="E218" s="4">
+        <v>0.61</v>
       </c>
       <c r="F218">
         <v>25.68</v>
       </c>
       <c r="G218">
         <v>42</v>
+      </c>
+      <c r="I218">
+        <f t="shared" si="1"/>
+        <v>0.61142857142857143</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -7180,19 +7195,23 @@
         <v>167</v>
       </c>
       <c r="C219" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
       </c>
-      <c r="E219">
-        <v>38.15</v>
+      <c r="E219" s="4">
+        <v>1.58</v>
       </c>
       <c r="F219">
         <v>38.15</v>
       </c>
       <c r="G219">
         <v>24</v>
+      </c>
+      <c r="I219">
+        <f t="shared" si="1"/>
+        <v>1.5895833333333333</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -7208,7 +7227,7 @@
       <c r="D220" t="s">
         <v>184</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="4">
         <v>6.94</v>
       </c>
       <c r="F220">
@@ -7226,19 +7245,23 @@
         <v>167</v>
       </c>
       <c r="C221" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
       </c>
-      <c r="E221">
-        <v>35.76</v>
+      <c r="E221" s="4">
+        <v>0.59</v>
       </c>
       <c r="F221">
         <v>35.76</v>
       </c>
       <c r="G221">
         <v>60</v>
+      </c>
+      <c r="I221">
+        <f>F221/G221</f>
+        <v>0.59599999999999997</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -7254,7 +7277,7 @@
       <c r="D222" t="s">
         <v>184</v>
       </c>
-      <c r="E222">
+      <c r="E222" s="4">
         <v>13.68</v>
       </c>
       <c r="F222">
@@ -7277,7 +7300,7 @@
       <c r="D223" t="s">
         <v>184</v>
       </c>
-      <c r="E223">
+      <c r="E223" s="4">
         <v>15.13</v>
       </c>
       <c r="F223">
@@ -7300,7 +7323,7 @@
       <c r="D224" t="s">
         <v>185</v>
       </c>
-      <c r="E224" s="3">
+      <c r="E224" s="4">
         <v>1.87</v>
       </c>
       <c r="F224" s="3">
@@ -7327,7 +7350,7 @@
       <c r="D225" t="s">
         <v>185</v>
       </c>
-      <c r="E225" s="3">
+      <c r="E225" s="4">
         <v>4.75</v>
       </c>
       <c r="F225" s="3">
@@ -7337,7 +7360,7 @@
         <v>20</v>
       </c>
       <c r="I225">
-        <f t="shared" ref="I225:I261" si="1">F225/G225</f>
+        <f t="shared" ref="I225:I261" si="2">F225/G225</f>
         <v>4.75</v>
       </c>
     </row>
@@ -7354,7 +7377,7 @@
       <c r="D226" t="s">
         <v>185</v>
       </c>
-      <c r="E226" s="3">
+      <c r="E226" s="4">
         <v>2</v>
       </c>
       <c r="F226" s="3">
@@ -7364,7 +7387,7 @@
         <v>22</v>
       </c>
       <c r="I226">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -7381,7 +7404,7 @@
       <c r="D227" t="s">
         <v>185</v>
       </c>
-      <c r="E227" s="3">
+      <c r="E227" s="4">
         <v>2</v>
       </c>
       <c r="F227" s="3">
@@ -7391,7 +7414,7 @@
         <v>22</v>
       </c>
       <c r="I227">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -7408,7 +7431,7 @@
       <c r="D228" t="s">
         <v>185</v>
       </c>
-      <c r="E228" s="3">
+      <c r="E228" s="4">
         <v>2.6</v>
       </c>
       <c r="F228" s="3">
@@ -7418,7 +7441,7 @@
         <v>20</v>
       </c>
       <c r="I228">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.6</v>
       </c>
     </row>
@@ -7435,7 +7458,7 @@
       <c r="D229" t="s">
         <v>185</v>
       </c>
-      <c r="E229" s="3">
+      <c r="E229" s="4">
         <v>2.8</v>
       </c>
       <c r="F229" s="3">
@@ -7445,7 +7468,7 @@
         <v>20</v>
       </c>
       <c r="I229">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.8</v>
       </c>
     </row>
@@ -7462,7 +7485,7 @@
       <c r="D230" t="s">
         <v>185</v>
       </c>
-      <c r="E230" s="3">
+      <c r="E230" s="4">
         <v>2.5</v>
       </c>
       <c r="F230" s="3">
@@ -7472,7 +7495,7 @@
         <v>24</v>
       </c>
       <c r="I230">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
     </row>
@@ -7489,7 +7512,7 @@
       <c r="D231" t="s">
         <v>185</v>
       </c>
-      <c r="E231" s="3">
+      <c r="E231" s="4">
         <v>4</v>
       </c>
       <c r="F231" s="3">
@@ -7499,7 +7522,7 @@
         <v>20</v>
       </c>
       <c r="I231">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -7516,7 +7539,7 @@
       <c r="D232" t="s">
         <v>185</v>
       </c>
-      <c r="E232" s="3">
+      <c r="E232" s="4">
         <v>2.34</v>
       </c>
       <c r="F232" s="3">
@@ -7526,7 +7549,7 @@
         <v>24</v>
       </c>
       <c r="I232">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3333333333333335</v>
       </c>
     </row>
@@ -7543,7 +7566,7 @@
       <c r="D233" t="s">
         <v>185</v>
       </c>
-      <c r="E233" s="3">
+      <c r="E233" s="4">
         <v>2.34</v>
       </c>
       <c r="F233" s="3">
@@ -7553,7 +7576,7 @@
         <v>24</v>
       </c>
       <c r="I233">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3333333333333335</v>
       </c>
     </row>
@@ -7570,7 +7593,7 @@
       <c r="D234" t="s">
         <v>185</v>
       </c>
-      <c r="E234" s="3">
+      <c r="E234" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F234" s="3">
@@ -7580,7 +7603,7 @@
         <v>20</v>
       </c>
       <c r="I234">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -7597,7 +7620,7 @@
       <c r="D235" t="s">
         <v>185</v>
       </c>
-      <c r="E235" s="3">
+      <c r="E235" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F235" s="3">
@@ -7607,7 +7630,7 @@
         <v>20</v>
       </c>
       <c r="I235">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -7624,7 +7647,7 @@
       <c r="D236" t="s">
         <v>185</v>
       </c>
-      <c r="E236" s="3">
+      <c r="E236" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F236" s="3">
@@ -7634,7 +7657,7 @@
         <v>30</v>
       </c>
       <c r="I236">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
     </row>
@@ -7651,7 +7674,7 @@
       <c r="D237" t="s">
         <v>185</v>
       </c>
-      <c r="E237" s="3">
+      <c r="E237" s="4">
         <v>13</v>
       </c>
       <c r="F237" s="3">
@@ -7661,7 +7684,7 @@
         <v>1</v>
       </c>
       <c r="I237">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
     </row>
@@ -7678,7 +7701,7 @@
       <c r="D238" t="s">
         <v>185</v>
       </c>
-      <c r="E238" s="3">
+      <c r="E238" s="4">
         <v>13.67</v>
       </c>
       <c r="F238" s="3">
@@ -7688,7 +7711,7 @@
         <v>15</v>
       </c>
       <c r="I238">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.666666666666666</v>
       </c>
     </row>
@@ -7705,7 +7728,7 @@
       <c r="D239" t="s">
         <v>185</v>
       </c>
-      <c r="E239" s="3">
+      <c r="E239" s="4">
         <v>1.4</v>
       </c>
       <c r="F239" s="3">
@@ -7715,7 +7738,7 @@
         <v>30</v>
       </c>
       <c r="I239">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
     </row>
@@ -7732,7 +7755,7 @@
       <c r="D240" t="s">
         <v>185</v>
       </c>
-      <c r="E240" s="3">
+      <c r="E240" s="4">
         <v>2</v>
       </c>
       <c r="F240" s="3">
@@ -7742,7 +7765,7 @@
         <v>22</v>
       </c>
       <c r="I240">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -7759,7 +7782,7 @@
       <c r="D241" t="s">
         <v>185</v>
       </c>
-      <c r="E241" s="3">
+      <c r="E241" s="4">
         <v>2</v>
       </c>
       <c r="F241" s="3">
@@ -7769,7 +7792,7 @@
         <v>22</v>
       </c>
       <c r="I241">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -7786,7 +7809,7 @@
       <c r="D242" t="s">
         <v>185</v>
       </c>
-      <c r="E242" s="3">
+      <c r="E242" s="4">
         <v>2</v>
       </c>
       <c r="F242" s="3">
@@ -7796,7 +7819,7 @@
         <v>22</v>
       </c>
       <c r="I242">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -7813,7 +7836,7 @@
       <c r="D243" t="s">
         <v>185</v>
       </c>
-      <c r="E243" s="3">
+      <c r="E243" s="4">
         <v>6.4</v>
       </c>
       <c r="F243" s="3">
@@ -7823,7 +7846,7 @@
         <v>20</v>
       </c>
       <c r="I243">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.4</v>
       </c>
     </row>
@@ -7840,7 +7863,7 @@
       <c r="D244" t="s">
         <v>185</v>
       </c>
-      <c r="E244" s="3">
+      <c r="E244" s="4">
         <v>3.67</v>
       </c>
       <c r="F244" s="3">
@@ -7850,7 +7873,7 @@
         <v>15</v>
       </c>
       <c r="I244">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.6666666666666665</v>
       </c>
     </row>
@@ -7867,7 +7890,7 @@
       <c r="D245" t="s">
         <v>185</v>
       </c>
-      <c r="E245" s="3">
+      <c r="E245" s="4">
         <v>5</v>
       </c>
       <c r="F245" s="3">
@@ -7877,7 +7900,7 @@
         <v>15</v>
       </c>
       <c r="I245">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
@@ -7894,7 +7917,7 @@
       <c r="D246" t="s">
         <v>185</v>
       </c>
-      <c r="E246" s="3">
+      <c r="E246" s="4">
         <v>3.08</v>
       </c>
       <c r="F246" s="3">
@@ -7904,7 +7927,7 @@
         <v>42</v>
       </c>
       <c r="I246">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0714285714285716</v>
       </c>
     </row>
@@ -7921,7 +7944,7 @@
       <c r="D247" t="s">
         <v>185</v>
       </c>
-      <c r="E247" s="3">
+      <c r="E247" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F247" s="3">
@@ -7931,7 +7954,7 @@
         <v>20</v>
       </c>
       <c r="I247">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -7948,7 +7971,7 @@
       <c r="D248" t="s">
         <v>185</v>
       </c>
-      <c r="E248" s="3">
+      <c r="E248" s="4">
         <v>1.98</v>
       </c>
       <c r="F248" s="3">
@@ -7958,7 +7981,7 @@
         <v>42</v>
       </c>
       <c r="I248">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.9761904761904763</v>
       </c>
     </row>
@@ -7975,7 +7998,7 @@
       <c r="D249" t="s">
         <v>185</v>
       </c>
-      <c r="E249" s="3">
+      <c r="E249" s="4">
         <v>1.26</v>
       </c>
       <c r="F249" s="3">
@@ -7985,7 +8008,7 @@
         <v>35</v>
       </c>
       <c r="I249">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2571428571428571</v>
       </c>
     </row>
@@ -8002,7 +8025,7 @@
       <c r="D250" t="s">
         <v>185</v>
       </c>
-      <c r="E250" s="3">
+      <c r="E250" s="4">
         <v>5.14</v>
       </c>
       <c r="F250" s="3">
@@ -8012,7 +8035,7 @@
         <v>15</v>
       </c>
       <c r="I250">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8029,7 +8052,7 @@
       <c r="D251" t="s">
         <v>185</v>
       </c>
-      <c r="E251" s="3">
+      <c r="E251" s="4">
         <v>5.14</v>
       </c>
       <c r="F251" s="3">
@@ -8039,7 +8062,7 @@
         <v>15</v>
       </c>
       <c r="I251">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8056,7 +8079,7 @@
       <c r="D252" t="s">
         <v>185</v>
       </c>
-      <c r="E252" s="3">
+      <c r="E252" s="4">
         <v>5.14</v>
       </c>
       <c r="F252" s="3">
@@ -8066,7 +8089,7 @@
         <v>15</v>
       </c>
       <c r="I252">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8083,7 +8106,7 @@
       <c r="D253" t="s">
         <v>185</v>
       </c>
-      <c r="E253" s="3">
+      <c r="E253" s="4">
         <v>5.14</v>
       </c>
       <c r="F253" s="3">
@@ -8093,7 +8116,7 @@
         <v>15</v>
       </c>
       <c r="I253">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8110,7 +8133,7 @@
       <c r="D254" t="s">
         <v>185</v>
       </c>
-      <c r="E254" s="3">
+      <c r="E254" s="4">
         <v>5.14</v>
       </c>
       <c r="F254" s="3">
@@ -8120,7 +8143,7 @@
         <v>15</v>
       </c>
       <c r="I254">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8137,7 +8160,7 @@
       <c r="D255" t="s">
         <v>185</v>
       </c>
-      <c r="E255" s="3">
+      <c r="E255" s="4">
         <v>5.14</v>
       </c>
       <c r="F255" s="3">
@@ -8147,7 +8170,7 @@
         <v>15</v>
       </c>
       <c r="I255">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8164,7 +8187,7 @@
       <c r="D256" t="s">
         <v>185</v>
       </c>
-      <c r="E256" s="3">
+      <c r="E256" s="4">
         <v>5.14</v>
       </c>
       <c r="F256" s="3">
@@ -8174,7 +8197,7 @@
         <v>15</v>
       </c>
       <c r="I256">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.1333333333333337</v>
       </c>
     </row>
@@ -8191,7 +8214,7 @@
       <c r="D257" t="s">
         <v>185</v>
       </c>
-      <c r="E257" s="3">
+      <c r="E257" s="4">
         <v>108</v>
       </c>
       <c r="F257" s="3">
@@ -8201,7 +8224,7 @@
         <v>24</v>
       </c>
       <c r="I257">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.5</v>
       </c>
     </row>
@@ -8218,7 +8241,7 @@
       <c r="D258" t="s">
         <v>185</v>
       </c>
-      <c r="E258" s="3">
+      <c r="E258" s="4">
         <v>2.44</v>
       </c>
       <c r="F258" s="3">
@@ -8245,7 +8268,7 @@
       <c r="D259" t="s">
         <v>185</v>
       </c>
-      <c r="E259" s="3">
+      <c r="E259" s="4">
         <v>9.5</v>
       </c>
       <c r="F259" s="3">
@@ -8255,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="I259">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.5</v>
       </c>
     </row>
@@ -8272,7 +8295,7 @@
       <c r="D260" t="s">
         <v>185</v>
       </c>
-      <c r="E260" s="3">
+      <c r="E260" s="4">
         <v>2.56</v>
       </c>
       <c r="F260" s="3">
@@ -8282,24 +8305,24 @@
         <v>30</v>
       </c>
       <c r="I260">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5666666666666669</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B261" t="s">
         <v>393</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C261" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C261" s="2" t="s">
+      <c r="D261" t="s">
         <v>395</v>
       </c>
-      <c r="D261" t="s">
-        <v>396</v>
-      </c>
-      <c r="E261" s="3">
+      <c r="E261" s="4">
         <v>50</v>
       </c>
       <c r="F261" s="3">
@@ -8309,7 +8332,7 @@
         <v>6</v>
       </c>
       <c r="I261">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.3333333333333339</v>
       </c>
     </row>
@@ -8337,7 +8360,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -14094,7 +14117,7 @@
         <v>167</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>184</v>
@@ -14140,7 +14163,7 @@
         <v>167</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>184</v>
@@ -14255,7 +14278,7 @@
         <v>167</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D258" s="8" t="s">
         <v>184</v>
@@ -14278,7 +14301,7 @@
         <v>167</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>184</v>
@@ -14301,7 +14324,7 @@
         <v>167</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>184</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3337DE-FF8E-461E-BA70-A8615FA67388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F31491-9937-418F-B03D-B3E820A46C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="402">
   <si>
     <t>categoria</t>
   </si>
@@ -1216,6 +1216,21 @@
   </si>
   <si>
     <t>DOC Gui Paçoquinha Rolha Pote com 32 Unid de 16g</t>
+  </si>
+  <si>
+    <t>Tipo de comissão</t>
+  </si>
+  <si>
+    <t>Valor da Comissão</t>
+  </si>
+  <si>
+    <t>Fixo</t>
+  </si>
+  <si>
+    <t>Percentual</t>
+  </si>
+  <si>
+    <t>Custo</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1755,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1770,6 +1785,8 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="48">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2134,7 +2151,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I261"/>
+  <dimension ref="A1:J261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2142,9 +2159,11 @@
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2166,8 +2185,17 @@
       <c r="G1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="I1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>376</v>
       </c>
@@ -2189,8 +2217,14 @@
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>377</v>
       </c>
@@ -2212,8 +2246,14 @@
       <c r="G3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>378</v>
       </c>
@@ -2235,8 +2275,14 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I4">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>379</v>
       </c>
@@ -2258,8 +2304,14 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I5">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>380</v>
       </c>
@@ -2281,8 +2333,14 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>381</v>
       </c>
@@ -2304,8 +2362,14 @@
       <c r="G7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>382</v>
       </c>
@@ -2327,8 +2391,14 @@
       <c r="G8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>383</v>
       </c>
@@ -2350,8 +2420,14 @@
       <c r="G9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>384</v>
       </c>
@@ -2373,8 +2449,14 @@
       <c r="G10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I10">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>211</v>
       </c>
@@ -2396,8 +2478,14 @@
       <c r="G11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I11" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>212</v>
       </c>
@@ -2419,8 +2507,14 @@
       <c r="G12">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>213</v>
       </c>
@@ -2442,8 +2536,14 @@
       <c r="G13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>214</v>
       </c>
@@ -2465,8 +2565,14 @@
       <c r="G14">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>215</v>
       </c>
@@ -2488,8 +2594,14 @@
       <c r="G15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I15" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>216</v>
       </c>
@@ -2511,8 +2623,14 @@
       <c r="G16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>217</v>
       </c>
@@ -2534,8 +2652,14 @@
       <c r="G17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I17" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>218</v>
       </c>
@@ -2557,8 +2681,14 @@
       <c r="G18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I18" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>219</v>
       </c>
@@ -2580,8 +2710,14 @@
       <c r="G19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I19" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>220</v>
       </c>
@@ -2603,8 +2739,14 @@
       <c r="G20">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>221</v>
       </c>
@@ -2626,8 +2768,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>222</v>
       </c>
@@ -2649,8 +2797,14 @@
       <c r="G22">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>223</v>
       </c>
@@ -2672,8 +2826,14 @@
       <c r="G23">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>224</v>
       </c>
@@ -2695,8 +2855,14 @@
       <c r="G24">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>225</v>
       </c>
@@ -2718,8 +2884,14 @@
       <c r="G25">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>226</v>
       </c>
@@ -2741,8 +2913,14 @@
       <c r="G26">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>227</v>
       </c>
@@ -2764,8 +2942,14 @@
       <c r="G27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>228</v>
       </c>
@@ -2787,8 +2971,14 @@
       <c r="G28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>229</v>
       </c>
@@ -2810,8 +3000,14 @@
       <c r="G29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I29" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>230</v>
       </c>
@@ -2833,8 +3029,14 @@
       <c r="G30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I30" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>231</v>
       </c>
@@ -2856,8 +3058,14 @@
       <c r="G31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I31" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>232</v>
       </c>
@@ -2879,8 +3087,14 @@
       <c r="G32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I32" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>233</v>
       </c>
@@ -2902,8 +3116,14 @@
       <c r="G33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I33" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>234</v>
       </c>
@@ -2925,8 +3145,14 @@
       <c r="G34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I34" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>235</v>
       </c>
@@ -2948,8 +3174,14 @@
       <c r="G35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I35" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>236</v>
       </c>
@@ -2971,8 +3203,14 @@
       <c r="G36">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I36" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>237</v>
       </c>
@@ -2994,8 +3232,14 @@
       <c r="G37">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I37" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>238</v>
       </c>
@@ -3017,8 +3261,14 @@
       <c r="G38">
         <v>12</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I38" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>239</v>
       </c>
@@ -3040,8 +3290,14 @@
       <c r="G39">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I39" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>240</v>
       </c>
@@ -3063,8 +3319,14 @@
       <c r="G40">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I40" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>241</v>
       </c>
@@ -3086,8 +3348,14 @@
       <c r="G41">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I41" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>242</v>
       </c>
@@ -3109,8 +3377,14 @@
       <c r="G42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I42" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>243</v>
       </c>
@@ -3132,8 +3406,14 @@
       <c r="G43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I43" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>244</v>
       </c>
@@ -3155,8 +3435,14 @@
       <c r="G44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I44" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>245</v>
       </c>
@@ -3178,8 +3464,14 @@
       <c r="G45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I45" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>246</v>
       </c>
@@ -3201,8 +3493,14 @@
       <c r="G46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I46" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>247</v>
       </c>
@@ -3224,8 +3522,14 @@
       <c r="G47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>248</v>
       </c>
@@ -3247,8 +3551,14 @@
       <c r="G48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I48" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>249</v>
       </c>
@@ -3270,8 +3580,14 @@
       <c r="G49">
         <v>30</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I49" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>250</v>
       </c>
@@ -3293,8 +3609,14 @@
       <c r="G50">
         <v>30</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I50" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>251</v>
       </c>
@@ -3316,8 +3638,14 @@
       <c r="G51">
         <v>36</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I51" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>252</v>
       </c>
@@ -3339,8 +3667,14 @@
       <c r="G52">
         <v>36</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I52" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>253</v>
       </c>
@@ -3362,8 +3696,14 @@
       <c r="G53">
         <v>36</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>254</v>
       </c>
@@ -3385,8 +3725,14 @@
       <c r="G54">
         <v>36</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>255</v>
       </c>
@@ -3408,8 +3754,14 @@
       <c r="G55">
         <v>12</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I55" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>256</v>
       </c>
@@ -3431,8 +3783,14 @@
       <c r="G56">
         <v>12</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I56" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>257</v>
       </c>
@@ -3454,8 +3812,14 @@
       <c r="G57">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I57" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>258</v>
       </c>
@@ -3477,8 +3841,14 @@
       <c r="G58">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I58" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>259</v>
       </c>
@@ -3500,8 +3870,14 @@
       <c r="G59">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I59" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>260</v>
       </c>
@@ -3523,8 +3899,14 @@
       <c r="G60">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I60" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>261</v>
       </c>
@@ -3546,8 +3928,14 @@
       <c r="G61">
         <v>20</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I61" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>262</v>
       </c>
@@ -3569,8 +3957,14 @@
       <c r="G62">
         <v>20</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I62" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>263</v>
       </c>
@@ -3592,8 +3986,14 @@
       <c r="G63">
         <v>20</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I63" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>264</v>
       </c>
@@ -3615,8 +4015,14 @@
       <c r="G64">
         <v>20</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I64" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>265</v>
       </c>
@@ -3638,8 +4044,14 @@
       <c r="G65">
         <v>20</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I65" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>266</v>
       </c>
@@ -3661,8 +4073,14 @@
       <c r="G66">
         <v>20</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I66" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>267</v>
       </c>
@@ -3684,8 +4102,14 @@
       <c r="G67">
         <v>12</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I67" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>268</v>
       </c>
@@ -3707,8 +4131,14 @@
       <c r="G68">
         <v>12</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I68" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>269</v>
       </c>
@@ -3730,8 +4160,14 @@
       <c r="G69">
         <v>12</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I69" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>270</v>
       </c>
@@ -3753,8 +4189,14 @@
       <c r="G70">
         <v>12</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I70" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>271</v>
       </c>
@@ -3776,8 +4218,14 @@
       <c r="G71">
         <v>12</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I71" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>272</v>
       </c>
@@ -3799,8 +4247,14 @@
       <c r="G72">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I72" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>273</v>
       </c>
@@ -3822,8 +4276,14 @@
       <c r="G73">
         <v>6</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I73" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>274</v>
       </c>
@@ -3845,8 +4305,14 @@
       <c r="G74">
         <v>12</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I74" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>275</v>
       </c>
@@ -3868,8 +4334,14 @@
       <c r="G75">
         <v>4</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I75" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>276</v>
       </c>
@@ -3891,8 +4363,14 @@
       <c r="G76">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I76" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>277</v>
       </c>
@@ -3914,8 +4392,14 @@
       <c r="G77">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I77" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>278</v>
       </c>
@@ -3937,8 +4421,14 @@
       <c r="G78">
         <v>6</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I78" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>279</v>
       </c>
@@ -3960,8 +4450,14 @@
       <c r="G79">
         <v>4</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I79" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>280</v>
       </c>
@@ -3983,8 +4479,14 @@
       <c r="G80">
         <v>12</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I80" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>281</v>
       </c>
@@ -4006,8 +4508,14 @@
       <c r="G81">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I81" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>282</v>
       </c>
@@ -4029,8 +4537,14 @@
       <c r="G82">
         <v>12</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I82" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>283</v>
       </c>
@@ -4052,8 +4566,14 @@
       <c r="G83">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I83" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>284</v>
       </c>
@@ -4075,8 +4595,14 @@
       <c r="G84">
         <v>12</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I84" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>285</v>
       </c>
@@ -4098,8 +4624,14 @@
       <c r="G85">
         <v>12</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I85" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>286</v>
       </c>
@@ -4121,8 +4653,14 @@
       <c r="G86">
         <v>12</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I86" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>287</v>
       </c>
@@ -4144,8 +4682,14 @@
       <c r="G87">
         <v>12</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I87" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>288</v>
       </c>
@@ -4167,8 +4711,14 @@
       <c r="G88">
         <v>12</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I88" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>289</v>
       </c>
@@ -4190,8 +4740,14 @@
       <c r="G89">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I89" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>290</v>
       </c>
@@ -4213,8 +4769,14 @@
       <c r="G90">
         <v>6</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I90" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>291</v>
       </c>
@@ -4236,8 +4798,14 @@
       <c r="G91">
         <v>12</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I91" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>292</v>
       </c>
@@ -4259,8 +4827,14 @@
       <c r="G92">
         <v>12</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I92" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>293</v>
       </c>
@@ -4282,8 +4856,14 @@
       <c r="G93">
         <v>12</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I93" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>294</v>
       </c>
@@ -4305,8 +4885,14 @@
       <c r="G94">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I94" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>295</v>
       </c>
@@ -4328,8 +4914,14 @@
       <c r="G95">
         <v>12</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I95" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>296</v>
       </c>
@@ -4351,8 +4943,14 @@
       <c r="G96">
         <v>12</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I96" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>297</v>
       </c>
@@ -4374,8 +4972,14 @@
       <c r="G97">
         <v>12</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I97" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>298</v>
       </c>
@@ -4397,8 +5001,14 @@
       <c r="G98">
         <v>12</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I98" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>299</v>
       </c>
@@ -4420,8 +5030,14 @@
       <c r="G99">
         <v>12</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I99" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>300</v>
       </c>
@@ -4443,8 +5059,14 @@
       <c r="G100">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I100" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>301</v>
       </c>
@@ -4466,8 +5088,14 @@
       <c r="G101">
         <v>12</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I101" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>302</v>
       </c>
@@ -4489,8 +5117,14 @@
       <c r="G102">
         <v>12</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I102" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>303</v>
       </c>
@@ -4512,8 +5146,14 @@
       <c r="G103">
         <v>12</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I103" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>304</v>
       </c>
@@ -4535,8 +5175,14 @@
       <c r="G104">
         <v>12</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H104" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I104" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>305</v>
       </c>
@@ -4558,8 +5204,14 @@
       <c r="G105">
         <v>12</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I105" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>306</v>
       </c>
@@ -4581,8 +5233,14 @@
       <c r="G106">
         <v>12</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I106" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>307</v>
       </c>
@@ -4604,8 +5262,14 @@
       <c r="G107">
         <v>12</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I107" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>308</v>
       </c>
@@ -4627,8 +5291,14 @@
       <c r="G108">
         <v>12</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H108" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I108" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>309</v>
       </c>
@@ -4650,8 +5320,14 @@
       <c r="G109">
         <v>12</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H109" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I109" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>310</v>
       </c>
@@ -4673,8 +5349,14 @@
       <c r="G110">
         <v>12</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H110" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I110" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>311</v>
       </c>
@@ -4696,8 +5378,14 @@
       <c r="G111">
         <v>12</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I111" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>312</v>
       </c>
@@ -4719,8 +5407,14 @@
       <c r="G112">
         <v>12</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I112" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>313</v>
       </c>
@@ -4742,8 +5436,14 @@
       <c r="G113">
         <v>12</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I113" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>314</v>
       </c>
@@ -4765,8 +5465,14 @@
       <c r="G114">
         <v>10</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I114" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>315</v>
       </c>
@@ -4788,8 +5494,14 @@
       <c r="G115">
         <v>20</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H115" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I115" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>316</v>
       </c>
@@ -4811,8 +5523,14 @@
       <c r="G116">
         <v>20</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I116" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>317</v>
       </c>
@@ -4834,8 +5552,14 @@
       <c r="G117">
         <v>12</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I117" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>20236</v>
       </c>
@@ -4857,8 +5581,14 @@
       <c r="G118">
         <v>12</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I118" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>20328</v>
       </c>
@@ -4880,8 +5610,14 @@
       <c r="G119">
         <v>12</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I119" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>20205</v>
       </c>
@@ -4903,8 +5639,14 @@
       <c r="G120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I120" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>20250</v>
       </c>
@@ -4926,8 +5668,14 @@
       <c r="G121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I121" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>20212</v>
       </c>
@@ -4949,8 +5697,14 @@
       <c r="G122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I122" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>20267</v>
       </c>
@@ -4972,8 +5726,14 @@
       <c r="G123">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I123" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>20366</v>
       </c>
@@ -4995,8 +5755,14 @@
       <c r="G124">
         <v>12</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I124" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>20403</v>
       </c>
@@ -5018,8 +5784,14 @@
       <c r="G125">
         <v>12</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I125" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>20410</v>
       </c>
@@ -5041,8 +5813,14 @@
       <c r="G126">
         <v>12</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I126" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>20441</v>
       </c>
@@ -5064,8 +5842,14 @@
       <c r="G127">
         <v>12</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I127" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>20496</v>
       </c>
@@ -5087,8 +5871,14 @@
       <c r="G128">
         <v>12</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I128" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>20540</v>
       </c>
@@ -5110,8 +5900,14 @@
       <c r="G129">
         <v>12</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I129" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>20465</v>
       </c>
@@ -5133,8 +5929,14 @@
       <c r="G130">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I130" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>20519</v>
       </c>
@@ -5156,8 +5958,14 @@
       <c r="G131">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I131" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>20564</v>
       </c>
@@ -5179,8 +5987,14 @@
       <c r="G132">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I132" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>20472</v>
       </c>
@@ -5202,8 +6016,14 @@
       <c r="G133">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I133" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>20526</v>
       </c>
@@ -5225,8 +6045,14 @@
       <c r="G134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I134" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>20489</v>
       </c>
@@ -5248,8 +6074,14 @@
       <c r="G135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I135" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>20533</v>
       </c>
@@ -5272,8 +6104,14 @@
         <f t="shared" ref="G136" si="0">F136/E136</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I136" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>20588</v>
       </c>
@@ -5295,8 +6133,14 @@
       <c r="G137">
         <v>12</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I137" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>20618</v>
       </c>
@@ -5318,8 +6162,14 @@
       <c r="G138">
         <v>12</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I138" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>20625</v>
       </c>
@@ -5341,8 +6191,14 @@
       <c r="G139">
         <v>12</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H139" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I139" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>20656</v>
       </c>
@@ -5364,8 +6220,14 @@
       <c r="G140">
         <v>12</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I140" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>20601</v>
       </c>
@@ -5387,8 +6249,14 @@
       <c r="G141">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I141" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>20649</v>
       </c>
@@ -5410,8 +6278,14 @@
       <c r="G142">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I142" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>21</v>
       </c>
@@ -5433,8 +6307,14 @@
       <c r="G143">
         <v>12</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I143" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>20687</v>
       </c>
@@ -5456,8 +6336,14 @@
       <c r="G144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I144" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>20694</v>
       </c>
@@ -5479,8 +6365,14 @@
       <c r="G145">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I145" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>20700</v>
       </c>
@@ -5502,8 +6394,14 @@
       <c r="G146">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I146" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>20717</v>
       </c>
@@ -5525,8 +6423,14 @@
       <c r="G147">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I147" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>22049</v>
       </c>
@@ -5548,8 +6452,14 @@
       <c r="G148">
         <v>30</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I148" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>22056</v>
       </c>
@@ -5571,8 +6481,14 @@
       <c r="G149">
         <v>30</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I149" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>20809</v>
       </c>
@@ -5594,8 +6510,14 @@
       <c r="G150">
         <v>36</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I150" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>20816</v>
       </c>
@@ -5617,8 +6539,14 @@
       <c r="G151">
         <v>36</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I151" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>20847</v>
       </c>
@@ -5640,8 +6568,14 @@
       <c r="G152">
         <v>12</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I152" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>20854</v>
       </c>
@@ -5663,8 +6597,14 @@
       <c r="G153">
         <v>12</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I153" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>20861</v>
       </c>
@@ -5686,8 +6626,14 @@
       <c r="G154">
         <v>12</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I154" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>20960</v>
       </c>
@@ -5709,8 +6655,14 @@
       <c r="G155">
         <v>12</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H155" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I155" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>20984</v>
       </c>
@@ -5732,8 +6684,14 @@
       <c r="G156">
         <v>12</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I156" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>22</v>
       </c>
@@ -5755,8 +6713,14 @@
       <c r="G157">
         <v>12</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H157" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I157" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>23</v>
       </c>
@@ -5778,8 +6742,14 @@
       <c r="G158">
         <v>12</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I158" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>21059</v>
       </c>
@@ -5801,8 +6771,14 @@
       <c r="G159">
         <v>20</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I159" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>21097</v>
       </c>
@@ -5824,8 +6800,14 @@
       <c r="G160">
         <v>20</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I160" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>21103</v>
       </c>
@@ -5847,8 +6829,14 @@
       <c r="G161">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I161" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>21165</v>
       </c>
@@ -5870,8 +6858,14 @@
       <c r="G162">
         <v>12</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I162" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>21172</v>
       </c>
@@ -5893,8 +6887,14 @@
       <c r="G163">
         <v>12</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I163" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>21189</v>
       </c>
@@ -5916,8 +6916,14 @@
       <c r="G164">
         <v>12</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I164" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>21196</v>
       </c>
@@ -5939,8 +6945,14 @@
       <c r="G165">
         <v>12</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I165" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>21424</v>
       </c>
@@ -5962,8 +6974,14 @@
       <c r="G166">
         <v>12</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I166" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>21431</v>
       </c>
@@ -5985,8 +7003,14 @@
       <c r="G167">
         <v>4</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I167" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>21448</v>
       </c>
@@ -6008,8 +7032,14 @@
       <c r="G168">
         <v>5</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I168" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>21462</v>
       </c>
@@ -6031,8 +7061,14 @@
       <c r="G169">
         <v>5</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I169" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>21479</v>
       </c>
@@ -6054,8 +7090,14 @@
       <c r="G170">
         <v>6</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I170" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>21486</v>
       </c>
@@ -6077,8 +7119,14 @@
       <c r="G171">
         <v>6</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I171" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>21493</v>
       </c>
@@ -6100,8 +7148,14 @@
       <c r="G172">
         <v>12</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I172" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>21509</v>
       </c>
@@ -6123,8 +7177,14 @@
       <c r="G173">
         <v>12</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I173" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>21523</v>
       </c>
@@ -6146,8 +7206,14 @@
       <c r="G174">
         <v>12</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I174" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>24</v>
       </c>
@@ -6169,8 +7235,14 @@
       <c r="G175">
         <v>12</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I175" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>21561</v>
       </c>
@@ -6192,8 +7264,14 @@
       <c r="G176">
         <v>12</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I176" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>21578</v>
       </c>
@@ -6215,8 +7293,14 @@
       <c r="G177">
         <v>12</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I177" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>21585</v>
       </c>
@@ -6238,8 +7322,14 @@
       <c r="G178">
         <v>12</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I178" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>21592</v>
       </c>
@@ -6261,8 +7351,14 @@
       <c r="G179">
         <v>12</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I179" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>21608</v>
       </c>
@@ -6284,8 +7380,14 @@
       <c r="G180">
         <v>12</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I180" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>22421</v>
       </c>
@@ -6307,8 +7409,14 @@
       <c r="G181">
         <v>12</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I181" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>22353</v>
       </c>
@@ -6330,8 +7438,14 @@
       <c r="G182">
         <v>12</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I182" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>22360</v>
       </c>
@@ -6353,8 +7467,14 @@
       <c r="G183">
         <v>12</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I183" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>21714</v>
       </c>
@@ -6376,8 +7496,14 @@
       <c r="G184">
         <v>12</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I184" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>22339</v>
       </c>
@@ -6399,8 +7525,14 @@
       <c r="G185">
         <v>12</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I185" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>22391</v>
       </c>
@@ -6422,8 +7554,14 @@
       <c r="G186">
         <v>12</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I186" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>21745</v>
       </c>
@@ -6445,8 +7583,14 @@
       <c r="G187">
         <v>12</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I187" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>21752</v>
       </c>
@@ -6468,8 +7612,14 @@
       <c r="G188">
         <v>12</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H188" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I188" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>21783</v>
       </c>
@@ -6491,8 +7641,14 @@
       <c r="G189">
         <v>12</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H189" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I189" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>21790</v>
       </c>
@@ -6514,8 +7670,14 @@
       <c r="G190">
         <v>12</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H190" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I190" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>21844</v>
       </c>
@@ -6537,8 +7699,14 @@
       <c r="G191">
         <v>20</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H191" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I191" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>21899</v>
       </c>
@@ -6559,6 +7727,12 @@
       </c>
       <c r="G192">
         <v>20</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I192" s="13">
+        <v>0.03</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -6583,6 +7757,12 @@
       <c r="G193">
         <v>10</v>
       </c>
+      <c r="H193" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I193" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
@@ -6606,6 +7786,12 @@
       <c r="G194">
         <v>10</v>
       </c>
+      <c r="H194" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I194" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
@@ -6629,6 +7815,12 @@
       <c r="G195">
         <v>10</v>
       </c>
+      <c r="H195" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I195" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
@@ -6652,6 +7844,12 @@
       <c r="G196">
         <v>10</v>
       </c>
+      <c r="H196" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I196" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
@@ -6675,6 +7873,12 @@
       <c r="G197">
         <v>10</v>
       </c>
+      <c r="H197" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I197" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
@@ -6698,6 +7902,12 @@
       <c r="G198">
         <v>10</v>
       </c>
+      <c r="H198" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I198" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
@@ -6721,6 +7931,12 @@
       <c r="G199">
         <v>10</v>
       </c>
+      <c r="H199" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I199" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
@@ -6744,6 +7960,12 @@
       <c r="G200">
         <v>10</v>
       </c>
+      <c r="H200" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I200" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
@@ -6767,6 +7989,12 @@
       <c r="G201">
         <v>24</v>
       </c>
+      <c r="H201" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I201" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
@@ -6790,6 +8018,12 @@
       <c r="G202">
         <v>24</v>
       </c>
+      <c r="H202" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I202" s="13">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
@@ -6813,6 +8047,12 @@
       <c r="G203">
         <v>12</v>
       </c>
+      <c r="H203" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I203" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
@@ -6836,6 +8076,12 @@
       <c r="G204">
         <v>12</v>
       </c>
+      <c r="H204" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I204" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
@@ -6859,6 +8105,12 @@
       <c r="G205">
         <v>30</v>
       </c>
+      <c r="H205" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I205" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
@@ -6882,9 +8134,11 @@
       <c r="G206">
         <v>32</v>
       </c>
-      <c r="I206">
-        <f>26.64/32</f>
-        <v>0.83250000000000002</v>
+      <c r="H206" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I206" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -6909,9 +8163,11 @@
       <c r="G207">
         <v>32</v>
       </c>
-      <c r="I207">
-        <f>29.8/32</f>
-        <v>0.93125000000000002</v>
+      <c r="H207" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I207" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -6936,6 +8192,12 @@
       <c r="G208">
         <v>1</v>
       </c>
+      <c r="H208" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I208" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
@@ -6959,6 +8221,12 @@
       <c r="G209">
         <v>1</v>
       </c>
+      <c r="H209" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I209" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
@@ -6982,6 +8250,12 @@
       <c r="G210">
         <v>1</v>
       </c>
+      <c r="H210" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I210" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
@@ -7005,9 +8279,11 @@
       <c r="G211">
         <v>63</v>
       </c>
-      <c r="I211">
-        <f>F211/G211</f>
-        <v>0.40603174603174602</v>
+      <c r="H211" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I211" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -7032,9 +8308,11 @@
       <c r="G212">
         <v>56</v>
       </c>
-      <c r="I212">
-        <f>F212/G212</f>
-        <v>0.42589285714285718</v>
+      <c r="H212" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I212" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -7059,6 +8337,12 @@
       <c r="G213">
         <v>16</v>
       </c>
+      <c r="H213" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I213" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
@@ -7082,6 +8366,12 @@
       <c r="G214">
         <v>16</v>
       </c>
+      <c r="H214" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I214" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
@@ -7105,6 +8395,12 @@
       <c r="G215">
         <v>16</v>
       </c>
+      <c r="H215" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I215" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
@@ -7128,9 +8424,11 @@
       <c r="G216">
         <v>42</v>
       </c>
-      <c r="I216">
-        <f>F216/G216</f>
-        <v>0.61142857142857143</v>
+      <c r="H216" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I216" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -7155,9 +8453,11 @@
       <c r="G217">
         <v>42</v>
       </c>
-      <c r="I217">
-        <f t="shared" ref="I217:I219" si="1">F217/G217</f>
-        <v>0.61142857142857143</v>
+      <c r="H217" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I217" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -7182,9 +8482,11 @@
       <c r="G218">
         <v>42</v>
       </c>
-      <c r="I218">
-        <f t="shared" si="1"/>
-        <v>0.61142857142857143</v>
+      <c r="H218" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I218" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -7209,9 +8511,11 @@
       <c r="G219">
         <v>24</v>
       </c>
-      <c r="I219">
-        <f t="shared" si="1"/>
-        <v>1.5895833333333333</v>
+      <c r="H219" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I219" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -7236,6 +8540,12 @@
       <c r="G220">
         <v>25</v>
       </c>
+      <c r="H220" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I220" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
@@ -7259,9 +8569,11 @@
       <c r="G221">
         <v>60</v>
       </c>
-      <c r="I221">
-        <f>F221/G221</f>
-        <v>0.59599999999999997</v>
+      <c r="H221" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I221" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -7286,6 +8598,12 @@
       <c r="G222">
         <v>12</v>
       </c>
+      <c r="H222" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I222" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
@@ -7309,6 +8627,12 @@
       <c r="G223">
         <v>12</v>
       </c>
+      <c r="H223" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I223" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
@@ -7332,9 +8656,11 @@
       <c r="G224" s="4">
         <v>30</v>
       </c>
-      <c r="I224">
-        <f>F224/G224</f>
-        <v>1.8666666666666667</v>
+      <c r="H224" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I224" s="14">
+        <v>16</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -7359,9 +8685,11 @@
       <c r="G225" s="4">
         <v>20</v>
       </c>
-      <c r="I225">
-        <f t="shared" ref="I225:I261" si="2">F225/G225</f>
-        <v>4.75</v>
+      <c r="H225" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I225" s="14">
+        <v>27</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -7386,9 +8714,11 @@
       <c r="G226" s="4">
         <v>22</v>
       </c>
-      <c r="I226">
-        <f t="shared" si="2"/>
-        <v>2</v>
+      <c r="H226" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I226" s="14">
+        <v>12</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -7413,9 +8743,11 @@
       <c r="G227" s="4">
         <v>22</v>
       </c>
-      <c r="I227">
-        <f t="shared" si="2"/>
-        <v>2</v>
+      <c r="H227" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I227" s="14">
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -7440,9 +8772,11 @@
       <c r="G228" s="4">
         <v>20</v>
       </c>
-      <c r="I228">
-        <f t="shared" si="2"/>
-        <v>2.6</v>
+      <c r="H228" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I228" s="14">
+        <v>14</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -7467,9 +8801,11 @@
       <c r="G229" s="4">
         <v>20</v>
       </c>
-      <c r="I229">
-        <f t="shared" si="2"/>
-        <v>2.8</v>
+      <c r="H229" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I229" s="14">
+        <v>18</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -7494,9 +8830,11 @@
       <c r="G230" s="4">
         <v>24</v>
       </c>
-      <c r="I230">
-        <f t="shared" si="2"/>
-        <v>2.5</v>
+      <c r="H230" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I230" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -7521,9 +8859,11 @@
       <c r="G231" s="4">
         <v>20</v>
       </c>
-      <c r="I231">
-        <f t="shared" si="2"/>
-        <v>4</v>
+      <c r="H231" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I231" s="14">
+        <v>18</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
@@ -7548,9 +8888,11 @@
       <c r="G232" s="4">
         <v>24</v>
       </c>
-      <c r="I232">
-        <f t="shared" si="2"/>
-        <v>2.3333333333333335</v>
+      <c r="H232" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I232" s="14">
+        <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -7575,9 +8917,11 @@
       <c r="G233" s="4">
         <v>24</v>
       </c>
-      <c r="I233">
-        <f t="shared" si="2"/>
-        <v>2.3333333333333335</v>
+      <c r="H233" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I233" s="14">
+        <v>18</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -7602,9 +8946,11 @@
       <c r="G234" s="4">
         <v>20</v>
       </c>
-      <c r="I234">
-        <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+      <c r="H234" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I234" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
@@ -7629,9 +8975,11 @@
       <c r="G235" s="4">
         <v>20</v>
       </c>
-      <c r="I235">
-        <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+      <c r="H235" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I235" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -7648,7 +8996,7 @@
         <v>185</v>
       </c>
       <c r="E236" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="F236" s="3">
         <v>75</v>
@@ -7656,9 +9004,11 @@
       <c r="G236" s="4">
         <v>30</v>
       </c>
-      <c r="I236">
-        <f t="shared" si="2"/>
-        <v>2.5</v>
+      <c r="H236" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I236" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -7683,9 +9033,11 @@
       <c r="G237" s="4">
         <v>1</v>
       </c>
-      <c r="I237">
-        <f t="shared" si="2"/>
-        <v>13</v>
+      <c r="H237" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I237" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
@@ -7710,9 +9062,11 @@
       <c r="G238" s="4">
         <v>15</v>
       </c>
-      <c r="I238">
-        <f t="shared" si="2"/>
-        <v>13.666666666666666</v>
+      <c r="H238" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I238" s="14">
+        <v>20</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -7737,9 +9091,11 @@
       <c r="G239" s="4">
         <v>30</v>
       </c>
-      <c r="I239">
-        <f t="shared" si="2"/>
-        <v>1.4</v>
+      <c r="H239" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I239" s="14">
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -7764,9 +9120,11 @@
       <c r="G240" s="4">
         <v>22</v>
       </c>
-      <c r="I240">
-        <f t="shared" si="2"/>
-        <v>2</v>
+      <c r="H240" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I240" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
@@ -7791,9 +9149,11 @@
       <c r="G241" s="4">
         <v>22</v>
       </c>
-      <c r="I241">
-        <f t="shared" si="2"/>
-        <v>2</v>
+      <c r="H241" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I241" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -7818,9 +9178,11 @@
       <c r="G242" s="4">
         <v>22</v>
       </c>
-      <c r="I242">
-        <f t="shared" si="2"/>
-        <v>2</v>
+      <c r="H242" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I242" s="14">
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
@@ -7845,9 +9207,11 @@
       <c r="G243" s="4">
         <v>20</v>
       </c>
-      <c r="I243">
-        <f t="shared" si="2"/>
-        <v>6.4</v>
+      <c r="H243" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I243" s="14">
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
@@ -7872,9 +9236,11 @@
       <c r="G244" s="4">
         <v>15</v>
       </c>
-      <c r="I244">
-        <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+      <c r="H244" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I244" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
@@ -7899,9 +9265,11 @@
       <c r="G245" s="4">
         <v>15</v>
       </c>
-      <c r="I245">
-        <f t="shared" si="2"/>
-        <v>5</v>
+      <c r="H245" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I245" s="14">
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -7926,9 +9294,11 @@
       <c r="G246" s="4">
         <v>42</v>
       </c>
-      <c r="I246">
-        <f t="shared" si="2"/>
-        <v>3.0714285714285716</v>
+      <c r="H246" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I246" s="14">
+        <v>30</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -7953,9 +9323,11 @@
       <c r="G247" s="4">
         <v>20</v>
       </c>
-      <c r="I247">
-        <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+      <c r="H247" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I247" s="14">
+        <v>12</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -7980,9 +9352,11 @@
       <c r="G248" s="4">
         <v>42</v>
       </c>
-      <c r="I248">
-        <f t="shared" si="2"/>
-        <v>1.9761904761904763</v>
+      <c r="H248" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I248" s="14">
+        <v>21</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -8007,9 +9381,11 @@
       <c r="G249" s="4">
         <v>35</v>
       </c>
-      <c r="I249">
-        <f t="shared" si="2"/>
-        <v>1.2571428571428571</v>
+      <c r="H249" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I249" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -8034,9 +9410,11 @@
       <c r="G250" s="4">
         <v>15</v>
       </c>
-      <c r="I250">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H250" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I250" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
@@ -8061,9 +9439,11 @@
       <c r="G251" s="4">
         <v>15</v>
       </c>
-      <c r="I251">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H251" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I251" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -8088,9 +9468,11 @@
       <c r="G252" s="4">
         <v>15</v>
       </c>
-      <c r="I252">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H252" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I252" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -8115,9 +9497,11 @@
       <c r="G253" s="4">
         <v>15</v>
       </c>
-      <c r="I253">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H253" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I253" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -8142,9 +9526,11 @@
       <c r="G254" s="4">
         <v>15</v>
       </c>
-      <c r="I254">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H254" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I254" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
@@ -8169,9 +9555,11 @@
       <c r="G255" s="4">
         <v>15</v>
       </c>
-      <c r="I255">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H255" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I255" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -8196,9 +9584,11 @@
       <c r="G256" s="4">
         <v>15</v>
       </c>
-      <c r="I256">
-        <f t="shared" si="2"/>
-        <v>5.1333333333333337</v>
+      <c r="H256" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I256" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
@@ -8223,9 +9613,11 @@
       <c r="G257" s="4">
         <v>24</v>
       </c>
-      <c r="I257">
-        <f t="shared" si="2"/>
-        <v>4.5</v>
+      <c r="H257" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I257" s="14">
+        <v>30</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -8250,9 +9642,11 @@
       <c r="G258" s="4">
         <v>30</v>
       </c>
-      <c r="I258">
-        <f>F258/G258</f>
-        <v>2.4333333333333331</v>
+      <c r="H258" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I258" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -8277,9 +9671,11 @@
       <c r="G259" s="4">
         <v>1</v>
       </c>
-      <c r="I259">
-        <f t="shared" si="2"/>
-        <v>9.5</v>
+      <c r="H259" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I259" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -8304,9 +9700,11 @@
       <c r="G260" s="4">
         <v>30</v>
       </c>
-      <c r="I260">
-        <f t="shared" si="2"/>
-        <v>2.5666666666666669</v>
+      <c r="H260" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I260" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -8331,9 +9729,11 @@
       <c r="G261" s="4">
         <v>6</v>
       </c>
-      <c r="I261">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333339</v>
+      <c r="H261" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I261" s="14">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F31491-9937-418F-B03D-B3E820A46C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054D75E4-5E25-406D-9989-B432ADED61DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="414">
   <si>
     <t>categoria</t>
   </si>
@@ -1231,6 +1231,42 @@
   </si>
   <si>
     <t>Custo</t>
+  </si>
+  <si>
+    <t>01050411</t>
+  </si>
+  <si>
+    <t>Slg Fritop 50g Requeijão</t>
+  </si>
+  <si>
+    <t>Slg Fritop 50g Queijo</t>
+  </si>
+  <si>
+    <t>01050412</t>
+  </si>
+  <si>
+    <t>01050413</t>
+  </si>
+  <si>
+    <t>Slg Fritop 50g Presunto</t>
+  </si>
+  <si>
+    <t>Slg Fritop 50g Cebola</t>
+  </si>
+  <si>
+    <t>01050414</t>
+  </si>
+  <si>
+    <t>01050415</t>
+  </si>
+  <si>
+    <t>Slg Fritop 50g Bacon Liso</t>
+  </si>
+  <si>
+    <t>01050416</t>
+  </si>
+  <si>
+    <t>Slg Fritop 50g Churrasco</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2187,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J261"/>
+  <dimension ref="A1:J267"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2223,6 +2259,9 @@
       <c r="I2">
         <v>3.3</v>
       </c>
+      <c r="J2">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2252,6 +2291,9 @@
       <c r="I3">
         <v>3.3</v>
       </c>
+      <c r="J3">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2281,6 +2323,9 @@
       <c r="I4">
         <v>3.3</v>
       </c>
+      <c r="J4">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -2310,6 +2355,9 @@
       <c r="I5">
         <v>3.3</v>
       </c>
+      <c r="J5">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2339,6 +2387,9 @@
       <c r="I6">
         <v>3.3</v>
       </c>
+      <c r="J6">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -2368,6 +2419,9 @@
       <c r="I7">
         <v>3.3</v>
       </c>
+      <c r="J7">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2397,6 +2451,9 @@
       <c r="I8">
         <v>3.3</v>
       </c>
+      <c r="J8">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -2426,6 +2483,9 @@
       <c r="I9">
         <v>3.3</v>
       </c>
+      <c r="J9">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -2455,6 +2515,9 @@
       <c r="I10">
         <v>3.3</v>
       </c>
+      <c r="J10">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -8027,199 +8090,205 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>146</v>
+        <v>402</v>
       </c>
       <c r="B203" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C203" t="s">
-        <v>168</v>
+        <v>403</v>
       </c>
       <c r="D203" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="E203" s="4">
-        <v>6.94</v>
+        <v>1.99</v>
       </c>
       <c r="F203">
-        <v>83.28</v>
+        <f>E203*24</f>
+        <v>47.76</v>
       </c>
       <c r="G203">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>400</v>
       </c>
       <c r="I203" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>147</v>
+        <v>405</v>
       </c>
       <c r="B204" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C204" t="s">
-        <v>169</v>
+        <v>404</v>
       </c>
       <c r="D204" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="E204" s="4">
-        <v>6.94</v>
+        <v>1.99</v>
       </c>
       <c r="F204">
-        <v>83.28</v>
+        <f t="shared" ref="F204:F208" si="1">E204*24</f>
+        <v>47.76</v>
       </c>
       <c r="G204">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>400</v>
       </c>
       <c r="I204" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>148</v>
+        <v>406</v>
       </c>
       <c r="B205" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C205" t="s">
-        <v>170</v>
+        <v>407</v>
       </c>
       <c r="D205" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="E205" s="4">
-        <v>3.96</v>
+        <v>1.99</v>
       </c>
       <c r="F205">
-        <v>118.8</v>
+        <f t="shared" si="1"/>
+        <v>47.76</v>
       </c>
       <c r="G205">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>400</v>
       </c>
       <c r="I205" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>149</v>
+        <v>409</v>
       </c>
       <c r="B206" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C206" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D206" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="E206" s="4">
-        <v>0.84</v>
+        <v>1.99</v>
       </c>
       <c r="F206">
-        <v>26.64</v>
+        <f t="shared" si="1"/>
+        <v>47.76</v>
       </c>
       <c r="G206">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>400</v>
       </c>
       <c r="I206" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>150</v>
+        <v>410</v>
       </c>
       <c r="B207" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C207" t="s">
-        <v>172</v>
+        <v>411</v>
       </c>
       <c r="D207" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="E207" s="4">
-        <v>0.93</v>
+        <v>1.99</v>
       </c>
       <c r="F207">
-        <v>29.8</v>
+        <f t="shared" si="1"/>
+        <v>47.76</v>
       </c>
       <c r="G207">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>400</v>
       </c>
       <c r="I207" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>151</v>
+        <v>412</v>
       </c>
       <c r="B208" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C208" t="s">
-        <v>173</v>
+        <v>413</v>
       </c>
       <c r="D208" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="E208" s="4">
-        <v>12.99</v>
+        <v>1.99</v>
       </c>
       <c r="F208">
-        <v>12.99</v>
+        <f t="shared" si="1"/>
+        <v>47.76</v>
       </c>
       <c r="G208">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>400</v>
       </c>
       <c r="I208" s="13">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B209" t="s">
         <v>167</v>
       </c>
       <c r="C209" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D209" t="s">
         <v>184</v>
       </c>
       <c r="E209" s="4">
-        <v>12.99</v>
+        <v>6.94</v>
       </c>
       <c r="F209">
-        <v>12.99</v>
+        <v>83.28</v>
       </c>
       <c r="G209">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>400</v>
@@ -8230,25 +8299,25 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B210" t="s">
         <v>167</v>
       </c>
       <c r="C210" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
       </c>
       <c r="E210" s="4">
-        <v>12.99</v>
+        <v>6.94</v>
       </c>
       <c r="F210">
-        <v>12.99</v>
+        <v>83.28</v>
       </c>
       <c r="G210">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>400</v>
@@ -8259,25 +8328,25 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B211" t="s">
         <v>167</v>
       </c>
       <c r="C211" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D211" t="s">
         <v>184</v>
       </c>
       <c r="E211" s="4">
-        <v>0.41</v>
+        <v>3.96</v>
       </c>
       <c r="F211">
-        <v>25.58</v>
+        <v>118.8</v>
       </c>
       <c r="G211">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>400</v>
@@ -8288,25 +8357,25 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B212" t="s">
         <v>167</v>
       </c>
       <c r="C212" t="s">
-        <v>177</v>
+        <v>396</v>
       </c>
       <c r="D212" t="s">
         <v>184</v>
       </c>
       <c r="E212" s="4">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="F212">
-        <v>23.85</v>
+        <v>26.64</v>
       </c>
       <c r="G212">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>400</v>
@@ -8317,25 +8386,25 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B213" t="s">
         <v>167</v>
       </c>
       <c r="C213" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D213" t="s">
         <v>184</v>
       </c>
       <c r="E213" s="4">
-        <v>3.82</v>
+        <v>0.93</v>
       </c>
       <c r="F213">
-        <v>61.12</v>
+        <v>29.8</v>
       </c>
       <c r="G213">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>400</v>
@@ -8346,25 +8415,25 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B214" t="s">
         <v>167</v>
       </c>
       <c r="C214" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D214" t="s">
         <v>184</v>
       </c>
       <c r="E214" s="4">
-        <v>3.82</v>
+        <v>12.99</v>
       </c>
       <c r="F214">
-        <v>61.12</v>
+        <v>12.99</v>
       </c>
       <c r="G214">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>400</v>
@@ -8375,25 +8444,25 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B215" t="s">
         <v>167</v>
       </c>
       <c r="C215" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D215" t="s">
         <v>184</v>
       </c>
       <c r="E215" s="4">
-        <v>3.82</v>
+        <v>12.99</v>
       </c>
       <c r="F215">
-        <v>61.12</v>
+        <v>12.99</v>
       </c>
       <c r="G215">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>400</v>
@@ -8404,25 +8473,25 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B216" t="s">
         <v>167</v>
       </c>
       <c r="C216" t="s">
-        <v>386</v>
+        <v>175</v>
       </c>
       <c r="D216" t="s">
         <v>184</v>
       </c>
       <c r="E216" s="4">
-        <v>0.61</v>
+        <v>12.99</v>
       </c>
       <c r="F216">
-        <v>25.68</v>
+        <v>12.99</v>
       </c>
       <c r="G216">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>400</v>
@@ -8433,25 +8502,25 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B217" t="s">
         <v>167</v>
       </c>
       <c r="C217" t="s">
-        <v>387</v>
+        <v>176</v>
       </c>
       <c r="D217" t="s">
         <v>184</v>
       </c>
       <c r="E217" s="4">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="F217">
-        <v>25.68</v>
+        <v>25.58</v>
       </c>
       <c r="G217">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>400</v>
@@ -8462,25 +8531,25 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B218" t="s">
         <v>167</v>
       </c>
       <c r="C218" t="s">
-        <v>388</v>
+        <v>177</v>
       </c>
       <c r="D218" t="s">
         <v>184</v>
       </c>
       <c r="E218" s="4">
-        <v>0.61</v>
+        <v>0.43</v>
       </c>
       <c r="F218">
-        <v>25.68</v>
+        <v>23.85</v>
       </c>
       <c r="G218">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>400</v>
@@ -8491,25 +8560,25 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B219" t="s">
         <v>167</v>
       </c>
       <c r="C219" t="s">
-        <v>389</v>
+        <v>178</v>
       </c>
       <c r="D219" t="s">
         <v>184</v>
       </c>
       <c r="E219" s="4">
-        <v>1.58</v>
+        <v>3.82</v>
       </c>
       <c r="F219">
-        <v>38.15</v>
+        <v>61.12</v>
       </c>
       <c r="G219">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>400</v>
@@ -8520,25 +8589,25 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B220" t="s">
         <v>167</v>
       </c>
       <c r="C220" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D220" t="s">
         <v>184</v>
       </c>
       <c r="E220" s="4">
-        <v>6.94</v>
+        <v>3.82</v>
       </c>
       <c r="F220">
-        <v>173.5</v>
+        <v>61.12</v>
       </c>
       <c r="G220">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>400</v>
@@ -8549,25 +8618,25 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B221" t="s">
         <v>167</v>
       </c>
       <c r="C221" t="s">
-        <v>390</v>
+        <v>180</v>
       </c>
       <c r="D221" t="s">
         <v>184</v>
       </c>
       <c r="E221" s="4">
-        <v>0.59</v>
+        <v>3.82</v>
       </c>
       <c r="F221">
-        <v>35.76</v>
+        <v>61.12</v>
       </c>
       <c r="G221">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>400</v>
@@ -8578,25 +8647,25 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B222" t="s">
         <v>167</v>
       </c>
       <c r="C222" t="s">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="D222" t="s">
         <v>184</v>
       </c>
       <c r="E222" s="4">
-        <v>13.68</v>
+        <v>0.61</v>
       </c>
       <c r="F222">
-        <v>164.16</v>
+        <v>25.68</v>
       </c>
       <c r="G222">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>400</v>
@@ -8607,25 +8676,25 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B223" t="s">
         <v>167</v>
       </c>
       <c r="C223" t="s">
-        <v>183</v>
+        <v>387</v>
       </c>
       <c r="D223" t="s">
         <v>184</v>
       </c>
       <c r="E223" s="4">
-        <v>15.13</v>
+        <v>0.61</v>
       </c>
       <c r="F223">
-        <v>181.56</v>
+        <v>25.68</v>
       </c>
       <c r="G223">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>400</v>
@@ -8636,225 +8705,225 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>318</v>
+        <v>161</v>
       </c>
       <c r="B224" t="s">
         <v>167</v>
       </c>
-      <c r="C224" s="2" t="s">
-        <v>186</v>
+      <c r="C224" t="s">
+        <v>388</v>
       </c>
       <c r="D224" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E224" s="4">
-        <v>1.87</v>
-      </c>
-      <c r="F224" s="3">
-        <v>56</v>
-      </c>
-      <c r="G224" s="4">
-        <v>30</v>
+        <v>0.61</v>
+      </c>
+      <c r="F224">
+        <v>25.68</v>
+      </c>
+      <c r="G224">
+        <v>42</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I224" s="14">
-        <v>16</v>
+        <v>400</v>
+      </c>
+      <c r="I224" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>319</v>
+        <v>162</v>
       </c>
       <c r="B225" t="s">
         <v>167</v>
       </c>
-      <c r="C225" s="5" t="s">
-        <v>385</v>
+      <c r="C225" t="s">
+        <v>389</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E225" s="4">
-        <v>4.75</v>
-      </c>
-      <c r="F225" s="3">
-        <v>95</v>
-      </c>
-      <c r="G225" s="4">
-        <v>20</v>
+        <v>1.58</v>
+      </c>
+      <c r="F225">
+        <v>38.15</v>
+      </c>
+      <c r="G225">
+        <v>24</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I225" s="14">
-        <v>27</v>
+        <v>400</v>
+      </c>
+      <c r="I225" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>320</v>
+        <v>163</v>
       </c>
       <c r="B226" t="s">
         <v>167</v>
       </c>
-      <c r="C226" s="2" t="s">
-        <v>187</v>
+      <c r="C226" t="s">
+        <v>181</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E226" s="4">
-        <v>2</v>
-      </c>
-      <c r="F226" s="3">
-        <v>44</v>
-      </c>
-      <c r="G226" s="4">
-        <v>22</v>
+        <v>6.94</v>
+      </c>
+      <c r="F226">
+        <v>173.5</v>
+      </c>
+      <c r="G226">
+        <v>25</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I226" s="14">
-        <v>12</v>
+        <v>400</v>
+      </c>
+      <c r="I226" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>321</v>
+        <v>164</v>
       </c>
       <c r="B227" t="s">
         <v>167</v>
       </c>
-      <c r="C227" s="2" t="s">
-        <v>188</v>
+      <c r="C227" t="s">
+        <v>390</v>
       </c>
       <c r="D227" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E227" s="4">
-        <v>2</v>
-      </c>
-      <c r="F227" s="3">
-        <v>44</v>
-      </c>
-      <c r="G227" s="4">
-        <v>22</v>
+        <v>0.59</v>
+      </c>
+      <c r="F227">
+        <v>35.76</v>
+      </c>
+      <c r="G227">
+        <v>60</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I227" s="14">
-        <v>12</v>
+        <v>400</v>
+      </c>
+      <c r="I227" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>322</v>
+        <v>165</v>
       </c>
       <c r="B228" t="s">
         <v>167</v>
       </c>
-      <c r="C228" s="2" t="s">
-        <v>189</v>
+      <c r="C228" t="s">
+        <v>182</v>
       </c>
       <c r="D228" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E228" s="4">
-        <v>2.6</v>
-      </c>
-      <c r="F228" s="3">
-        <v>52</v>
-      </c>
-      <c r="G228" s="4">
-        <v>20</v>
+        <v>13.68</v>
+      </c>
+      <c r="F228">
+        <v>164.16</v>
+      </c>
+      <c r="G228">
+        <v>12</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I228" s="14">
-        <v>14</v>
+        <v>400</v>
+      </c>
+      <c r="I228" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
       <c r="B229" t="s">
         <v>167</v>
       </c>
-      <c r="C229" s="2" t="s">
-        <v>190</v>
+      <c r="C229" t="s">
+        <v>183</v>
       </c>
       <c r="D229" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E229" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="F229" s="3">
-        <v>56</v>
-      </c>
-      <c r="G229" s="4">
-        <v>20</v>
+        <v>15.13</v>
+      </c>
+      <c r="F229">
+        <v>181.56</v>
+      </c>
+      <c r="G229">
+        <v>12</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I229" s="14">
-        <v>18</v>
+        <v>400</v>
+      </c>
+      <c r="I229" s="13">
+        <v>0.05</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B230" t="s">
         <v>167</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D230" t="s">
         <v>185</v>
       </c>
       <c r="E230" s="4">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="F230" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G230" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I230" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B231" t="s">
         <v>167</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>192</v>
+      <c r="C231" s="5" t="s">
+        <v>385</v>
       </c>
       <c r="D231" t="s">
         <v>185</v>
       </c>
       <c r="E231" s="4">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="F231" s="3">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="G231" s="4">
         <v>20</v>
@@ -8863,85 +8932,85 @@
         <v>399</v>
       </c>
       <c r="I231" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B232" t="s">
         <v>167</v>
       </c>
-      <c r="C232" s="5" t="s">
-        <v>193</v>
+      <c r="C232" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="D232" t="s">
         <v>185</v>
       </c>
       <c r="E232" s="4">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="F232" s="3">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G232" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I232" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="B233" t="s">
         <v>167</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D233" t="s">
         <v>185</v>
       </c>
       <c r="E233" s="4">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="F233" s="3">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G233" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I233" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B234" t="s">
         <v>167</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D234" t="s">
         <v>185</v>
       </c>
       <c r="E234" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="F234" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G234" s="4">
         <v>20</v>
@@ -8950,27 +9019,27 @@
         <v>399</v>
       </c>
       <c r="I234" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B235" t="s">
         <v>167</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D235" t="s">
         <v>185</v>
       </c>
       <c r="E235" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="F235" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G235" s="4">
         <v>20</v>
@@ -8979,18 +9048,18 @@
         <v>399</v>
       </c>
       <c r="I235" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B236" t="s">
         <v>167</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -8999,10 +9068,10 @@
         <v>2.5</v>
       </c>
       <c r="F236" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G236" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>399</v>
@@ -9013,112 +9082,112 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B237" t="s">
         <v>167</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D237" t="s">
         <v>185</v>
       </c>
       <c r="E237" s="4">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F237" s="3">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="G237" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I237" s="14">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B238" t="s">
         <v>167</v>
       </c>
-      <c r="C238" s="2" t="s">
-        <v>199</v>
+      <c r="C238" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="D238" t="s">
         <v>185</v>
       </c>
       <c r="E238" s="4">
-        <v>13.67</v>
+        <v>2.34</v>
       </c>
       <c r="F238" s="3">
-        <v>205</v>
+        <v>56</v>
       </c>
       <c r="G238" s="4">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I238" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B239" t="s">
         <v>167</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D239" t="s">
         <v>185</v>
       </c>
       <c r="E239" s="4">
-        <v>1.4</v>
+        <v>2.34</v>
       </c>
       <c r="F239" s="3">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G239" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I239" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B240" t="s">
         <v>167</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D240" t="s">
         <v>185</v>
       </c>
       <c r="E240" s="4">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F240" s="3">
         <v>44</v>
       </c>
       <c r="G240" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>399</v>
@@ -9129,25 +9198,25 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B241" t="s">
         <v>167</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D241" t="s">
         <v>185</v>
       </c>
       <c r="E241" s="4">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F241" s="3">
         <v>44</v>
       </c>
       <c r="G241" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>399</v>
@@ -9158,80 +9227,80 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B242" t="s">
         <v>167</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
       </c>
       <c r="E242" s="4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F242" s="3">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="G242" s="4">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I242" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B243" t="s">
         <v>167</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D243" t="s">
         <v>185</v>
       </c>
       <c r="E243" s="4">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="F243" s="3">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="G243" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I243" s="14">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B244" t="s">
         <v>167</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
       </c>
       <c r="E244" s="4">
-        <v>3.67</v>
+        <v>13.67</v>
       </c>
       <c r="F244" s="3">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="G244" s="4">
         <v>15</v>
@@ -9240,172 +9309,172 @@
         <v>399</v>
       </c>
       <c r="I244" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B245" t="s">
         <v>167</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D245" t="s">
         <v>185</v>
       </c>
       <c r="E245" s="4">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="F245" s="3">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G245" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I245" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B246" t="s">
         <v>167</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D246" t="s">
         <v>185</v>
       </c>
       <c r="E246" s="4">
-        <v>3.08</v>
+        <v>2</v>
       </c>
       <c r="F246" s="3">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="G246" s="4">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I246" s="14">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B247" t="s">
         <v>167</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
       </c>
       <c r="E247" s="4">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="F247" s="3">
         <v>44</v>
       </c>
       <c r="G247" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I247" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B248" t="s">
         <v>167</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
       </c>
       <c r="E248" s="4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="F248" s="3">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G248" s="4">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I248" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B249" t="s">
         <v>167</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D249" t="s">
         <v>185</v>
       </c>
       <c r="E249" s="4">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="F249" s="3">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G249" s="4">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I249" s="14">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B250" t="s">
         <v>167</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>361</v>
+        <v>205</v>
       </c>
       <c r="D250" t="s">
         <v>185</v>
       </c>
       <c r="E250" s="4">
-        <v>5.14</v>
+        <v>3.67</v>
       </c>
       <c r="F250" s="3">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G250" s="4">
         <v>15</v>
@@ -9419,22 +9488,22 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B251" t="s">
         <v>167</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>360</v>
+        <v>206</v>
       </c>
       <c r="D251" t="s">
         <v>185</v>
       </c>
       <c r="E251" s="4">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="F251" s="3">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G251" s="4">
         <v>15</v>
@@ -9443,134 +9512,134 @@
         <v>399</v>
       </c>
       <c r="I251" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B252" t="s">
         <v>167</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>359</v>
+        <v>207</v>
       </c>
       <c r="D252" t="s">
         <v>185</v>
       </c>
       <c r="E252" s="4">
-        <v>5.14</v>
+        <v>3.08</v>
       </c>
       <c r="F252" s="3">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="G252" s="4">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I252" s="14">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B253" t="s">
         <v>167</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>358</v>
+        <v>208</v>
       </c>
       <c r="D253" t="s">
         <v>185</v>
       </c>
       <c r="E253" s="4">
-        <v>5.14</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F253" s="3">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="G253" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I253" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B254" t="s">
         <v>167</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>357</v>
+        <v>209</v>
       </c>
       <c r="D254" t="s">
         <v>185</v>
       </c>
       <c r="E254" s="4">
-        <v>5.14</v>
+        <v>1.98</v>
       </c>
       <c r="F254" s="3">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G254" s="4">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I254" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B255" t="s">
         <v>167</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>356</v>
+        <v>210</v>
       </c>
       <c r="D255" t="s">
         <v>185</v>
       </c>
       <c r="E255" s="4">
-        <v>5.14</v>
+        <v>1.26</v>
       </c>
       <c r="F255" s="3">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="G255" s="4">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I255" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B256" t="s">
         <v>167</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D256" t="s">
         <v>185</v>
@@ -9593,146 +9662,320 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B257" t="s">
         <v>167</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D257" t="s">
         <v>185</v>
       </c>
       <c r="E257" s="4">
-        <v>108</v>
+        <v>5.14</v>
       </c>
       <c r="F257" s="3">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="G257" s="4">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I257" s="14">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B258" t="s">
         <v>167</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D258" t="s">
         <v>185</v>
       </c>
       <c r="E258" s="4">
-        <v>2.44</v>
+        <v>5.14</v>
       </c>
       <c r="F258" s="3">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G258" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I258" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B259" t="s">
         <v>167</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D259" t="s">
         <v>185</v>
       </c>
       <c r="E259" s="4">
-        <v>9.5</v>
+        <v>5.14</v>
       </c>
       <c r="F259" s="3">
-        <v>9.5</v>
+        <v>77</v>
       </c>
       <c r="G259" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I259" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B260" t="s">
         <v>167</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D260" t="s">
         <v>185</v>
       </c>
       <c r="E260" s="4">
-        <v>2.56</v>
+        <v>5.14</v>
       </c>
       <c r="F260" s="3">
         <v>77</v>
       </c>
       <c r="G260" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I260" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="B261" t="s">
-        <v>393</v>
+        <v>167</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="D261" t="s">
-        <v>395</v>
+        <v>185</v>
       </c>
       <c r="E261" s="4">
-        <v>50</v>
+        <v>5.14</v>
       </c>
       <c r="F261" s="3">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G261" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>399</v>
       </c>
       <c r="I261" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B262" t="s">
+        <v>167</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D262" t="s">
+        <v>185</v>
+      </c>
+      <c r="E262" s="4">
+        <v>5.14</v>
+      </c>
+      <c r="F262" s="3">
+        <v>77</v>
+      </c>
+      <c r="G262" s="4">
+        <v>15</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I262" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B263" t="s">
+        <v>167</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D263" t="s">
+        <v>185</v>
+      </c>
+      <c r="E263" s="4">
+        <v>108</v>
+      </c>
+      <c r="F263" s="3">
+        <v>108</v>
+      </c>
+      <c r="G263" s="4">
+        <v>24</v>
+      </c>
+      <c r="H263" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I263" s="14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B264" t="s">
+        <v>167</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D264" t="s">
+        <v>185</v>
+      </c>
+      <c r="E264" s="4">
+        <v>2.44</v>
+      </c>
+      <c r="F264" s="3">
+        <v>73</v>
+      </c>
+      <c r="G264" s="4">
+        <v>30</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I264" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B265" t="s">
+        <v>167</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D265" t="s">
+        <v>185</v>
+      </c>
+      <c r="E265" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="F265" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G265" s="4">
+        <v>1</v>
+      </c>
+      <c r="H265" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I265" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B266" t="s">
+        <v>167</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D266" t="s">
+        <v>185</v>
+      </c>
+      <c r="E266" s="4">
+        <v>2.56</v>
+      </c>
+      <c r="F266" s="3">
+        <v>77</v>
+      </c>
+      <c r="G266" s="4">
+        <v>30</v>
+      </c>
+      <c r="H266" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I266" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B267" t="s">
+        <v>393</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D267" t="s">
+        <v>395</v>
+      </c>
+      <c r="E267" s="4">
+        <v>50</v>
+      </c>
+      <c r="F267" s="3">
+        <v>50</v>
+      </c>
+      <c r="G267" s="4">
+        <v>6</v>
+      </c>
+      <c r="H267" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I267" s="14">
         <v>10</v>
       </c>
     </row>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C22E6C5-1D0A-47F6-BA1E-6F6A9867EFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE86DC-19A1-4AA1-BA55-55F1E6809660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="423">
   <si>
     <t>categoria</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Erv SP270 500g Erva Mate Menta Boldo</t>
-  </si>
-  <si>
-    <t>Pet</t>
   </si>
   <si>
     <t>Prime Full</t>
@@ -1381,6 +1378,805 @@
   <si>
     <t>PRIME FULL PEITORAL E GUIA P/ CAES SEDA AMERICANA  C/20UN</t>
   </si>
+  <si>
+    <t>Pet Var</t>
+  </si>
+  <si>
+    <t>20182P</t>
+  </si>
+  <si>
+    <t>20236P</t>
+  </si>
+  <si>
+    <t>20328P</t>
+  </si>
+  <si>
+    <t>20243P</t>
+  </si>
+  <si>
+    <t>20205P</t>
+  </si>
+  <si>
+    <t>20250P</t>
+  </si>
+  <si>
+    <t>20212P</t>
+  </si>
+  <si>
+    <t>20267P</t>
+  </si>
+  <si>
+    <t>20366P</t>
+  </si>
+  <si>
+    <t>20403P</t>
+  </si>
+  <si>
+    <t>20410P</t>
+  </si>
+  <si>
+    <t>20441P</t>
+  </si>
+  <si>
+    <t>20496P</t>
+  </si>
+  <si>
+    <t>20540P</t>
+  </si>
+  <si>
+    <t>20458P</t>
+  </si>
+  <si>
+    <t>20502P</t>
+  </si>
+  <si>
+    <t>20557P</t>
+  </si>
+  <si>
+    <t>20465P</t>
+  </si>
+  <si>
+    <t>20519P</t>
+  </si>
+  <si>
+    <t>20564P</t>
+  </si>
+  <si>
+    <t>20472P</t>
+  </si>
+  <si>
+    <t>20526P</t>
+  </si>
+  <si>
+    <t>20489P</t>
+  </si>
+  <si>
+    <t>20533P</t>
+  </si>
+  <si>
+    <t>20588P</t>
+  </si>
+  <si>
+    <t>20618P</t>
+  </si>
+  <si>
+    <t>20625P</t>
+  </si>
+  <si>
+    <t>20656P</t>
+  </si>
+  <si>
+    <t>20595P</t>
+  </si>
+  <si>
+    <t>20632P</t>
+  </si>
+  <si>
+    <t>20601P</t>
+  </si>
+  <si>
+    <t>20649P</t>
+  </si>
+  <si>
+    <t>20687P</t>
+  </si>
+  <si>
+    <t>20694P</t>
+  </si>
+  <si>
+    <t>20700P</t>
+  </si>
+  <si>
+    <t>20717P</t>
+  </si>
+  <si>
+    <t>20724P</t>
+  </si>
+  <si>
+    <t>22049P</t>
+  </si>
+  <si>
+    <t>22056P</t>
+  </si>
+  <si>
+    <t>20809P</t>
+  </si>
+  <si>
+    <t>20816P</t>
+  </si>
+  <si>
+    <t>20823P</t>
+  </si>
+  <si>
+    <t>20830P</t>
+  </si>
+  <si>
+    <t>20847P</t>
+  </si>
+  <si>
+    <t>20854P</t>
+  </si>
+  <si>
+    <t>20861P</t>
+  </si>
+  <si>
+    <t>20878P</t>
+  </si>
+  <si>
+    <t>20960P</t>
+  </si>
+  <si>
+    <t>20984P</t>
+  </si>
+  <si>
+    <t>20977P</t>
+  </si>
+  <si>
+    <t>20991P</t>
+  </si>
+  <si>
+    <t>21059P</t>
+  </si>
+  <si>
+    <t>21066P</t>
+  </si>
+  <si>
+    <t>21073P</t>
+  </si>
+  <si>
+    <t>21080P</t>
+  </si>
+  <si>
+    <t>21097P</t>
+  </si>
+  <si>
+    <t>21103P</t>
+  </si>
+  <si>
+    <t>21141P</t>
+  </si>
+  <si>
+    <t>21158P</t>
+  </si>
+  <si>
+    <t>21165P</t>
+  </si>
+  <si>
+    <t>21172P</t>
+  </si>
+  <si>
+    <t>21189P</t>
+  </si>
+  <si>
+    <t>21196P</t>
+  </si>
+  <si>
+    <t>21202P</t>
+  </si>
+  <si>
+    <t>21424P</t>
+  </si>
+  <si>
+    <t>21431P</t>
+  </si>
+  <si>
+    <t>21448P</t>
+  </si>
+  <si>
+    <t>21462P</t>
+  </si>
+  <si>
+    <t>21479P</t>
+  </si>
+  <si>
+    <t>21486P</t>
+  </si>
+  <si>
+    <t>21493P</t>
+  </si>
+  <si>
+    <t>21509P</t>
+  </si>
+  <si>
+    <t>21516P</t>
+  </si>
+  <si>
+    <t>21523P</t>
+  </si>
+  <si>
+    <t>22162P</t>
+  </si>
+  <si>
+    <t>21530P</t>
+  </si>
+  <si>
+    <t>22155P</t>
+  </si>
+  <si>
+    <t>21547P</t>
+  </si>
+  <si>
+    <t>21554P</t>
+  </si>
+  <si>
+    <t>22094P</t>
+  </si>
+  <si>
+    <t>21561P</t>
+  </si>
+  <si>
+    <t>21578P</t>
+  </si>
+  <si>
+    <t>21585P</t>
+  </si>
+  <si>
+    <t>21592P</t>
+  </si>
+  <si>
+    <t>21608P</t>
+  </si>
+  <si>
+    <t>22421P</t>
+  </si>
+  <si>
+    <t>22438P</t>
+  </si>
+  <si>
+    <t>22353P</t>
+  </si>
+  <si>
+    <t>22360P</t>
+  </si>
+  <si>
+    <t>22377P</t>
+  </si>
+  <si>
+    <t>22414P</t>
+  </si>
+  <si>
+    <t>21714P</t>
+  </si>
+  <si>
+    <t>22186P</t>
+  </si>
+  <si>
+    <t>22339P</t>
+  </si>
+  <si>
+    <t>22346P</t>
+  </si>
+  <si>
+    <t>21721P</t>
+  </si>
+  <si>
+    <t>22391P</t>
+  </si>
+  <si>
+    <t>22407P</t>
+  </si>
+  <si>
+    <t>21745P</t>
+  </si>
+  <si>
+    <t>21752P</t>
+  </si>
+  <si>
+    <t>21776P</t>
+  </si>
+  <si>
+    <t>21783P</t>
+  </si>
+  <si>
+    <t>21790P</t>
+  </si>
+  <si>
+    <t>22315P</t>
+  </si>
+  <si>
+    <t>21844P</t>
+  </si>
+  <si>
+    <t>21899P</t>
+  </si>
+  <si>
+    <t>Pet Shop</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PRIME FULL ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO -                                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   PROMOÇÃO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PRIME FULL ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">      PROMOÇÃO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL ALIM.PREM. ESP. P/CÃES RPM CARNE E FRANGO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL ALIM.PREM. ESP.P/CÃES AD. CARNE E FRANGO          </t>
+  </si>
+  <si>
+    <t>PRIME FULL ALIM. PREM. ESP. P/ GATOS ADULTO MIX CARNE E FRANGO</t>
+  </si>
+  <si>
+    <t>PRIME FULL ALIM. PREM. ESP. P/ GATOS FILHOTE CARNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL ALIM. PREM. ESP. P/ GATOS CASTRADO SALMÃO </t>
+  </si>
+  <si>
+    <t>HONEY PET ALIM. PREM. P/CÃES AD.CARNE E FRANGO                            PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>HONEY PET ALIM. PREM. P/CÃES RPM CARNE E FRANGO                         PROMOÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONEY PET ALIM. PREM. P/CÃES AD.CARNE E FRANGO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONEY PET ALIM. PREM. P/CÃES RPM CARNE E FRANGO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONEY PET ALIM. PREM. P/CÃES AD.CARNE E FRANGO </t>
+  </si>
+  <si>
+    <r>
+      <t>HONEY PET ALIM. PREM. P/CÃES FILH.CARNE E FRANGO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HONEY PET ALIM. PREM. P/GATOS CARNE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                          PROMOÇÃO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HONEY PET ALIM. PREM. P/GATOS CAST.CARNE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                            PROMOÇÃO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>PITZ PET ALIM. PREMIUM. P/CÃES AD.CARNE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                          </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PITZ PET ALIM. PREMIUM. P/CÃES AD.CARNE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                           </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PITZ PET ALIM. PREMIUM. P/CÃES AD.CARNE </t>
+  </si>
+  <si>
+    <t>PITZ PET ALIM. PREMIUM. P/CÃES AD.CARNE</t>
+  </si>
+  <si>
+    <t>PRIME FULL SNACK P/ GATOS PEIXE                                                                    PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>PRIME FULL SNACK P/ GATOS CARNE                                                                 PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>HONEY PET BIFINHO  P/ CÃES ADULTO CARNE                                                    PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>HONEY PET BIFINHO  P/ CÃES PQ. PORTE CARNE                                               PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>HONEY PET BISCOITOS P/ CÃES ADULTO INTEGRAL                                          PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>HONEY PET BISCOITOS P/ CÃES MINI INTEGRAL                                                PROMOÇÃO</t>
+  </si>
+  <si>
+    <r>
+      <t>PRIME FULL OSSO NO P/ CAES N 2/3  C/3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    45G          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                           </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PRIME FULL OSSO NO P/ CAES N 3/4 C/2    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 45G </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                           </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PRIME FULL OSSO NO P/ CAES N 4/5 C/1    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 45G</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                        </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL OSSO NO P/ CAES N 5/6 C/1                              60G                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL OSSO NO P/ CAES N 6/7 C/1                               80G                                                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL OSSO NO P/ CAES N 7/8 C/1                             110G                                                                                   </t>
+  </si>
+  <si>
+    <t>HONEY PET AREIA SANITÁRIA P/ GATOS - 4KG                                                PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>HONEY PET  AREIA SANITÁRIA PERFUMADA P/ GATOS - 4KG                      PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>SHAMPOO CONDICIONADOR ANTIPULGAS/CARRAPATOS  -500ML (LANÇAMENTO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIME FULL BRINQUEDO P/ CÃES ADESTRADOG M                                   PROMOÇÃO             </t>
+  </si>
+  <si>
+    <r>
+      <t>PRIME FULL  BRINQUEDO P/ CAES BRINQFULL P</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                      PROMOÇÃO                        </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PRIME FULL  BRINQUEDO P/ CAES BRINQFULL M   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                  PROMOÇÃO                            </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>PRIME FULL BRINQUEDO CAO GALINHA COLORIDA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PROMOÇÃO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PRIME FULL  BRINQUEDO P/ GATOS M            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PROMOÇÃO</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1389,7 +2185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1554,6 +2350,19 @@
       <b/>
       <sz val="14"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2273,14 +3082,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:J195"/>
+  <dimension ref="A1:J303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="108.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -2309,18 +3118,18 @@
         <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" t="s">
         <v>174</v>
       </c>
-      <c r="I1" t="s">
-        <v>175</v>
-      </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -2341,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I2">
         <v>3.3</v>
@@ -2352,7 +3161,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -2373,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I3">
         <v>3.3</v>
@@ -2384,7 +3193,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -2405,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I4">
         <v>3.3</v>
@@ -2416,7 +3225,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -2437,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I5">
         <v>3.3</v>
@@ -2448,7 +3257,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -2469,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I6">
         <v>3.3</v>
@@ -2480,7 +3289,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -2501,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I7">
         <v>3.3</v>
@@ -2512,7 +3321,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -2533,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I8">
         <v>3.3</v>
@@ -2544,7 +3353,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
@@ -2565,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I9">
         <v>3.3</v>
@@ -2576,13 +3385,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -2597,7 +3406,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I10">
         <v>3.3</v>
@@ -2611,13 +3420,13 @@
         <v>20182</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1">
         <v>11.040353499252712</v>
@@ -2629,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I11" s="1">
         <v>0.03</v>
@@ -2641,13 +3450,13 @@
         <v>20236</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1">
         <v>11.040353499252712</v>
@@ -2659,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I12" s="1">
         <v>0.03</v>
@@ -2671,13 +3480,13 @@
         <v>20328</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1">
         <v>11.69016830203392</v>
@@ -2689,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I13" s="1">
         <v>0.03</v>
@@ -2701,13 +3510,13 @@
         <v>20199</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1">
         <v>22.015846213793999</v>
@@ -2719,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I14" s="1">
         <v>0.03</v>
@@ -2731,13 +3540,13 @@
         <v>20243</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1">
         <v>22.015846213793999</v>
@@ -2749,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I15" s="1">
         <v>0.03</v>
@@ -2761,13 +3570,13 @@
         <v>20205</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1">
         <v>41.932096604830235</v>
@@ -2779,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I16" s="1">
         <v>0.03</v>
@@ -2790,13 +3599,13 @@
         <v>20250</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1">
         <v>41.932096604830235</v>
@@ -2808,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I17" s="1">
         <v>0.03</v>
@@ -2819,13 +3628,13 @@
         <v>20212</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="1">
         <v>62.933146657332863</v>
@@ -2837,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I18" s="1">
         <v>0.03</v>
@@ -2848,13 +3657,13 @@
         <v>20267</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="1">
         <v>62.933146657332863</v>
@@ -2866,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I19" s="1">
         <v>0.03</v>
@@ -2877,13 +3686,13 @@
         <v>20366</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1">
         <v>12.332770489673981</v>
@@ -2895,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I20" s="1">
         <v>0.03</v>
@@ -2906,13 +3715,13 @@
         <v>20403</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1">
         <v>12.332770489673981</v>
@@ -2924,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I21" s="1">
         <v>0.03</v>
@@ -2935,13 +3744,13 @@
         <v>20410</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1">
         <v>12.332770489673981</v>
@@ -2953,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I22" s="1">
         <v>0.03</v>
@@ -2964,13 +3773,13 @@
         <v>20441</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1">
         <v>10.384465515001947</v>
@@ -2982,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I23" s="1">
         <v>0.03</v>
@@ -2993,13 +3802,13 @@
         <v>20496</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1">
         <v>10.384465515001947</v>
@@ -3011,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I24" s="1">
         <v>0.03</v>
@@ -3022,13 +3831,13 @@
         <v>20540</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1">
         <v>10.384465515001947</v>
@@ -3040,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I25" s="1">
         <v>0.03</v>
@@ -3051,13 +3860,13 @@
         <v>20458</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" s="1">
         <v>21.366411222236653</v>
@@ -3069,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I26" s="1">
         <v>0.03</v>
@@ -3080,13 +3889,13 @@
         <v>20502</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E27" s="1">
         <v>21.366411222236653</v>
@@ -3098,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I27" s="1">
         <v>0.03</v>
@@ -3109,13 +3918,13 @@
         <v>20557</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1">
         <v>22.015846213793999</v>
@@ -3127,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I28" s="1">
         <v>0.03</v>
@@ -3138,13 +3947,13 @@
         <v>20465</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" s="1">
         <v>34.931746587329364</v>
@@ -3156,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I29" s="1">
         <v>0.03</v>
@@ -3167,13 +3976,13 @@
         <v>20519</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" s="1">
         <v>34.931746587329364</v>
@@ -3185,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I30" s="1">
         <v>0.03</v>
@@ -3196,13 +4005,13 @@
         <v>20564</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E31" s="1">
         <v>41.932096604830235</v>
@@ -3214,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I31" s="1">
         <v>0.03</v>
@@ -3225,13 +4034,13 @@
         <v>20472</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E32" s="1">
         <v>55.932796639831992</v>
@@ -3243,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I32" s="1">
         <v>0.03</v>
@@ -3254,13 +4063,13 @@
         <v>20526</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E33" s="1">
         <v>55.932796639831992</v>
@@ -3272,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I33" s="1">
         <v>0.03</v>
@@ -3283,13 +4092,13 @@
         <v>20489</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E34" s="1">
         <v>76.933846692334612</v>
@@ -3301,7 +4110,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I34" s="1">
         <v>0.03</v>
@@ -3312,13 +4121,13 @@
         <v>20533</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E35" s="1">
         <v>76.933846692334612</v>
@@ -3330,7 +4139,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I35" s="1">
         <v>0.03</v>
@@ -3341,13 +4150,13 @@
         <v>20588</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E36" s="1">
         <v>11.040353499252712</v>
@@ -3359,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I36" s="1">
         <v>0.03</v>
@@ -3370,13 +4179,13 @@
         <v>20618</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1">
         <v>11.040353499252712</v>
@@ -3388,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I37" s="1">
         <v>0.03</v>
@@ -3399,13 +4208,13 @@
         <v>20625</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E38" s="1">
         <v>11.040353499252712</v>
@@ -3417,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I38" s="1">
         <v>0.03</v>
@@ -3428,13 +4237,13 @@
         <v>20656</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E39" s="1">
         <v>11.040353499252712</v>
@@ -3446,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I39" s="1">
         <v>0.03</v>
@@ -3457,13 +4266,13 @@
         <v>20595</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E40" s="1">
         <v>22.665281205351341</v>
@@ -3475,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I40" s="1">
         <v>0.03</v>
@@ -3486,13 +4295,13 @@
         <v>20632</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" s="1">
         <v>22.665281205351341</v>
@@ -3504,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I41" s="1">
         <v>0.03</v>
@@ -3515,13 +4324,13 @@
         <v>20601</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E42" s="1">
         <v>76.933846692334612</v>
@@ -3533,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I42" s="1">
         <v>0.03</v>
@@ -3544,13 +4353,13 @@
         <v>20649</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E43" s="1">
         <v>76.933846692334612</v>
@@ -3562,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I43" s="1">
         <v>0.03</v>
@@ -3573,13 +4382,13 @@
         <v>20663</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E44" s="1">
         <v>9.0855955318872574</v>
@@ -3591,7 +4400,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I44" s="1">
         <v>0.03</v>
@@ -3602,13 +4411,13 @@
         <v>20670</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E45" s="1">
         <v>16.889784247465556</v>
@@ -3620,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I45" s="1">
         <v>0.03</v>
@@ -3631,13 +4440,13 @@
         <v>20687</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E46" s="1">
         <v>27.92748652621264</v>
@@ -3649,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I46" s="1">
         <v>0.03</v>
@@ -3660,13 +4469,13 @@
         <v>20694</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47" s="1">
         <v>32.131606580329013</v>
@@ -3678,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I47" s="1">
         <v>0.03</v>
@@ -3689,13 +4498,13 @@
         <v>20700</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E48" s="1">
         <v>53.13265663283164</v>
@@ -3707,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I48" s="1">
         <v>0.03</v>
@@ -3718,13 +4527,13 @@
         <v>20717</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E49" s="1">
         <v>69.933496674833734</v>
@@ -3736,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I49" s="1">
         <v>0.03</v>
@@ -3747,13 +4556,13 @@
         <v>20724</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E50" s="1">
         <v>82.528349433011343</v>
@@ -3765,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I50" s="1">
         <v>0.03</v>
@@ -3776,13 +4585,13 @@
         <v>22049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" s="1">
         <v>3.5900509439616419</v>
@@ -3794,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I51" s="1">
         <v>0.03</v>
@@ -3805,13 +4614,13 @@
         <v>22056</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E52" s="1">
         <v>3.5900509439616419</v>
@@ -3823,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I52" s="1">
         <v>0.03</v>
@@ -3834,13 +4643,13 @@
         <v>20809</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E53" s="1">
         <v>2.1516332034761758</v>
@@ -3852,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I53" s="1">
         <v>0.03</v>
@@ -3863,13 +4672,13 @@
         <v>20816</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E54" s="1">
         <v>2.1516332034761758</v>
@@ -3881,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I54" s="1">
         <v>0.03</v>
@@ -3892,13 +4701,13 @@
         <v>20823</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E55" s="1">
         <v>2.1516332034761758</v>
@@ -3910,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I55" s="1">
         <v>0.03</v>
@@ -3921,13 +4730,13 @@
         <v>20830</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E56" s="1">
         <v>2.1516332034761758</v>
@@ -3939,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I56" s="1">
         <v>0.03</v>
@@ -3950,13 +4759,13 @@
         <v>20847</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E57" s="1">
         <v>8.3903082643636804</v>
@@ -3968,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I57" s="1">
         <v>0.03</v>
@@ -3979,13 +4788,13 @@
         <v>20854</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E58" s="1">
         <v>8.3903082643636804</v>
@@ -3997,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I58" s="1">
         <v>0.03</v>
@@ -4008,13 +4817,13 @@
         <v>20861</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59" s="1">
         <v>17.940717628705148</v>
@@ -4026,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I59" s="1">
         <v>0.03</v>
@@ -4037,13 +4846,13 @@
         <v>20878</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E60" s="1">
         <v>17.940717628705148</v>
@@ -4055,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I60" s="1">
         <v>0.03</v>
@@ -4066,13 +4875,13 @@
         <v>20960</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E61" s="1">
         <v>5.9334731795025473</v>
@@ -4084,7 +4893,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I61" s="1">
         <v>0.03</v>
@@ -4095,13 +4904,13 @@
         <v>20984</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E62" s="1">
         <v>5.9334731795025473</v>
@@ -4113,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I62" s="1">
         <v>0.03</v>
@@ -4124,13 +4933,13 @@
         <v>20977</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E63" s="1">
         <v>10.789899838061535</v>
@@ -4142,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I63" s="1">
         <v>0.03</v>
@@ -4153,13 +4962,13 @@
         <v>20991</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E64" s="1">
         <v>10.789899838061535</v>
@@ -4171,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I64" s="1">
         <v>0.03</v>
@@ -4182,13 +4991,13 @@
         <v>21059</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E65" s="1">
         <v>2.9907102187593648</v>
@@ -4200,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I65" s="1">
         <v>0.03</v>
@@ -4211,13 +5020,13 @@
         <v>21066</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E66" s="1">
         <v>2.9907102187593648</v>
@@ -4229,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I66" s="1">
         <v>0.03</v>
@@ -4240,13 +5049,13 @@
         <v>21073</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E67" s="1">
         <v>2.9907102187593648</v>
@@ -4258,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I67" s="1">
         <v>0.03</v>
@@ -4269,13 +5078,13 @@
         <v>21080</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E68" s="1">
         <v>5.9334731795025473</v>
@@ -4287,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I68" s="1">
         <v>0.03</v>
@@ -4298,13 +5107,13 @@
         <v>21097</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E69" s="1">
         <v>5.9334731795025473</v>
@@ -4316,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I69" s="1">
         <v>0.03</v>
@@ -4327,13 +5136,13 @@
         <v>21103</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E70" s="1">
         <v>5.9334731795025473</v>
@@ -4345,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I70" s="1">
         <v>0.03</v>
@@ -4356,13 +5165,13 @@
         <v>21141</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E71" s="1">
         <v>11.926880431525321</v>
@@ -4374,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I71" s="1">
         <v>0.03</v>
@@ -4385,13 +5194,13 @@
         <v>21158</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E72" s="1">
         <v>5.9334731795025473</v>
@@ -4403,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I72" s="1">
         <v>0.03</v>
@@ -4414,13 +5223,13 @@
         <v>21165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E73" s="1">
         <v>5.9334731795025473</v>
@@ -4432,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I73" s="1">
         <v>0.03</v>
@@ -4443,13 +5252,13 @@
         <v>21172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E74" s="1">
         <v>5.9334731795025473</v>
@@ -4461,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I74" s="1">
         <v>0.03</v>
@@ -4472,13 +5281,13 @@
         <v>21189</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E75" s="1">
         <v>8.3847767455798614</v>
@@ -4490,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I75" s="1">
         <v>0.03</v>
@@ -4501,13 +5310,13 @@
         <v>21196</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E76" s="1">
         <v>8.9900443804725914</v>
@@ -4519,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I76" s="1">
         <v>0.03</v>
@@ -4530,13 +5339,13 @@
         <v>21202</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E77" s="1">
         <v>9.5903556648473582</v>
@@ -4548,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I77" s="1">
         <v>0.03</v>
@@ -4559,13 +5368,13 @@
         <v>21424</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E78" s="1">
         <v>11.926880431525321</v>
@@ -4577,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I78" s="1">
         <v>0.03</v>
@@ -4588,13 +5397,13 @@
         <v>21431</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E79" s="1">
         <v>47.887323943661976</v>
@@ -4606,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I79" s="1">
         <v>0.03</v>
@@ -4617,13 +5426,13 @@
         <v>21448</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E80" s="1">
         <v>5.9402376095043801</v>
@@ -4635,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I80" s="1">
         <v>0.03</v>
@@ -4646,13 +5455,13 @@
         <v>21462</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E81" s="1">
         <v>5.9402376095043801</v>
@@ -4664,7 +5473,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I81" s="1">
         <v>0.03</v>
@@ -4675,13 +5484,13 @@
         <v>21479</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E82" s="1">
         <v>11.327539706323043</v>
@@ -4693,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I82" s="1">
         <v>0.03</v>
@@ -4704,13 +5513,13 @@
         <v>21486</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E83" s="1">
         <v>11.327539706323043</v>
@@ -4722,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I83" s="1">
         <v>0.03</v>
@@ -4733,13 +5542,13 @@
         <v>21493</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E84" s="1">
         <v>11.327539706323043</v>
@@ -4751,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I84" s="1">
         <v>0.03</v>
@@ -4762,13 +5571,13 @@
         <v>21509</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E85" s="1">
         <v>11.327539706323043</v>
@@ -4780,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I85" s="1">
         <v>0.03</v>
@@ -4791,13 +5600,13 @@
         <v>21516</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E86" s="1">
         <v>11.327539706323043</v>
@@ -4809,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I86" s="1">
         <v>0.03</v>
@@ -4820,13 +5629,13 @@
         <v>21523</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E87" s="1">
         <v>11.327539706323043</v>
@@ -4838,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I87" s="1">
         <v>0.03</v>
@@ -4849,13 +5658,13 @@
         <v>12529</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E88" s="1">
         <v>11.978570998615542</v>
@@ -4867,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I88" s="1">
         <v>0.03</v>
@@ -4878,13 +5687,13 @@
         <v>22162</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E89" s="1">
         <v>15.522924782738986</v>
@@ -4896,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I89" s="1">
         <v>0.03</v>
@@ -4907,13 +5716,13 @@
         <v>21530</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E90" s="1">
         <v>7.731495355109379</v>
@@ -4925,7 +5734,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I90" s="1">
         <v>0.03</v>
@@ -4936,13 +5745,13 @@
         <v>22155</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E91" s="1">
         <v>7.731495355109379</v>
@@ -4954,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I91" s="1">
         <v>0.03</v>
@@ -4965,13 +5774,13 @@
         <v>21547</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E92" s="1">
         <v>3.5900509439616419</v>
@@ -4983,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I92" s="1">
         <v>0.03</v>
@@ -4994,13 +5803,13 @@
         <v>21554</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E93" s="1">
         <v>17.940717628705148</v>
@@ -5012,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I93" s="1">
         <v>0.03</v>
@@ -5023,13 +5832,13 @@
         <v>22094</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E94" s="1">
         <v>9.5897804965815041</v>
@@ -5041,7 +5850,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I94" s="1">
         <v>0.03</v>
@@ -5052,13 +5861,13 @@
         <v>21561</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E95" s="1">
         <v>7.7854360203775848</v>
@@ -5070,7 +5879,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I95" s="1">
         <v>0.03</v>
@@ -5081,13 +5890,13 @@
         <v>21578</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E96" s="1">
         <v>9.5897804965815041</v>
@@ -5099,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I96" s="1">
         <v>0.03</v>
@@ -5110,13 +5919,13 @@
         <v>21585</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E97" s="1">
         <v>11.340453618144725</v>
@@ -5128,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I97" s="1">
         <v>0.03</v>
@@ -5139,13 +5948,13 @@
         <v>21592</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E98" s="1">
         <v>11.940477619104763</v>
@@ -5157,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I98" s="1">
         <v>0.03</v>
@@ -5168,13 +5977,13 @@
         <v>21608</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E99" s="1">
         <v>15.540621624864993</v>
@@ -5186,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I99" s="1">
         <v>0.03</v>
@@ -5197,13 +6006,13 @@
         <v>22421</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E100" s="1">
         <v>9.5834581959844165</v>
@@ -5215,7 +6024,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I100" s="1">
         <v>0.03</v>
@@ -5226,13 +6035,13 @@
         <v>22438</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E101" s="1">
         <v>15.522924782738986</v>
@@ -5244,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I101" s="1">
         <v>0.03</v>
@@ -5255,13 +6064,13 @@
         <v>22353</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E102" s="1">
         <v>7.1860952951753072</v>
@@ -5273,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I102" s="1">
         <v>0.03</v>
@@ -5284,13 +6093,13 @@
         <v>22360</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E103" s="1">
         <v>9.5834581959844165</v>
@@ -5302,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I103" s="1">
         <v>0.03</v>
@@ -5313,13 +6122,13 @@
         <v>22377</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E104" s="1">
         <v>17.920287683548096</v>
@@ -5331,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I104" s="1">
         <v>0.03</v>
@@ -5342,13 +6151,13 @@
         <v>22414</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E105" s="1">
         <v>17.940717628705148</v>
@@ -5360,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I105" s="1">
         <v>0.03</v>
@@ -5371,13 +6180,13 @@
         <v>21714</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E106" s="1">
         <v>11.926880431525321</v>
@@ -5389,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I106" s="1">
         <v>0.03</v>
@@ -5400,13 +6209,13 @@
         <v>22186</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E107" s="1">
         <v>11.940477619104763</v>
@@ -5418,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I107" s="1">
         <v>0.03</v>
@@ -5429,13 +6238,13 @@
         <v>22339</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E108" s="1">
         <v>11.926880431525321</v>
@@ -5447,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I108" s="1">
         <v>0.03</v>
@@ -5458,13 +6267,13 @@
         <v>22346</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E109" s="1">
         <v>21.51633203476176</v>
@@ -5476,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I109" s="1">
         <v>0.03</v>
@@ -5487,13 +6296,13 @@
         <v>21721</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E110" s="1">
         <v>23.91369493557087</v>
@@ -5505,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I110" s="1">
         <v>0.03</v>
@@ -5516,13 +6325,13 @@
         <v>22391</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E111" s="1">
         <v>9.5897804965815041</v>
@@ -5534,7 +6343,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I111" s="1">
         <v>0.03</v>
@@ -5545,13 +6354,13 @@
         <v>22407</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E112" s="1">
         <v>11.926880431525321</v>
@@ -5563,7 +6372,7 @@
         <v>1</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I112" s="1">
         <v>0.03</v>
@@ -5574,13 +6383,13 @@
         <v>21745</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E113" s="1">
         <v>15.522924782738986</v>
@@ -5592,7 +6401,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I113" s="1">
         <v>0.03</v>
@@ -5603,13 +6412,13 @@
         <v>21752</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E114" s="1">
         <v>21.570272700029967</v>
@@ -5621,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I114" s="1">
         <v>0.03</v>
@@ -5632,13 +6441,13 @@
         <v>21776</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E115" s="1">
         <v>20.916991309559481</v>
@@ -5650,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I115" s="1">
         <v>0.03</v>
@@ -5661,13 +6470,13 @@
         <v>21783</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E116" s="1">
         <v>21.570272700029967</v>
@@ -5679,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I116" s="1">
         <v>0.03</v>
@@ -5690,13 +6499,13 @@
         <v>21790</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E117" s="1">
         <v>14.324243332334431</v>
@@ -5708,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I117" s="1">
         <v>0.03</v>
@@ -5719,13 +6528,13 @@
         <v>22315</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E118" s="1">
         <v>29.941197647905913</v>
@@ -5737,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I118" s="1">
         <v>0.03</v>
@@ -5748,13 +6557,13 @@
         <v>21844</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E119" s="1">
         <v>21.594863794551781</v>
@@ -5766,7 +6575,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I119" s="1">
         <v>0.03</v>
@@ -5777,13 +6586,13 @@
         <v>21899</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E120" s="1">
         <v>23.91369493557087</v>
@@ -5795,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I120" s="1">
         <v>0.03</v>
@@ -5803,16 +6612,16 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E121" s="1">
         <v>5.99</v>
@@ -5824,7 +6633,7 @@
         <v>10</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I121" s="1">
         <v>0.03</v>
@@ -5832,16 +6641,16 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E122" s="1">
         <v>5.99</v>
@@ -5853,7 +6662,7 @@
         <v>10</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I122" s="1">
         <v>0.03</v>
@@ -5861,16 +6670,16 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E123" s="1">
         <v>5.99</v>
@@ -5882,7 +6691,7 @@
         <v>10</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I123" s="1">
         <v>0.03</v>
@@ -5890,16 +6699,16 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E124" s="1">
         <v>5.99</v>
@@ -5911,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I124" s="1">
         <v>0.03</v>
@@ -5919,16 +6728,16 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E125" s="1">
         <v>5.99</v>
@@ -5940,7 +6749,7 @@
         <v>10</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I125" s="1">
         <v>0.03</v>
@@ -5948,16 +6757,16 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E126" s="1">
         <v>5.99</v>
@@ -5969,7 +6778,7 @@
         <v>10</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I126" s="1">
         <v>0.03</v>
@@ -5977,16 +6786,16 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E127" s="1">
         <v>5.99</v>
@@ -5998,7 +6807,7 @@
         <v>10</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I127" s="1">
         <v>0.03</v>
@@ -6006,16 +6815,16 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E128" s="1">
         <v>5.99</v>
@@ -6027,7 +6836,7 @@
         <v>10</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I128" s="1">
         <v>0.03</v>
@@ -6035,16 +6844,16 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E129" s="1">
         <v>3.5</v>
@@ -6056,7 +6865,7 @@
         <v>24</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I129" s="1">
         <v>0.03</v>
@@ -6064,16 +6873,16 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E130" s="1">
         <v>3.5</v>
@@ -6085,7 +6894,7 @@
         <v>24</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I130" s="1">
         <v>0.03</v>
@@ -6093,16 +6902,16 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E131" s="1">
         <v>1.99</v>
@@ -6115,7 +6924,7 @@
         <v>24</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I131" s="1">
         <v>0.03</v>
@@ -6123,16 +6932,16 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E132" s="1">
         <v>1.99</v>
@@ -6145,7 +6954,7 @@
         <v>24</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I132" s="1">
         <v>0.03</v>
@@ -6153,16 +6962,16 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E133" s="1">
         <v>1.99</v>
@@ -6175,7 +6984,7 @@
         <v>24</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I133" s="1">
         <v>0.03</v>
@@ -6183,16 +6992,16 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E134" s="1">
         <v>1.99</v>
@@ -6205,7 +7014,7 @@
         <v>24</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I134" s="1">
         <v>0.03</v>
@@ -6213,16 +7022,16 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E135" s="1">
         <v>1.99</v>
@@ -6235,7 +7044,7 @@
         <v>24</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I135" s="1">
         <v>0.03</v>
@@ -6243,16 +7052,16 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E136" s="1">
         <v>1.99</v>
@@ -6265,7 +7074,7 @@
         <v>24</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I136" s="1">
         <v>0.03</v>
@@ -6273,16 +7082,16 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D137" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E137" s="1">
         <v>6.94</v>
@@ -6294,7 +7103,7 @@
         <v>12</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I137" s="1">
         <v>0.05</v>
@@ -6302,16 +7111,16 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E138" s="1">
         <v>6.94</v>
@@ -6323,7 +7132,7 @@
         <v>12</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I138" s="1">
         <v>0.05</v>
@@ -6331,16 +7140,16 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E139" s="1">
         <v>3.96</v>
@@ -6352,7 +7161,7 @@
         <v>30</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I139" s="1">
         <v>0.05</v>
@@ -6360,16 +7169,16 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E140" s="1">
         <v>0.84</v>
@@ -6381,7 +7190,7 @@
         <v>32</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I140" s="1">
         <v>0.05</v>
@@ -6389,16 +7198,16 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E141" s="1">
         <v>0.93</v>
@@ -6410,7 +7219,7 @@
         <v>32</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I141" s="1">
         <v>0.05</v>
@@ -6418,16 +7227,16 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E142" s="1">
         <v>12.99</v>
@@ -6439,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I142" s="1">
         <v>0.05</v>
@@ -6447,16 +7256,16 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E143" s="1">
         <v>12.99</v>
@@ -6468,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I143" s="1">
         <v>0.05</v>
@@ -6476,16 +7285,16 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E144" s="1">
         <v>12.99</v>
@@ -6497,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I144" s="1">
         <v>0.05</v>
@@ -6505,16 +7314,16 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E145" s="1">
         <v>0.41</v>
@@ -6526,7 +7335,7 @@
         <v>63</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I145" s="1">
         <v>0.05</v>
@@ -6534,16 +7343,16 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E146" s="1">
         <v>0.43</v>
@@ -6555,7 +7364,7 @@
         <v>56</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I146" s="1">
         <v>0.05</v>
@@ -6563,16 +7372,16 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E147" s="1">
         <v>3.82</v>
@@ -6584,7 +7393,7 @@
         <v>16</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I147" s="1">
         <v>0.05</v>
@@ -6592,16 +7401,16 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E148" s="1">
         <v>3.82</v>
@@ -6613,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I148" s="1">
         <v>0.05</v>
@@ -6621,16 +7430,16 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E149" s="1">
         <v>3.82</v>
@@ -6642,7 +7451,7 @@
         <v>16</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I149" s="1">
         <v>0.05</v>
@@ -6650,16 +7459,16 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E150" s="1">
         <v>0.61</v>
@@ -6671,7 +7480,7 @@
         <v>42</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I150" s="1">
         <v>0.05</v>
@@ -6679,16 +7488,16 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E151" s="1">
         <v>0.61</v>
@@ -6700,7 +7509,7 @@
         <v>42</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I151" s="1">
         <v>0.05</v>
@@ -6708,16 +7517,16 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E152" s="1">
         <v>0.61</v>
@@ -6729,7 +7538,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I152" s="1">
         <v>0.05</v>
@@ -6737,16 +7546,16 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E153" s="1">
         <v>1.58</v>
@@ -6758,7 +7567,7 @@
         <v>24</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I153" s="1">
         <v>0.05</v>
@@ -6766,16 +7575,16 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E154" s="1">
         <v>6.94</v>
@@ -6787,7 +7596,7 @@
         <v>25</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I154" s="1">
         <v>0.05</v>
@@ -6795,16 +7604,16 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E155" s="1">
         <v>0.59</v>
@@ -6816,7 +7625,7 @@
         <v>60</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I155" s="1">
         <v>0.05</v>
@@ -6824,16 +7633,16 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E156" s="1">
         <v>13.68</v>
@@ -6845,7 +7654,7 @@
         <v>12</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I156" s="1">
         <v>0.05</v>
@@ -6853,16 +7662,16 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C157" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E157" s="1">
         <v>15.13</v>
@@ -6874,7 +7683,7 @@
         <v>12</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I157" s="1">
         <v>0.05</v>
@@ -6882,16 +7691,16 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E158" s="1">
         <v>1.87</v>
@@ -6903,7 +7712,7 @@
         <v>30</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I158" s="1">
         <v>16</v>
@@ -6911,16 +7720,16 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E159" s="1">
         <v>4.75</v>
@@ -6932,7 +7741,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I159" s="1">
         <v>27</v>
@@ -6940,16 +7749,16 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -6961,7 +7770,7 @@
         <v>22</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I160" s="1">
         <v>12</v>
@@ -6969,16 +7778,16 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -6990,7 +7799,7 @@
         <v>22</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I161" s="1">
         <v>12</v>
@@ -6998,16 +7807,16 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E162" s="1">
         <v>2.6</v>
@@ -7019,7 +7828,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I162" s="1">
         <v>14</v>
@@ -7027,16 +7836,16 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E163" s="1">
         <v>2.8</v>
@@ -7048,7 +7857,7 @@
         <v>20</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I163" s="1">
         <v>18</v>
@@ -7056,16 +7865,16 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E164" s="1">
         <v>2.5</v>
@@ -7077,7 +7886,7 @@
         <v>24</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I164" s="1">
         <v>15</v>
@@ -7085,16 +7894,16 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E165" s="1">
         <v>4</v>
@@ -7106,7 +7915,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I165" s="1">
         <v>18</v>
@@ -7114,16 +7923,16 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E166" s="1">
         <v>2.34</v>
@@ -7135,7 +7944,7 @@
         <v>24</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I166" s="1">
         <v>18</v>
@@ -7143,16 +7952,16 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E167" s="1">
         <v>2.34</v>
@@ -7164,7 +7973,7 @@
         <v>24</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I167" s="1">
         <v>18</v>
@@ -7172,16 +7981,16 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E168" s="1">
         <v>2.2000000000000002</v>
@@ -7193,7 +8002,7 @@
         <v>20</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I168" s="1">
         <v>11</v>
@@ -7201,16 +8010,16 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E169" s="1">
         <v>2.2000000000000002</v>
@@ -7222,7 +8031,7 @@
         <v>20</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I169" s="1">
         <v>11</v>
@@ -7230,16 +8039,16 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E170" s="1">
         <v>2.5</v>
@@ -7251,7 +8060,7 @@
         <v>30</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I170" s="1">
         <v>15</v>
@@ -7259,16 +8068,16 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E171" s="1">
         <v>13</v>
@@ -7280,7 +8089,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I171" s="1">
         <v>5</v>
@@ -7288,16 +8097,16 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E172" s="1">
         <v>13.67</v>
@@ -7309,7 +8118,7 @@
         <v>15</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I172" s="1">
         <v>20</v>
@@ -7317,16 +8126,16 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E173" s="1">
         <v>1.4</v>
@@ -7338,7 +8147,7 @@
         <v>30</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I173" s="1">
         <v>10</v>
@@ -7346,16 +8155,16 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E174" s="1">
         <v>2</v>
@@ -7367,7 +8176,7 @@
         <v>22</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I174" s="1">
         <v>11</v>
@@ -7375,16 +8184,16 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E175" s="1">
         <v>2</v>
@@ -7396,7 +8205,7 @@
         <v>22</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I175" s="1">
         <v>11</v>
@@ -7404,16 +8213,16 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E176" s="1">
         <v>2</v>
@@ -7425,7 +8234,7 @@
         <v>22</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I176" s="1">
         <v>11</v>
@@ -7433,16 +8242,16 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E177" s="1">
         <v>6.4</v>
@@ -7454,7 +8263,7 @@
         <v>20</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I177" s="1">
         <v>23</v>
@@ -7462,16 +8271,16 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E178" s="1">
         <v>3.67</v>
@@ -7483,7 +8292,7 @@
         <v>15</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I178" s="1">
         <v>15</v>
@@ -7491,16 +8300,16 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -7512,7 +8321,7 @@
         <v>15</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I179" s="1">
         <v>20</v>
@@ -7520,16 +8329,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E180" s="1">
         <v>3.08</v>
@@ -7541,7 +8350,7 @@
         <v>42</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I180" s="1">
         <v>30</v>
@@ -7549,16 +8358,16 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E181" s="1">
         <v>2.2000000000000002</v>
@@ -7570,7 +8379,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I181" s="1">
         <v>12</v>
@@ -7578,16 +8387,16 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E182" s="1">
         <v>1.98</v>
@@ -7599,7 +8408,7 @@
         <v>42</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I182" s="1">
         <v>21</v>
@@ -7607,16 +8416,16 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E183" s="1">
         <v>1.26</v>
@@ -7628,7 +8437,7 @@
         <v>35</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I183" s="1">
         <v>5</v>
@@ -7636,16 +8445,16 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E184" s="1">
         <v>5.14</v>
@@ -7657,7 +8466,7 @@
         <v>15</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I184" s="1">
         <v>15</v>
@@ -7665,16 +8474,16 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E185" s="1">
         <v>5.14</v>
@@ -7686,7 +8495,7 @@
         <v>15</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I185" s="1">
         <v>15</v>
@@ -7694,16 +8503,16 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E186" s="1">
         <v>5.14</v>
@@ -7715,7 +8524,7 @@
         <v>15</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I186" s="1">
         <v>15</v>
@@ -7723,16 +8532,16 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E187" s="1">
         <v>5.14</v>
@@ -7744,7 +8553,7 @@
         <v>15</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I187" s="1">
         <v>15</v>
@@ -7752,16 +8561,16 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E188" s="1">
         <v>5.14</v>
@@ -7773,7 +8582,7 @@
         <v>15</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I188" s="1">
         <v>15</v>
@@ -7781,16 +8590,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E189" s="1">
         <v>5.14</v>
@@ -7802,7 +8611,7 @@
         <v>15</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I189" s="1">
         <v>15</v>
@@ -7810,16 +8619,16 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E190" s="1">
         <v>5.14</v>
@@ -7831,7 +8640,7 @@
         <v>15</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I190" s="1">
         <v>15</v>
@@ -7839,16 +8648,16 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E191" s="1">
         <v>108</v>
@@ -7860,7 +8669,7 @@
         <v>24</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I191" s="1">
         <v>30</v>
@@ -7868,16 +8677,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E192" s="1">
         <v>2.44</v>
@@ -7889,7 +8698,7 @@
         <v>30</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
@@ -7897,16 +8706,16 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="D193" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E193" s="1">
         <v>9.5</v>
@@ -7918,7 +8727,7 @@
         <v>1</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
@@ -7926,16 +8735,16 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="D194" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E194" s="1">
         <v>2.56</v>
@@ -7947,7 +8756,7 @@
         <v>30</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
@@ -7955,16 +8764,16 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E195" s="1">
         <v>50</v>
@@ -7976,10 +8785,3137 @@
         <v>6</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I195" s="1">
         <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A196" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="1">
+        <v>9.27</v>
+      </c>
+      <c r="F196" s="1">
+        <v>103.2</v>
+      </c>
+      <c r="G196" s="1">
+        <v>1</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I196" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A197" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E197" s="1">
+        <v>9.27</v>
+      </c>
+      <c r="F197" s="1">
+        <v>103.2</v>
+      </c>
+      <c r="G197" s="1">
+        <v>1</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I197" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="1">
+        <v>9.2666666666666675</v>
+      </c>
+      <c r="F198" s="1">
+        <v>111.2</v>
+      </c>
+      <c r="G198" s="1">
+        <v>1</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I198" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>20199</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E199" s="1">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F199" s="1">
+        <v>103.56</v>
+      </c>
+      <c r="G199" s="1">
+        <v>1</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I199" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="1">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F200" s="1">
+        <v>103.56</v>
+      </c>
+      <c r="G200" s="1">
+        <v>1</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I200" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="1">
+        <v>33.26</v>
+      </c>
+      <c r="F201" s="1">
+        <v>33.26</v>
+      </c>
+      <c r="G201" s="1">
+        <v>1</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I201" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" s="1">
+        <v>33.26</v>
+      </c>
+      <c r="F202" s="1">
+        <v>33.26</v>
+      </c>
+      <c r="G202" s="1">
+        <v>1</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I202" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" s="1">
+        <v>53.26</v>
+      </c>
+      <c r="F203" s="1">
+        <v>53.26</v>
+      </c>
+      <c r="G203" s="1">
+        <v>1</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I203" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E204" s="1">
+        <v>53.26</v>
+      </c>
+      <c r="F204" s="1">
+        <v>53.26</v>
+      </c>
+      <c r="G204" s="1">
+        <v>1</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I204" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E205" s="1">
+        <v>11.32</v>
+      </c>
+      <c r="F205" s="1">
+        <v>135.84</v>
+      </c>
+      <c r="G205" s="1">
+        <v>1</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I205" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206" s="1">
+        <v>11.32</v>
+      </c>
+      <c r="F206" s="1">
+        <v>135.84</v>
+      </c>
+      <c r="G206" s="1">
+        <v>1</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I206" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E207" s="1">
+        <v>11.32</v>
+      </c>
+      <c r="F207" s="1">
+        <v>135.84</v>
+      </c>
+      <c r="G207" s="1">
+        <v>1</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I207" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="F208" s="1">
+        <v>103.2</v>
+      </c>
+      <c r="G208" s="1">
+        <v>1</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I208" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="F209" s="1">
+        <v>103.2</v>
+      </c>
+      <c r="G209" s="1">
+        <v>1</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I209" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="F210" s="1">
+        <v>103.2</v>
+      </c>
+      <c r="G210" s="1">
+        <v>1</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I210" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="1">
+        <v>16.599999999999998</v>
+      </c>
+      <c r="F211" s="1">
+        <v>99.6</v>
+      </c>
+      <c r="G211" s="1">
+        <v>1</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I211" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E212" s="1">
+        <v>16.599999999999998</v>
+      </c>
+      <c r="F212" s="1">
+        <v>99.6</v>
+      </c>
+      <c r="G212" s="1">
+        <v>1</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I212" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213" s="1">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F213" s="1">
+        <v>103.56</v>
+      </c>
+      <c r="G213" s="1">
+        <v>1</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I213" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E214" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="F214" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="G214" s="1">
+        <v>1</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I214" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E215" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="F215" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="G215" s="1">
+        <v>1</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I215" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A216" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E216" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="F216" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="G216" s="1">
+        <v>1</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I216" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E217" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="F217" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="G217" s="1">
+        <v>1</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I217" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E218" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="F218" s="1">
+        <v>43.9</v>
+      </c>
+      <c r="G218" s="1">
+        <v>1</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I218" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E219" s="1">
+        <v>62</v>
+      </c>
+      <c r="F219" s="1">
+        <v>62</v>
+      </c>
+      <c r="G219" s="1">
+        <v>1</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I219" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E220" s="1">
+        <v>62</v>
+      </c>
+      <c r="F220" s="1">
+        <v>62</v>
+      </c>
+      <c r="G220" s="1">
+        <v>1</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I220" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E221" s="1">
+        <v>7.94</v>
+      </c>
+      <c r="F221" s="1">
+        <v>95.28</v>
+      </c>
+      <c r="G221" s="1">
+        <v>1</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I221" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E222" s="1">
+        <v>7.94</v>
+      </c>
+      <c r="F222" s="1">
+        <v>95.28</v>
+      </c>
+      <c r="G222" s="1">
+        <v>1</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I222" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E223" s="1">
+        <v>7.94</v>
+      </c>
+      <c r="F223" s="1">
+        <v>95.28</v>
+      </c>
+      <c r="G223" s="1">
+        <v>1</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I223" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E224" s="1">
+        <v>7.94</v>
+      </c>
+      <c r="F224" s="1">
+        <v>95.28</v>
+      </c>
+      <c r="G224" s="1">
+        <v>1</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I224" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E225" s="1">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F225" s="1">
+        <v>103.56</v>
+      </c>
+      <c r="G225" s="1">
+        <v>1</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I225" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" s="1">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="F226" s="1">
+        <v>103.56</v>
+      </c>
+      <c r="G226" s="1">
+        <v>1</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I226" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E227" s="1">
+        <v>59.9</v>
+      </c>
+      <c r="F227" s="1">
+        <v>59.9</v>
+      </c>
+      <c r="G227" s="1">
+        <v>1</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I227" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E228" s="1">
+        <v>59.9</v>
+      </c>
+      <c r="F228" s="1">
+        <v>59.9</v>
+      </c>
+      <c r="G228" s="1">
+        <v>1</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I228" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E229" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="F229" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="G229" s="1">
+        <v>1</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I229" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E230" s="1">
+        <v>26.6</v>
+      </c>
+      <c r="F230" s="1">
+        <v>26.6</v>
+      </c>
+      <c r="G230" s="1">
+        <v>1</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I230" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E231" s="1">
+        <v>42.78</v>
+      </c>
+      <c r="F231" s="1">
+        <v>42.78</v>
+      </c>
+      <c r="G231" s="1">
+        <v>1</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I231" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E232" s="1">
+        <v>56.9</v>
+      </c>
+      <c r="F232" s="1">
+        <v>56.9</v>
+      </c>
+      <c r="G232" s="1">
+        <v>1</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I232" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E233" s="1">
+        <v>67.7</v>
+      </c>
+      <c r="F233" s="1">
+        <v>67.7</v>
+      </c>
+      <c r="G233" s="1">
+        <v>1</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I233" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E234" s="1">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F234" s="1">
+        <v>73.5</v>
+      </c>
+      <c r="G234" s="1">
+        <v>1</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I234" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E235" s="1">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F235" s="1">
+        <v>73.5</v>
+      </c>
+      <c r="G235" s="1">
+        <v>1</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I235" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E236" s="1">
+        <v>1.6194444444444445</v>
+      </c>
+      <c r="F236" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="G236" s="1">
+        <v>1</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I236" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E237" s="1">
+        <v>1.6194444444444445</v>
+      </c>
+      <c r="F237" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="G237" s="1">
+        <v>1</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I237" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E238" s="1">
+        <v>1.6194444444444445</v>
+      </c>
+      <c r="F238" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="G238" s="1">
+        <v>1</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I238" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E239" s="1">
+        <v>1.6194444444444445</v>
+      </c>
+      <c r="F239" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="G239" s="1">
+        <v>1</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I239" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240" s="1">
+        <v>6.81</v>
+      </c>
+      <c r="F240" s="1">
+        <v>81.72</v>
+      </c>
+      <c r="G240" s="1">
+        <v>1</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I240" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E241" s="1">
+        <v>6.81</v>
+      </c>
+      <c r="F241" s="1">
+        <v>81.72</v>
+      </c>
+      <c r="G241" s="1">
+        <v>1</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I241" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E242" s="1">
+        <v>13.26</v>
+      </c>
+      <c r="F242" s="1">
+        <v>159.12</v>
+      </c>
+      <c r="G242" s="1">
+        <v>1</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I242" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243" s="1">
+        <v>13.26</v>
+      </c>
+      <c r="F243" s="1">
+        <v>159.12</v>
+      </c>
+      <c r="G243" s="1">
+        <v>1</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I243" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E244" s="1">
+        <v>3.69</v>
+      </c>
+      <c r="F244" s="1">
+        <v>44.28</v>
+      </c>
+      <c r="G244" s="1">
+        <v>1</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I244" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E245" s="1">
+        <v>3.69</v>
+      </c>
+      <c r="F245" s="1">
+        <v>44.28</v>
+      </c>
+      <c r="G245" s="1">
+        <v>1</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I245" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E246" s="1">
+        <v>8.6875</v>
+      </c>
+      <c r="F246" s="1">
+        <v>104.25</v>
+      </c>
+      <c r="G246" s="1">
+        <v>1</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I246" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E247" s="1">
+        <v>8.6875</v>
+      </c>
+      <c r="F247" s="1">
+        <v>104.25</v>
+      </c>
+      <c r="G247" s="1">
+        <v>1</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I247" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A248" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E248" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="F248" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="G248" s="1">
+        <v>1</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I248" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A249" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E249" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="F249" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="G249" s="1">
+        <v>1</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I249" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A250" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E250" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="F250" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="G250" s="1">
+        <v>1</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I250" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A251" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251" s="1">
+        <v>4.0600000000000005</v>
+      </c>
+      <c r="F251" s="1">
+        <v>81.2</v>
+      </c>
+      <c r="G251" s="1">
+        <v>1</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I251" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A252" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E252" s="1">
+        <v>4.0600000000000005</v>
+      </c>
+      <c r="F252" s="1">
+        <v>81.2</v>
+      </c>
+      <c r="G252" s="1">
+        <v>1</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I252" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A253" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253" s="1">
+        <v>4.0600000000000005</v>
+      </c>
+      <c r="F253" s="1">
+        <v>81.2</v>
+      </c>
+      <c r="G253" s="1">
+        <v>1</v>
+      </c>
+      <c r="H253" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I253" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A254" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E254" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F254" s="1">
+        <v>112.2</v>
+      </c>
+      <c r="G254" s="1">
+        <v>1</v>
+      </c>
+      <c r="H254" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I254" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A255" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E255" s="1">
+        <v>5.2299999999999995</v>
+      </c>
+      <c r="F255" s="1">
+        <v>62.76</v>
+      </c>
+      <c r="G255" s="1">
+        <v>1</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I255" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A256" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E256" s="1">
+        <v>5.2299999999999995</v>
+      </c>
+      <c r="F256" s="1">
+        <v>62.76</v>
+      </c>
+      <c r="G256" s="1">
+        <v>1</v>
+      </c>
+      <c r="H256" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I256" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A257" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" s="1">
+        <v>5.2299999999999995</v>
+      </c>
+      <c r="F257" s="1">
+        <v>62.76</v>
+      </c>
+      <c r="G257" s="1">
+        <v>1</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I257" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E258" s="1">
+        <v>5.8233333333333333</v>
+      </c>
+      <c r="F258" s="1">
+        <v>69.88</v>
+      </c>
+      <c r="G258" s="1">
+        <v>1</v>
+      </c>
+      <c r="H258" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I258" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259" s="1">
+        <v>7.5799999999999992</v>
+      </c>
+      <c r="F259" s="1">
+        <v>90.96</v>
+      </c>
+      <c r="G259" s="1">
+        <v>1</v>
+      </c>
+      <c r="H259" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I259" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F260" s="1">
+        <v>56.1</v>
+      </c>
+      <c r="G260" s="1">
+        <v>1</v>
+      </c>
+      <c r="H260" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I260" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261" s="1">
+        <v>9.93</v>
+      </c>
+      <c r="F261" s="1">
+        <v>119.16</v>
+      </c>
+      <c r="G261" s="1">
+        <v>1</v>
+      </c>
+      <c r="H261" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I261" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E262" s="1">
+        <v>39.9</v>
+      </c>
+      <c r="F262" s="1">
+        <v>159.6</v>
+      </c>
+      <c r="G262" s="1">
+        <v>1</v>
+      </c>
+      <c r="H262" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I262" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E263" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F263" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="G263" s="1">
+        <v>1</v>
+      </c>
+      <c r="H263" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I263" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E264" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F264" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="G264" s="1">
+        <v>1</v>
+      </c>
+      <c r="H264" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I264" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E265" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F265" s="1">
+        <v>56.1</v>
+      </c>
+      <c r="G265" s="1">
+        <v>1</v>
+      </c>
+      <c r="H265" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I265" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E266" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F266" s="1">
+        <v>56.1</v>
+      </c>
+      <c r="G266" s="1">
+        <v>1</v>
+      </c>
+      <c r="H266" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I266" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E267" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F267" s="1">
+        <v>112.2</v>
+      </c>
+      <c r="G267" s="1">
+        <v>1</v>
+      </c>
+      <c r="H267" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I267" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E268" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F268" s="1">
+        <v>112.2</v>
+      </c>
+      <c r="G268" s="1">
+        <v>1</v>
+      </c>
+      <c r="H268" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I268" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E269" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F269" s="1">
+        <v>112.2</v>
+      </c>
+      <c r="G269" s="1">
+        <v>1</v>
+      </c>
+      <c r="H269" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I269" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E270" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F270" s="1">
+        <v>112.2</v>
+      </c>
+      <c r="G270" s="1">
+        <v>1</v>
+      </c>
+      <c r="H270" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I270" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E271" s="1">
+        <v>9.3533333333333335</v>
+      </c>
+      <c r="F271" s="1">
+        <v>112.24</v>
+      </c>
+      <c r="G271" s="1">
+        <v>1</v>
+      </c>
+      <c r="H271" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I271" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E272" s="1">
+        <v>11.705833333333333</v>
+      </c>
+      <c r="F272" s="1">
+        <v>140.47</v>
+      </c>
+      <c r="G272" s="1">
+        <v>1</v>
+      </c>
+      <c r="H272" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I272" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E273" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="F273" s="1">
+        <v>66</v>
+      </c>
+      <c r="G273" s="1">
+        <v>1</v>
+      </c>
+      <c r="H273" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I273" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E274" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="F274" s="1">
+        <v>66</v>
+      </c>
+      <c r="G274" s="1">
+        <v>1</v>
+      </c>
+      <c r="H274" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I274" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E275" s="1">
+        <v>2.7216666666666662</v>
+      </c>
+      <c r="F275" s="1">
+        <v>32.659999999999997</v>
+      </c>
+      <c r="G275" s="1">
+        <v>1</v>
+      </c>
+      <c r="H275" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I275" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E276" s="1">
+        <v>11.049999999999999</v>
+      </c>
+      <c r="F276" s="1">
+        <v>132.6</v>
+      </c>
+      <c r="G276" s="1">
+        <v>1</v>
+      </c>
+      <c r="H276" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I276" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E277" s="1">
+        <v>7.7216666666666667</v>
+      </c>
+      <c r="F277" s="1">
+        <v>46.33</v>
+      </c>
+      <c r="G277" s="1">
+        <v>1</v>
+      </c>
+      <c r="H277" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I277" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E278" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="F278" s="1">
+        <v>66</v>
+      </c>
+      <c r="G278" s="1">
+        <v>1</v>
+      </c>
+      <c r="H278" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I278" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E279" s="1">
+        <v>7.7216666666666667</v>
+      </c>
+      <c r="F279" s="1">
+        <v>92.66</v>
+      </c>
+      <c r="G279" s="1">
+        <v>1</v>
+      </c>
+      <c r="H279" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I279" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E280" s="1">
+        <v>8.8324999999999996</v>
+      </c>
+      <c r="F280" s="1">
+        <v>105.99</v>
+      </c>
+      <c r="G280" s="1">
+        <v>1</v>
+      </c>
+      <c r="H280" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I280" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E281" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="F281" s="1">
+        <v>126</v>
+      </c>
+      <c r="G281" s="1">
+        <v>1</v>
+      </c>
+      <c r="H281" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I281" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E282" s="1">
+        <v>11.055</v>
+      </c>
+      <c r="F282" s="1">
+        <v>132.66</v>
+      </c>
+      <c r="G282" s="1">
+        <v>1</v>
+      </c>
+      <c r="H282" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I282" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E283" s="1">
+        <v>6.6108333333333329</v>
+      </c>
+      <c r="F283" s="1">
+        <v>79.33</v>
+      </c>
+      <c r="G283" s="1">
+        <v>1</v>
+      </c>
+      <c r="H283" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I283" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E284" s="1">
+        <v>11.055</v>
+      </c>
+      <c r="F284" s="1">
+        <v>132.66</v>
+      </c>
+      <c r="G284" s="1">
+        <v>1</v>
+      </c>
+      <c r="H284" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I284" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E285" s="1">
+        <v>4.9441666666666668</v>
+      </c>
+      <c r="F285" s="1">
+        <v>59.33</v>
+      </c>
+      <c r="G285" s="1">
+        <v>1</v>
+      </c>
+      <c r="H285" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I285" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E286" s="1">
+        <v>7.7216666666666667</v>
+      </c>
+      <c r="F286" s="1">
+        <v>92.66</v>
+      </c>
+      <c r="G286" s="1">
+        <v>1</v>
+      </c>
+      <c r="H286" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I286" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A287" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E287" s="1">
+        <v>14.38</v>
+      </c>
+      <c r="F287" s="1">
+        <v>172.56</v>
+      </c>
+      <c r="G287" s="1">
+        <v>1</v>
+      </c>
+      <c r="H287" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I287" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A288" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E288" s="1">
+        <v>11.055</v>
+      </c>
+      <c r="F288" s="1">
+        <v>132.66</v>
+      </c>
+      <c r="G288" s="1">
+        <v>1</v>
+      </c>
+      <c r="H288" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I288" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A289" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E289" s="1">
+        <v>8.8324999999999996</v>
+      </c>
+      <c r="F289" s="1">
+        <v>105.99</v>
+      </c>
+      <c r="G289" s="1">
+        <v>1</v>
+      </c>
+      <c r="H289" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I289" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E290" s="1">
+        <v>8.8324999999999996</v>
+      </c>
+      <c r="F290" s="1">
+        <v>105.99</v>
+      </c>
+      <c r="G290" s="1">
+        <v>1</v>
+      </c>
+      <c r="H290" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I290" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A291" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E291" s="1">
+        <v>11.055</v>
+      </c>
+      <c r="F291" s="1">
+        <v>132.66</v>
+      </c>
+      <c r="G291" s="1">
+        <v>1</v>
+      </c>
+      <c r="H291" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I291" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E292" s="1">
+        <v>16.610833333333336</v>
+      </c>
+      <c r="F292" s="1">
+        <v>199.33</v>
+      </c>
+      <c r="G292" s="1">
+        <v>1</v>
+      </c>
+      <c r="H292" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I292" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A293" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E293" s="1">
+        <v>22.165833333333335</v>
+      </c>
+      <c r="F293" s="1">
+        <v>265.99</v>
+      </c>
+      <c r="G293" s="1">
+        <v>1</v>
+      </c>
+      <c r="H293" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I293" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A294" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E294" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="F294" s="1">
+        <v>66</v>
+      </c>
+      <c r="G294" s="1">
+        <v>1</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I294" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A295" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E295" s="1">
+        <v>11.055</v>
+      </c>
+      <c r="F295" s="1">
+        <v>132.66</v>
+      </c>
+      <c r="G295" s="1">
+        <v>1</v>
+      </c>
+      <c r="H295" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I295" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A296" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E296" s="1">
+        <v>11.049999999999999</v>
+      </c>
+      <c r="F296" s="1">
+        <v>132.6</v>
+      </c>
+      <c r="G296" s="1">
+        <v>1</v>
+      </c>
+      <c r="H296" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I296" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A297" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E297" s="1">
+        <v>16.610833333333336</v>
+      </c>
+      <c r="F297" s="1">
+        <v>199.33</v>
+      </c>
+      <c r="G297" s="1">
+        <v>1</v>
+      </c>
+      <c r="H297" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I297" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E298" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="F298" s="1">
+        <v>186</v>
+      </c>
+      <c r="G298" s="1">
+        <v>1</v>
+      </c>
+      <c r="H298" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I298" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E299" s="1">
+        <v>16.055</v>
+      </c>
+      <c r="F299" s="1">
+        <v>192.66</v>
+      </c>
+      <c r="G299" s="1">
+        <v>1</v>
+      </c>
+      <c r="H299" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I299" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A300" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E300" s="1">
+        <v>11.055</v>
+      </c>
+      <c r="F300" s="1">
+        <v>132.66</v>
+      </c>
+      <c r="G300" s="1">
+        <v>1</v>
+      </c>
+      <c r="H300" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I300" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E301" s="1">
+        <v>22.166</v>
+      </c>
+      <c r="F301" s="1">
+        <v>221.66</v>
+      </c>
+      <c r="G301" s="1">
+        <v>1</v>
+      </c>
+      <c r="H301" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I301" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E302" s="1">
+        <v>16.611000000000001</v>
+      </c>
+      <c r="F302" s="1">
+        <v>332.22</v>
+      </c>
+      <c r="G302" s="1">
+        <v>1</v>
+      </c>
+      <c r="H302" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I302" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B303" s="1"/>
+      <c r="C303" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E303" s="1">
+        <v>19.943999999999999</v>
+      </c>
+      <c r="F303" s="1">
+        <v>398.88</v>
+      </c>
+      <c r="G303" s="1">
+        <v>1</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I303" s="1">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE86DC-19A1-4AA1-BA55-55F1E6809660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF044150-F649-4216-A33D-2F1800074D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$304</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="428">
   <si>
     <t>categoria</t>
   </si>
@@ -2176,6 +2176,21 @@
       </rPr>
       <t>PROMOÇÃO</t>
     </r>
+  </si>
+  <si>
+    <t>01030538</t>
+  </si>
+  <si>
+    <t>Doce WK Leite Ninho</t>
+  </si>
+  <si>
+    <t>52,65</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>1,51</t>
   </si>
 </sst>
 </file>
@@ -3082,11 +3097,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:N304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5703125" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
@@ -7312,7 +7327,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
@@ -7341,7 +7356,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>40</v>
       </c>
@@ -7370,7 +7385,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>41</v>
       </c>
@@ -7399,7 +7414,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>42</v>
       </c>
@@ -7428,7 +7443,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>43</v>
       </c>
@@ -7457,7 +7472,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>44</v>
       </c>
@@ -7486,7 +7501,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>45</v>
       </c>
@@ -7515,7 +7530,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>46</v>
       </c>
@@ -7544,7 +7559,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>47</v>
       </c>
@@ -7573,7 +7588,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>48</v>
       </c>
@@ -7602,7 +7617,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>49</v>
       </c>
@@ -7631,7 +7646,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>50</v>
       </c>
@@ -7660,7 +7675,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>51</v>
       </c>
@@ -7689,7 +7704,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>95</v>
       </c>
@@ -7703,10 +7718,10 @@
         <v>69</v>
       </c>
       <c r="E158" s="1">
-        <v>1.87</v>
+        <v>2.0570000000000004</v>
       </c>
       <c r="F158" s="1">
-        <v>56</v>
+        <v>61.600000000000009</v>
       </c>
       <c r="G158" s="1">
         <v>30</v>
@@ -7717,8 +7732,18 @@
       <c r="I158" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K158" s="1"/>
+      <c r="L158" s="1">
+        <v>2.0570000000000004</v>
+      </c>
+      <c r="M158" s="1">
+        <v>61.600000000000009</v>
+      </c>
+      <c r="N158" s="1">
+        <v>2.0570000000000004</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>96</v>
       </c>
@@ -7732,10 +7757,10 @@
         <v>69</v>
       </c>
       <c r="E159" s="1">
-        <v>4.75</v>
+        <v>5.2250000000000005</v>
       </c>
       <c r="F159" s="1">
-        <v>95</v>
+        <v>104.50000000000001</v>
       </c>
       <c r="G159" s="1">
         <v>20</v>
@@ -7746,8 +7771,17 @@
       <c r="I159" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L159" s="1">
+        <v>5.2250000000000005</v>
+      </c>
+      <c r="M159" s="1">
+        <v>104.50000000000001</v>
+      </c>
+      <c r="N159" s="1">
+        <v>5.2250000000000005</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>97</v>
       </c>
@@ -7761,10 +7795,10 @@
         <v>69</v>
       </c>
       <c r="E160" s="1">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F160" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G160" s="1">
         <v>22</v>
@@ -7775,8 +7809,17 @@
       <c r="I160" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L160" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M160" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N160" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>98</v>
       </c>
@@ -7790,10 +7833,10 @@
         <v>69</v>
       </c>
       <c r="E161" s="1">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F161" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G161" s="1">
         <v>22</v>
@@ -7804,8 +7847,17 @@
       <c r="I161" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L161" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M161" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N161" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>99</v>
       </c>
@@ -7819,10 +7871,10 @@
         <v>69</v>
       </c>
       <c r="E162" s="1">
-        <v>2.6</v>
+        <v>2.8600000000000003</v>
       </c>
       <c r="F162" s="1">
-        <v>52</v>
+        <v>57.2</v>
       </c>
       <c r="G162" s="1">
         <v>20</v>
@@ -7833,8 +7885,17 @@
       <c r="I162" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L162" s="1">
+        <v>2.8600000000000003</v>
+      </c>
+      <c r="M162" s="1">
+        <v>57.2</v>
+      </c>
+      <c r="N162" s="1">
+        <v>2.8600000000000003</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>100</v>
       </c>
@@ -7848,10 +7909,10 @@
         <v>69</v>
       </c>
       <c r="E163" s="1">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="F163" s="1">
-        <v>56</v>
+        <v>61.600000000000009</v>
       </c>
       <c r="G163" s="1">
         <v>20</v>
@@ -7862,8 +7923,17 @@
       <c r="I163" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L163" s="1">
+        <v>3.08</v>
+      </c>
+      <c r="M163" s="1">
+        <v>61.600000000000009</v>
+      </c>
+      <c r="N163" s="1">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>101</v>
       </c>
@@ -7877,10 +7947,10 @@
         <v>69</v>
       </c>
       <c r="E164" s="1">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="F164" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G164" s="1">
         <v>24</v>
@@ -7891,8 +7961,17 @@
       <c r="I164" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L164" s="1">
+        <v>2.75</v>
+      </c>
+      <c r="M164" s="1">
+        <v>66</v>
+      </c>
+      <c r="N164" s="1">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>102</v>
       </c>
@@ -7906,10 +7985,10 @@
         <v>69</v>
       </c>
       <c r="E165" s="1">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F165" s="1">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G165" s="1">
         <v>20</v>
@@ -7920,8 +7999,17 @@
       <c r="I165" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L165" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M165" s="1">
+        <v>88</v>
+      </c>
+      <c r="N165" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>103</v>
       </c>
@@ -7935,10 +8023,10 @@
         <v>69</v>
       </c>
       <c r="E166" s="1">
-        <v>2.34</v>
+        <v>2.5739999999999998</v>
       </c>
       <c r="F166" s="1">
-        <v>56</v>
+        <v>61.600000000000009</v>
       </c>
       <c r="G166" s="1">
         <v>24</v>
@@ -7949,8 +8037,17 @@
       <c r="I166" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L166" s="1">
+        <v>2.5739999999999998</v>
+      </c>
+      <c r="M166" s="1">
+        <v>61.600000000000009</v>
+      </c>
+      <c r="N166" s="1">
+        <v>2.5739999999999998</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>121</v>
       </c>
@@ -7964,10 +8061,10 @@
         <v>69</v>
       </c>
       <c r="E167" s="1">
-        <v>2.34</v>
+        <v>2.5739999999999998</v>
       </c>
       <c r="F167" s="1">
-        <v>56</v>
+        <v>61.600000000000009</v>
       </c>
       <c r="G167" s="1">
         <v>24</v>
@@ -7978,8 +8075,17 @@
       <c r="I167" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L167" s="1">
+        <v>2.5739999999999998</v>
+      </c>
+      <c r="M167" s="1">
+        <v>61.600000000000009</v>
+      </c>
+      <c r="N167" s="1">
+        <v>2.5739999999999998</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>104</v>
       </c>
@@ -7993,10 +8099,10 @@
         <v>69</v>
       </c>
       <c r="E168" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.4200000000000004</v>
       </c>
       <c r="F168" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G168" s="1">
         <v>20</v>
@@ -8007,8 +8113,17 @@
       <c r="I168" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L168" s="1">
+        <v>2.4200000000000004</v>
+      </c>
+      <c r="M168" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N168" s="1">
+        <v>2.4200000000000004</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>105</v>
       </c>
@@ -8022,10 +8137,10 @@
         <v>69</v>
       </c>
       <c r="E169" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.4200000000000004</v>
       </c>
       <c r="F169" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G169" s="1">
         <v>20</v>
@@ -8036,8 +8151,17 @@
       <c r="I169" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L169" s="1">
+        <v>2.4200000000000004</v>
+      </c>
+      <c r="M169" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N169" s="1">
+        <v>2.4200000000000004</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>106</v>
       </c>
@@ -8051,10 +8175,10 @@
         <v>69</v>
       </c>
       <c r="E170" s="1">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="F170" s="1">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="G170" s="1">
         <v>30</v>
@@ -8065,8 +8189,17 @@
       <c r="I170" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L170" s="1">
+        <v>2.75</v>
+      </c>
+      <c r="M170" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="N170" s="1">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>107</v>
       </c>
@@ -8080,10 +8213,10 @@
         <v>69</v>
       </c>
       <c r="E171" s="1">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="F171" s="1">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="G171" s="1">
         <v>1</v>
@@ -8094,8 +8227,17 @@
       <c r="I171" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L171" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="M171" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="N171" s="1">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>108</v>
       </c>
@@ -8109,10 +8251,10 @@
         <v>69</v>
       </c>
       <c r="E172" s="1">
-        <v>13.67</v>
+        <v>15.037000000000001</v>
       </c>
       <c r="F172" s="1">
-        <v>205</v>
+        <v>225.50000000000003</v>
       </c>
       <c r="G172" s="1">
         <v>15</v>
@@ -8123,8 +8265,17 @@
       <c r="I172" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L172" s="1">
+        <v>15.037000000000001</v>
+      </c>
+      <c r="M172" s="1">
+        <v>225.50000000000003</v>
+      </c>
+      <c r="N172" s="1">
+        <v>15.037000000000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>109</v>
       </c>
@@ -8138,10 +8289,10 @@
         <v>69</v>
       </c>
       <c r="E173" s="1">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="F173" s="1">
-        <v>42</v>
+        <v>46.2</v>
       </c>
       <c r="G173" s="1">
         <v>30</v>
@@ -8152,8 +8303,17 @@
       <c r="I173" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L173" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="M173" s="1">
+        <v>46.2</v>
+      </c>
+      <c r="N173" s="1">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>110</v>
       </c>
@@ -8167,10 +8327,10 @@
         <v>69</v>
       </c>
       <c r="E174" s="1">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F174" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G174" s="1">
         <v>22</v>
@@ -8181,8 +8341,17 @@
       <c r="I174" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L174" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M174" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N174" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>111</v>
       </c>
@@ -8196,10 +8365,10 @@
         <v>69</v>
       </c>
       <c r="E175" s="1">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F175" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G175" s="1">
         <v>22</v>
@@ -8210,8 +8379,17 @@
       <c r="I175" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L175" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M175" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N175" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>112</v>
       </c>
@@ -8225,10 +8403,10 @@
         <v>69</v>
       </c>
       <c r="E176" s="1">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F176" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G176" s="1">
         <v>22</v>
@@ -8239,8 +8417,17 @@
       <c r="I176" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L176" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M176" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N176" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>113</v>
       </c>
@@ -8254,10 +8441,10 @@
         <v>69</v>
       </c>
       <c r="E177" s="1">
-        <v>6.4</v>
+        <v>7.0400000000000009</v>
       </c>
       <c r="F177" s="1">
-        <v>128</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="G177" s="1">
         <v>20</v>
@@ -8268,8 +8455,17 @@
       <c r="I177" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L177" s="1">
+        <v>7.0400000000000009</v>
+      </c>
+      <c r="M177" s="1">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="N177" s="1">
+        <v>7.0400000000000009</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>114</v>
       </c>
@@ -8283,10 +8479,10 @@
         <v>69</v>
       </c>
       <c r="E178" s="1">
-        <v>3.67</v>
+        <v>4.0369999999999999</v>
       </c>
       <c r="F178" s="1">
-        <v>55</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="G178" s="1">
         <v>15</v>
@@ -8297,8 +8493,17 @@
       <c r="I178" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L178" s="1">
+        <v>4.0369999999999999</v>
+      </c>
+      <c r="M178" s="1">
+        <v>60.500000000000007</v>
+      </c>
+      <c r="N178" s="1">
+        <v>4.0369999999999999</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>115</v>
       </c>
@@ -8312,10 +8517,10 @@
         <v>69</v>
       </c>
       <c r="E179" s="1">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F179" s="1">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="G179" s="1">
         <v>15</v>
@@ -8326,8 +8531,17 @@
       <c r="I179" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L179" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="M179" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="N179" s="1">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>116</v>
       </c>
@@ -8341,10 +8555,10 @@
         <v>69</v>
       </c>
       <c r="E180" s="1">
-        <v>3.08</v>
+        <v>3.3880000000000003</v>
       </c>
       <c r="F180" s="1">
-        <v>129</v>
+        <v>141.9</v>
       </c>
       <c r="G180" s="1">
         <v>42</v>
@@ -8355,8 +8569,17 @@
       <c r="I180" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L180" s="1">
+        <v>3.3880000000000003</v>
+      </c>
+      <c r="M180" s="1">
+        <v>141.9</v>
+      </c>
+      <c r="N180" s="1">
+        <v>3.3880000000000003</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>117</v>
       </c>
@@ -8370,10 +8593,10 @@
         <v>69</v>
       </c>
       <c r="E181" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.4200000000000004</v>
       </c>
       <c r="F181" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G181" s="1">
         <v>20</v>
@@ -8384,8 +8607,17 @@
       <c r="I181" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L181" s="1">
+        <v>2.4200000000000004</v>
+      </c>
+      <c r="M181" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N181" s="1">
+        <v>2.4200000000000004</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>118</v>
       </c>
@@ -8399,10 +8631,10 @@
         <v>69</v>
       </c>
       <c r="E182" s="1">
-        <v>1.98</v>
+        <v>2.1779999999999999</v>
       </c>
       <c r="F182" s="1">
-        <v>83</v>
+        <v>91.300000000000011</v>
       </c>
       <c r="G182" s="1">
         <v>42</v>
@@ -8413,8 +8645,17 @@
       <c r="I182" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L182" s="1">
+        <v>2.1779999999999999</v>
+      </c>
+      <c r="M182" s="1">
+        <v>91.300000000000011</v>
+      </c>
+      <c r="N182" s="1">
+        <v>2.1779999999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>119</v>
       </c>
@@ -8428,10 +8669,10 @@
         <v>69</v>
       </c>
       <c r="E183" s="1">
-        <v>1.26</v>
+        <v>1.3860000000000001</v>
       </c>
       <c r="F183" s="1">
-        <v>44</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="G183" s="1">
         <v>35</v>
@@ -8442,8 +8683,17 @@
       <c r="I183" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L183" s="1">
+        <v>1.3860000000000001</v>
+      </c>
+      <c r="M183" s="1">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="N183" s="1">
+        <v>1.3860000000000001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>120</v>
       </c>
@@ -8457,10 +8707,10 @@
         <v>69</v>
       </c>
       <c r="E184" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F184" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G184" s="1">
         <v>15</v>
@@ -8471,8 +8721,17 @@
       <c r="I184" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L184" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M184" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N184" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>122</v>
       </c>
@@ -8486,10 +8745,10 @@
         <v>69</v>
       </c>
       <c r="E185" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F185" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G185" s="1">
         <v>15</v>
@@ -8500,8 +8759,17 @@
       <c r="I185" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L185" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M185" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N185" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>123</v>
       </c>
@@ -8515,10 +8783,10 @@
         <v>69</v>
       </c>
       <c r="E186" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F186" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G186" s="1">
         <v>15</v>
@@ -8529,8 +8797,17 @@
       <c r="I186" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L186" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M186" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N186" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>124</v>
       </c>
@@ -8544,10 +8821,10 @@
         <v>69</v>
       </c>
       <c r="E187" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F187" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G187" s="1">
         <v>15</v>
@@ -8558,8 +8835,17 @@
       <c r="I187" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L187" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M187" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N187" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>125</v>
       </c>
@@ -8573,10 +8859,10 @@
         <v>69</v>
       </c>
       <c r="E188" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F188" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G188" s="1">
         <v>15</v>
@@ -8587,8 +8873,17 @@
       <c r="I188" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L188" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M188" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N188" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>126</v>
       </c>
@@ -8602,10 +8897,10 @@
         <v>69</v>
       </c>
       <c r="E189" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F189" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G189" s="1">
         <v>15</v>
@@ -8616,8 +8911,17 @@
       <c r="I189" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L189" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M189" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N189" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>127</v>
       </c>
@@ -8631,10 +8935,10 @@
         <v>69</v>
       </c>
       <c r="E190" s="1">
-        <v>5.14</v>
+        <v>5.6539999999999999</v>
       </c>
       <c r="F190" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G190" s="1">
         <v>15</v>
@@ -8645,8 +8949,17 @@
       <c r="I190" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L190" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+      <c r="M190" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N190" s="1">
+        <v>5.6539999999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>128</v>
       </c>
@@ -8660,10 +8973,10 @@
         <v>69</v>
       </c>
       <c r="E191" s="1">
-        <v>108</v>
+        <v>118.80000000000001</v>
       </c>
       <c r="F191" s="1">
-        <v>108</v>
+        <v>118.80000000000001</v>
       </c>
       <c r="G191" s="1">
         <v>24</v>
@@ -8674,8 +8987,17 @@
       <c r="I191" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L191" s="1">
+        <v>118.80000000000001</v>
+      </c>
+      <c r="M191" s="1">
+        <v>118.80000000000001</v>
+      </c>
+      <c r="N191" s="1">
+        <v>118.80000000000001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>129</v>
       </c>
@@ -8689,10 +9011,10 @@
         <v>69</v>
       </c>
       <c r="E192" s="1">
-        <v>2.44</v>
+        <v>2.6840000000000002</v>
       </c>
       <c r="F192" s="1">
-        <v>73</v>
+        <v>80.300000000000011</v>
       </c>
       <c r="G192" s="1">
         <v>30</v>
@@ -8703,8 +9025,17 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L192" s="1">
+        <v>2.6840000000000002</v>
+      </c>
+      <c r="M192" s="1">
+        <v>80.300000000000011</v>
+      </c>
+      <c r="N192" s="1">
+        <v>2.6840000000000002</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>139</v>
       </c>
@@ -8718,10 +9049,10 @@
         <v>69</v>
       </c>
       <c r="E193" s="1">
-        <v>9.5</v>
+        <v>10.450000000000001</v>
       </c>
       <c r="F193" s="1">
-        <v>9.5</v>
+        <v>10.450000000000001</v>
       </c>
       <c r="G193" s="1">
         <v>1</v>
@@ -8732,8 +9063,17 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L193" s="1">
+        <v>10.450000000000001</v>
+      </c>
+      <c r="M193" s="1">
+        <v>10.450000000000001</v>
+      </c>
+      <c r="N193" s="1">
+        <v>10.450000000000001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>141</v>
       </c>
@@ -8747,10 +9087,10 @@
         <v>69</v>
       </c>
       <c r="E194" s="1">
-        <v>2.56</v>
+        <v>2.8160000000000003</v>
       </c>
       <c r="F194" s="1">
-        <v>77</v>
+        <v>84.7</v>
       </c>
       <c r="G194" s="1">
         <v>30</v>
@@ -8761,74 +9101,85 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L194" s="1">
+        <v>2.8160000000000003</v>
+      </c>
+      <c r="M194" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="N194" s="1">
+        <v>2.8160000000000003</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L195" s="1"/>
+      <c r="M195" s="1"/>
+      <c r="N195" s="1"/>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B196" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="C196" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D196" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E195" s="1">
+      <c r="E196" s="1">
         <v>50</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F196" s="1">
         <v>50</v>
       </c>
-      <c r="G195" s="1">
+      <c r="G196" s="1">
         <v>6</v>
       </c>
-      <c r="H195" s="1" t="s">
+      <c r="H196" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I195" s="1">
+      <c r="I196" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A196" s="1" t="s">
+    <row r="197" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A197" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E196" s="1">
-        <v>9.27</v>
-      </c>
-      <c r="F196" s="1">
-        <v>103.2</v>
-      </c>
-      <c r="G196" s="1">
-        <v>1</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I196" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A197" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>17</v>
@@ -8849,24 +9200,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E198" s="1">
-        <v>9.2666666666666675</v>
+        <v>9.27</v>
       </c>
       <c r="F198" s="1">
-        <v>111.2</v>
+        <v>103.2</v>
       </c>
       <c r="G198" s="1">
         <v>1</v>
@@ -8878,24 +9229,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="1">
-        <v>20199</v>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E199" s="1">
-        <v>17.260000000000002</v>
+        <v>9.2666666666666675</v>
       </c>
       <c r="F199" s="1">
-        <v>103.56</v>
+        <v>111.2</v>
       </c>
       <c r="G199" s="1">
         <v>1</v>
@@ -8907,15 +9258,15 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>280</v>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>20199</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>17</v>
@@ -8936,24 +9287,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E201" s="1">
-        <v>33.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F201" s="1">
-        <v>33.26</v>
+        <v>103.56</v>
       </c>
       <c r="G201" s="1">
         <v>1</v>
@@ -8965,15 +9316,15 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>386</v>
+        <v>190</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>17</v>
@@ -8994,24 +9345,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E203" s="1">
-        <v>53.26</v>
+        <v>33.26</v>
       </c>
       <c r="F203" s="1">
-        <v>53.26</v>
+        <v>33.26</v>
       </c>
       <c r="G203" s="1">
         <v>1</v>
@@ -9023,15 +9374,15 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>17</v>
@@ -9052,24 +9403,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E205" s="1">
-        <v>11.32</v>
+        <v>53.26</v>
       </c>
       <c r="F205" s="1">
-        <v>135.84</v>
+        <v>53.26</v>
       </c>
       <c r="G205" s="1">
         <v>1</v>
@@ -9081,15 +9432,15 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>17</v>
@@ -9110,15 +9461,15 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>17</v>
@@ -9139,24 +9490,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E208" s="1">
-        <v>8.6</v>
+        <v>11.32</v>
       </c>
       <c r="F208" s="1">
-        <v>103.2</v>
+        <v>135.84</v>
       </c>
       <c r="G208" s="1">
         <v>1</v>
@@ -9170,13 +9521,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>17</v>
@@ -9199,13 +9550,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>201</v>
+        <v>392</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>17</v>
@@ -9228,22 +9579,22 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>393</v>
+        <v>201</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E211" s="1">
-        <v>16.599999999999998</v>
+        <v>8.6</v>
       </c>
       <c r="F211" s="1">
-        <v>99.6</v>
+        <v>103.2</v>
       </c>
       <c r="G211" s="1">
         <v>1</v>
@@ -9257,13 +9608,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>17</v>
@@ -9286,22 +9637,22 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>201</v>
+        <v>394</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E213" s="1">
-        <v>17.260000000000002</v>
+        <v>16.599999999999998</v>
       </c>
       <c r="F213" s="1">
-        <v>103.56</v>
+        <v>99.6</v>
       </c>
       <c r="G213" s="1">
         <v>1</v>
@@ -9315,22 +9666,22 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>395</v>
+        <v>201</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E214" s="1">
-        <v>28.5</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F214" s="1">
-        <v>28.5</v>
+        <v>103.56</v>
       </c>
       <c r="G214" s="1">
         <v>1</v>
@@ -9344,13 +9695,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>200</v>
+        <v>395</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>17</v>
@@ -9371,24 +9722,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>396</v>
+        <v>200</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E216" s="1">
-        <v>34.4</v>
+        <v>28.5</v>
       </c>
       <c r="F216" s="1">
-        <v>34.4</v>
+        <v>28.5</v>
       </c>
       <c r="G216" s="1">
         <v>1</v>
@@ -9400,24 +9751,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E217" s="1">
-        <v>43.9</v>
+        <v>34.4</v>
       </c>
       <c r="F217" s="1">
-        <v>43.9</v>
+        <v>34.4</v>
       </c>
       <c r="G217" s="1">
         <v>1</v>
@@ -9431,13 +9782,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>200</v>
+        <v>395</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>17</v>
@@ -9460,22 +9811,22 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E219" s="1">
-        <v>62</v>
+        <v>43.9</v>
       </c>
       <c r="F219" s="1">
-        <v>62</v>
+        <v>43.9</v>
       </c>
       <c r="G219" s="1">
         <v>1</v>
@@ -9489,13 +9840,13 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>17</v>
@@ -9518,22 +9869,22 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E221" s="1">
-        <v>7.94</v>
+        <v>62</v>
       </c>
       <c r="F221" s="1">
-        <v>95.28</v>
+        <v>62</v>
       </c>
       <c r="G221" s="1">
         <v>1</v>
@@ -9547,13 +9898,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>17</v>
@@ -9576,13 +9927,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>17</v>
@@ -9605,13 +9956,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>17</v>
@@ -9634,22 +9985,22 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E225" s="1">
-        <v>17.260000000000002</v>
+        <v>7.94</v>
       </c>
       <c r="F225" s="1">
-        <v>103.56</v>
+        <v>95.28</v>
       </c>
       <c r="G225" s="1">
         <v>1</v>
@@ -9663,13 +10014,13 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>17</v>
@@ -9690,24 +10041,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>397</v>
+        <v>208</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E227" s="1">
-        <v>59.9</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F227" s="1">
-        <v>59.9</v>
+        <v>103.56</v>
       </c>
       <c r="G227" s="1">
         <v>1</v>
@@ -9721,13 +10072,13 @@
     </row>
     <row r="228" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>17</v>
@@ -9750,22 +10101,22 @@
     </row>
     <row r="229" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E229" s="1">
-        <v>23.9</v>
+        <v>59.9</v>
       </c>
       <c r="F229" s="1">
-        <v>23.9</v>
+        <v>59.9</v>
       </c>
       <c r="G229" s="1">
         <v>1</v>
@@ -9779,22 +10130,22 @@
     </row>
     <row r="230" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E230" s="1">
-        <v>26.6</v>
+        <v>23.9</v>
       </c>
       <c r="F230" s="1">
-        <v>26.6</v>
+        <v>23.9</v>
       </c>
       <c r="G230" s="1">
         <v>1</v>
@@ -9806,24 +10157,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E231" s="1">
-        <v>42.78</v>
+        <v>26.6</v>
       </c>
       <c r="F231" s="1">
-        <v>42.78</v>
+        <v>26.6</v>
       </c>
       <c r="G231" s="1">
         <v>1</v>
@@ -9837,22 +10188,22 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E232" s="1">
-        <v>56.9</v>
+        <v>42.78</v>
       </c>
       <c r="F232" s="1">
-        <v>56.9</v>
+        <v>42.78</v>
       </c>
       <c r="G232" s="1">
         <v>1</v>
@@ -9866,22 +10217,22 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E233" s="1">
-        <v>67.7</v>
+        <v>56.9</v>
       </c>
       <c r="F233" s="1">
-        <v>67.7</v>
+        <v>56.9</v>
       </c>
       <c r="G233" s="1">
         <v>1</v>
@@ -9895,22 +10246,22 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E234" s="1">
-        <v>2.4500000000000002</v>
+        <v>67.7</v>
       </c>
       <c r="F234" s="1">
-        <v>73.5</v>
+        <v>67.7</v>
       </c>
       <c r="G234" s="1">
         <v>1</v>
@@ -9924,13 +10275,13 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>17</v>
@@ -9953,22 +10304,22 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>215</v>
+        <v>404</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E236" s="1">
-        <v>1.6194444444444445</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F236" s="1">
-        <v>58.3</v>
+        <v>73.5</v>
       </c>
       <c r="G236" s="1">
         <v>1</v>
@@ -9982,13 +10333,13 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>17</v>
@@ -10011,13 +10362,13 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>17</v>
@@ -10040,13 +10391,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>17</v>
@@ -10069,22 +10420,22 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E240" s="1">
-        <v>6.81</v>
+        <v>1.6194444444444445</v>
       </c>
       <c r="F240" s="1">
-        <v>81.72</v>
+        <v>58.3</v>
       </c>
       <c r="G240" s="1">
         <v>1</v>
@@ -10098,13 +10449,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>17</v>
@@ -10127,22 +10478,22 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>405</v>
+        <v>219</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E242" s="1">
-        <v>13.26</v>
+        <v>6.81</v>
       </c>
       <c r="F242" s="1">
-        <v>159.12</v>
+        <v>81.72</v>
       </c>
       <c r="G242" s="1">
         <v>1</v>
@@ -10156,13 +10507,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>17</v>
@@ -10185,22 +10536,22 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E244" s="1">
-        <v>3.69</v>
+        <v>13.26</v>
       </c>
       <c r="F244" s="1">
-        <v>44.28</v>
+        <v>159.12</v>
       </c>
       <c r="G244" s="1">
         <v>1</v>
@@ -10214,13 +10565,13 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>17</v>
@@ -10243,22 +10594,22 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>221</v>
+        <v>408</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E246" s="1">
-        <v>8.6875</v>
+        <v>3.69</v>
       </c>
       <c r="F246" s="1">
-        <v>104.25</v>
+        <v>44.28</v>
       </c>
       <c r="G246" s="1">
         <v>1</v>
@@ -10272,13 +10623,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>17</v>
@@ -10299,24 +10650,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E248" s="1">
-        <v>2.29</v>
+        <v>8.6875</v>
       </c>
       <c r="F248" s="1">
-        <v>45.8</v>
+        <v>104.25</v>
       </c>
       <c r="G248" s="1">
         <v>1</v>
@@ -10330,13 +10681,13 @@
     </row>
     <row r="249" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>17</v>
@@ -10359,13 +10710,13 @@
     </row>
     <row r="250" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>17</v>
@@ -10388,22 +10739,22 @@
     </row>
     <row r="251" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E251" s="1">
-        <v>4.0600000000000005</v>
+        <v>2.29</v>
       </c>
       <c r="F251" s="1">
-        <v>81.2</v>
+        <v>45.8</v>
       </c>
       <c r="G251" s="1">
         <v>1</v>
@@ -10417,13 +10768,13 @@
     </row>
     <row r="252" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>17</v>
@@ -10446,13 +10797,13 @@
     </row>
     <row r="253" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>17</v>
@@ -10475,22 +10826,22 @@
     </row>
     <row r="254" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E254" s="1">
-        <v>9.35</v>
+        <v>4.0600000000000005</v>
       </c>
       <c r="F254" s="1">
-        <v>112.2</v>
+        <v>81.2</v>
       </c>
       <c r="G254" s="1">
         <v>1</v>
@@ -10504,22 +10855,22 @@
     </row>
     <row r="255" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>409</v>
+        <v>226</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E255" s="1">
-        <v>5.2299999999999995</v>
+        <v>9.35</v>
       </c>
       <c r="F255" s="1">
-        <v>62.76</v>
+        <v>112.2</v>
       </c>
       <c r="G255" s="1">
         <v>1</v>
@@ -10533,13 +10884,13 @@
     </row>
     <row r="256" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>17</v>
@@ -10562,13 +10913,13 @@
     </row>
     <row r="257" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>17</v>
@@ -10589,24 +10940,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E258" s="1">
-        <v>5.8233333333333333</v>
+        <v>5.2299999999999995</v>
       </c>
       <c r="F258" s="1">
-        <v>69.88</v>
+        <v>62.76</v>
       </c>
       <c r="G258" s="1">
         <v>1</v>
@@ -10620,22 +10971,22 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E259" s="1">
-        <v>7.5799999999999992</v>
+        <v>5.8233333333333333</v>
       </c>
       <c r="F259" s="1">
-        <v>90.96</v>
+        <v>69.88</v>
       </c>
       <c r="G259" s="1">
         <v>1</v>
@@ -10649,22 +11000,22 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E260" s="1">
-        <v>9.35</v>
+        <v>7.5799999999999992</v>
       </c>
       <c r="F260" s="1">
-        <v>56.1</v>
+        <v>90.96</v>
       </c>
       <c r="G260" s="1">
         <v>1</v>
@@ -10678,22 +11029,22 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>233</v>
+        <v>414</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E261" s="1">
-        <v>9.93</v>
+        <v>9.35</v>
       </c>
       <c r="F261" s="1">
-        <v>119.16</v>
+        <v>56.1</v>
       </c>
       <c r="G261" s="1">
         <v>1</v>
@@ -10707,22 +11058,22 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E262" s="1">
-        <v>39.9</v>
+        <v>9.93</v>
       </c>
       <c r="F262" s="1">
-        <v>159.6</v>
+        <v>119.16</v>
       </c>
       <c r="G262" s="1">
         <v>1</v>
@@ -10736,22 +11087,22 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>415</v>
+        <v>234</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E263" s="1">
-        <v>4.9000000000000004</v>
+        <v>39.9</v>
       </c>
       <c r="F263" s="1">
-        <v>24.5</v>
+        <v>159.6</v>
       </c>
       <c r="G263" s="1">
         <v>1</v>
@@ -10765,13 +11116,13 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>17</v>
@@ -10794,22 +11145,22 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>237</v>
+        <v>416</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E265" s="1">
-        <v>9.35</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F265" s="1">
-        <v>56.1</v>
+        <v>24.5</v>
       </c>
       <c r="G265" s="1">
         <v>1</v>
@@ -10823,13 +11174,13 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>17</v>
@@ -10852,13 +11203,13 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>17</v>
@@ -10867,7 +11218,7 @@
         <v>9.35</v>
       </c>
       <c r="F267" s="1">
-        <v>112.2</v>
+        <v>56.1</v>
       </c>
       <c r="G267" s="1">
         <v>1</v>
@@ -10881,13 +11232,13 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>17</v>
@@ -10910,13 +11261,13 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>17</v>
@@ -10939,13 +11290,13 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>17</v>
@@ -10968,22 +11319,22 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>417</v>
+        <v>242</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E271" s="1">
-        <v>9.3533333333333335</v>
+        <v>9.35</v>
       </c>
       <c r="F271" s="1">
-        <v>112.24</v>
+        <v>112.2</v>
       </c>
       <c r="G271" s="1">
         <v>1</v>
@@ -10997,22 +11348,22 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>244</v>
+        <v>417</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E272" s="1">
-        <v>11.705833333333333</v>
+        <v>9.3533333333333335</v>
       </c>
       <c r="F272" s="1">
-        <v>140.47</v>
+        <v>112.24</v>
       </c>
       <c r="G272" s="1">
         <v>1</v>
@@ -11026,22 +11377,22 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E273" s="1">
-        <v>5.5</v>
+        <v>11.705833333333333</v>
       </c>
       <c r="F273" s="1">
-        <v>66</v>
+        <v>140.47</v>
       </c>
       <c r="G273" s="1">
         <v>1</v>
@@ -11055,13 +11406,13 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>17</v>
@@ -11084,22 +11435,22 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E275" s="1">
-        <v>2.7216666666666662</v>
+        <v>5.5</v>
       </c>
       <c r="F275" s="1">
-        <v>32.659999999999997</v>
+        <v>66</v>
       </c>
       <c r="G275" s="1">
         <v>1</v>
@@ -11113,22 +11464,22 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E276" s="1">
-        <v>11.049999999999999</v>
+        <v>2.7216666666666662</v>
       </c>
       <c r="F276" s="1">
-        <v>132.6</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="G276" s="1">
         <v>1</v>
@@ -11142,22 +11493,22 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E277" s="1">
-        <v>7.7216666666666667</v>
+        <v>11.049999999999999</v>
       </c>
       <c r="F277" s="1">
-        <v>46.33</v>
+        <v>132.6</v>
       </c>
       <c r="G277" s="1">
         <v>1</v>
@@ -11171,22 +11522,22 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E278" s="1">
-        <v>5.5</v>
+        <v>7.7216666666666667</v>
       </c>
       <c r="F278" s="1">
-        <v>66</v>
+        <v>46.33</v>
       </c>
       <c r="G278" s="1">
         <v>1</v>
@@ -11200,22 +11551,22 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E279" s="1">
-        <v>7.7216666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="F279" s="1">
-        <v>92.66</v>
+        <v>66</v>
       </c>
       <c r="G279" s="1">
         <v>1</v>
@@ -11229,22 +11580,22 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E280" s="1">
-        <v>8.8324999999999996</v>
+        <v>7.7216666666666667</v>
       </c>
       <c r="F280" s="1">
-        <v>105.99</v>
+        <v>92.66</v>
       </c>
       <c r="G280" s="1">
         <v>1</v>
@@ -11258,22 +11609,22 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E281" s="1">
-        <v>10.5</v>
+        <v>8.8324999999999996</v>
       </c>
       <c r="F281" s="1">
-        <v>126</v>
+        <v>105.99</v>
       </c>
       <c r="G281" s="1">
         <v>1</v>
@@ -11287,22 +11638,22 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E282" s="1">
-        <v>11.055</v>
+        <v>10.5</v>
       </c>
       <c r="F282" s="1">
-        <v>132.66</v>
+        <v>126</v>
       </c>
       <c r="G282" s="1">
         <v>1</v>
@@ -11316,22 +11667,22 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>418</v>
+        <v>254</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E283" s="1">
-        <v>6.6108333333333329</v>
+        <v>11.055</v>
       </c>
       <c r="F283" s="1">
-        <v>79.33</v>
+        <v>132.66</v>
       </c>
       <c r="G283" s="1">
         <v>1</v>
@@ -11345,22 +11696,22 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E284" s="1">
-        <v>11.055</v>
+        <v>6.6108333333333329</v>
       </c>
       <c r="F284" s="1">
-        <v>132.66</v>
+        <v>79.33</v>
       </c>
       <c r="G284" s="1">
         <v>1</v>
@@ -11372,24 +11723,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>419</v>
+        <v>256</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E285" s="1">
-        <v>4.9441666666666668</v>
+        <v>11.055</v>
       </c>
       <c r="F285" s="1">
-        <v>59.33</v>
+        <v>132.66</v>
       </c>
       <c r="G285" s="1">
         <v>1</v>
@@ -11403,22 +11754,22 @@
     </row>
     <row r="286" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E286" s="1">
-        <v>7.7216666666666667</v>
+        <v>4.9441666666666668</v>
       </c>
       <c r="F286" s="1">
-        <v>92.66</v>
+        <v>59.33</v>
       </c>
       <c r="G286" s="1">
         <v>1</v>
@@ -11432,22 +11783,22 @@
     </row>
     <row r="287" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E287" s="1">
-        <v>14.38</v>
+        <v>7.7216666666666667</v>
       </c>
       <c r="F287" s="1">
-        <v>172.56</v>
+        <v>92.66</v>
       </c>
       <c r="G287" s="1">
         <v>1</v>
@@ -11461,22 +11812,22 @@
     </row>
     <row r="288" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E288" s="1">
-        <v>11.055</v>
+        <v>14.38</v>
       </c>
       <c r="F288" s="1">
-        <v>132.66</v>
+        <v>172.56</v>
       </c>
       <c r="G288" s="1">
         <v>1</v>
@@ -11490,22 +11841,22 @@
     </row>
     <row r="289" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>421</v>
+        <v>260</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E289" s="1">
-        <v>8.8324999999999996</v>
+        <v>11.055</v>
       </c>
       <c r="F289" s="1">
-        <v>105.99</v>
+        <v>132.66</v>
       </c>
       <c r="G289" s="1">
         <v>1</v>
@@ -11519,13 +11870,13 @@
     </row>
     <row r="290" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>262</v>
+        <v>421</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>17</v>
@@ -11548,22 +11899,22 @@
     </row>
     <row r="291" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E291" s="1">
-        <v>11.055</v>
+        <v>8.8324999999999996</v>
       </c>
       <c r="F291" s="1">
-        <v>132.66</v>
+        <v>105.99</v>
       </c>
       <c r="G291" s="1">
         <v>1</v>
@@ -11575,24 +11926,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E292" s="1">
-        <v>16.610833333333336</v>
+        <v>11.055</v>
       </c>
       <c r="F292" s="1">
-        <v>199.33</v>
+        <v>132.66</v>
       </c>
       <c r="G292" s="1">
         <v>1</v>
@@ -11604,24 +11955,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E293" s="1">
-        <v>22.165833333333335</v>
+        <v>16.610833333333336</v>
       </c>
       <c r="F293" s="1">
-        <v>265.99</v>
+        <v>199.33</v>
       </c>
       <c r="G293" s="1">
         <v>1</v>
@@ -11635,22 +11986,22 @@
     </row>
     <row r="294" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>422</v>
+        <v>265</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E294" s="1">
-        <v>5.5</v>
+        <v>22.165833333333335</v>
       </c>
       <c r="F294" s="1">
-        <v>66</v>
+        <v>265.99</v>
       </c>
       <c r="G294" s="1">
         <v>1</v>
@@ -11664,22 +12015,22 @@
     </row>
     <row r="295" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>267</v>
+        <v>422</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E295" s="1">
-        <v>11.055</v>
+        <v>5.5</v>
       </c>
       <c r="F295" s="1">
-        <v>132.66</v>
+        <v>66</v>
       </c>
       <c r="G295" s="1">
         <v>1</v>
@@ -11693,22 +12044,22 @@
     </row>
     <row r="296" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E296" s="1">
-        <v>11.049999999999999</v>
+        <v>11.055</v>
       </c>
       <c r="F296" s="1">
-        <v>132.6</v>
+        <v>132.66</v>
       </c>
       <c r="G296" s="1">
         <v>1</v>
@@ -11722,22 +12073,22 @@
     </row>
     <row r="297" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E297" s="1">
-        <v>16.610833333333336</v>
+        <v>11.049999999999999</v>
       </c>
       <c r="F297" s="1">
-        <v>199.33</v>
+        <v>132.6</v>
       </c>
       <c r="G297" s="1">
         <v>1</v>
@@ -11749,24 +12100,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E298" s="1">
-        <v>15.5</v>
+        <v>16.610833333333336</v>
       </c>
       <c r="F298" s="1">
-        <v>186</v>
+        <v>199.33</v>
       </c>
       <c r="G298" s="1">
         <v>1</v>
@@ -11780,22 +12131,22 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E299" s="1">
-        <v>16.055</v>
+        <v>15.5</v>
       </c>
       <c r="F299" s="1">
-        <v>192.66</v>
+        <v>186</v>
       </c>
       <c r="G299" s="1">
         <v>1</v>
@@ -11807,24 +12158,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E300" s="1">
-        <v>11.055</v>
+        <v>16.055</v>
       </c>
       <c r="F300" s="1">
-        <v>132.66</v>
+        <v>192.66</v>
       </c>
       <c r="G300" s="1">
         <v>1</v>
@@ -11836,24 +12187,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E301" s="1">
-        <v>22.166</v>
+        <v>11.055</v>
       </c>
       <c r="F301" s="1">
-        <v>221.66</v>
+        <v>132.66</v>
       </c>
       <c r="G301" s="1">
         <v>1</v>
@@ -11867,59 +12218,88 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C302" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E302" s="1">
+        <v>22.166</v>
+      </c>
+      <c r="F302" s="1">
+        <v>221.66</v>
+      </c>
+      <c r="G302" s="1">
+        <v>1</v>
+      </c>
+      <c r="H302" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I302" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C303" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D302" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E302" s="1">
+      <c r="D303" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E303" s="1">
         <v>16.611000000000001</v>
       </c>
-      <c r="F302" s="1">
+      <c r="F303" s="1">
         <v>332.22</v>
       </c>
-      <c r="G302" s="1">
-        <v>1</v>
-      </c>
-      <c r="H302" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I302" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B303" s="1"/>
-      <c r="C303" s="1" t="s">
+      <c r="G303" s="1">
+        <v>1</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I303" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B304" s="1"/>
+      <c r="C304" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D303" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E303" s="1">
+      <c r="D304" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E304" s="1">
         <v>19.943999999999999</v>
       </c>
-      <c r="F303" s="1">
+      <c r="F304" s="1">
         <v>398.88</v>
       </c>
-      <c r="G303" s="1">
-        <v>1</v>
-      </c>
-      <c r="H303" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I303" s="1">
+      <c r="G304" s="1">
+        <v>1</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I304" s="1">
         <v>0.03</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J195" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
+  <autoFilter ref="A1:J304" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF044150-F649-4216-A33D-2F1800074D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D612AD1-391F-4AF3-B151-FAF6DF726836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="427">
   <si>
     <t>categoria</t>
   </si>
@@ -2188,9 +2188,6 @@
   </si>
   <si>
     <t>35</t>
-  </si>
-  <si>
-    <t>1,51</t>
   </si>
 </sst>
 </file>
@@ -9124,8 +9121,8 @@
       <c r="D195" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E195" s="1" t="s">
-        <v>427</v>
+      <c r="E195" s="1">
+        <v>1.51</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>425</v>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D612AD1-391F-4AF3-B151-FAF6DF726836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ACE905-0D14-4376-82DD-D18D25B2DCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$303</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="428">
   <si>
     <t>categoria</t>
   </si>
@@ -2178,9 +2178,6 @@
     </r>
   </si>
   <si>
-    <t>01030538</t>
-  </si>
-  <si>
     <t>Doce WK Leite Ninho</t>
   </si>
   <si>
@@ -2188,6 +2185,12 @@
   </si>
   <si>
     <t>35</t>
+  </si>
+  <si>
+    <t>1030538</t>
+  </si>
+  <si>
+    <t>17,65</t>
   </si>
 </sst>
 </file>
@@ -9110,73 +9113,71 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>423</v>
+        <v>168</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>424</v>
+        <v>170</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E195" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="H195" s="1"/>
-      <c r="I195" s="1"/>
-      <c r="J195">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="L195" s="1"/>
-      <c r="M195" s="1"/>
-      <c r="N195" s="1"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="F195" s="1">
+        <v>50</v>
+      </c>
+      <c r="G195" s="1">
+        <v>6</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I195" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>168</v>
+        <v>277</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>169</v>
+        <v>383</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>170</v>
+        <v>384</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="E196" s="1">
-        <v>50</v>
+        <v>9.27</v>
       </c>
       <c r="F196" s="1">
-        <v>50</v>
+        <v>103.2</v>
       </c>
       <c r="G196" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I196" s="1">
-        <v>10</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="197" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>17</v>
@@ -9197,24 +9198,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="198" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>385</v>
+        <v>192</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E198" s="1">
-        <v>9.27</v>
+        <v>9.2666666666666675</v>
       </c>
       <c r="F198" s="1">
-        <v>103.2</v>
+        <v>111.2</v>
       </c>
       <c r="G198" s="1">
         <v>1</v>
@@ -9227,23 +9228,23 @@
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="1" t="s">
-        <v>279</v>
+      <c r="A199" s="1">
+        <v>20199</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E199" s="1">
-        <v>9.2666666666666675</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F199" s="1">
-        <v>111.2</v>
+        <v>103.56</v>
       </c>
       <c r="G199" s="1">
         <v>1</v>
@@ -9256,14 +9257,14 @@
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="1">
-        <v>20199</v>
+      <c r="A200" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>17</v>
@@ -9286,22 +9287,22 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E201" s="1">
-        <v>17.260000000000002</v>
+        <v>33.26</v>
       </c>
       <c r="F201" s="1">
-        <v>103.56</v>
+        <v>33.26</v>
       </c>
       <c r="G201" s="1">
         <v>1</v>
@@ -9315,13 +9316,13 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>190</v>
+        <v>386</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>17</v>
@@ -9344,22 +9345,22 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E203" s="1">
-        <v>33.26</v>
+        <v>53.26</v>
       </c>
       <c r="F203" s="1">
-        <v>33.26</v>
+        <v>53.26</v>
       </c>
       <c r="G203" s="1">
         <v>1</v>
@@ -9373,13 +9374,13 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>17</v>
@@ -9402,22 +9403,22 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E205" s="1">
-        <v>53.26</v>
+        <v>11.32</v>
       </c>
       <c r="F205" s="1">
-        <v>53.26</v>
+        <v>135.84</v>
       </c>
       <c r="G205" s="1">
         <v>1</v>
@@ -9431,13 +9432,13 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>17</v>
@@ -9460,13 +9461,13 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>17</v>
@@ -9489,22 +9490,22 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E208" s="1">
-        <v>11.32</v>
+        <v>8.6</v>
       </c>
       <c r="F208" s="1">
-        <v>135.84</v>
+        <v>103.2</v>
       </c>
       <c r="G208" s="1">
         <v>1</v>
@@ -9518,13 +9519,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>17</v>
@@ -9547,13 +9548,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>392</v>
+        <v>201</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>17</v>
@@ -9576,22 +9577,22 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>201</v>
+        <v>393</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E211" s="1">
-        <v>8.6</v>
+        <v>16.599999999999998</v>
       </c>
       <c r="F211" s="1">
-        <v>103.2</v>
+        <v>99.6</v>
       </c>
       <c r="G211" s="1">
         <v>1</v>
@@ -9605,13 +9606,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>17</v>
@@ -9634,22 +9635,22 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>394</v>
+        <v>201</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E213" s="1">
-        <v>16.599999999999998</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F213" s="1">
-        <v>99.6</v>
+        <v>103.56</v>
       </c>
       <c r="G213" s="1">
         <v>1</v>
@@ -9663,22 +9664,22 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>201</v>
+        <v>395</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E214" s="1">
-        <v>17.260000000000002</v>
+        <v>28.5</v>
       </c>
       <c r="F214" s="1">
-        <v>103.56</v>
+        <v>28.5</v>
       </c>
       <c r="G214" s="1">
         <v>1</v>
@@ -9692,13 +9693,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>395</v>
+        <v>200</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>17</v>
@@ -9719,24 +9720,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>200</v>
+        <v>396</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E216" s="1">
-        <v>28.5</v>
+        <v>34.4</v>
       </c>
       <c r="F216" s="1">
-        <v>28.5</v>
+        <v>34.4</v>
       </c>
       <c r="G216" s="1">
         <v>1</v>
@@ -9748,24 +9749,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E217" s="1">
-        <v>34.4</v>
+        <v>43.9</v>
       </c>
       <c r="F217" s="1">
-        <v>34.4</v>
+        <v>43.9</v>
       </c>
       <c r="G217" s="1">
         <v>1</v>
@@ -9779,13 +9780,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>395</v>
+        <v>200</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>17</v>
@@ -9808,22 +9809,22 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E219" s="1">
-        <v>43.9</v>
+        <v>62</v>
       </c>
       <c r="F219" s="1">
-        <v>43.9</v>
+        <v>62</v>
       </c>
       <c r="G219" s="1">
         <v>1</v>
@@ -9837,13 +9838,13 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>17</v>
@@ -9866,22 +9867,22 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E221" s="1">
-        <v>62</v>
+        <v>7.94</v>
       </c>
       <c r="F221" s="1">
-        <v>62</v>
+        <v>95.28</v>
       </c>
       <c r="G221" s="1">
         <v>1</v>
@@ -9895,13 +9896,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>17</v>
@@ -9924,13 +9925,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>17</v>
@@ -9953,13 +9954,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>17</v>
@@ -9982,22 +9983,22 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E225" s="1">
-        <v>7.94</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F225" s="1">
-        <v>95.28</v>
+        <v>103.56</v>
       </c>
       <c r="G225" s="1">
         <v>1</v>
@@ -10011,13 +10012,13 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>17</v>
@@ -10038,24 +10039,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>208</v>
+        <v>397</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E227" s="1">
-        <v>17.260000000000002</v>
+        <v>59.9</v>
       </c>
       <c r="F227" s="1">
-        <v>103.56</v>
+        <v>59.9</v>
       </c>
       <c r="G227" s="1">
         <v>1</v>
@@ -10069,13 +10070,13 @@
     </row>
     <row r="228" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>17</v>
@@ -10098,22 +10099,22 @@
     </row>
     <row r="229" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E229" s="1">
-        <v>59.9</v>
+        <v>23.9</v>
       </c>
       <c r="F229" s="1">
-        <v>59.9</v>
+        <v>23.9</v>
       </c>
       <c r="G229" s="1">
         <v>1</v>
@@ -10127,22 +10128,22 @@
     </row>
     <row r="230" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E230" s="1">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="F230" s="1">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="G230" s="1">
         <v>1</v>
@@ -10154,24 +10155,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E231" s="1">
-        <v>26.6</v>
+        <v>42.78</v>
       </c>
       <c r="F231" s="1">
-        <v>26.6</v>
+        <v>42.78</v>
       </c>
       <c r="G231" s="1">
         <v>1</v>
@@ -10185,22 +10186,22 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E232" s="1">
-        <v>42.78</v>
+        <v>56.9</v>
       </c>
       <c r="F232" s="1">
-        <v>42.78</v>
+        <v>56.9</v>
       </c>
       <c r="G232" s="1">
         <v>1</v>
@@ -10214,22 +10215,22 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E233" s="1">
-        <v>56.9</v>
+        <v>67.7</v>
       </c>
       <c r="F233" s="1">
-        <v>56.9</v>
+        <v>67.7</v>
       </c>
       <c r="G233" s="1">
         <v>1</v>
@@ -10243,22 +10244,22 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E234" s="1">
-        <v>67.7</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F234" s="1">
-        <v>67.7</v>
+        <v>73.5</v>
       </c>
       <c r="G234" s="1">
         <v>1</v>
@@ -10272,13 +10273,13 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>17</v>
@@ -10301,22 +10302,22 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>404</v>
+        <v>215</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E236" s="1">
-        <v>2.4500000000000002</v>
+        <v>1.6194444444444445</v>
       </c>
       <c r="F236" s="1">
-        <v>73.5</v>
+        <v>58.3</v>
       </c>
       <c r="G236" s="1">
         <v>1</v>
@@ -10330,13 +10331,13 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>17</v>
@@ -10359,13 +10360,13 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>17</v>
@@ -10388,13 +10389,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>17</v>
@@ -10417,22 +10418,22 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E240" s="1">
-        <v>1.6194444444444445</v>
+        <v>6.81</v>
       </c>
       <c r="F240" s="1">
-        <v>58.3</v>
+        <v>81.72</v>
       </c>
       <c r="G240" s="1">
         <v>1</v>
@@ -10446,13 +10447,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>17</v>
@@ -10475,22 +10476,22 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>219</v>
+        <v>405</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E242" s="1">
-        <v>6.81</v>
+        <v>13.26</v>
       </c>
       <c r="F242" s="1">
-        <v>81.72</v>
+        <v>159.12</v>
       </c>
       <c r="G242" s="1">
         <v>1</v>
@@ -10504,13 +10505,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>17</v>
@@ -10533,22 +10534,22 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E244" s="1">
-        <v>13.26</v>
+        <v>3.69</v>
       </c>
       <c r="F244" s="1">
-        <v>159.12</v>
+        <v>44.28</v>
       </c>
       <c r="G244" s="1">
         <v>1</v>
@@ -10562,13 +10563,13 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>17</v>
@@ -10591,22 +10592,22 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>408</v>
+        <v>221</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E246" s="1">
-        <v>3.69</v>
+        <v>8.6875</v>
       </c>
       <c r="F246" s="1">
-        <v>44.28</v>
+        <v>104.25</v>
       </c>
       <c r="G246" s="1">
         <v>1</v>
@@ -10620,13 +10621,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>17</v>
@@ -10647,24 +10648,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E248" s="1">
-        <v>8.6875</v>
+        <v>2.29</v>
       </c>
       <c r="F248" s="1">
-        <v>104.25</v>
+        <v>45.8</v>
       </c>
       <c r="G248" s="1">
         <v>1</v>
@@ -10678,13 +10679,13 @@
     </row>
     <row r="249" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>17</v>
@@ -10707,13 +10708,13 @@
     </row>
     <row r="250" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>17</v>
@@ -10736,22 +10737,22 @@
     </row>
     <row r="251" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E251" s="1">
-        <v>2.29</v>
+        <v>4.0600000000000005</v>
       </c>
       <c r="F251" s="1">
-        <v>45.8</v>
+        <v>81.2</v>
       </c>
       <c r="G251" s="1">
         <v>1</v>
@@ -10765,13 +10766,13 @@
     </row>
     <row r="252" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>17</v>
@@ -10794,13 +10795,13 @@
     </row>
     <row r="253" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>17</v>
@@ -10823,22 +10824,22 @@
     </row>
     <row r="254" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E254" s="1">
-        <v>4.0600000000000005</v>
+        <v>9.35</v>
       </c>
       <c r="F254" s="1">
-        <v>81.2</v>
+        <v>112.2</v>
       </c>
       <c r="G254" s="1">
         <v>1</v>
@@ -10852,22 +10853,22 @@
     </row>
     <row r="255" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>226</v>
+        <v>409</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E255" s="1">
-        <v>9.35</v>
+        <v>5.2299999999999995</v>
       </c>
       <c r="F255" s="1">
-        <v>112.2</v>
+        <v>62.76</v>
       </c>
       <c r="G255" s="1">
         <v>1</v>
@@ -10881,13 +10882,13 @@
     </row>
     <row r="256" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>17</v>
@@ -10910,13 +10911,13 @@
     </row>
     <row r="257" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>17</v>
@@ -10937,24 +10938,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E258" s="1">
-        <v>5.2299999999999995</v>
+        <v>5.8233333333333333</v>
       </c>
       <c r="F258" s="1">
-        <v>62.76</v>
+        <v>69.88</v>
       </c>
       <c r="G258" s="1">
         <v>1</v>
@@ -10968,22 +10969,22 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E259" s="1">
-        <v>5.8233333333333333</v>
+        <v>7.5799999999999992</v>
       </c>
       <c r="F259" s="1">
-        <v>69.88</v>
+        <v>90.96</v>
       </c>
       <c r="G259" s="1">
         <v>1</v>
@@ -10997,22 +10998,22 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E260" s="1">
-        <v>7.5799999999999992</v>
+        <v>9.35</v>
       </c>
       <c r="F260" s="1">
-        <v>90.96</v>
+        <v>56.1</v>
       </c>
       <c r="G260" s="1">
         <v>1</v>
@@ -11026,22 +11027,22 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>414</v>
+        <v>233</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E261" s="1">
-        <v>9.35</v>
+        <v>9.93</v>
       </c>
       <c r="F261" s="1">
-        <v>56.1</v>
+        <v>119.16</v>
       </c>
       <c r="G261" s="1">
         <v>1</v>
@@ -11055,22 +11056,22 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E262" s="1">
-        <v>9.93</v>
+        <v>39.9</v>
       </c>
       <c r="F262" s="1">
-        <v>119.16</v>
+        <v>159.6</v>
       </c>
       <c r="G262" s="1">
         <v>1</v>
@@ -11084,22 +11085,22 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>234</v>
+        <v>415</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E263" s="1">
-        <v>39.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F263" s="1">
-        <v>159.6</v>
+        <v>24.5</v>
       </c>
       <c r="G263" s="1">
         <v>1</v>
@@ -11113,13 +11114,13 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>17</v>
@@ -11142,22 +11143,22 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>416</v>
+        <v>237</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E265" s="1">
-        <v>4.9000000000000004</v>
+        <v>9.35</v>
       </c>
       <c r="F265" s="1">
-        <v>24.5</v>
+        <v>56.1</v>
       </c>
       <c r="G265" s="1">
         <v>1</v>
@@ -11171,13 +11172,13 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>17</v>
@@ -11200,13 +11201,13 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>17</v>
@@ -11215,7 +11216,7 @@
         <v>9.35</v>
       </c>
       <c r="F267" s="1">
-        <v>56.1</v>
+        <v>112.2</v>
       </c>
       <c r="G267" s="1">
         <v>1</v>
@@ -11229,13 +11230,13 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>17</v>
@@ -11258,13 +11259,13 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>17</v>
@@ -11287,13 +11288,13 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>17</v>
@@ -11316,22 +11317,22 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>242</v>
+        <v>417</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E271" s="1">
-        <v>9.35</v>
+        <v>9.3533333333333335</v>
       </c>
       <c r="F271" s="1">
-        <v>112.2</v>
+        <v>112.24</v>
       </c>
       <c r="G271" s="1">
         <v>1</v>
@@ -11345,22 +11346,22 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>417</v>
+        <v>244</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E272" s="1">
-        <v>9.3533333333333335</v>
+        <v>11.705833333333333</v>
       </c>
       <c r="F272" s="1">
-        <v>112.24</v>
+        <v>140.47</v>
       </c>
       <c r="G272" s="1">
         <v>1</v>
@@ -11374,22 +11375,22 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E273" s="1">
-        <v>11.705833333333333</v>
+        <v>5.5</v>
       </c>
       <c r="F273" s="1">
-        <v>140.47</v>
+        <v>66</v>
       </c>
       <c r="G273" s="1">
         <v>1</v>
@@ -11403,13 +11404,13 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>17</v>
@@ -11432,22 +11433,22 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E275" s="1">
-        <v>5.5</v>
+        <v>2.7216666666666662</v>
       </c>
       <c r="F275" s="1">
-        <v>66</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="G275" s="1">
         <v>1</v>
@@ -11461,22 +11462,22 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E276" s="1">
-        <v>2.7216666666666662</v>
+        <v>11.049999999999999</v>
       </c>
       <c r="F276" s="1">
-        <v>32.659999999999997</v>
+        <v>132.6</v>
       </c>
       <c r="G276" s="1">
         <v>1</v>
@@ -11490,22 +11491,22 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E277" s="1">
-        <v>11.049999999999999</v>
+        <v>7.7216666666666667</v>
       </c>
       <c r="F277" s="1">
-        <v>132.6</v>
+        <v>46.33</v>
       </c>
       <c r="G277" s="1">
         <v>1</v>
@@ -11519,22 +11520,22 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E278" s="1">
-        <v>7.7216666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="F278" s="1">
-        <v>46.33</v>
+        <v>66</v>
       </c>
       <c r="G278" s="1">
         <v>1</v>
@@ -11548,22 +11549,22 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E279" s="1">
-        <v>5.5</v>
+        <v>7.7216666666666667</v>
       </c>
       <c r="F279" s="1">
-        <v>66</v>
+        <v>92.66</v>
       </c>
       <c r="G279" s="1">
         <v>1</v>
@@ -11577,22 +11578,22 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E280" s="1">
-        <v>7.7216666666666667</v>
+        <v>8.8324999999999996</v>
       </c>
       <c r="F280" s="1">
-        <v>92.66</v>
+        <v>105.99</v>
       </c>
       <c r="G280" s="1">
         <v>1</v>
@@ -11606,22 +11607,22 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E281" s="1">
-        <v>8.8324999999999996</v>
+        <v>10.5</v>
       </c>
       <c r="F281" s="1">
-        <v>105.99</v>
+        <v>126</v>
       </c>
       <c r="G281" s="1">
         <v>1</v>
@@ -11635,22 +11636,22 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E282" s="1">
-        <v>10.5</v>
+        <v>11.055</v>
       </c>
       <c r="F282" s="1">
-        <v>126</v>
+        <v>132.66</v>
       </c>
       <c r="G282" s="1">
         <v>1</v>
@@ -11664,22 +11665,22 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>254</v>
+        <v>418</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E283" s="1">
-        <v>11.055</v>
+        <v>6.6108333333333329</v>
       </c>
       <c r="F283" s="1">
-        <v>132.66</v>
+        <v>79.33</v>
       </c>
       <c r="G283" s="1">
         <v>1</v>
@@ -11693,22 +11694,22 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>418</v>
+        <v>256</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E284" s="1">
-        <v>6.6108333333333329</v>
+        <v>11.055</v>
       </c>
       <c r="F284" s="1">
-        <v>79.33</v>
+        <v>132.66</v>
       </c>
       <c r="G284" s="1">
         <v>1</v>
@@ -11720,24 +11721,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>256</v>
+        <v>419</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E285" s="1">
-        <v>11.055</v>
+        <v>4.9441666666666668</v>
       </c>
       <c r="F285" s="1">
-        <v>132.66</v>
+        <v>59.33</v>
       </c>
       <c r="G285" s="1">
         <v>1</v>
@@ -11751,22 +11752,22 @@
     </row>
     <row r="286" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E286" s="1">
-        <v>4.9441666666666668</v>
+        <v>7.7216666666666667</v>
       </c>
       <c r="F286" s="1">
-        <v>59.33</v>
+        <v>92.66</v>
       </c>
       <c r="G286" s="1">
         <v>1</v>
@@ -11780,22 +11781,22 @@
     </row>
     <row r="287" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>420</v>
+        <v>259</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E287" s="1">
-        <v>7.7216666666666667</v>
+        <v>14.38</v>
       </c>
       <c r="F287" s="1">
-        <v>92.66</v>
+        <v>172.56</v>
       </c>
       <c r="G287" s="1">
         <v>1</v>
@@ -11809,22 +11810,22 @@
     </row>
     <row r="288" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E288" s="1">
-        <v>14.38</v>
+        <v>11.055</v>
       </c>
       <c r="F288" s="1">
-        <v>172.56</v>
+        <v>132.66</v>
       </c>
       <c r="G288" s="1">
         <v>1</v>
@@ -11838,22 +11839,22 @@
     </row>
     <row r="289" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>260</v>
+        <v>421</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E289" s="1">
-        <v>11.055</v>
+        <v>8.8324999999999996</v>
       </c>
       <c r="F289" s="1">
-        <v>132.66</v>
+        <v>105.99</v>
       </c>
       <c r="G289" s="1">
         <v>1</v>
@@ -11867,13 +11868,13 @@
     </row>
     <row r="290" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>421</v>
+        <v>262</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>17</v>
@@ -11896,22 +11897,22 @@
     </row>
     <row r="291" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E291" s="1">
-        <v>8.8324999999999996</v>
+        <v>11.055</v>
       </c>
       <c r="F291" s="1">
-        <v>105.99</v>
+        <v>132.66</v>
       </c>
       <c r="G291" s="1">
         <v>1</v>
@@ -11923,24 +11924,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E292" s="1">
-        <v>11.055</v>
+        <v>16.610833333333336</v>
       </c>
       <c r="F292" s="1">
-        <v>132.66</v>
+        <v>199.33</v>
       </c>
       <c r="G292" s="1">
         <v>1</v>
@@ -11952,24 +11953,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E293" s="1">
-        <v>16.610833333333336</v>
+        <v>22.165833333333335</v>
       </c>
       <c r="F293" s="1">
-        <v>199.33</v>
+        <v>265.99</v>
       </c>
       <c r="G293" s="1">
         <v>1</v>
@@ -11983,22 +11984,22 @@
     </row>
     <row r="294" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>265</v>
+        <v>422</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E294" s="1">
-        <v>22.165833333333335</v>
+        <v>5.5</v>
       </c>
       <c r="F294" s="1">
-        <v>265.99</v>
+        <v>66</v>
       </c>
       <c r="G294" s="1">
         <v>1</v>
@@ -12012,22 +12013,22 @@
     </row>
     <row r="295" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>422</v>
+        <v>267</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E295" s="1">
-        <v>5.5</v>
+        <v>11.055</v>
       </c>
       <c r="F295" s="1">
-        <v>66</v>
+        <v>132.66</v>
       </c>
       <c r="G295" s="1">
         <v>1</v>
@@ -12041,22 +12042,22 @@
     </row>
     <row r="296" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E296" s="1">
-        <v>11.055</v>
+        <v>11.049999999999999</v>
       </c>
       <c r="F296" s="1">
-        <v>132.66</v>
+        <v>132.6</v>
       </c>
       <c r="G296" s="1">
         <v>1</v>
@@ -12070,22 +12071,22 @@
     </row>
     <row r="297" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E297" s="1">
-        <v>11.049999999999999</v>
+        <v>16.610833333333336</v>
       </c>
       <c r="F297" s="1">
-        <v>132.6</v>
+        <v>199.33</v>
       </c>
       <c r="G297" s="1">
         <v>1</v>
@@ -12097,24 +12098,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E298" s="1">
-        <v>16.610833333333336</v>
+        <v>15.5</v>
       </c>
       <c r="F298" s="1">
-        <v>199.33</v>
+        <v>186</v>
       </c>
       <c r="G298" s="1">
         <v>1</v>
@@ -12128,22 +12129,22 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E299" s="1">
-        <v>15.5</v>
+        <v>16.055</v>
       </c>
       <c r="F299" s="1">
-        <v>186</v>
+        <v>192.66</v>
       </c>
       <c r="G299" s="1">
         <v>1</v>
@@ -12155,24 +12156,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E300" s="1">
-        <v>16.055</v>
+        <v>11.055</v>
       </c>
       <c r="F300" s="1">
-        <v>192.66</v>
+        <v>132.66</v>
       </c>
       <c r="G300" s="1">
         <v>1</v>
@@ -12184,24 +12185,24 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E301" s="1">
-        <v>11.055</v>
+        <v>22.166</v>
       </c>
       <c r="F301" s="1">
-        <v>132.66</v>
+        <v>221.66</v>
       </c>
       <c r="G301" s="1">
         <v>1</v>
@@ -12215,22 +12216,22 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E302" s="1">
-        <v>22.166</v>
+        <v>16.611000000000001</v>
       </c>
       <c r="F302" s="1">
-        <v>221.66</v>
+        <v>332.22</v>
       </c>
       <c r="G302" s="1">
         <v>1</v>
@@ -12243,23 +12244,18 @@
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>383</v>
-      </c>
+      <c r="B303" s="1"/>
       <c r="C303" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E303" s="1">
-        <v>16.611000000000001</v>
+        <v>19.943999999999999</v>
       </c>
       <c r="F303" s="1">
-        <v>332.22</v>
+        <v>398.88</v>
       </c>
       <c r="G303" s="1">
         <v>1</v>
@@ -12272,31 +12268,36 @@
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B304" s="1"/>
+      <c r="A304" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="C304" s="1" t="s">
-        <v>275</v>
+        <v>423</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E304" s="1">
-        <v>19.943999999999999</v>
-      </c>
-      <c r="F304" s="1">
-        <v>398.88</v>
-      </c>
-      <c r="G304" s="1">
-        <v>1</v>
+        <v>1.51</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I304" s="1">
-        <v>0.03</v>
+        <v>175</v>
+      </c>
+      <c r="I304" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J304" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
+  <autoFilter ref="A1:J303" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ACE905-0D14-4376-82DD-D18D25B2DCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDF9CCE-250D-47B4-B76B-14A2DB0DDFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$304</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="431">
   <si>
     <t>categoria</t>
   </si>
@@ -2187,10 +2187,19 @@
     <t>35</t>
   </si>
   <si>
-    <t>1030538</t>
-  </si>
-  <si>
     <t>17,65</t>
+  </si>
+  <si>
+    <t>01030538</t>
+  </si>
+  <si>
+    <t>11,64</t>
+  </si>
+  <si>
+    <t>17,74</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
 </sst>
 </file>
@@ -3097,7 +3106,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:N304"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:P304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -3142,7 +3152,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>153</v>
       </c>
@@ -3174,7 +3184,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>154</v>
       </c>
@@ -3206,7 +3216,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>155</v>
       </c>
@@ -3238,7 +3248,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>156</v>
       </c>
@@ -3270,7 +3280,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>157</v>
       </c>
@@ -3302,7 +3312,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>158</v>
       </c>
@@ -3334,7 +3344,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>159</v>
       </c>
@@ -3366,7 +3376,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>160</v>
       </c>
@@ -3398,7 +3408,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>161</v>
       </c>
@@ -3430,7 +3440,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>20182</v>
       </c>
@@ -3460,7 +3470,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>20236</v>
       </c>
@@ -3490,7 +3500,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>20328</v>
       </c>
@@ -3520,7 +3530,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>20199</v>
       </c>
@@ -3550,7 +3560,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>20243</v>
       </c>
@@ -3580,7 +3590,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>20205</v>
       </c>
@@ -3609,7 +3619,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>20250</v>
       </c>
@@ -3638,7 +3648,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>20212</v>
       </c>
@@ -3667,7 +3677,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>20267</v>
       </c>
@@ -3696,7 +3706,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>20366</v>
       </c>
@@ -3725,7 +3735,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20403</v>
       </c>
@@ -3754,7 +3764,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20410</v>
       </c>
@@ -3783,7 +3793,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>20441</v>
       </c>
@@ -3812,7 +3822,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20496</v>
       </c>
@@ -3841,7 +3851,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>20540</v>
       </c>
@@ -3870,7 +3880,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>20458</v>
       </c>
@@ -3899,7 +3909,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>20502</v>
       </c>
@@ -3928,7 +3938,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>20557</v>
       </c>
@@ -3957,7 +3967,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>20465</v>
       </c>
@@ -3986,7 +3996,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>20519</v>
       </c>
@@ -4015,7 +4025,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>20564</v>
       </c>
@@ -4044,7 +4054,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>20472</v>
       </c>
@@ -4073,7 +4083,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>20526</v>
       </c>
@@ -4102,7 +4112,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>20489</v>
       </c>
@@ -4131,7 +4141,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>20533</v>
       </c>
@@ -4160,7 +4170,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>20588</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>20618</v>
       </c>
@@ -4218,7 +4228,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>20625</v>
       </c>
@@ -4247,7 +4257,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>20656</v>
       </c>
@@ -4276,7 +4286,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>20595</v>
       </c>
@@ -4305,7 +4315,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>20632</v>
       </c>
@@ -4334,7 +4344,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>20601</v>
       </c>
@@ -4363,7 +4373,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>20649</v>
       </c>
@@ -4392,7 +4402,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>20663</v>
       </c>
@@ -4421,7 +4431,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>20670</v>
       </c>
@@ -4450,7 +4460,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>20687</v>
       </c>
@@ -4479,7 +4489,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>20694</v>
       </c>
@@ -4508,7 +4518,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>20700</v>
       </c>
@@ -4537,7 +4547,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>20717</v>
       </c>
@@ -4566,7 +4576,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>20724</v>
       </c>
@@ -4595,7 +4605,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>22049</v>
       </c>
@@ -4624,7 +4634,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>22056</v>
       </c>
@@ -4653,7 +4663,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>20809</v>
       </c>
@@ -4682,7 +4692,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>20816</v>
       </c>
@@ -4711,7 +4721,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>20823</v>
       </c>
@@ -4740,7 +4750,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>20830</v>
       </c>
@@ -4769,7 +4779,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>20847</v>
       </c>
@@ -4798,7 +4808,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>20854</v>
       </c>
@@ -4827,7 +4837,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>20861</v>
       </c>
@@ -4856,7 +4866,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>20878</v>
       </c>
@@ -4885,7 +4895,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>20960</v>
       </c>
@@ -4914,7 +4924,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>20984</v>
       </c>
@@ -4943,7 +4953,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>20977</v>
       </c>
@@ -4972,7 +4982,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>20991</v>
       </c>
@@ -5001,7 +5011,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>21059</v>
       </c>
@@ -5030,7 +5040,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>21066</v>
       </c>
@@ -5059,7 +5069,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>21073</v>
       </c>
@@ -5088,7 +5098,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>21080</v>
       </c>
@@ -5117,7 +5127,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>21097</v>
       </c>
@@ -5146,7 +5156,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>21103</v>
       </c>
@@ -5175,7 +5185,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>21141</v>
       </c>
@@ -5204,7 +5214,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>21158</v>
       </c>
@@ -5233,7 +5243,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>21165</v>
       </c>
@@ -5262,7 +5272,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>21172</v>
       </c>
@@ -5291,7 +5301,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>21189</v>
       </c>
@@ -5320,7 +5330,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>21196</v>
       </c>
@@ -5349,7 +5359,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>21202</v>
       </c>
@@ -5378,7 +5388,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>21424</v>
       </c>
@@ -5407,7 +5417,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>21431</v>
       </c>
@@ -5436,7 +5446,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>21448</v>
       </c>
@@ -5465,7 +5475,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>21462</v>
       </c>
@@ -5494,7 +5504,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>21479</v>
       </c>
@@ -5523,7 +5533,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>21486</v>
       </c>
@@ -5552,7 +5562,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>21493</v>
       </c>
@@ -5581,7 +5591,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>21509</v>
       </c>
@@ -5610,7 +5620,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>21516</v>
       </c>
@@ -5639,7 +5649,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>21523</v>
       </c>
@@ -5668,7 +5678,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>12529</v>
       </c>
@@ -5697,7 +5707,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>22162</v>
       </c>
@@ -5726,7 +5736,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>21530</v>
       </c>
@@ -5755,7 +5765,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>22155</v>
       </c>
@@ -5784,7 +5794,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>21547</v>
       </c>
@@ -5813,7 +5823,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>21554</v>
       </c>
@@ -5842,7 +5852,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>22094</v>
       </c>
@@ -5871,7 +5881,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>21561</v>
       </c>
@@ -5900,7 +5910,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>21578</v>
       </c>
@@ -5929,7 +5939,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>21585</v>
       </c>
@@ -5958,7 +5968,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>21592</v>
       </c>
@@ -5987,7 +5997,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>21608</v>
       </c>
@@ -6016,7 +6026,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>22421</v>
       </c>
@@ -6045,7 +6055,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>22438</v>
       </c>
@@ -6074,7 +6084,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>22353</v>
       </c>
@@ -6103,7 +6113,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>22360</v>
       </c>
@@ -6132,7 +6142,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>22377</v>
       </c>
@@ -6161,7 +6171,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>22414</v>
       </c>
@@ -6190,7 +6200,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>21714</v>
       </c>
@@ -6219,7 +6229,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>22186</v>
       </c>
@@ -6248,7 +6258,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>22339</v>
       </c>
@@ -6277,7 +6287,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>22346</v>
       </c>
@@ -6306,7 +6316,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>21721</v>
       </c>
@@ -6335,7 +6345,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>22391</v>
       </c>
@@ -6364,7 +6374,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>22407</v>
       </c>
@@ -6393,7 +6403,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>21745</v>
       </c>
@@ -6422,7 +6432,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>21752</v>
       </c>
@@ -6451,7 +6461,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>21776</v>
       </c>
@@ -6480,7 +6490,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>21783</v>
       </c>
@@ -6509,7 +6519,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>21790</v>
       </c>
@@ -6538,7 +6548,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>22315</v>
       </c>
@@ -6567,7 +6577,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>21844</v>
       </c>
@@ -6596,7 +6606,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>21899</v>
       </c>
@@ -6625,7 +6635,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>143</v>
       </c>
@@ -6654,7 +6664,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>144</v>
       </c>
@@ -6683,7 +6693,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>145</v>
       </c>
@@ -6712,7 +6722,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>146</v>
       </c>
@@ -6741,7 +6751,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>147</v>
       </c>
@@ -6770,7 +6780,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>148</v>
       </c>
@@ -6799,7 +6809,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>149</v>
       </c>
@@ -6828,7 +6838,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>150</v>
       </c>
@@ -6857,7 +6867,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>151</v>
       </c>
@@ -6886,7 +6896,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>152</v>
       </c>
@@ -6915,7 +6925,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>178</v>
       </c>
@@ -6945,7 +6955,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>181</v>
       </c>
@@ -6975,7 +6985,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>182</v>
       </c>
@@ -7005,7 +7015,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>185</v>
       </c>
@@ -7035,7 +7045,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>186</v>
       </c>
@@ -7065,7 +7075,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>188</v>
       </c>
@@ -7095,7 +7105,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>31</v>
       </c>
@@ -7124,7 +7134,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>32</v>
       </c>
@@ -7153,7 +7163,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>33</v>
       </c>
@@ -7182,7 +7192,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>34</v>
       </c>
@@ -7211,7 +7221,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>35</v>
       </c>
@@ -7240,7 +7250,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>36</v>
       </c>
@@ -7269,7 +7279,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>37</v>
       </c>
@@ -7298,7 +7308,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>38</v>
       </c>
@@ -7327,7 +7337,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
@@ -7356,7 +7366,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>40</v>
       </c>
@@ -7385,7 +7395,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>41</v>
       </c>
@@ -7414,7 +7424,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>42</v>
       </c>
@@ -7443,7 +7453,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>43</v>
       </c>
@@ -7472,7 +7482,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>44</v>
       </c>
@@ -7501,7 +7511,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>45</v>
       </c>
@@ -7530,7 +7540,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>46</v>
       </c>
@@ -7559,7 +7569,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>47</v>
       </c>
@@ -7588,7 +7598,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>48</v>
       </c>
@@ -7617,7 +7627,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>49</v>
       </c>
@@ -7646,7 +7656,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>50</v>
       </c>
@@ -7675,7 +7685,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>51</v>
       </c>
@@ -7819,7 +7829,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>98</v>
       </c>
@@ -7857,7 +7867,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>99</v>
       </c>
@@ -7895,7 +7905,7 @@
         <v>2.8600000000000003</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>100</v>
       </c>
@@ -7933,7 +7943,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>101</v>
       </c>
@@ -7971,7 +7981,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>102</v>
       </c>
@@ -8009,7 +8019,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>103</v>
       </c>
@@ -8047,7 +8057,7 @@
         <v>2.5739999999999998</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>121</v>
       </c>
@@ -8085,7 +8095,7 @@
         <v>2.5739999999999998</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>104</v>
       </c>
@@ -8123,7 +8133,7 @@
         <v>2.4200000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>105</v>
       </c>
@@ -8137,13 +8147,13 @@
         <v>69</v>
       </c>
       <c r="E169" s="1">
-        <v>2.4200000000000004</v>
+        <v>0.96</v>
       </c>
       <c r="F169" s="1">
         <v>48.400000000000006</v>
       </c>
-      <c r="G169" s="1">
-        <v>20</v>
+      <c r="G169" s="1" t="s">
+        <v>430</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>175</v>
@@ -8160,8 +8170,12 @@
       <c r="N169" s="1">
         <v>2.4200000000000004</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P169">
+        <f>48.4/50</f>
+        <v>0.96799999999999997</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>106</v>
       </c>
@@ -8199,7 +8213,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>107</v>
       </c>
@@ -8237,7 +8251,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>108</v>
       </c>
@@ -8265,6 +8279,7 @@
       <c r="I172" s="1">
         <v>20</v>
       </c>
+      <c r="J172" s="1"/>
       <c r="L172" s="1">
         <v>15.037000000000001</v>
       </c>
@@ -8275,7 +8290,7 @@
         <v>15.037000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>109</v>
       </c>
@@ -8300,20 +8315,14 @@
       <c r="H173" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I173" s="1">
-        <v>10</v>
-      </c>
-      <c r="L173" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="M173" s="1">
-        <v>46.2</v>
-      </c>
-      <c r="N173" s="1">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I173" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="L173" s="1"/>
+      <c r="M173" s="1"/>
+      <c r="N173" s="1"/>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>110</v>
       </c>
@@ -8351,7 +8360,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>111</v>
       </c>
@@ -8389,7 +8398,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>112</v>
       </c>
@@ -8607,6 +8616,7 @@
       <c r="I181" s="1">
         <v>12</v>
       </c>
+      <c r="J181" s="1"/>
       <c r="L181" s="1">
         <v>2.4200000000000004</v>
       </c>
@@ -8718,8 +8728,8 @@
       <c r="H184" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I184" s="1">
-        <v>15</v>
+      <c r="I184" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="L184" s="1">
         <v>5.6539999999999999</v>
@@ -8756,8 +8766,8 @@
       <c r="H185" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I185" s="1">
-        <v>15</v>
+      <c r="I185" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="L185" s="1">
         <v>5.6539999999999999</v>
@@ -8794,8 +8804,8 @@
       <c r="H186" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I186" s="1">
-        <v>15</v>
+      <c r="I186" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="L186" s="1">
         <v>5.6539999999999999</v>
@@ -8832,8 +8842,8 @@
       <c r="H187" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I187" s="1">
-        <v>15</v>
+      <c r="I187" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="L187" s="1">
         <v>5.6539999999999999</v>
@@ -8870,8 +8880,12 @@
       <c r="H188" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I188" s="1">
-        <v>15</v>
+      <c r="I188" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="J188" s="1">
+        <f>F189-J189</f>
+        <v>17.740000000000009</v>
       </c>
       <c r="L188" s="1">
         <v>5.6539999999999999</v>
@@ -8908,8 +8922,11 @@
       <c r="H189" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I189" s="1">
-        <v>15</v>
+      <c r="I189" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="J189" s="1">
+        <v>66.959999999999994</v>
       </c>
       <c r="L189" s="1">
         <v>5.6539999999999999</v>
@@ -8946,8 +8963,8 @@
       <c r="H190" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I190" s="1">
-        <v>15</v>
+      <c r="I190" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="L190" s="1">
         <v>5.6539999999999999</v>
@@ -9101,6 +9118,7 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
+      <c r="J194" s="1"/>
       <c r="L194" s="1">
         <v>2.8160000000000003</v>
       </c>
@@ -9111,7 +9129,7 @@
         <v>2.8160000000000003</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>168</v>
       </c>
@@ -9140,7 +9158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>277</v>
       </c>
@@ -9169,7 +9187,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="197" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>278</v>
       </c>
@@ -9198,7 +9216,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>279</v>
       </c>
@@ -9227,7 +9245,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>20199</v>
       </c>
@@ -9256,7 +9274,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>280</v>
       </c>
@@ -9285,7 +9303,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>281</v>
       </c>
@@ -9314,7 +9332,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>282</v>
       </c>
@@ -9343,7 +9361,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>283</v>
       </c>
@@ -9372,7 +9390,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>284</v>
       </c>
@@ -9401,7 +9419,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>285</v>
       </c>
@@ -9430,7 +9448,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>286</v>
       </c>
@@ -9459,7 +9477,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>287</v>
       </c>
@@ -9488,7 +9506,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>288</v>
       </c>
@@ -9517,7 +9535,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>289</v>
       </c>
@@ -9546,7 +9564,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>290</v>
       </c>
@@ -9575,7 +9593,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>291</v>
       </c>
@@ -9604,7 +9622,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>292</v>
       </c>
@@ -9633,7 +9651,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>293</v>
       </c>
@@ -9662,7 +9680,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>294</v>
       </c>
@@ -9691,7 +9709,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>295</v>
       </c>
@@ -9720,7 +9738,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>296</v>
       </c>
@@ -9749,7 +9767,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>297</v>
       </c>
@@ -9778,7 +9796,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>298</v>
       </c>
@@ -9807,7 +9825,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>299</v>
       </c>
@@ -9836,7 +9854,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>300</v>
       </c>
@@ -9865,7 +9883,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>301</v>
       </c>
@@ -9894,7 +9912,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>302</v>
       </c>
@@ -9923,7 +9941,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>303</v>
       </c>
@@ -9952,7 +9970,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>304</v>
       </c>
@@ -9981,7 +9999,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>305</v>
       </c>
@@ -10010,7 +10028,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>306</v>
       </c>
@@ -10039,7 +10057,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>307</v>
       </c>
@@ -10068,7 +10086,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>308</v>
       </c>
@@ -10097,7 +10115,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>309</v>
       </c>
@@ -10126,7 +10144,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>310</v>
       </c>
@@ -10155,7 +10173,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>311</v>
       </c>
@@ -10184,7 +10202,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>312</v>
       </c>
@@ -10213,7 +10231,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>313</v>
       </c>
@@ -10242,7 +10260,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>314</v>
       </c>
@@ -10271,7 +10289,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>315</v>
       </c>
@@ -10300,7 +10318,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>316</v>
       </c>
@@ -10329,7 +10347,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>317</v>
       </c>
@@ -10358,7 +10376,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>318</v>
       </c>
@@ -10387,7 +10405,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>319</v>
       </c>
@@ -10416,7 +10434,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>320</v>
       </c>
@@ -10445,7 +10463,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>321</v>
       </c>
@@ -10474,7 +10492,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>322</v>
       </c>
@@ -10503,7 +10521,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>323</v>
       </c>
@@ -10532,7 +10550,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>324</v>
       </c>
@@ -10561,7 +10579,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>325</v>
       </c>
@@ -10590,7 +10608,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>326</v>
       </c>
@@ -10619,7 +10637,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>327</v>
       </c>
@@ -10648,7 +10666,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>328</v>
       </c>
@@ -10677,7 +10695,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>329</v>
       </c>
@@ -10706,7 +10724,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>330</v>
       </c>
@@ -10735,7 +10753,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>331</v>
       </c>
@@ -10764,7 +10782,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>332</v>
       </c>
@@ -10793,7 +10811,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>333</v>
       </c>
@@ -10822,7 +10840,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>334</v>
       </c>
@@ -10851,7 +10869,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>335</v>
       </c>
@@ -10880,7 +10898,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>336</v>
       </c>
@@ -10909,7 +10927,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>337</v>
       </c>
@@ -10938,7 +10956,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>338</v>
       </c>
@@ -10967,7 +10985,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>339</v>
       </c>
@@ -10996,7 +11014,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>340</v>
       </c>
@@ -11025,7 +11043,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>341</v>
       </c>
@@ -11054,7 +11072,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>342</v>
       </c>
@@ -11083,7 +11101,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>343</v>
       </c>
@@ -11112,7 +11130,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>344</v>
       </c>
@@ -11141,7 +11159,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>345</v>
       </c>
@@ -11170,7 +11188,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>346</v>
       </c>
@@ -11199,7 +11217,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>347</v>
       </c>
@@ -11228,7 +11246,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>348</v>
       </c>
@@ -11257,7 +11275,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>349</v>
       </c>
@@ -11286,7 +11304,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>350</v>
       </c>
@@ -11315,7 +11333,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>351</v>
       </c>
@@ -11344,7 +11362,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>352</v>
       </c>
@@ -11373,7 +11391,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>353</v>
       </c>
@@ -11402,7 +11420,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>354</v>
       </c>
@@ -11431,7 +11449,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>355</v>
       </c>
@@ -11460,7 +11478,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>356</v>
       </c>
@@ -11489,7 +11507,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>357</v>
       </c>
@@ -11518,7 +11536,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>358</v>
       </c>
@@ -11547,7 +11565,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>359</v>
       </c>
@@ -11576,7 +11594,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>360</v>
       </c>
@@ -11605,7 +11623,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>361</v>
       </c>
@@ -11634,7 +11652,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>362</v>
       </c>
@@ -11663,7 +11681,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>363</v>
       </c>
@@ -11692,7 +11710,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>364</v>
       </c>
@@ -11721,7 +11739,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>365</v>
       </c>
@@ -11750,7 +11768,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>366</v>
       </c>
@@ -11779,7 +11797,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>367</v>
       </c>
@@ -11808,7 +11826,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>368</v>
       </c>
@@ -11837,7 +11855,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>369</v>
       </c>
@@ -11866,7 +11884,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>370</v>
       </c>
@@ -11895,7 +11913,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>371</v>
       </c>
@@ -11924,7 +11942,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>372</v>
       </c>
@@ -11953,7 +11971,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>373</v>
       </c>
@@ -11982,7 +12000,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>374</v>
       </c>
@@ -12011,7 +12029,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>375</v>
       </c>
@@ -12040,7 +12058,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>376</v>
       </c>
@@ -12069,7 +12087,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>377</v>
       </c>
@@ -12098,7 +12116,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>378</v>
       </c>
@@ -12127,7 +12145,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>379</v>
       </c>
@@ -12156,7 +12174,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>380</v>
       </c>
@@ -12185,7 +12203,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>381</v>
       </c>
@@ -12214,7 +12232,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>382</v>
       </c>
@@ -12243,7 +12261,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="B303" s="1"/>
       <c r="C303" s="1" t="s">
         <v>275</v>
@@ -12267,9 +12285,9 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>52</v>
@@ -12293,11 +12311,20 @@
         <v>175</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
+      </c>
+      <c r="J304">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J303" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
+  <autoFilter ref="A1:J304" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="WK"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDF9CCE-250D-47B4-B76B-14A2DB0DDFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A6FF9-507F-4DA5-BA88-5A973E989284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$305</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="433">
   <si>
     <t>categoria</t>
   </si>
@@ -2200,6 +2200,12 @@
   </si>
   <si>
     <t>50</t>
+  </si>
+  <si>
+    <t>01030539</t>
+  </si>
+  <si>
+    <t>Doce WK Pururuca Porkão Natural</t>
   </si>
 </sst>
 </file>
@@ -3106,8 +3112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:P304"/>
+  <dimension ref="A1:P308"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -3152,7 +3157,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>153</v>
       </c>
@@ -3184,7 +3189,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>154</v>
       </c>
@@ -3216,7 +3221,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>155</v>
       </c>
@@ -3248,7 +3253,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>156</v>
       </c>
@@ -3280,7 +3285,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>157</v>
       </c>
@@ -3312,7 +3317,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>158</v>
       </c>
@@ -3344,7 +3349,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>159</v>
       </c>
@@ -3376,7 +3381,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>160</v>
       </c>
@@ -3408,7 +3413,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>161</v>
       </c>
@@ -3440,7 +3445,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>20182</v>
       </c>
@@ -3470,7 +3475,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>20236</v>
       </c>
@@ -3500,7 +3505,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>20328</v>
       </c>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>20199</v>
       </c>
@@ -3560,7 +3565,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>20243</v>
       </c>
@@ -3590,7 +3595,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>20205</v>
       </c>
@@ -3619,7 +3624,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>20250</v>
       </c>
@@ -3648,7 +3653,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>20212</v>
       </c>
@@ -3677,7 +3682,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>20267</v>
       </c>
@@ -3706,7 +3711,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>20366</v>
       </c>
@@ -3735,7 +3740,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20403</v>
       </c>
@@ -3764,7 +3769,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20410</v>
       </c>
@@ -3793,7 +3798,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>20441</v>
       </c>
@@ -3822,7 +3827,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20496</v>
       </c>
@@ -3851,7 +3856,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>20540</v>
       </c>
@@ -3880,7 +3885,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>20458</v>
       </c>
@@ -3909,7 +3914,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>20502</v>
       </c>
@@ -3938,7 +3943,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>20557</v>
       </c>
@@ -3967,7 +3972,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>20465</v>
       </c>
@@ -3996,7 +4001,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>20519</v>
       </c>
@@ -4025,7 +4030,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>20564</v>
       </c>
@@ -4054,7 +4059,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>20472</v>
       </c>
@@ -4083,7 +4088,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>20526</v>
       </c>
@@ -4112,7 +4117,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>20489</v>
       </c>
@@ -4141,7 +4146,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>20533</v>
       </c>
@@ -4170,7 +4175,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>20588</v>
       </c>
@@ -4199,7 +4204,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>20618</v>
       </c>
@@ -4228,7 +4233,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>20625</v>
       </c>
@@ -4257,7 +4262,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>20656</v>
       </c>
@@ -4286,7 +4291,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>20595</v>
       </c>
@@ -4315,7 +4320,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>20632</v>
       </c>
@@ -4344,7 +4349,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>20601</v>
       </c>
@@ -4373,7 +4378,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>20649</v>
       </c>
@@ -4402,7 +4407,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>20663</v>
       </c>
@@ -4431,7 +4436,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>20670</v>
       </c>
@@ -4460,7 +4465,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>20687</v>
       </c>
@@ -4489,7 +4494,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>20694</v>
       </c>
@@ -4518,7 +4523,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>20700</v>
       </c>
@@ -4547,7 +4552,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>20717</v>
       </c>
@@ -4576,7 +4581,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>20724</v>
       </c>
@@ -4605,7 +4610,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>22049</v>
       </c>
@@ -4634,7 +4639,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>22056</v>
       </c>
@@ -4663,7 +4668,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>20809</v>
       </c>
@@ -4692,7 +4697,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>20816</v>
       </c>
@@ -4721,7 +4726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>20823</v>
       </c>
@@ -4750,7 +4755,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>20830</v>
       </c>
@@ -4779,7 +4784,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>20847</v>
       </c>
@@ -4808,7 +4813,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>20854</v>
       </c>
@@ -4837,7 +4842,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>20861</v>
       </c>
@@ -4866,7 +4871,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>20878</v>
       </c>
@@ -4895,7 +4900,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>20960</v>
       </c>
@@ -4924,7 +4929,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>20984</v>
       </c>
@@ -4953,7 +4958,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>20977</v>
       </c>
@@ -4982,7 +4987,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>20991</v>
       </c>
@@ -5011,7 +5016,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>21059</v>
       </c>
@@ -5040,7 +5045,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>21066</v>
       </c>
@@ -5069,7 +5074,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>21073</v>
       </c>
@@ -5098,7 +5103,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>21080</v>
       </c>
@@ -5127,7 +5132,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>21097</v>
       </c>
@@ -5156,7 +5161,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>21103</v>
       </c>
@@ -5185,7 +5190,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>21141</v>
       </c>
@@ -5214,7 +5219,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>21158</v>
       </c>
@@ -5243,7 +5248,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>21165</v>
       </c>
@@ -5272,7 +5277,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>21172</v>
       </c>
@@ -5301,7 +5306,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>21189</v>
       </c>
@@ -5330,7 +5335,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>21196</v>
       </c>
@@ -5359,7 +5364,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>21202</v>
       </c>
@@ -5388,7 +5393,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>21424</v>
       </c>
@@ -5417,7 +5422,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>21431</v>
       </c>
@@ -5446,7 +5451,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>21448</v>
       </c>
@@ -5475,7 +5480,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>21462</v>
       </c>
@@ -5504,7 +5509,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>21479</v>
       </c>
@@ -5533,7 +5538,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>21486</v>
       </c>
@@ -5562,7 +5567,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>21493</v>
       </c>
@@ -5591,7 +5596,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>21509</v>
       </c>
@@ -5620,7 +5625,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>21516</v>
       </c>
@@ -5649,7 +5654,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>21523</v>
       </c>
@@ -5678,7 +5683,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>12529</v>
       </c>
@@ -5707,7 +5712,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>22162</v>
       </c>
@@ -5736,7 +5741,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>21530</v>
       </c>
@@ -5765,7 +5770,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>22155</v>
       </c>
@@ -5794,7 +5799,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>21547</v>
       </c>
@@ -5823,7 +5828,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>21554</v>
       </c>
@@ -5852,7 +5857,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>22094</v>
       </c>
@@ -5881,7 +5886,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>21561</v>
       </c>
@@ -5910,7 +5915,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>21578</v>
       </c>
@@ -5939,7 +5944,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>21585</v>
       </c>
@@ -5968,7 +5973,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>21592</v>
       </c>
@@ -5997,7 +6002,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>21608</v>
       </c>
@@ -6026,7 +6031,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>22421</v>
       </c>
@@ -6055,7 +6060,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>22438</v>
       </c>
@@ -6084,7 +6089,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>22353</v>
       </c>
@@ -6113,7 +6118,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>22360</v>
       </c>
@@ -6142,7 +6147,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>22377</v>
       </c>
@@ -6171,7 +6176,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>22414</v>
       </c>
@@ -6200,7 +6205,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>21714</v>
       </c>
@@ -6229,7 +6234,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>22186</v>
       </c>
@@ -6258,7 +6263,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>22339</v>
       </c>
@@ -6287,7 +6292,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>22346</v>
       </c>
@@ -6316,7 +6321,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>21721</v>
       </c>
@@ -6345,7 +6350,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>22391</v>
       </c>
@@ -6374,7 +6379,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>22407</v>
       </c>
@@ -6403,7 +6408,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>21745</v>
       </c>
@@ -6432,7 +6437,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>21752</v>
       </c>
@@ -6461,7 +6466,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>21776</v>
       </c>
@@ -6490,7 +6495,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>21783</v>
       </c>
@@ -6519,7 +6524,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>21790</v>
       </c>
@@ -6548,7 +6553,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>22315</v>
       </c>
@@ -6577,7 +6582,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>21844</v>
       </c>
@@ -6606,7 +6611,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>21899</v>
       </c>
@@ -6635,7 +6640,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>143</v>
       </c>
@@ -6664,7 +6669,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>144</v>
       </c>
@@ -6693,7 +6698,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>145</v>
       </c>
@@ -6722,7 +6727,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>146</v>
       </c>
@@ -6751,7 +6756,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>147</v>
       </c>
@@ -6780,7 +6785,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>148</v>
       </c>
@@ -6809,7 +6814,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>149</v>
       </c>
@@ -6838,7 +6843,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>150</v>
       </c>
@@ -6867,7 +6872,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>151</v>
       </c>
@@ -6896,7 +6901,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>152</v>
       </c>
@@ -6925,7 +6930,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>178</v>
       </c>
@@ -6955,7 +6960,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>181</v>
       </c>
@@ -6985,7 +6990,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>182</v>
       </c>
@@ -7015,7 +7020,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>185</v>
       </c>
@@ -7045,7 +7050,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>186</v>
       </c>
@@ -7075,7 +7080,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>188</v>
       </c>
@@ -7105,7 +7110,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>31</v>
       </c>
@@ -7134,7 +7139,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>32</v>
       </c>
@@ -7163,7 +7168,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>33</v>
       </c>
@@ -7192,7 +7197,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>34</v>
       </c>
@@ -7221,7 +7226,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>35</v>
       </c>
@@ -7250,7 +7255,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>36</v>
       </c>
@@ -7279,7 +7284,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>37</v>
       </c>
@@ -7308,7 +7313,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>38</v>
       </c>
@@ -7337,7 +7342,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
@@ -7366,7 +7371,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>40</v>
       </c>
@@ -7395,7 +7400,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>41</v>
       </c>
@@ -7424,7 +7429,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>42</v>
       </c>
@@ -7453,7 +7458,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>43</v>
       </c>
@@ -7482,7 +7487,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>44</v>
       </c>
@@ -7511,7 +7516,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>45</v>
       </c>
@@ -7540,7 +7545,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>46</v>
       </c>
@@ -7569,7 +7574,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>47</v>
       </c>
@@ -7598,7 +7603,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>48</v>
       </c>
@@ -7627,7 +7632,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>49</v>
       </c>
@@ -7656,7 +7661,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>50</v>
       </c>
@@ -7685,7 +7690,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>51</v>
       </c>
@@ -8436,7 +8441,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>113</v>
       </c>
@@ -8474,7 +8479,7 @@
         <v>7.0400000000000009</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>114</v>
       </c>
@@ -8512,7 +8517,7 @@
         <v>4.0369999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>115</v>
       </c>
@@ -8550,7 +8555,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>116</v>
       </c>
@@ -8588,7 +8593,7 @@
         <v>3.3880000000000003</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>117</v>
       </c>
@@ -8627,7 +8632,7 @@
         <v>2.4200000000000004</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>118</v>
       </c>
@@ -8665,7 +8670,7 @@
         <v>2.1779999999999999</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>119</v>
       </c>
@@ -8703,7 +8708,7 @@
         <v>1.3860000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>120</v>
       </c>
@@ -8741,7 +8746,7 @@
         <v>5.6539999999999999</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>122</v>
       </c>
@@ -8779,7 +8784,7 @@
         <v>5.6539999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>123</v>
       </c>
@@ -8817,7 +8822,7 @@
         <v>5.6539999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>124</v>
       </c>
@@ -8855,7 +8860,7 @@
         <v>5.6539999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>125</v>
       </c>
@@ -8897,7 +8902,7 @@
         <v>5.6539999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>126</v>
       </c>
@@ -8938,7 +8943,7 @@
         <v>5.6539999999999999</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>127</v>
       </c>
@@ -8975,8 +8980,11 @@
       <c r="N190" s="1">
         <v>5.6539999999999999</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P190" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>128</v>
       </c>
@@ -8990,10 +8998,10 @@
         <v>69</v>
       </c>
       <c r="E191" s="1">
-        <v>118.80000000000001</v>
+        <v>5</v>
       </c>
       <c r="F191" s="1">
-        <v>118.80000000000001</v>
+        <v>120</v>
       </c>
       <c r="G191" s="1">
         <v>24</v>
@@ -9013,8 +9021,16 @@
       <c r="N191" s="1">
         <v>118.80000000000001</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O191">
+        <f>78*1.08</f>
+        <v>84.240000000000009</v>
+      </c>
+      <c r="P191">
+        <f>O191*1.5</f>
+        <v>126.36000000000001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>129</v>
       </c>
@@ -9129,7 +9145,7 @@
         <v>2.8160000000000003</v>
       </c>
     </row>
-    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>168</v>
       </c>
@@ -9158,7 +9174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:14" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>277</v>
       </c>
@@ -9187,7 +9203,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="197" spans="1:14" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>278</v>
       </c>
@@ -9216,7 +9232,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>279</v>
       </c>
@@ -9245,7 +9261,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>20199</v>
       </c>
@@ -9274,7 +9290,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>280</v>
       </c>
@@ -9303,7 +9319,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>281</v>
       </c>
@@ -9332,7 +9348,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>282</v>
       </c>
@@ -9361,7 +9377,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>283</v>
       </c>
@@ -9390,7 +9406,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>284</v>
       </c>
@@ -9419,7 +9435,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>285</v>
       </c>
@@ -9448,7 +9464,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>286</v>
       </c>
@@ -9477,7 +9493,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>287</v>
       </c>
@@ -9506,7 +9522,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>288</v>
       </c>
@@ -9535,7 +9551,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>289</v>
       </c>
@@ -9564,7 +9580,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>290</v>
       </c>
@@ -9593,7 +9609,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>291</v>
       </c>
@@ -9622,7 +9638,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>292</v>
       </c>
@@ -9651,7 +9667,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>293</v>
       </c>
@@ -9680,7 +9696,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>294</v>
       </c>
@@ -9709,7 +9725,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>295</v>
       </c>
@@ -9738,7 +9754,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>296</v>
       </c>
@@ -9767,7 +9783,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>297</v>
       </c>
@@ -9796,7 +9812,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>298</v>
       </c>
@@ -9825,7 +9841,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>299</v>
       </c>
@@ -9854,7 +9870,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>300</v>
       </c>
@@ -9883,7 +9899,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>301</v>
       </c>
@@ -9912,7 +9928,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>302</v>
       </c>
@@ -9941,7 +9957,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>303</v>
       </c>
@@ -9970,7 +9986,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>304</v>
       </c>
@@ -9999,7 +10015,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>305</v>
       </c>
@@ -10028,7 +10044,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>306</v>
       </c>
@@ -10057,7 +10073,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>307</v>
       </c>
@@ -10086,7 +10102,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>308</v>
       </c>
@@ -10115,7 +10131,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>309</v>
       </c>
@@ -10144,7 +10160,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>310</v>
       </c>
@@ -10173,7 +10189,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>311</v>
       </c>
@@ -10202,7 +10218,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>312</v>
       </c>
@@ -10231,7 +10247,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>313</v>
       </c>
@@ -10260,7 +10276,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>314</v>
       </c>
@@ -10289,7 +10305,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>315</v>
       </c>
@@ -10318,7 +10334,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>316</v>
       </c>
@@ -10347,7 +10363,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>317</v>
       </c>
@@ -10376,7 +10392,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>318</v>
       </c>
@@ -10405,7 +10421,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>319</v>
       </c>
@@ -10434,7 +10450,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>320</v>
       </c>
@@ -10463,7 +10479,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>321</v>
       </c>
@@ -10492,7 +10508,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>322</v>
       </c>
@@ -10521,7 +10537,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>323</v>
       </c>
@@ -10550,7 +10566,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>324</v>
       </c>
@@ -10579,7 +10595,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>325</v>
       </c>
@@ -10608,7 +10624,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>326</v>
       </c>
@@ -10637,7 +10653,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>327</v>
       </c>
@@ -10666,7 +10682,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>328</v>
       </c>
@@ -10695,7 +10711,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>329</v>
       </c>
@@ -10724,7 +10740,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>330</v>
       </c>
@@ -10753,7 +10769,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>331</v>
       </c>
@@ -10782,7 +10798,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>332</v>
       </c>
@@ -10811,7 +10827,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>333</v>
       </c>
@@ -10840,7 +10856,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>334</v>
       </c>
@@ -10869,7 +10885,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>335</v>
       </c>
@@ -10898,7 +10914,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>336</v>
       </c>
@@ -10927,7 +10943,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>337</v>
       </c>
@@ -10956,7 +10972,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>338</v>
       </c>
@@ -10985,7 +11001,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>339</v>
       </c>
@@ -11014,7 +11030,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>340</v>
       </c>
@@ -11043,7 +11059,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>341</v>
       </c>
@@ -11072,7 +11088,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>342</v>
       </c>
@@ -11101,7 +11117,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>343</v>
       </c>
@@ -11130,7 +11146,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>344</v>
       </c>
@@ -11159,7 +11175,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>345</v>
       </c>
@@ -11188,7 +11204,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>346</v>
       </c>
@@ -11217,7 +11233,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>347</v>
       </c>
@@ -11246,7 +11262,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>348</v>
       </c>
@@ -11275,7 +11291,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>349</v>
       </c>
@@ -11304,7 +11320,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>350</v>
       </c>
@@ -11333,7 +11349,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>351</v>
       </c>
@@ -11362,7 +11378,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>352</v>
       </c>
@@ -11391,7 +11407,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>353</v>
       </c>
@@ -11420,7 +11436,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>354</v>
       </c>
@@ -11449,7 +11465,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>355</v>
       </c>
@@ -11478,7 +11494,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>356</v>
       </c>
@@ -11507,7 +11523,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>357</v>
       </c>
@@ -11536,7 +11552,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>358</v>
       </c>
@@ -11565,7 +11581,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>359</v>
       </c>
@@ -11594,7 +11610,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>360</v>
       </c>
@@ -11623,7 +11639,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>361</v>
       </c>
@@ -11652,7 +11668,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>362</v>
       </c>
@@ -11681,7 +11697,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>363</v>
       </c>
@@ -11710,7 +11726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>364</v>
       </c>
@@ -11739,7 +11755,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>365</v>
       </c>
@@ -11768,7 +11784,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>366</v>
       </c>
@@ -11797,7 +11813,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>367</v>
       </c>
@@ -11826,7 +11842,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>368</v>
       </c>
@@ -11855,7 +11871,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>369</v>
       </c>
@@ -11884,7 +11900,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="290" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>370</v>
       </c>
@@ -11913,7 +11929,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>371</v>
       </c>
@@ -11942,7 +11958,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>372</v>
       </c>
@@ -11971,7 +11987,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>373</v>
       </c>
@@ -12000,7 +12016,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>374</v>
       </c>
@@ -12029,7 +12045,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>375</v>
       </c>
@@ -12058,7 +12074,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>376</v>
       </c>
@@ -12087,7 +12103,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>377</v>
       </c>
@@ -12116,7 +12132,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>378</v>
       </c>
@@ -12145,7 +12161,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>379</v>
       </c>
@@ -12174,7 +12190,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>380</v>
       </c>
@@ -12203,7 +12219,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>381</v>
       </c>
@@ -12232,7 +12248,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>382</v>
       </c>
@@ -12261,7 +12277,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B303" s="1"/>
       <c r="C303" s="1" t="s">
         <v>275</v>
@@ -12317,14 +12333,43 @@
         <v>39</v>
       </c>
     </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="F305" s="1">
+        <v>52.64</v>
+      </c>
+      <c r="G305" s="1">
+        <v>20</v>
+      </c>
+      <c r="H305" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I305" s="1">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C308">
+        <f>2.43*1.3</f>
+        <v>3.1590000000000003</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J304" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="WK"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J305" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A6FF9-507F-4DA5-BA88-5A973E989284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917E302D-E204-4E12-AD26-2941974A0E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="439">
   <si>
     <t>categoria</t>
   </si>
@@ -2206,6 +2206,24 @@
   </si>
   <si>
     <t>Doce WK Pururuca Porkão Natural</t>
+  </si>
+  <si>
+    <t>01030540</t>
+  </si>
+  <si>
+    <t>Doce WK Pururuca Porkão Limão</t>
+  </si>
+  <si>
+    <t>01030541</t>
+  </si>
+  <si>
+    <t>Doce WK Pururuca Porkão Pimenta</t>
+  </si>
+  <si>
+    <t>01030542</t>
+  </si>
+  <si>
+    <t>Doce WK Amendoin Petisco</t>
   </si>
 </sst>
 </file>
@@ -9056,7 +9074,10 @@
         <v>175</v>
       </c>
       <c r="I192" s="1">
-        <v>0</v>
+        <v>23.06</v>
+      </c>
+      <c r="J192">
+        <v>57.24</v>
       </c>
       <c r="L192" s="1">
         <v>2.6840000000000002</v>
@@ -12333,7 +12354,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>431</v>
       </c>
@@ -12362,10 +12383,94 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C308">
-        <f>2.43*1.3</f>
-        <v>3.1590000000000003</v>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="F306" s="1">
+        <v>52.64</v>
+      </c>
+      <c r="G306" s="1">
+        <v>20</v>
+      </c>
+      <c r="H306" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I306" s="1">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="F307" s="1">
+        <v>52.64</v>
+      </c>
+      <c r="G307" s="1">
+        <v>20</v>
+      </c>
+      <c r="H307" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I307" s="1">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C308" t="s">
+        <v>438</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="F308" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="G308" s="1">
+        <v>30</v>
+      </c>
+      <c r="H308" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I308" s="1">
+        <v>27.46</v>
+      </c>
+      <c r="J308">
+        <v>57.24</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917E302D-E204-4E12-AD26-2941974A0E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296D3C01-C621-4DFF-A2D7-EF61628E6E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="514">
   <si>
     <t>categoria</t>
   </si>
@@ -449,9 +449,6 @@
   </si>
   <si>
     <t>01030537</t>
-  </si>
-  <si>
-    <t>Doce WK Manedouca Espeto com 30</t>
   </si>
   <si>
     <t>01050401</t>
@@ -2224,6 +2221,234 @@
   </si>
   <si>
     <t>Doce WK Amendoin Petisco</t>
+  </si>
+  <si>
+    <t>Doce WK Manedona Espeto com 30</t>
+  </si>
+  <si>
+    <t>01030543</t>
+  </si>
+  <si>
+    <t>01030544</t>
+  </si>
+  <si>
+    <t>Doce WK Pingo Bel Ouro de Minas Pote com 21 Unid</t>
+  </si>
+  <si>
+    <t>Doce WK Brigadeiro Ouro de Minas Pote com 21 Unid</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>RLD</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>1653</t>
+  </si>
+  <si>
+    <t>RLD Macarrão Instantaneo Adria Carne 75g</t>
+  </si>
+  <si>
+    <t>RLD Macarrão Instantaneo Adria Galinha Caipira 75g</t>
+  </si>
+  <si>
+    <t>3156</t>
+  </si>
+  <si>
+    <t>RLD Macarrão Instantaneo Adria Galinha Suave 75g</t>
+  </si>
+  <si>
+    <t>3156A</t>
+  </si>
+  <si>
+    <t>RLD Macarrão Instantaneo Adria Tomate 75g</t>
+  </si>
+  <si>
+    <t>RLD Cooquie Piraque 80g Goiabinha</t>
+  </si>
+  <si>
+    <t>3744</t>
+  </si>
+  <si>
+    <t>RLD Cooquie Piraque 80g Gotas de Chocolate</t>
+  </si>
+  <si>
+    <t>3743</t>
+  </si>
+  <si>
+    <t>RLD Cooquie Piraque 80g Chocolate</t>
+  </si>
+  <si>
+    <t>3906</t>
+  </si>
+  <si>
+    <t>RLD Sequilhos Itamaraty 100g Limão</t>
+  </si>
+  <si>
+    <t>3907</t>
+  </si>
+  <si>
+    <t>RLD Sequilhos Itamaraty 100g Leite Condensado</t>
+  </si>
+  <si>
+    <t>3909</t>
+  </si>
+  <si>
+    <t>RLD Sequilhos Itamaraty 100g Broa de Milho</t>
+  </si>
+  <si>
+    <t>3908</t>
+  </si>
+  <si>
+    <t>RLD Sequilhos Itamaraty 100g Tradicional</t>
+  </si>
+  <si>
+    <t>2193</t>
+  </si>
+  <si>
+    <t>RLD Stick Look Itamaraty 55g Brigadeiro</t>
+  </si>
+  <si>
+    <t>3,36</t>
+  </si>
+  <si>
+    <t>955</t>
+  </si>
+  <si>
+    <t>RLD Stick Look Itamaraty 55g Floresta Negra</t>
+  </si>
+  <si>
+    <t>932</t>
+  </si>
+  <si>
+    <t>RLD Stick Look Itamaraty 55g Doce de Leite</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>RLD Stick Look Itamaraty 55g Napolitano</t>
+  </si>
+  <si>
+    <t>1476</t>
+  </si>
+  <si>
+    <t>RLD Wafer Itamaraty 80g Atrevidos Napolitano</t>
+  </si>
+  <si>
+    <t>1930</t>
+  </si>
+  <si>
+    <t>RLD Wafer Itamaraty 80g Atrevidos Brigadeiro</t>
+  </si>
+  <si>
+    <t>1399</t>
+  </si>
+  <si>
+    <t>RLD Wafer Itamaraty 80g Atrevidos Chocolate Branco</t>
+  </si>
+  <si>
+    <t>1780</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Recheado Luam 110g Luanesco Baunilha</t>
+  </si>
+  <si>
+    <t>1796</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Recheado Luam 110g Luanesco Duo Chocolate</t>
+  </si>
+  <si>
+    <t>1781</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Recheado Luam 110g Luanesco Morango</t>
+  </si>
+  <si>
+    <t>3063</t>
+  </si>
+  <si>
+    <t>RLD Rosquinha Luam 300g Banana e Canela</t>
+  </si>
+  <si>
+    <t>1784</t>
+  </si>
+  <si>
+    <t>RLD Rosquinha Luam 300g Chocolate</t>
+  </si>
+  <si>
+    <t>1782</t>
+  </si>
+  <si>
+    <t>RLD Rosquinha Luam 300g Coco</t>
+  </si>
+  <si>
+    <t>4217</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Salgado Tuc´s 100g Cracker Cebola</t>
+  </si>
+  <si>
+    <t>2839</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Salgado Tuc´s 100g Cracker Original</t>
+  </si>
+  <si>
+    <t>2839A</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Salgado Tuc´s 100g Cracker Integral</t>
+  </si>
+  <si>
+    <t>3691</t>
+  </si>
+  <si>
+    <t>RLD Biscoito Nestlé 130g Passatempo</t>
+  </si>
+  <si>
+    <t>992</t>
+  </si>
+  <si>
+    <t>RLD Moranguete Bel Caixa com 36 13g</t>
+  </si>
+  <si>
+    <t>2767</t>
+  </si>
+  <si>
+    <t>RLD Moranguete Bel Caixa com 50 9g</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>RLD Chicle Trident Display com 21 Hortelã</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>RLD Chicle Trident Display com 21 Menta</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>RLD Chicle Trident Display com 21 Tutty Fruti</t>
   </si>
 </sst>
 </file>
@@ -3130,10 +3355,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:P308"/>
+  <dimension ref="A1:P343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="74.5703125" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" style="3" customWidth="1"/>
@@ -3166,18 +3392,18 @@
         <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" t="s">
         <v>173</v>
       </c>
-      <c r="I1" t="s">
-        <v>174</v>
-      </c>
       <c r="J1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -3198,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I2">
         <v>3.3</v>
@@ -3209,7 +3435,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -3230,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I3">
         <v>3.3</v>
@@ -3241,7 +3467,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -3262,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I4">
         <v>3.3</v>
@@ -3273,7 +3499,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -3294,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I5">
         <v>3.3</v>
@@ -3305,7 +3531,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -3326,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I6">
         <v>3.3</v>
@@ -3337,7 +3563,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -3358,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I7">
         <v>3.3</v>
@@ -3369,7 +3595,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -3390,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I8">
         <v>3.3</v>
@@ -3401,7 +3627,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
@@ -3422,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I9">
         <v>3.3</v>
@@ -3433,7 +3659,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -3454,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I10">
         <v>3.3</v>
@@ -3468,10 +3694,10 @@
         <v>20182</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
@@ -3486,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I11" s="1">
         <v>0.03</v>
@@ -3498,10 +3724,10 @@
         <v>20236</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
@@ -3516,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I12" s="1">
         <v>0.03</v>
@@ -3528,10 +3754,10 @@
         <v>20328</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
@@ -3546,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I13" s="1">
         <v>0.03</v>
@@ -3558,10 +3784,10 @@
         <v>20199</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>17</v>
@@ -3576,7 +3802,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I14" s="1">
         <v>0.03</v>
@@ -3588,10 +3814,10 @@
         <v>20243</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>17</v>
@@ -3606,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I15" s="1">
         <v>0.03</v>
@@ -3618,10 +3844,10 @@
         <v>20205</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>17</v>
@@ -3636,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I16" s="1">
         <v>0.03</v>
@@ -3647,10 +3873,10 @@
         <v>20250</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>17</v>
@@ -3665,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I17" s="1">
         <v>0.03</v>
@@ -3676,10 +3902,10 @@
         <v>20212</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>17</v>
@@ -3694,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I18" s="1">
         <v>0.03</v>
@@ -3705,10 +3931,10 @@
         <v>20267</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>17</v>
@@ -3723,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I19" s="1">
         <v>0.03</v>
@@ -3734,10 +3960,10 @@
         <v>20366</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>17</v>
@@ -3752,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I20" s="1">
         <v>0.03</v>
@@ -3763,10 +3989,10 @@
         <v>20403</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>17</v>
@@ -3781,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I21" s="1">
         <v>0.03</v>
@@ -3792,10 +4018,10 @@
         <v>20410</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>17</v>
@@ -3810,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I22" s="1">
         <v>0.03</v>
@@ -3821,10 +4047,10 @@
         <v>20441</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>17</v>
@@ -3839,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I23" s="1">
         <v>0.03</v>
@@ -3850,10 +4076,10 @@
         <v>20496</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>17</v>
@@ -3868,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I24" s="1">
         <v>0.03</v>
@@ -3879,10 +4105,10 @@
         <v>20540</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>17</v>
@@ -3897,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I25" s="1">
         <v>0.03</v>
@@ -3908,10 +4134,10 @@
         <v>20458</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>17</v>
@@ -3926,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I26" s="1">
         <v>0.03</v>
@@ -3937,10 +4163,10 @@
         <v>20502</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>17</v>
@@ -3955,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I27" s="1">
         <v>0.03</v>
@@ -3966,10 +4192,10 @@
         <v>20557</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>17</v>
@@ -3984,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I28" s="1">
         <v>0.03</v>
@@ -3995,10 +4221,10 @@
         <v>20465</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>17</v>
@@ -4013,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I29" s="1">
         <v>0.03</v>
@@ -4024,10 +4250,10 @@
         <v>20519</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>17</v>
@@ -4042,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I30" s="1">
         <v>0.03</v>
@@ -4053,10 +4279,10 @@
         <v>20564</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>17</v>
@@ -4071,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I31" s="1">
         <v>0.03</v>
@@ -4082,10 +4308,10 @@
         <v>20472</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>17</v>
@@ -4100,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I32" s="1">
         <v>0.03</v>
@@ -4111,10 +4337,10 @@
         <v>20526</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>17</v>
@@ -4129,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I33" s="1">
         <v>0.03</v>
@@ -4140,10 +4366,10 @@
         <v>20489</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>17</v>
@@ -4158,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I34" s="1">
         <v>0.03</v>
@@ -4169,10 +4395,10 @@
         <v>20533</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>17</v>
@@ -4187,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I35" s="1">
         <v>0.03</v>
@@ -4198,10 +4424,10 @@
         <v>20588</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>17</v>
@@ -4216,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I36" s="1">
         <v>0.03</v>
@@ -4227,10 +4453,10 @@
         <v>20618</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>17</v>
@@ -4245,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I37" s="1">
         <v>0.03</v>
@@ -4256,10 +4482,10 @@
         <v>20625</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>17</v>
@@ -4274,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I38" s="1">
         <v>0.03</v>
@@ -4285,10 +4511,10 @@
         <v>20656</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>17</v>
@@ -4303,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I39" s="1">
         <v>0.03</v>
@@ -4314,10 +4540,10 @@
         <v>20595</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>17</v>
@@ -4332,7 +4558,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I40" s="1">
         <v>0.03</v>
@@ -4343,10 +4569,10 @@
         <v>20632</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>17</v>
@@ -4361,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I41" s="1">
         <v>0.03</v>
@@ -4372,10 +4598,10 @@
         <v>20601</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>17</v>
@@ -4390,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I42" s="1">
         <v>0.03</v>
@@ -4401,10 +4627,10 @@
         <v>20649</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>17</v>
@@ -4419,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I43" s="1">
         <v>0.03</v>
@@ -4430,10 +4656,10 @@
         <v>20663</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>17</v>
@@ -4448,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I44" s="1">
         <v>0.03</v>
@@ -4459,10 +4685,10 @@
         <v>20670</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>17</v>
@@ -4477,7 +4703,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I45" s="1">
         <v>0.03</v>
@@ -4488,10 +4714,10 @@
         <v>20687</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>17</v>
@@ -4506,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I46" s="1">
         <v>0.03</v>
@@ -4517,10 +4743,10 @@
         <v>20694</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>17</v>
@@ -4535,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I47" s="1">
         <v>0.03</v>
@@ -4546,10 +4772,10 @@
         <v>20700</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>17</v>
@@ -4564,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I48" s="1">
         <v>0.03</v>
@@ -4575,10 +4801,10 @@
         <v>20717</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>17</v>
@@ -4593,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I49" s="1">
         <v>0.03</v>
@@ -4604,10 +4830,10 @@
         <v>20724</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>17</v>
@@ -4622,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I50" s="1">
         <v>0.03</v>
@@ -4633,10 +4859,10 @@
         <v>22049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>17</v>
@@ -4651,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I51" s="1">
         <v>0.03</v>
@@ -4662,10 +4888,10 @@
         <v>22056</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>17</v>
@@ -4680,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I52" s="1">
         <v>0.03</v>
@@ -4691,10 +4917,10 @@
         <v>20809</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>17</v>
@@ -4709,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I53" s="1">
         <v>0.03</v>
@@ -4720,10 +4946,10 @@
         <v>20816</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>17</v>
@@ -4738,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I54" s="1">
         <v>0.03</v>
@@ -4749,10 +4975,10 @@
         <v>20823</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>17</v>
@@ -4767,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I55" s="1">
         <v>0.03</v>
@@ -4778,10 +5004,10 @@
         <v>20830</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>17</v>
@@ -4796,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I56" s="1">
         <v>0.03</v>
@@ -4807,10 +5033,10 @@
         <v>20847</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>17</v>
@@ -4825,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I57" s="1">
         <v>0.03</v>
@@ -4836,10 +5062,10 @@
         <v>20854</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>17</v>
@@ -4854,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I58" s="1">
         <v>0.03</v>
@@ -4865,10 +5091,10 @@
         <v>20861</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>17</v>
@@ -4883,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I59" s="1">
         <v>0.03</v>
@@ -4894,10 +5120,10 @@
         <v>20878</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>17</v>
@@ -4912,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I60" s="1">
         <v>0.03</v>
@@ -4923,10 +5149,10 @@
         <v>20960</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>17</v>
@@ -4941,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I61" s="1">
         <v>0.03</v>
@@ -4952,10 +5178,10 @@
         <v>20984</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>17</v>
@@ -4970,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I62" s="1">
         <v>0.03</v>
@@ -4981,10 +5207,10 @@
         <v>20977</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>17</v>
@@ -4999,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I63" s="1">
         <v>0.03</v>
@@ -5010,10 +5236,10 @@
         <v>20991</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>17</v>
@@ -5028,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I64" s="1">
         <v>0.03</v>
@@ -5039,10 +5265,10 @@
         <v>21059</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>17</v>
@@ -5057,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I65" s="1">
         <v>0.03</v>
@@ -5068,10 +5294,10 @@
         <v>21066</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>17</v>
@@ -5086,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I66" s="1">
         <v>0.03</v>
@@ -5097,10 +5323,10 @@
         <v>21073</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>17</v>
@@ -5115,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I67" s="1">
         <v>0.03</v>
@@ -5126,10 +5352,10 @@
         <v>21080</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>17</v>
@@ -5144,7 +5370,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I68" s="1">
         <v>0.03</v>
@@ -5155,10 +5381,10 @@
         <v>21097</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>17</v>
@@ -5173,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I69" s="1">
         <v>0.03</v>
@@ -5184,10 +5410,10 @@
         <v>21103</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>17</v>
@@ -5202,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I70" s="1">
         <v>0.03</v>
@@ -5213,10 +5439,10 @@
         <v>21141</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>17</v>
@@ -5231,7 +5457,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I71" s="1">
         <v>0.03</v>
@@ -5242,10 +5468,10 @@
         <v>21158</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>17</v>
@@ -5260,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I72" s="1">
         <v>0.03</v>
@@ -5271,10 +5497,10 @@
         <v>21165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>17</v>
@@ -5289,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I73" s="1">
         <v>0.03</v>
@@ -5300,10 +5526,10 @@
         <v>21172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>17</v>
@@ -5318,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I74" s="1">
         <v>0.03</v>
@@ -5329,10 +5555,10 @@
         <v>21189</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>17</v>
@@ -5347,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I75" s="1">
         <v>0.03</v>
@@ -5358,10 +5584,10 @@
         <v>21196</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>17</v>
@@ -5376,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I76" s="1">
         <v>0.03</v>
@@ -5387,10 +5613,10 @@
         <v>21202</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>17</v>
@@ -5405,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I77" s="1">
         <v>0.03</v>
@@ -5416,10 +5642,10 @@
         <v>21424</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>17</v>
@@ -5434,7 +5660,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I78" s="1">
         <v>0.03</v>
@@ -5445,10 +5671,10 @@
         <v>21431</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>17</v>
@@ -5463,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I79" s="1">
         <v>0.03</v>
@@ -5474,10 +5700,10 @@
         <v>21448</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>17</v>
@@ -5492,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I80" s="1">
         <v>0.03</v>
@@ -5503,10 +5729,10 @@
         <v>21462</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>17</v>
@@ -5521,7 +5747,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I81" s="1">
         <v>0.03</v>
@@ -5532,10 +5758,10 @@
         <v>21479</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>17</v>
@@ -5550,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I82" s="1">
         <v>0.03</v>
@@ -5561,10 +5787,10 @@
         <v>21486</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>17</v>
@@ -5579,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I83" s="1">
         <v>0.03</v>
@@ -5590,10 +5816,10 @@
         <v>21493</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>17</v>
@@ -5608,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I84" s="1">
         <v>0.03</v>
@@ -5619,10 +5845,10 @@
         <v>21509</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>17</v>
@@ -5637,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I85" s="1">
         <v>0.03</v>
@@ -5648,10 +5874,10 @@
         <v>21516</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>17</v>
@@ -5666,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I86" s="1">
         <v>0.03</v>
@@ -5677,10 +5903,10 @@
         <v>21523</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>17</v>
@@ -5695,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I87" s="1">
         <v>0.03</v>
@@ -5706,10 +5932,10 @@
         <v>12529</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>17</v>
@@ -5724,7 +5950,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I88" s="1">
         <v>0.03</v>
@@ -5735,10 +5961,10 @@
         <v>22162</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>17</v>
@@ -5753,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I89" s="1">
         <v>0.03</v>
@@ -5764,10 +5990,10 @@
         <v>21530</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>17</v>
@@ -5782,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I90" s="1">
         <v>0.03</v>
@@ -5793,10 +6019,10 @@
         <v>22155</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>17</v>
@@ -5811,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I91" s="1">
         <v>0.03</v>
@@ -5822,10 +6048,10 @@
         <v>21547</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>17</v>
@@ -5840,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I92" s="1">
         <v>0.03</v>
@@ -5851,10 +6077,10 @@
         <v>21554</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>17</v>
@@ -5869,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I93" s="1">
         <v>0.03</v>
@@ -5880,10 +6106,10 @@
         <v>22094</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>17</v>
@@ -5898,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I94" s="1">
         <v>0.03</v>
@@ -5909,10 +6135,10 @@
         <v>21561</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>17</v>
@@ -5927,7 +6153,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I95" s="1">
         <v>0.03</v>
@@ -5938,10 +6164,10 @@
         <v>21578</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>17</v>
@@ -5956,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I96" s="1">
         <v>0.03</v>
@@ -5967,10 +6193,10 @@
         <v>21585</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>17</v>
@@ -5985,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I97" s="1">
         <v>0.03</v>
@@ -5996,10 +6222,10 @@
         <v>21592</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>17</v>
@@ -6014,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I98" s="1">
         <v>0.03</v>
@@ -6025,10 +6251,10 @@
         <v>21608</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>17</v>
@@ -6043,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I99" s="1">
         <v>0.03</v>
@@ -6054,10 +6280,10 @@
         <v>22421</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>17</v>
@@ -6072,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I100" s="1">
         <v>0.03</v>
@@ -6083,10 +6309,10 @@
         <v>22438</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>17</v>
@@ -6101,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I101" s="1">
         <v>0.03</v>
@@ -6112,10 +6338,10 @@
         <v>22353</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>17</v>
@@ -6130,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I102" s="1">
         <v>0.03</v>
@@ -6141,10 +6367,10 @@
         <v>22360</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>17</v>
@@ -6159,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I103" s="1">
         <v>0.03</v>
@@ -6170,10 +6396,10 @@
         <v>22377</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>17</v>
@@ -6188,7 +6414,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I104" s="1">
         <v>0.03</v>
@@ -6199,10 +6425,10 @@
         <v>22414</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>17</v>
@@ -6217,7 +6443,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I105" s="1">
         <v>0.03</v>
@@ -6228,10 +6454,10 @@
         <v>21714</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>17</v>
@@ -6246,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I106" s="1">
         <v>0.03</v>
@@ -6257,10 +6483,10 @@
         <v>22186</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>17</v>
@@ -6275,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I107" s="1">
         <v>0.03</v>
@@ -6286,10 +6512,10 @@
         <v>22339</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>17</v>
@@ -6304,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I108" s="1">
         <v>0.03</v>
@@ -6315,10 +6541,10 @@
         <v>22346</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>17</v>
@@ -6333,7 +6559,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I109" s="1">
         <v>0.03</v>
@@ -6344,10 +6570,10 @@
         <v>21721</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>17</v>
@@ -6362,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I110" s="1">
         <v>0.03</v>
@@ -6373,10 +6599,10 @@
         <v>22391</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>17</v>
@@ -6391,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I111" s="1">
         <v>0.03</v>
@@ -6402,10 +6628,10 @@
         <v>22407</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>17</v>
@@ -6420,7 +6646,7 @@
         <v>1</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I112" s="1">
         <v>0.03</v>
@@ -6431,10 +6657,10 @@
         <v>21745</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>17</v>
@@ -6449,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I113" s="1">
         <v>0.03</v>
@@ -6460,10 +6686,10 @@
         <v>21752</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>17</v>
@@ -6478,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I114" s="1">
         <v>0.03</v>
@@ -6489,10 +6715,10 @@
         <v>21776</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>17</v>
@@ -6507,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I115" s="1">
         <v>0.03</v>
@@ -6518,10 +6744,10 @@
         <v>21783</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>17</v>
@@ -6536,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I116" s="1">
         <v>0.03</v>
@@ -6547,10 +6773,10 @@
         <v>21790</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>17</v>
@@ -6565,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I117" s="1">
         <v>0.03</v>
@@ -6576,10 +6802,10 @@
         <v>22315</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>17</v>
@@ -6594,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I118" s="1">
         <v>0.03</v>
@@ -6605,10 +6831,10 @@
         <v>21844</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>17</v>
@@ -6623,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I119" s="1">
         <v>0.03</v>
@@ -6634,10 +6860,10 @@
         <v>21899</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>17</v>
@@ -6652,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I120" s="1">
         <v>0.03</v>
@@ -6660,7 +6886,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
@@ -6681,7 +6907,7 @@
         <v>10</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I121" s="1">
         <v>0.03</v>
@@ -6689,7 +6915,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -6710,7 +6936,7 @@
         <v>10</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I122" s="1">
         <v>0.03</v>
@@ -6718,7 +6944,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -6739,7 +6965,7 @@
         <v>10</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I123" s="1">
         <v>0.03</v>
@@ -6747,7 +6973,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>19</v>
@@ -6768,7 +6994,7 @@
         <v>10</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I124" s="1">
         <v>0.03</v>
@@ -6776,7 +7002,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>19</v>
@@ -6797,7 +7023,7 @@
         <v>10</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I125" s="1">
         <v>0.03</v>
@@ -6805,7 +7031,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>19</v>
@@ -6826,7 +7052,7 @@
         <v>10</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I126" s="1">
         <v>0.03</v>
@@ -6834,7 +7060,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>19</v>
@@ -6855,7 +7081,7 @@
         <v>10</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I127" s="1">
         <v>0.03</v>
@@ -6863,7 +7089,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>19</v>
@@ -6884,7 +7110,7 @@
         <v>10</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I128" s="1">
         <v>0.03</v>
@@ -6892,7 +7118,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>19</v>
@@ -6913,7 +7139,7 @@
         <v>24</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I129" s="1">
         <v>0.03</v>
@@ -6921,7 +7147,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>19</v>
@@ -6942,7 +7168,7 @@
         <v>24</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I130" s="1">
         <v>0.03</v>
@@ -6950,13 +7176,13 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>20</v>
@@ -6972,7 +7198,7 @@
         <v>24</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I131" s="1">
         <v>0.03</v>
@@ -6980,13 +7206,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>20</v>
@@ -7002,7 +7228,7 @@
         <v>24</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I132" s="1">
         <v>0.03</v>
@@ -7010,13 +7236,13 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>20</v>
@@ -7032,7 +7258,7 @@
         <v>24</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I133" s="1">
         <v>0.03</v>
@@ -7040,13 +7266,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>20</v>
@@ -7062,7 +7288,7 @@
         <v>24</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I134" s="1">
         <v>0.03</v>
@@ -7070,13 +7296,13 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>20</v>
@@ -7092,7 +7318,7 @@
         <v>24</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I135" s="1">
         <v>0.03</v>
@@ -7100,13 +7326,13 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>20</v>
@@ -7122,7 +7348,7 @@
         <v>24</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I136" s="1">
         <v>0.03</v>
@@ -7151,7 +7377,7 @@
         <v>12</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I137" s="1">
         <v>0.05</v>
@@ -7180,7 +7406,7 @@
         <v>12</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I138" s="1">
         <v>0.05</v>
@@ -7209,7 +7435,7 @@
         <v>30</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I139" s="1">
         <v>0.05</v>
@@ -7223,7 +7449,7 @@
         <v>52</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>68</v>
@@ -7238,7 +7464,7 @@
         <v>32</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I140" s="1">
         <v>0.05</v>
@@ -7267,7 +7493,7 @@
         <v>32</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I141" s="1">
         <v>0.05</v>
@@ -7296,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I142" s="1">
         <v>0.05</v>
@@ -7325,7 +7551,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I143" s="1">
         <v>0.05</v>
@@ -7354,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I144" s="1">
         <v>0.05</v>
@@ -7383,7 +7609,7 @@
         <v>63</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I145" s="1">
         <v>0.05</v>
@@ -7412,7 +7638,7 @@
         <v>56</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I146" s="1">
         <v>0.05</v>
@@ -7441,7 +7667,7 @@
         <v>16</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I147" s="1">
         <v>0.05</v>
@@ -7470,7 +7696,7 @@
         <v>16</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I148" s="1">
         <v>0.05</v>
@@ -7499,7 +7725,7 @@
         <v>16</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I149" s="1">
         <v>0.05</v>
@@ -7513,7 +7739,7 @@
         <v>52</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>68</v>
@@ -7528,7 +7754,7 @@
         <v>42</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I150" s="1">
         <v>0.05</v>
@@ -7542,7 +7768,7 @@
         <v>52</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>68</v>
@@ -7557,7 +7783,7 @@
         <v>42</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I151" s="1">
         <v>0.05</v>
@@ -7571,7 +7797,7 @@
         <v>52</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>68</v>
@@ -7586,7 +7812,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I152" s="1">
         <v>0.05</v>
@@ -7600,7 +7826,7 @@
         <v>52</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>68</v>
@@ -7615,7 +7841,7 @@
         <v>24</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I153" s="1">
         <v>0.05</v>
@@ -7644,7 +7870,7 @@
         <v>25</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I154" s="1">
         <v>0.05</v>
@@ -7658,7 +7884,7 @@
         <v>52</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>68</v>
@@ -7673,7 +7899,7 @@
         <v>60</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I155" s="1">
         <v>0.05</v>
@@ -7702,7 +7928,7 @@
         <v>12</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I156" s="1">
         <v>0.05</v>
@@ -7731,7 +7957,7 @@
         <v>12</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I157" s="1">
         <v>0.05</v>
@@ -7760,7 +7986,7 @@
         <v>30</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I158" s="1">
         <v>16</v>
@@ -7784,7 +8010,7 @@
         <v>52</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>69</v>
@@ -7799,7 +8025,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I159" s="1">
         <v>27</v>
@@ -7837,7 +8063,7 @@
         <v>22</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I160" s="1">
         <v>12</v>
@@ -7875,7 +8101,7 @@
         <v>22</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I161" s="1">
         <v>12</v>
@@ -7913,7 +8139,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I162" s="1">
         <v>14</v>
@@ -7951,7 +8177,7 @@
         <v>20</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I163" s="1">
         <v>18</v>
@@ -7989,7 +8215,7 @@
         <v>24</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I164" s="1">
         <v>15</v>
@@ -8027,7 +8253,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I165" s="1">
         <v>18</v>
@@ -8065,7 +8291,7 @@
         <v>24</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I166" s="1">
         <v>18</v>
@@ -8103,7 +8329,7 @@
         <v>24</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I167" s="1">
         <v>18</v>
@@ -8141,7 +8367,7 @@
         <v>20</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I168" s="1">
         <v>11</v>
@@ -8176,10 +8402,10 @@
         <v>48.400000000000006</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I169" s="1">
         <v>11</v>
@@ -8221,7 +8447,7 @@
         <v>30</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I170" s="1">
         <v>15</v>
@@ -8259,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I171" s="1">
         <v>5</v>
@@ -8297,7 +8523,7 @@
         <v>15</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I172" s="1">
         <v>20</v>
@@ -8336,10 +8562,10 @@
         <v>30</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
@@ -8368,7 +8594,7 @@
         <v>22</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I174" s="1">
         <v>11</v>
@@ -8406,7 +8632,7 @@
         <v>22</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I175" s="1">
         <v>11</v>
@@ -8444,7 +8670,7 @@
         <v>22</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I176" s="1">
         <v>11</v>
@@ -8482,7 +8708,7 @@
         <v>20</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I177" s="1">
         <v>23</v>
@@ -8520,7 +8746,7 @@
         <v>15</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I178" s="1">
         <v>15</v>
@@ -8558,7 +8784,7 @@
         <v>15</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I179" s="1">
         <v>20</v>
@@ -8596,7 +8822,7 @@
         <v>42</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I180" s="1">
         <v>30</v>
@@ -8634,7 +8860,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I181" s="1">
         <v>12</v>
@@ -8673,7 +8899,7 @@
         <v>42</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I182" s="1">
         <v>21</v>
@@ -8711,7 +8937,7 @@
         <v>35</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I183" s="1">
         <v>5</v>
@@ -8749,10 +8975,10 @@
         <v>15</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L184" s="1">
         <v>5.6539999999999999</v>
@@ -8787,10 +9013,10 @@
         <v>15</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L185" s="1">
         <v>5.6539999999999999</v>
@@ -8825,10 +9051,10 @@
         <v>15</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L186" s="1">
         <v>5.6539999999999999</v>
@@ -8863,10 +9089,10 @@
         <v>15</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L187" s="1">
         <v>5.6539999999999999</v>
@@ -8901,10 +9127,10 @@
         <v>15</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J188" s="1">
         <f>F189-J189</f>
@@ -8943,10 +9169,10 @@
         <v>15</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J189" s="1">
         <v>66.959999999999994</v>
@@ -8984,10 +9210,10 @@
         <v>15</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L190" s="1">
         <v>5.6539999999999999</v>
@@ -9025,7 +9251,7 @@
         <v>24</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I191" s="1">
         <v>30</v>
@@ -9071,7 +9297,7 @@
         <v>30</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I192" s="1">
         <v>23.06</v>
@@ -9112,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
@@ -9135,7 +9361,7 @@
         <v>52</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>142</v>
+        <v>438</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>69</v>
@@ -9150,7 +9376,7 @@
         <v>30</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
@@ -9168,16 +9394,16 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="E195" s="1">
         <v>50</v>
@@ -9189,7 +9415,7 @@
         <v>6</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I195" s="1">
         <v>10</v>
@@ -9197,13 +9423,13 @@
     </row>
     <row r="196" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>17</v>
@@ -9218,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I196" s="1">
         <v>0.03</v>
@@ -9226,13 +9452,13 @@
     </row>
     <row r="197" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>17</v>
@@ -9247,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I197" s="1">
         <v>0.03</v>
@@ -9255,13 +9481,13 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>17</v>
@@ -9276,7 +9502,7 @@
         <v>1</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I198" s="1">
         <v>0.03</v>
@@ -9287,10 +9513,10 @@
         <v>20199</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>17</v>
@@ -9305,7 +9531,7 @@
         <v>1</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I199" s="1">
         <v>0.03</v>
@@ -9313,13 +9539,13 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>17</v>
@@ -9334,7 +9560,7 @@
         <v>1</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I200" s="1">
         <v>0.03</v>
@@ -9342,13 +9568,13 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>17</v>
@@ -9363,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I201" s="1">
         <v>0.03</v>
@@ -9371,13 +9597,13 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>17</v>
@@ -9392,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I202" s="1">
         <v>0.03</v>
@@ -9400,13 +9626,13 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>17</v>
@@ -9421,7 +9647,7 @@
         <v>1</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I203" s="1">
         <v>0.03</v>
@@ -9429,13 +9655,13 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>17</v>
@@ -9450,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I204" s="1">
         <v>0.03</v>
@@ -9458,13 +9684,13 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>17</v>
@@ -9479,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I205" s="1">
         <v>0.03</v>
@@ -9487,13 +9713,13 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>17</v>
@@ -9508,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I206" s="1">
         <v>0.03</v>
@@ -9516,13 +9742,13 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>17</v>
@@ -9537,7 +9763,7 @@
         <v>1</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I207" s="1">
         <v>0.03</v>
@@ -9545,13 +9771,13 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>17</v>
@@ -9566,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I208" s="1">
         <v>0.03</v>
@@ -9574,13 +9800,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>17</v>
@@ -9595,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I209" s="1">
         <v>0.03</v>
@@ -9603,13 +9829,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>17</v>
@@ -9624,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I210" s="1">
         <v>0.03</v>
@@ -9632,13 +9858,13 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>17</v>
@@ -9653,7 +9879,7 @@
         <v>1</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I211" s="1">
         <v>0.03</v>
@@ -9661,13 +9887,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>17</v>
@@ -9682,7 +9908,7 @@
         <v>1</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I212" s="1">
         <v>0.03</v>
@@ -9690,13 +9916,13 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>17</v>
@@ -9711,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I213" s="1">
         <v>0.03</v>
@@ -9719,13 +9945,13 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>17</v>
@@ -9740,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I214" s="1">
         <v>0.03</v>
@@ -9748,13 +9974,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>17</v>
@@ -9769,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I215" s="1">
         <v>0.03</v>
@@ -9777,13 +10003,13 @@
     </row>
     <row r="216" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>17</v>
@@ -9798,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I216" s="1">
         <v>0.03</v>
@@ -9806,13 +10032,13 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>17</v>
@@ -9827,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I217" s="1">
         <v>0.03</v>
@@ -9835,13 +10061,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>17</v>
@@ -9856,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I218" s="1">
         <v>0.03</v>
@@ -9864,13 +10090,13 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>17</v>
@@ -9885,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I219" s="1">
         <v>0.03</v>
@@ -9893,13 +10119,13 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>17</v>
@@ -9914,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I220" s="1">
         <v>0.03</v>
@@ -9922,13 +10148,13 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>17</v>
@@ -9943,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I221" s="1">
         <v>0.03</v>
@@ -9951,13 +10177,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>17</v>
@@ -9972,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I222" s="1">
         <v>0.03</v>
@@ -9980,13 +10206,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>17</v>
@@ -10001,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I223" s="1">
         <v>0.03</v>
@@ -10009,13 +10235,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>17</v>
@@ -10030,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I224" s="1">
         <v>0.03</v>
@@ -10038,13 +10264,13 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>17</v>
@@ -10059,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I225" s="1">
         <v>0.03</v>
@@ -10067,13 +10293,13 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>17</v>
@@ -10088,7 +10314,7 @@
         <v>1</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I226" s="1">
         <v>0.03</v>
@@ -10096,13 +10322,13 @@
     </row>
     <row r="227" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>17</v>
@@ -10117,7 +10343,7 @@
         <v>1</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I227" s="1">
         <v>0.03</v>
@@ -10125,13 +10351,13 @@
     </row>
     <row r="228" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>17</v>
@@ -10146,7 +10372,7 @@
         <v>1</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I228" s="1">
         <v>0.03</v>
@@ -10154,13 +10380,13 @@
     </row>
     <row r="229" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>17</v>
@@ -10175,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I229" s="1">
         <v>0.03</v>
@@ -10183,13 +10409,13 @@
     </row>
     <row r="230" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>17</v>
@@ -10204,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I230" s="1">
         <v>0.03</v>
@@ -10212,13 +10438,13 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>17</v>
@@ -10233,7 +10459,7 @@
         <v>1</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I231" s="1">
         <v>0.03</v>
@@ -10241,13 +10467,13 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>17</v>
@@ -10262,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I232" s="1">
         <v>0.03</v>
@@ -10270,13 +10496,13 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>17</v>
@@ -10291,7 +10517,7 @@
         <v>1</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I233" s="1">
         <v>0.03</v>
@@ -10299,13 +10525,13 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>17</v>
@@ -10320,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I234" s="1">
         <v>0.03</v>
@@ -10328,13 +10554,13 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>17</v>
@@ -10349,7 +10575,7 @@
         <v>1</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I235" s="1">
         <v>0.03</v>
@@ -10357,13 +10583,13 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>17</v>
@@ -10378,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I236" s="1">
         <v>0.03</v>
@@ -10386,13 +10612,13 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>17</v>
@@ -10407,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I237" s="1">
         <v>0.03</v>
@@ -10415,13 +10641,13 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>17</v>
@@ -10436,7 +10662,7 @@
         <v>1</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I238" s="1">
         <v>0.03</v>
@@ -10444,13 +10670,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>17</v>
@@ -10465,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I239" s="1">
         <v>0.03</v>
@@ -10473,13 +10699,13 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>17</v>
@@ -10494,7 +10720,7 @@
         <v>1</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I240" s="1">
         <v>0.03</v>
@@ -10502,13 +10728,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>17</v>
@@ -10523,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I241" s="1">
         <v>0.03</v>
@@ -10531,13 +10757,13 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>17</v>
@@ -10552,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I242" s="1">
         <v>0.03</v>
@@ -10560,13 +10786,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>17</v>
@@ -10581,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I243" s="1">
         <v>0.03</v>
@@ -10589,13 +10815,13 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>17</v>
@@ -10610,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I244" s="1">
         <v>0.03</v>
@@ -10618,13 +10844,13 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>17</v>
@@ -10639,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I245" s="1">
         <v>0.03</v>
@@ -10647,13 +10873,13 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>17</v>
@@ -10668,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I246" s="1">
         <v>0.03</v>
@@ -10676,13 +10902,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>17</v>
@@ -10697,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I247" s="1">
         <v>0.03</v>
@@ -10705,13 +10931,13 @@
     </row>
     <row r="248" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>17</v>
@@ -10726,7 +10952,7 @@
         <v>1</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I248" s="1">
         <v>0.03</v>
@@ -10734,13 +10960,13 @@
     </row>
     <row r="249" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>17</v>
@@ -10755,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I249" s="1">
         <v>0.03</v>
@@ -10763,13 +10989,13 @@
     </row>
     <row r="250" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>17</v>
@@ -10784,7 +11010,7 @@
         <v>1</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I250" s="1">
         <v>0.03</v>
@@ -10792,13 +11018,13 @@
     </row>
     <row r="251" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>17</v>
@@ -10813,7 +11039,7 @@
         <v>1</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I251" s="1">
         <v>0.03</v>
@@ -10821,13 +11047,13 @@
     </row>
     <row r="252" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>17</v>
@@ -10842,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I252" s="1">
         <v>0.03</v>
@@ -10850,13 +11076,13 @@
     </row>
     <row r="253" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>17</v>
@@ -10871,7 +11097,7 @@
         <v>1</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I253" s="1">
         <v>0.03</v>
@@ -10879,13 +11105,13 @@
     </row>
     <row r="254" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>17</v>
@@ -10900,7 +11126,7 @@
         <v>1</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I254" s="1">
         <v>0.03</v>
@@ -10908,13 +11134,13 @@
     </row>
     <row r="255" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>17</v>
@@ -10929,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I255" s="1">
         <v>0.03</v>
@@ -10937,13 +11163,13 @@
     </row>
     <row r="256" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>17</v>
@@ -10958,7 +11184,7 @@
         <v>1</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I256" s="1">
         <v>0.03</v>
@@ -10966,13 +11192,13 @@
     </row>
     <row r="257" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>17</v>
@@ -10987,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I257" s="1">
         <v>0.03</v>
@@ -10995,13 +11221,13 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>17</v>
@@ -11016,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I258" s="1">
         <v>0.03</v>
@@ -11024,13 +11250,13 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>17</v>
@@ -11045,7 +11271,7 @@
         <v>1</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I259" s="1">
         <v>0.03</v>
@@ -11053,13 +11279,13 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>17</v>
@@ -11074,7 +11300,7 @@
         <v>1</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I260" s="1">
         <v>0.03</v>
@@ -11082,13 +11308,13 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>17</v>
@@ -11103,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I261" s="1">
         <v>0.03</v>
@@ -11111,13 +11337,13 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>17</v>
@@ -11132,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I262" s="1">
         <v>0.03</v>
@@ -11140,13 +11366,13 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>17</v>
@@ -11161,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I263" s="1">
         <v>0.03</v>
@@ -11169,13 +11395,13 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>17</v>
@@ -11190,7 +11416,7 @@
         <v>1</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I264" s="1">
         <v>0.03</v>
@@ -11198,13 +11424,13 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>17</v>
@@ -11219,7 +11445,7 @@
         <v>1</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I265" s="1">
         <v>0.03</v>
@@ -11227,13 +11453,13 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>17</v>
@@ -11248,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I266" s="1">
         <v>0.03</v>
@@ -11256,13 +11482,13 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>17</v>
@@ -11277,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I267" s="1">
         <v>0.03</v>
@@ -11285,13 +11511,13 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>17</v>
@@ -11306,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I268" s="1">
         <v>0.03</v>
@@ -11314,13 +11540,13 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>17</v>
@@ -11335,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I269" s="1">
         <v>0.03</v>
@@ -11343,13 +11569,13 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>17</v>
@@ -11364,7 +11590,7 @@
         <v>1</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I270" s="1">
         <v>0.03</v>
@@ -11372,13 +11598,13 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>17</v>
@@ -11393,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I271" s="1">
         <v>0.03</v>
@@ -11401,13 +11627,13 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>17</v>
@@ -11422,7 +11648,7 @@
         <v>1</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I272" s="1">
         <v>0.03</v>
@@ -11430,13 +11656,13 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>17</v>
@@ -11451,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I273" s="1">
         <v>0.03</v>
@@ -11459,13 +11685,13 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>17</v>
@@ -11480,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I274" s="1">
         <v>0.03</v>
@@ -11488,13 +11714,13 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>17</v>
@@ -11509,7 +11735,7 @@
         <v>1</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I275" s="1">
         <v>0.03</v>
@@ -11517,13 +11743,13 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>17</v>
@@ -11538,7 +11764,7 @@
         <v>1</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I276" s="1">
         <v>0.03</v>
@@ -11546,13 +11772,13 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>17</v>
@@ -11567,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I277" s="1">
         <v>0.03</v>
@@ -11575,13 +11801,13 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>17</v>
@@ -11596,7 +11822,7 @@
         <v>1</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I278" s="1">
         <v>0.03</v>
@@ -11604,13 +11830,13 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>17</v>
@@ -11625,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I279" s="1">
         <v>0.03</v>
@@ -11633,13 +11859,13 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>17</v>
@@ -11654,7 +11880,7 @@
         <v>1</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I280" s="1">
         <v>0.03</v>
@@ -11662,13 +11888,13 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>17</v>
@@ -11683,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I281" s="1">
         <v>0.03</v>
@@ -11691,13 +11917,13 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>17</v>
@@ -11712,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I282" s="1">
         <v>0.03</v>
@@ -11720,13 +11946,13 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>17</v>
@@ -11741,7 +11967,7 @@
         <v>1</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I283" s="1">
         <v>0.03</v>
@@ -11749,13 +11975,13 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>17</v>
@@ -11770,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I284" s="1">
         <v>0.03</v>
@@ -11778,13 +12004,13 @@
     </row>
     <row r="285" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>17</v>
@@ -11799,7 +12025,7 @@
         <v>1</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I285" s="1">
         <v>0.03</v>
@@ -11807,13 +12033,13 @@
     </row>
     <row r="286" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>17</v>
@@ -11828,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I286" s="1">
         <v>0.03</v>
@@ -11836,13 +12062,13 @@
     </row>
     <row r="287" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>17</v>
@@ -11857,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I287" s="1">
         <v>0.03</v>
@@ -11865,13 +12091,13 @@
     </row>
     <row r="288" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>17</v>
@@ -11886,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I288" s="1">
         <v>0.03</v>
@@ -11894,13 +12120,13 @@
     </row>
     <row r="289" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>17</v>
@@ -11915,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I289" s="1">
         <v>0.03</v>
@@ -11923,13 +12149,13 @@
     </row>
     <row r="290" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>17</v>
@@ -11944,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I290" s="1">
         <v>0.03</v>
@@ -11952,13 +12178,13 @@
     </row>
     <row r="291" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>17</v>
@@ -11973,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I291" s="1">
         <v>0.03</v>
@@ -11981,13 +12207,13 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>17</v>
@@ -12002,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I292" s="1">
         <v>0.03</v>
@@ -12010,13 +12236,13 @@
     </row>
     <row r="293" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>17</v>
@@ -12031,7 +12257,7 @@
         <v>1</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I293" s="1">
         <v>0.03</v>
@@ -12039,13 +12265,13 @@
     </row>
     <row r="294" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>17</v>
@@ -12060,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I294" s="1">
         <v>0.03</v>
@@ -12068,13 +12294,13 @@
     </row>
     <row r="295" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>17</v>
@@ -12089,7 +12315,7 @@
         <v>1</v>
       </c>
       <c r="H295" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I295" s="1">
         <v>0.03</v>
@@ -12097,13 +12323,13 @@
     </row>
     <row r="296" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>17</v>
@@ -12118,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I296" s="1">
         <v>0.03</v>
@@ -12126,13 +12352,13 @@
     </row>
     <row r="297" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>17</v>
@@ -12147,7 +12373,7 @@
         <v>1</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I297" s="1">
         <v>0.03</v>
@@ -12155,13 +12381,13 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>17</v>
@@ -12176,7 +12402,7 @@
         <v>1</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I298" s="1">
         <v>0.03</v>
@@ -12184,13 +12410,13 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>17</v>
@@ -12205,7 +12431,7 @@
         <v>1</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I299" s="1">
         <v>0.03</v>
@@ -12213,13 +12439,13 @@
     </row>
     <row r="300" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>17</v>
@@ -12234,7 +12460,7 @@
         <v>1</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I300" s="1">
         <v>0.03</v>
@@ -12242,13 +12468,13 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>17</v>
@@ -12263,7 +12489,7 @@
         <v>1</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I301" s="1">
         <v>0.03</v>
@@ -12271,13 +12497,13 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C302" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>17</v>
@@ -12292,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I302" s="1">
         <v>0.03</v>
@@ -12301,7 +12527,7 @@
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B303" s="1"/>
       <c r="C303" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>17</v>
@@ -12316,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I303" s="1">
         <v>0.03</v>
@@ -12324,13 +12550,13 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>69</v>
@@ -12339,16 +12565,16 @@
         <v>1.51</v>
       </c>
       <c r="F304" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G304" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G304" s="1" t="s">
+      <c r="H304" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I304" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="H304" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I304" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="J304">
         <v>39</v>
@@ -12356,13 +12582,13 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>69</v>
@@ -12377,7 +12603,7 @@
         <v>20</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I305" s="1">
         <v>10.53</v>
@@ -12385,13 +12611,13 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>69</v>
@@ -12406,7 +12632,7 @@
         <v>20</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I306" s="1">
         <v>10.53</v>
@@ -12414,13 +12640,13 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>69</v>
@@ -12435,7 +12661,7 @@
         <v>20</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I307" s="1">
         <v>10.53</v>
@@ -12443,13 +12669,13 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C308" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>69</v>
@@ -12464,13 +12690,1133 @@
         <v>30</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I308" s="1">
         <v>27.46</v>
       </c>
       <c r="J308">
         <v>57.24</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="3">
+        <v>2.15</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H309" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="J309" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="3">
+        <v>2.15</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H310" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I310" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="J310" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E311" s="3">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="F311" s="1">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="G311" s="1">
+        <v>1</v>
+      </c>
+      <c r="H311" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I311" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="J311" s="1">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E312" s="3">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="F312" s="1">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="G312" s="1">
+        <v>1</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I312" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="J312" s="1">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E313" s="3">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="F313" s="1">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="G313" s="1">
+        <v>1</v>
+      </c>
+      <c r="H313" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I313" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="J313" s="1">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E314" s="3">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="F314" s="1">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="G314" s="1">
+        <v>1</v>
+      </c>
+      <c r="H314" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I314" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="J314" s="1">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E315" s="3">
+        <v>4.49</v>
+      </c>
+      <c r="F315" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="G315" s="1">
+        <v>1</v>
+      </c>
+      <c r="H315" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I315" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="J315" s="1">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E316" s="3">
+        <v>4.49</v>
+      </c>
+      <c r="F316" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="G316" s="1">
+        <v>1</v>
+      </c>
+      <c r="H316" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I316" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="J316" s="1">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E317" s="3">
+        <v>4.49</v>
+      </c>
+      <c r="F317" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="G317" s="1">
+        <v>1</v>
+      </c>
+      <c r="H317" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I317" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="J317" s="1">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E318" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F318" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="G318" s="1">
+        <v>1</v>
+      </c>
+      <c r="H318" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I318" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="J318" s="1">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E319" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F319" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="G319" s="1">
+        <v>1</v>
+      </c>
+      <c r="H319" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I319" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="J319" s="1">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E320" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F320" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="G320" s="1">
+        <v>1</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I320" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="J320" s="1">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E321" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="F321" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="G321" s="1">
+        <v>1</v>
+      </c>
+      <c r="H321" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I321" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="J321" s="1">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E322" s="3">
+        <v>3.36</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G322" s="1">
+        <v>1</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I322" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J322" s="1">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E323" s="3">
+        <v>3.36</v>
+      </c>
+      <c r="F323" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G323" s="1">
+        <v>1</v>
+      </c>
+      <c r="H323" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I323" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J323" s="1">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E324" s="3">
+        <v>3.36</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G324" s="1">
+        <v>1</v>
+      </c>
+      <c r="H324" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I324" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J324" s="1">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E325" s="3">
+        <v>3.36</v>
+      </c>
+      <c r="F325" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G325" s="1">
+        <v>1</v>
+      </c>
+      <c r="H325" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I325" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J325" s="1">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E326" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="F326">
+        <v>2.74</v>
+      </c>
+      <c r="G326" s="1">
+        <v>1</v>
+      </c>
+      <c r="H326" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I326" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="J326" s="1">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E327" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="F327">
+        <v>2.74</v>
+      </c>
+      <c r="G327" s="1">
+        <v>1</v>
+      </c>
+      <c r="H327" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I327" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="J327" s="1">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E328" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="F328">
+        <v>2.74</v>
+      </c>
+      <c r="G328" s="1">
+        <v>1</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I328" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="J328" s="1">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E329" s="3">
+        <v>1.86</v>
+      </c>
+      <c r="F329">
+        <v>1.86</v>
+      </c>
+      <c r="G329" s="1">
+        <v>1</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I329" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J329" s="1">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E330" s="3">
+        <v>1.86</v>
+      </c>
+      <c r="F330">
+        <v>1.86</v>
+      </c>
+      <c r="G330" s="1">
+        <v>1</v>
+      </c>
+      <c r="H330" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I330" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J330" s="1">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E331" s="3">
+        <v>1.86</v>
+      </c>
+      <c r="F331">
+        <v>1.86</v>
+      </c>
+      <c r="G331" s="1">
+        <v>1</v>
+      </c>
+      <c r="H331" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I331" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J331" s="1">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E332" s="3">
+        <v>4.97</v>
+      </c>
+      <c r="F332">
+        <v>4.97</v>
+      </c>
+      <c r="G332" s="1">
+        <v>1</v>
+      </c>
+      <c r="H332" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I332" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="J332" s="1">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E333" s="3">
+        <v>4.97</v>
+      </c>
+      <c r="F333">
+        <v>4.97</v>
+      </c>
+      <c r="G333" s="1">
+        <v>1</v>
+      </c>
+      <c r="H333" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I333" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="J333" s="1">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E334" s="3">
+        <v>4.97</v>
+      </c>
+      <c r="F334">
+        <v>4.97</v>
+      </c>
+      <c r="G334" s="1">
+        <v>1</v>
+      </c>
+      <c r="H334" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I334" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="J334" s="1">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E335" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="F335">
+        <v>1.98</v>
+      </c>
+      <c r="G335" s="1">
+        <v>1</v>
+      </c>
+      <c r="H335" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I335" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="J335" s="1">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E336" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="F336">
+        <v>1.98</v>
+      </c>
+      <c r="G336" s="1">
+        <v>1</v>
+      </c>
+      <c r="H336" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I336" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="J336" s="1">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E337" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="F337">
+        <v>1.98</v>
+      </c>
+      <c r="G337" s="1">
+        <v>1</v>
+      </c>
+      <c r="H337" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I337" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="J337" s="1">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E338" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F338">
+        <v>3.1</v>
+      </c>
+      <c r="G338" s="1">
+        <v>1</v>
+      </c>
+      <c r="H338" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I338" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="J338" s="1">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E339" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="F339">
+        <v>30.6</v>
+      </c>
+      <c r="G339" s="1">
+        <v>36</v>
+      </c>
+      <c r="H339" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I339" s="1">
+        <v>6.12</v>
+      </c>
+      <c r="J339" s="1">
+        <v>24.48</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E340" s="3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F340">
+        <v>28.75</v>
+      </c>
+      <c r="G340" s="1">
+        <v>50</v>
+      </c>
+      <c r="H340" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I340" s="1">
+        <v>5.75</v>
+      </c>
+      <c r="J340" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E341" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="F341">
+        <v>50.15</v>
+      </c>
+      <c r="G341" s="1">
+        <v>21</v>
+      </c>
+      <c r="H341" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I341" s="1">
+        <v>8.35</v>
+      </c>
+      <c r="J341" s="1">
+        <v>41.79</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E342" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="F342">
+        <v>50.15</v>
+      </c>
+      <c r="G342" s="1">
+        <v>21</v>
+      </c>
+      <c r="H342" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I342" s="1">
+        <v>8.35</v>
+      </c>
+      <c r="J342" s="1">
+        <v>41.79</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E343" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="F343">
+        <v>50.15</v>
+      </c>
+      <c r="G343" s="1">
+        <v>21</v>
+      </c>
+      <c r="H343" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I343" s="1">
+        <v>8.35</v>
+      </c>
+      <c r="J343" s="1">
+        <v>41.79</v>
       </c>
     </row>
   </sheetData>

--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296D3C01-C621-4DFF-A2D7-EF61628E6E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54B5873-E66D-48E6-AA3D-210CB5938E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="base_de_produtos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">base_de_produtos!$A$1:$J$343</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="601">
   <si>
     <t>categoria</t>
   </si>
@@ -2247,208 +2247,469 @@
     <t>9</t>
   </si>
   <si>
-    <t>1654</t>
-  </si>
-  <si>
-    <t>RLD</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>1653</t>
-  </si>
-  <si>
-    <t>RLD Macarrão Instantaneo Adria Carne 75g</t>
-  </si>
-  <si>
-    <t>RLD Macarrão Instantaneo Adria Galinha Caipira 75g</t>
-  </si>
-  <si>
-    <t>3156</t>
-  </si>
-  <si>
-    <t>RLD Macarrão Instantaneo Adria Galinha Suave 75g</t>
-  </si>
-  <si>
-    <t>3156A</t>
-  </si>
-  <si>
-    <t>RLD Macarrão Instantaneo Adria Tomate 75g</t>
-  </si>
-  <si>
-    <t>RLD Cooquie Piraque 80g Goiabinha</t>
-  </si>
-  <si>
-    <t>3744</t>
-  </si>
-  <si>
-    <t>RLD Cooquie Piraque 80g Gotas de Chocolate</t>
-  </si>
-  <si>
-    <t>3743</t>
-  </si>
-  <si>
-    <t>RLD Cooquie Piraque 80g Chocolate</t>
-  </si>
-  <si>
-    <t>3906</t>
-  </si>
-  <si>
-    <t>RLD Sequilhos Itamaraty 100g Limão</t>
-  </si>
-  <si>
-    <t>3907</t>
-  </si>
-  <si>
-    <t>RLD Sequilhos Itamaraty 100g Leite Condensado</t>
-  </si>
-  <si>
-    <t>3909</t>
-  </si>
-  <si>
-    <t>RLD Sequilhos Itamaraty 100g Broa de Milho</t>
-  </si>
-  <si>
-    <t>3908</t>
-  </si>
-  <si>
-    <t>RLD Sequilhos Itamaraty 100g Tradicional</t>
-  </si>
-  <si>
-    <t>2193</t>
-  </si>
-  <si>
-    <t>RLD Stick Look Itamaraty 55g Brigadeiro</t>
-  </si>
-  <si>
-    <t>3,36</t>
-  </si>
-  <si>
-    <t>955</t>
-  </si>
-  <si>
-    <t>RLD Stick Look Itamaraty 55g Floresta Negra</t>
-  </si>
-  <si>
-    <t>932</t>
-  </si>
-  <si>
-    <t>RLD Stick Look Itamaraty 55g Doce de Leite</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>RLD Stick Look Itamaraty 55g Napolitano</t>
-  </si>
-  <si>
-    <t>1476</t>
-  </si>
-  <si>
-    <t>RLD Wafer Itamaraty 80g Atrevidos Napolitano</t>
-  </si>
-  <si>
-    <t>1930</t>
-  </si>
-  <si>
-    <t>RLD Wafer Itamaraty 80g Atrevidos Brigadeiro</t>
-  </si>
-  <si>
-    <t>1399</t>
-  </si>
-  <si>
-    <t>RLD Wafer Itamaraty 80g Atrevidos Chocolate Branco</t>
-  </si>
-  <si>
-    <t>1780</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Recheado Luam 110g Luanesco Baunilha</t>
-  </si>
-  <si>
-    <t>1796</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Recheado Luam 110g Luanesco Duo Chocolate</t>
-  </si>
-  <si>
-    <t>1781</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Recheado Luam 110g Luanesco Morango</t>
-  </si>
-  <si>
-    <t>3063</t>
-  </si>
-  <si>
-    <t>RLD Rosquinha Luam 300g Banana e Canela</t>
-  </si>
-  <si>
-    <t>1784</t>
-  </si>
-  <si>
-    <t>RLD Rosquinha Luam 300g Chocolate</t>
-  </si>
-  <si>
-    <t>1782</t>
-  </si>
-  <si>
-    <t>RLD Rosquinha Luam 300g Coco</t>
-  </si>
-  <si>
-    <t>4217</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Salgado Tuc´s 100g Cracker Cebola</t>
-  </si>
-  <si>
-    <t>2839</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Salgado Tuc´s 100g Cracker Original</t>
-  </si>
-  <si>
-    <t>2839A</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Salgado Tuc´s 100g Cracker Integral</t>
-  </si>
-  <si>
-    <t>3691</t>
-  </si>
-  <si>
-    <t>RLD Biscoito Nestlé 130g Passatempo</t>
-  </si>
-  <si>
-    <t>992</t>
-  </si>
-  <si>
-    <t>RLD Moranguete Bel Caixa com 36 13g</t>
-  </si>
-  <si>
-    <t>2767</t>
-  </si>
-  <si>
-    <t>RLD Moranguete Bel Caixa com 50 9g</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>RLD Chicle Trident Display com 21 Hortelã</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>RLD Chicle Trident Display com 21 Menta</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>RLD Chicle Trident Display com 21 Tutty Fruti</t>
+    <t>53</t>
+  </si>
+  <si>
+    <t>31,7</t>
+  </si>
+  <si>
+    <t>13,84</t>
+  </si>
+  <si>
+    <t>CLO0001</t>
+  </si>
+  <si>
+    <t>CLO0002</t>
+  </si>
+  <si>
+    <t>CLO0003</t>
+  </si>
+  <si>
+    <t>CLO0004</t>
+  </si>
+  <si>
+    <t>CLO0005</t>
+  </si>
+  <si>
+    <t>CLO0006</t>
+  </si>
+  <si>
+    <t>CLO0007</t>
+  </si>
+  <si>
+    <t>CLO0008</t>
+  </si>
+  <si>
+    <t>CLO0009</t>
+  </si>
+  <si>
+    <t>CLO0010</t>
+  </si>
+  <si>
+    <t>CLO0011</t>
+  </si>
+  <si>
+    <t>CLO0012</t>
+  </si>
+  <si>
+    <t>CLO0013</t>
+  </si>
+  <si>
+    <t>CLO0014</t>
+  </si>
+  <si>
+    <t>CLO0015</t>
+  </si>
+  <si>
+    <t>CLO0016</t>
+  </si>
+  <si>
+    <t>CLO0017</t>
+  </si>
+  <si>
+    <t>CLO0018</t>
+  </si>
+  <si>
+    <t>CLO0019</t>
+  </si>
+  <si>
+    <t>CLO0020</t>
+  </si>
+  <si>
+    <t>CLO0021</t>
+  </si>
+  <si>
+    <t>CLO0022</t>
+  </si>
+  <si>
+    <t>CLO0023</t>
+  </si>
+  <si>
+    <t>CLO0024</t>
+  </si>
+  <si>
+    <t>CLO0025</t>
+  </si>
+  <si>
+    <t>CLO0026</t>
+  </si>
+  <si>
+    <t>CLO0027</t>
+  </si>
+  <si>
+    <t>CLO0028</t>
+  </si>
+  <si>
+    <t>CLO0029</t>
+  </si>
+  <si>
+    <t>CLO0030</t>
+  </si>
+  <si>
+    <t>CLO0031</t>
+  </si>
+  <si>
+    <t>CLO0032</t>
+  </si>
+  <si>
+    <t>CLO0033</t>
+  </si>
+  <si>
+    <t>CLO0034</t>
+  </si>
+  <si>
+    <t>CLO0035</t>
+  </si>
+  <si>
+    <t>CLO0036</t>
+  </si>
+  <si>
+    <t>CLO0037</t>
+  </si>
+  <si>
+    <t>CLO0038</t>
+  </si>
+  <si>
+    <t>CLO0039</t>
+  </si>
+  <si>
+    <t>CLO0040</t>
+  </si>
+  <si>
+    <t>CLO0041</t>
+  </si>
+  <si>
+    <t>CLO0042</t>
+  </si>
+  <si>
+    <t>CLO0043</t>
+  </si>
+  <si>
+    <t>CLO0044</t>
+  </si>
+  <si>
+    <t>CLO0045</t>
+  </si>
+  <si>
+    <t>CLO0046</t>
+  </si>
+  <si>
+    <t>CLO0047</t>
+  </si>
+  <si>
+    <t>CLO0048</t>
+  </si>
+  <si>
+    <t>CLO0049</t>
+  </si>
+  <si>
+    <t>CLO0050</t>
+  </si>
+  <si>
+    <t>CLO0051</t>
+  </si>
+  <si>
+    <t>CLO0052</t>
+  </si>
+  <si>
+    <t>CLO0053</t>
+  </si>
+  <si>
+    <t>CLO0054</t>
+  </si>
+  <si>
+    <t>CLO0055</t>
+  </si>
+  <si>
+    <t>CLO0056</t>
+  </si>
+  <si>
+    <t>CLO0057</t>
+  </si>
+  <si>
+    <t>CLO0058</t>
+  </si>
+  <si>
+    <t>CLO0059</t>
+  </si>
+  <si>
+    <t>CLO0060</t>
+  </si>
+  <si>
+    <t>CLO0061</t>
+  </si>
+  <si>
+    <t>CLO0062</t>
+  </si>
+  <si>
+    <t>CLO0063</t>
+  </si>
+  <si>
+    <t>CLO0064</t>
+  </si>
+  <si>
+    <t>CLO0065</t>
+  </si>
+  <si>
+    <t>CLO0066</t>
+  </si>
+  <si>
+    <t>CLO0067</t>
+  </si>
+  <si>
+    <t>CLO0068</t>
+  </si>
+  <si>
+    <t>CLO0069</t>
+  </si>
+  <si>
+    <t>CLO0070</t>
+  </si>
+  <si>
+    <t>CLO0071</t>
+  </si>
+  <si>
+    <t>CLO0072</t>
+  </si>
+  <si>
+    <t>Garoto</t>
+  </si>
+  <si>
+    <t>Nestlé</t>
+  </si>
+  <si>
+    <t>Lacta</t>
+  </si>
+  <si>
+    <t>Trento</t>
+  </si>
+  <si>
+    <t>Bauduco</t>
+  </si>
+  <si>
+    <t>Pepsico</t>
+  </si>
+  <si>
+    <t>Diversos</t>
+  </si>
+  <si>
+    <t>Bombom Garoto Caixa 250g (ESGOTADO)</t>
+  </si>
+  <si>
+    <t>Bombom Nestlé Caixa 251g</t>
+  </si>
+  <si>
+    <t>Bombom Lacta Caixa</t>
+  </si>
+  <si>
+    <t>Bis Xtra Original 45g</t>
+  </si>
+  <si>
+    <t>Bis Xtra Oreo 45g</t>
+  </si>
+  <si>
+    <t>Bis Xtra Branco 45g</t>
+  </si>
+  <si>
+    <t>Bis Xtra Black 45g</t>
+  </si>
+  <si>
+    <t>Bombom Sonho de Valsa Pacote 1Kg</t>
+  </si>
+  <si>
+    <t>Baton Branco 30x16g</t>
+  </si>
+  <si>
+    <t>Trento Chocolate 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Branco 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Trufa 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Pistache 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Avelã 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Limão 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Morango 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Milk 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Dark 16x29g</t>
+  </si>
+  <si>
+    <t>Trento Maracujá 16x29g</t>
+  </si>
+  <si>
+    <t>KitKat Dark 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat Cotton Candy 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat Churros 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat Cherry Vanilla 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat Strawbeerry 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat Lemon 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat Ao Leite 41,5g</t>
+  </si>
+  <si>
+    <t>KitKat White 41,5g</t>
+  </si>
+  <si>
+    <t>Bis Branco Caixa 16 Unid</t>
+  </si>
+  <si>
+    <t>Bis Original Caixa 16 Unid</t>
+  </si>
+  <si>
+    <t>Barra 98g Recheados Sonho de Valsa</t>
+  </si>
+  <si>
+    <t>Barra 98g Recheados Ouro Branco</t>
+  </si>
+  <si>
+    <t>Barra 90g Recheados Pistache</t>
+  </si>
+  <si>
+    <t>Barra 90g Recheados Charge</t>
+  </si>
+  <si>
+    <t>Barra 90g Recheados Negresco</t>
+  </si>
+  <si>
+    <t>Barra 90g Recheados Prestigio</t>
+  </si>
+  <si>
+    <t>Barra 80g cacau Brasil Ao Leite</t>
+  </si>
+  <si>
+    <t>Barra 80g Cacau Brasil Meio Amargo</t>
+  </si>
+  <si>
+    <t>Barra 80g Cacau Brasil Branco</t>
+  </si>
+  <si>
+    <t>Barra 145g Criando Laços Amaro</t>
+  </si>
+  <si>
+    <t>Barra 145g Criando Laços Diamante Negro</t>
+  </si>
+  <si>
+    <t>Barra 145g Criando Laços Laka</t>
+  </si>
+  <si>
+    <t>Barra 145g Criando Laços Shot</t>
+  </si>
+  <si>
+    <t>Barra 145g Criando Laços Chocolate ao Leite</t>
+  </si>
+  <si>
+    <t>Barra 145g Criando Laços Diamante Negro/Branco</t>
+  </si>
+  <si>
+    <t>Barra 85g Alpino</t>
+  </si>
+  <si>
+    <t>Barra 80g Suflair</t>
+  </si>
+  <si>
+    <t>Barra 80g Suflair Duo</t>
+  </si>
+  <si>
+    <t>Barra 80g Diplomata</t>
+  </si>
+  <si>
+    <t>Barra 80g Prestigio</t>
+  </si>
+  <si>
+    <t>Barra 80g Classic</t>
+  </si>
+  <si>
+    <t>Barra 80g Duo</t>
+  </si>
+  <si>
+    <t>Barra 80g Crunch</t>
+  </si>
+  <si>
+    <t>Barra 80g Meio Amargo</t>
+  </si>
+  <si>
+    <t>Barra 80g Galak</t>
+  </si>
+  <si>
+    <t>Barra 80g Amaro</t>
+  </si>
+  <si>
+    <t>Barra 80g Ao Leite</t>
+  </si>
+  <si>
+    <t>Barra 80g Shot</t>
+  </si>
+  <si>
+    <t>Barra 80g Diamante Negro</t>
+  </si>
+  <si>
+    <t>Barra 80g Laka</t>
+  </si>
+  <si>
+    <t>Barra 80g Laka Diamante Negro</t>
+  </si>
+  <si>
+    <t>Barra 80g Oreo</t>
+  </si>
+  <si>
+    <t>Passatempo 130g</t>
+  </si>
+  <si>
+    <t>Wafer Bauduco 140g Avelã</t>
+  </si>
+  <si>
+    <t>Wafer Bauduco 140g Triplo Chocolate</t>
+  </si>
+  <si>
+    <t>Wafer Bauduco 140g Chocolate</t>
+  </si>
+  <si>
+    <t>Wafer Bauduco 140g Morango</t>
+  </si>
+  <si>
+    <t>Toddy 370g Pote</t>
+  </si>
+  <si>
+    <t>Nescau 350g Pote</t>
+  </si>
+  <si>
+    <t>Cha Mate Leão 250g</t>
+  </si>
+  <si>
+    <t>Leite em Pó Ninho Lata 380g</t>
+  </si>
+  <si>
+    <t>Energetico 250Ml Red Bull</t>
+  </si>
+  <si>
+    <t>Caninha 51 965Ml</t>
+  </si>
+  <si>
+    <t>CLO</t>
   </si>
 </sst>
 </file>
@@ -2937,7 +3198,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="47">
+  <cellStyleXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -2985,18 +3246,27 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="47" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="47">
+  <cellStyles count="48">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -3026,6 +3296,7 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
     <cellStyle name="Moeda 2" xfId="43" xr:uid="{0C61731C-E737-4A54-9036-17B400FE6FAB}"/>
     <cellStyle name="Moeda 2 2" xfId="44" xr:uid="{AA48D0B9-D8DC-46BB-B1FE-5B9A19F2820B}"/>
     <cellStyle name="Moeda 3" xfId="45" xr:uid="{93DB1087-9037-47BC-A973-7F702C06F25D}"/>
@@ -3355,49 +3626,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}">
-  <dimension ref="A1:P343"/>
+  <dimension ref="A1:P382"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="74.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3405,31 +3677,31 @@
       <c r="A2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3">
         <v>15.8</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>15.8</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I2">
-        <v>3.3</v>
-      </c>
-      <c r="J2">
+      <c r="I2" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J2" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3437,31 +3709,31 @@
       <c r="A3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3">
         <v>15.8</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>15.8</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I3">
-        <v>3.3</v>
-      </c>
-      <c r="J3">
+      <c r="I3" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J3" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3469,31 +3741,31 @@
       <c r="A4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3">
         <v>15.8</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>15.8</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I4">
-        <v>3.3</v>
-      </c>
-      <c r="J4">
+      <c r="I4" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J4" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3501,31 +3773,31 @@
       <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="3">
         <v>15.8</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>15.8</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I5">
-        <v>3.3</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J5" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3533,31 +3805,31 @@
       <c r="A6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3">
         <v>15.8</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>15.8</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I6">
-        <v>3.3</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J6" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3565,31 +3837,31 @@
       <c r="A7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="3">
         <v>15.8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>15.8</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I7">
-        <v>3.3</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J7" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3597,31 +3869,31 @@
       <c r="A8" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="3">
         <v>15.8</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>15.8</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I8">
-        <v>3.3</v>
-      </c>
-      <c r="J8">
+      <c r="I8" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J8" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3629,31 +3901,31 @@
       <c r="A9" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="3">
         <v>15.8</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>15.8</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I9">
-        <v>3.3</v>
-      </c>
-      <c r="J9">
+      <c r="I9" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J9" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -3661,31 +3933,31 @@
       <c r="A10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="3">
         <v>15.8</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>15.8</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I10">
-        <v>3.3</v>
-      </c>
-      <c r="J10">
+      <c r="I10" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J10" s="2">
         <v>11.7</v>
       </c>
     </row>
@@ -8065,8 +8337,11 @@
       <c r="H160" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I160" s="1">
-        <v>12</v>
+      <c r="I160" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J160" s="1">
+        <v>34.56</v>
       </c>
       <c r="L160" s="1">
         <v>2.2000000000000002</v>
@@ -8419,7 +8694,7 @@
       <c r="N169" s="1">
         <v>2.4200000000000004</v>
       </c>
-      <c r="P169">
+      <c r="P169" s="2">
         <f>48.4/50</f>
         <v>0.96799999999999997</v>
       </c>
@@ -8980,6 +9255,9 @@
       <c r="I184" s="1" t="s">
         <v>428</v>
       </c>
+      <c r="J184" s="1">
+        <v>66.959999999999994</v>
+      </c>
       <c r="L184" s="1">
         <v>5.6539999999999999</v>
       </c>
@@ -9018,6 +9296,9 @@
       <c r="I185" s="1" t="s">
         <v>428</v>
       </c>
+      <c r="J185" s="1">
+        <v>66.959999999999994</v>
+      </c>
       <c r="L185" s="1">
         <v>5.6539999999999999</v>
       </c>
@@ -9056,6 +9337,9 @@
       <c r="I186" s="1" t="s">
         <v>428</v>
       </c>
+      <c r="J186" s="1">
+        <v>66.959999999999994</v>
+      </c>
       <c r="L186" s="1">
         <v>5.6539999999999999</v>
       </c>
@@ -9094,6 +9378,9 @@
       <c r="I187" s="1" t="s">
         <v>428</v>
       </c>
+      <c r="J187" s="1">
+        <v>66.959999999999994</v>
+      </c>
       <c r="L187" s="1">
         <v>5.6539999999999999</v>
       </c>
@@ -9133,8 +9420,7 @@
         <v>428</v>
       </c>
       <c r="J188" s="1">
-        <f>F189-J189</f>
-        <v>17.740000000000009</v>
+        <v>66.959999999999994</v>
       </c>
       <c r="L188" s="1">
         <v>5.6539999999999999</v>
@@ -9215,6 +9501,9 @@
       <c r="I190" s="1" t="s">
         <v>428</v>
       </c>
+      <c r="J190" s="1">
+        <v>66.959999999999994</v>
+      </c>
       <c r="L190" s="1">
         <v>5.6539999999999999</v>
       </c>
@@ -9265,11 +9554,11 @@
       <c r="N191" s="1">
         <v>118.80000000000001</v>
       </c>
-      <c r="O191">
+      <c r="O191" s="2">
         <f>78*1.08</f>
         <v>84.240000000000009</v>
       </c>
-      <c r="P191">
+      <c r="P191" s="2">
         <f>O191*1.5</f>
         <v>126.36000000000001</v>
       </c>
@@ -9302,7 +9591,7 @@
       <c r="I192" s="1">
         <v>23.06</v>
       </c>
-      <c r="J192">
+      <c r="J192" s="2">
         <v>57.24</v>
       </c>
       <c r="L192" s="1">
@@ -9378,10 +9667,12 @@
       <c r="H194" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I194" s="1">
-        <v>0</v>
-      </c>
-      <c r="J194" s="1"/>
+      <c r="I194" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>446</v>
+      </c>
       <c r="L194" s="1">
         <v>2.8160000000000003</v>
       </c>
@@ -12576,7 +12867,7 @@
       <c r="I304" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="J304">
+      <c r="J304" s="2">
         <v>39</v>
       </c>
     </row>
@@ -12602,11 +12893,14 @@
       <c r="G305" s="1">
         <v>20</v>
       </c>
-      <c r="H305" s="2" t="s">
+      <c r="H305" s="4" t="s">
         <v>174</v>
       </c>
       <c r="I305" s="1">
         <v>10.53</v>
+      </c>
+      <c r="J305" s="1">
+        <v>39</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
@@ -12631,11 +12925,14 @@
       <c r="G306" s="1">
         <v>20</v>
       </c>
-      <c r="H306" s="2" t="s">
+      <c r="H306" s="4" t="s">
         <v>174</v>
       </c>
       <c r="I306" s="1">
         <v>10.53</v>
+      </c>
+      <c r="J306" s="1">
+        <v>39</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
@@ -12660,11 +12957,14 @@
       <c r="G307" s="1">
         <v>20</v>
       </c>
-      <c r="H307" s="2" t="s">
+      <c r="H307" s="4" t="s">
         <v>174</v>
       </c>
       <c r="I307" s="1">
         <v>10.53</v>
+      </c>
+      <c r="J307" s="1">
+        <v>39</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
@@ -12674,7 +12974,7 @@
       <c r="B308" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C308" t="s">
+      <c r="C308" s="2" t="s">
         <v>437</v>
       </c>
       <c r="D308" s="1" t="s">
@@ -12689,13 +12989,13 @@
       <c r="G308" s="1">
         <v>30</v>
       </c>
-      <c r="H308" s="2" t="s">
+      <c r="H308" s="4" t="s">
         <v>174</v>
       </c>
       <c r="I308" s="1">
         <v>27.46</v>
       </c>
-      <c r="J308">
+      <c r="J308" s="2">
         <v>57.24</v>
       </c>
     </row>
@@ -12721,7 +13021,7 @@
       <c r="G309" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="H309" s="2" t="s">
+      <c r="H309" s="4" t="s">
         <v>174</v>
       </c>
       <c r="I309" s="1" t="s">
@@ -12753,7 +13053,7 @@
       <c r="G310" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="H310" s="2" t="s">
+      <c r="H310" s="4" t="s">
         <v>174</v>
       </c>
       <c r="I310" s="1" t="s">
@@ -12764,1063 +13064,1945 @@
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A311" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C311" s="1" t="s">
+      <c r="A311" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E311" s="5">
+        <v>14.363499999999998</v>
+      </c>
+      <c r="F311" s="6">
+        <v>14.363499999999998</v>
+      </c>
+      <c r="G311" s="7">
+        <v>1</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I311" s="1"/>
+      <c r="J311" s="1"/>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E311" s="3">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="F311" s="1">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="G311" s="1">
-        <v>1</v>
-      </c>
-      <c r="H311" s="2" t="s">
+      <c r="B312" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E312" s="5">
+        <v>14.823499999999999</v>
+      </c>
+      <c r="F312" s="6">
+        <v>14.823499999999999</v>
+      </c>
+      <c r="G312" s="7">
+        <v>1</v>
+      </c>
+      <c r="H312" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I311" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="J311" s="1">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A312" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C312" s="1" t="s">
+      <c r="I312" s="1"/>
+      <c r="J312" s="1"/>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D312" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E312" s="3">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="F312" s="1">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="G312" s="1">
-        <v>1</v>
-      </c>
-      <c r="H312" s="2" t="s">
+      <c r="B313" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E313" s="5">
+        <v>14.938499999999999</v>
+      </c>
+      <c r="F313" s="6">
+        <v>14.938499999999999</v>
+      </c>
+      <c r="G313" s="7">
+        <v>1</v>
+      </c>
+      <c r="H313" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I312" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="J312" s="1">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A313" s="1" t="s">
+      <c r="I313" s="1"/>
+      <c r="J313" s="1"/>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C313" s="1" t="s">
+      <c r="B314" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E314" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F314" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G314" s="7">
+        <v>24</v>
+      </c>
+      <c r="H314" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I314" s="1"/>
+      <c r="J314" s="1"/>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D313" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E313" s="3">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="F313" s="1">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="G313" s="1">
-        <v>1</v>
-      </c>
-      <c r="H313" s="2" t="s">
+      <c r="B315" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E315" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F315" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G315" s="7">
+        <v>24</v>
+      </c>
+      <c r="H315" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I313" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="J313" s="1">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A314" s="1" t="s">
+      <c r="I315" s="1"/>
+      <c r="J315" s="1"/>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A316" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C314" s="1" t="s">
+      <c r="B316" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E316" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F316" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G316" s="7">
+        <v>24</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I316" s="1"/>
+      <c r="J316" s="1"/>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D314" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E314" s="3">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="F314" s="1">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="G314" s="1">
-        <v>1</v>
-      </c>
-      <c r="H314" s="2" t="s">
+      <c r="B317" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E317" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F317" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G317" s="7">
+        <v>24</v>
+      </c>
+      <c r="H317" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I314" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="J314" s="1">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A315" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C315" s="1" t="s">
+      <c r="I317" s="1"/>
+      <c r="J317" s="1"/>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A318" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D315" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E315" s="3">
-        <v>4.49</v>
-      </c>
-      <c r="F315" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="G315" s="1">
-        <v>1</v>
-      </c>
-      <c r="H315" s="2" t="s">
+      <c r="B318" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E318" s="5">
+        <v>60.374999999999993</v>
+      </c>
+      <c r="F318" s="6">
+        <v>60.374999999999993</v>
+      </c>
+      <c r="G318" s="7">
+        <v>1</v>
+      </c>
+      <c r="H318" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I315" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="J315" s="1">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A316" s="1" t="s">
+      <c r="I318" s="1"/>
+      <c r="J318" s="1"/>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A319" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C316" s="1" t="s">
+      <c r="B319" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E319" s="5">
+        <v>1.5295000000000001</v>
+      </c>
+      <c r="F319" s="6">
+        <v>45.885000000000005</v>
+      </c>
+      <c r="G319" s="7">
+        <v>30</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I319" s="1"/>
+      <c r="J319" s="1"/>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A320" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D316" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E316" s="3">
-        <v>4.49</v>
-      </c>
-      <c r="F316" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="G316" s="1">
-        <v>1</v>
-      </c>
-      <c r="H316" s="2" t="s">
+      <c r="B320" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E320" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F320" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G320" s="7">
+        <v>16</v>
+      </c>
+      <c r="H320" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I316" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="J316" s="1">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A317" s="1" t="s">
+      <c r="I320" s="1"/>
+      <c r="J320" s="1"/>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C317" s="1" t="s">
+      <c r="B321" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E321" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F321" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G321" s="7">
+        <v>16</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I321" s="1"/>
+      <c r="J321" s="1"/>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D317" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E317" s="3">
-        <v>4.49</v>
-      </c>
-      <c r="F317" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="G317" s="1">
-        <v>1</v>
-      </c>
-      <c r="H317" s="2" t="s">
+      <c r="B322" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E322" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F322" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G322" s="7">
+        <v>16</v>
+      </c>
+      <c r="H322" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I317" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="J317" s="1">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A318" s="1" t="s">
+      <c r="I322" s="1"/>
+      <c r="J322" s="1"/>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C318" s="1" t="s">
+      <c r="B323" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E323" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F323" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G323" s="7">
+        <v>16</v>
+      </c>
+      <c r="H323" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I323" s="1"/>
+      <c r="J323" s="1"/>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D318" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E318" s="3">
-        <v>2.99</v>
-      </c>
-      <c r="F318" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="G318" s="1">
-        <v>1</v>
-      </c>
-      <c r="H318" s="2" t="s">
+      <c r="B324" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E324" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F324" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G324" s="7">
+        <v>16</v>
+      </c>
+      <c r="H324" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I318" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="J318" s="1">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A319" s="1" t="s">
+      <c r="I324" s="1"/>
+      <c r="J324" s="1"/>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A325" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C319" s="1" t="s">
+      <c r="B325" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E325" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F325" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G325" s="7">
+        <v>16</v>
+      </c>
+      <c r="H325" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I325" s="1"/>
+      <c r="J325" s="1"/>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A326" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D319" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E319" s="3">
-        <v>2.99</v>
-      </c>
-      <c r="F319" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="G319" s="1">
-        <v>1</v>
-      </c>
-      <c r="H319" s="2" t="s">
+      <c r="B326" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E326" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F326" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G326" s="7">
+        <v>16</v>
+      </c>
+      <c r="H326" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I319" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="J319" s="1">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A320" s="1" t="s">
+      <c r="I326" s="1"/>
+      <c r="J326" s="1"/>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A327" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C320" s="1" t="s">
+      <c r="B327" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E327" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F327" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G327" s="7">
+        <v>16</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I327" s="1"/>
+      <c r="J327" s="1"/>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A328" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D320" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E320" s="3">
-        <v>2.99</v>
-      </c>
-      <c r="F320" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="G320" s="1">
-        <v>1</v>
-      </c>
-      <c r="H320" s="2" t="s">
+      <c r="B328" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E328" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F328" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G328" s="7">
+        <v>16</v>
+      </c>
+      <c r="H328" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I320" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="J320" s="1">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A321" s="1" t="s">
+      <c r="I328" s="1"/>
+      <c r="J328" s="1"/>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C321" s="1" t="s">
+      <c r="B329" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E329" s="5">
+        <v>2.4494999999999996</v>
+      </c>
+      <c r="F329" s="6">
+        <v>39.191999999999993</v>
+      </c>
+      <c r="G329" s="7">
+        <v>16</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I329" s="1"/>
+      <c r="J329" s="1"/>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D321" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E321" s="3">
-        <v>2.99</v>
-      </c>
-      <c r="F321" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="G321" s="1">
-        <v>1</v>
-      </c>
-      <c r="H321" s="2" t="s">
+      <c r="B330" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E330" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F330" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G330" s="7">
+        <v>24</v>
+      </c>
+      <c r="H330" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I321" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="J321" s="1">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A322" s="1" t="s">
+      <c r="I330" s="1"/>
+      <c r="J330" s="1"/>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A331" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C322" s="1" t="s">
+      <c r="B331" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E331" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F331" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G331" s="7">
+        <v>24</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I331" s="1"/>
+      <c r="J331" s="1"/>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A332" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D322" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E322" s="3">
-        <v>3.36</v>
-      </c>
-      <c r="F322" s="1" t="s">
+      <c r="B332" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E332" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F332" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G332" s="7">
+        <v>24</v>
+      </c>
+      <c r="H332" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I332" s="1"/>
+      <c r="J332" s="1"/>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="G322" s="1">
-        <v>1</v>
-      </c>
-      <c r="H322" s="2" t="s">
+      <c r="B333" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E333" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F333" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G333" s="7">
+        <v>24</v>
+      </c>
+      <c r="H333" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I322" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="J322" s="1">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A323" s="1" t="s">
+      <c r="I333" s="1"/>
+      <c r="J333" s="1"/>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A334" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C323" s="1" t="s">
+      <c r="B334" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E334" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F334" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G334" s="7">
+        <v>24</v>
+      </c>
+      <c r="H334" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I334" s="1"/>
+      <c r="J334" s="1"/>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A335" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D323" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E323" s="3">
-        <v>3.36</v>
-      </c>
-      <c r="F323" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="G323" s="1">
-        <v>1</v>
-      </c>
-      <c r="H323" s="2" t="s">
+      <c r="B335" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E335" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F335" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G335" s="7">
+        <v>24</v>
+      </c>
+      <c r="H335" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I323" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="J323" s="1">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A324" s="1" t="s">
+      <c r="I335" s="1"/>
+      <c r="J335" s="1"/>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A336" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C324" s="1" t="s">
+      <c r="B336" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E336" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F336" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G336" s="7">
+        <v>24</v>
+      </c>
+      <c r="H336" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I336" s="1"/>
+      <c r="J336" s="1"/>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A337" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D324" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E324" s="3">
-        <v>3.36</v>
-      </c>
-      <c r="F324" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="G324" s="1">
-        <v>1</v>
-      </c>
-      <c r="H324" s="2" t="s">
+      <c r="B337" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E337" s="5">
+        <v>3.6684999999999999</v>
+      </c>
+      <c r="F337" s="6">
+        <v>88.043999999999997</v>
+      </c>
+      <c r="G337" s="7">
+        <v>24</v>
+      </c>
+      <c r="H337" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I324" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="J324" s="1">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A325" s="1" t="s">
+      <c r="I337" s="1"/>
+      <c r="J337" s="1"/>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C325" s="1" t="s">
+      <c r="B338" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E338" s="5">
+        <v>6.3134999999999994</v>
+      </c>
+      <c r="F338" s="6">
+        <v>6.3134999999999994</v>
+      </c>
+      <c r="G338" s="7">
+        <v>1</v>
+      </c>
+      <c r="H338" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I338" s="1"/>
+      <c r="J338" s="1"/>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D325" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E325" s="3">
-        <v>3.36</v>
-      </c>
-      <c r="F325" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="G325" s="1">
-        <v>1</v>
-      </c>
-      <c r="H325" s="2" t="s">
+      <c r="B339" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E339" s="5">
+        <v>6.3134999999999994</v>
+      </c>
+      <c r="F339" s="6">
+        <v>6.3134999999999994</v>
+      </c>
+      <c r="G339" s="7">
+        <v>1</v>
+      </c>
+      <c r="H339" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I325" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="J325" s="1">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A326" s="1" t="s">
+      <c r="I339" s="1"/>
+      <c r="J339" s="1"/>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A340" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C326" s="1" t="s">
+      <c r="B340" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E340" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F340" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G340" s="7">
+        <v>17</v>
+      </c>
+      <c r="H340" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I340" s="1"/>
+      <c r="J340" s="1"/>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A341" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="D326" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E326" s="3">
-        <v>2.74</v>
-      </c>
-      <c r="F326">
-        <v>2.74</v>
-      </c>
-      <c r="G326" s="1">
-        <v>1</v>
-      </c>
-      <c r="H326" s="2" t="s">
+      <c r="B341" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E341" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F341" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G341" s="7">
+        <v>17</v>
+      </c>
+      <c r="H341" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I326" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="J326" s="1">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
+      <c r="I341" s="1"/>
+      <c r="J341" s="1"/>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A342" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C327" s="1" t="s">
+      <c r="B342" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E342" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F342" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G342" s="7">
+        <v>16</v>
+      </c>
+      <c r="H342" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I342" s="1"/>
+      <c r="J342" s="1"/>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A343" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D327" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E327" s="3">
-        <v>2.74</v>
-      </c>
-      <c r="F327">
-        <v>2.74</v>
-      </c>
-      <c r="G327" s="1">
-        <v>1</v>
-      </c>
-      <c r="H327" s="2" t="s">
+      <c r="B343" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E343" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F343" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G343" s="7">
+        <v>16</v>
+      </c>
+      <c r="H343" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I327" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="J327" s="1">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A328" s="1" t="s">
+      <c r="I343" s="1"/>
+      <c r="J343" s="1"/>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C328" s="1" t="s">
+      <c r="B344" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E344" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F344" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G344" s="7">
+        <v>16</v>
+      </c>
+      <c r="H344" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D328" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E328" s="3">
-        <v>2.74</v>
-      </c>
-      <c r="F328">
-        <v>2.74</v>
-      </c>
-      <c r="G328" s="1">
-        <v>1</v>
-      </c>
-      <c r="H328" s="2" t="s">
+      <c r="B345" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E345" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F345" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G345" s="7">
+        <v>16</v>
+      </c>
+      <c r="H345" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I328" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="J328" s="1">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A329" s="1" t="s">
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C329" s="1" t="s">
+      <c r="B346" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E346" s="5">
+        <v>7.4634999999999998</v>
+      </c>
+      <c r="F346" s="6">
+        <v>119.416</v>
+      </c>
+      <c r="G346" s="7">
+        <v>16</v>
+      </c>
+      <c r="H346" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D329" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E329" s="3">
-        <v>1.86</v>
-      </c>
-      <c r="F329">
-        <v>1.86</v>
-      </c>
-      <c r="G329" s="1">
-        <v>1</v>
-      </c>
-      <c r="H329" s="2" t="s">
+      <c r="B347" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E347" s="5">
+        <v>7.4634999999999998</v>
+      </c>
+      <c r="F347" s="6">
+        <v>119.416</v>
+      </c>
+      <c r="G347" s="7">
+        <v>16</v>
+      </c>
+      <c r="H347" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I329" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="J329" s="1">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A330" s="1" t="s">
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A348" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C330" s="1" t="s">
+      <c r="B348" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E348" s="5">
+        <v>7.4634999999999998</v>
+      </c>
+      <c r="F348" s="6">
+        <v>119.416</v>
+      </c>
+      <c r="G348" s="7">
+        <v>16</v>
+      </c>
+      <c r="H348" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A349" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D330" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E330" s="3">
-        <v>1.86</v>
-      </c>
-      <c r="F330">
-        <v>1.86</v>
-      </c>
-      <c r="G330" s="1">
-        <v>1</v>
-      </c>
-      <c r="H330" s="2" t="s">
+      <c r="B349" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E349" s="5">
+        <v>13.558499999999997</v>
+      </c>
+      <c r="F349" s="6">
+        <v>230.49449999999996</v>
+      </c>
+      <c r="G349" s="7">
+        <v>17</v>
+      </c>
+      <c r="H349" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I330" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="J330" s="1">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A331" s="1" t="s">
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C331" s="1" t="s">
+      <c r="B350" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E350" s="5">
+        <v>13.558499999999997</v>
+      </c>
+      <c r="F350" s="6">
+        <v>230.49449999999996</v>
+      </c>
+      <c r="G350" s="7">
+        <v>17</v>
+      </c>
+      <c r="H350" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D331" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E331" s="3">
-        <v>1.86</v>
-      </c>
-      <c r="F331">
-        <v>1.86</v>
-      </c>
-      <c r="G331" s="1">
-        <v>1</v>
-      </c>
-      <c r="H331" s="2" t="s">
+      <c r="B351" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E351" s="5">
+        <v>13.558499999999997</v>
+      </c>
+      <c r="F351" s="6">
+        <v>230.49449999999996</v>
+      </c>
+      <c r="G351" s="7">
+        <v>17</v>
+      </c>
+      <c r="H351" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I331" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="J331" s="1">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A332" s="1" t="s">
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A352" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C332" s="1" t="s">
+      <c r="B352" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E352" s="5">
+        <v>13.558499999999997</v>
+      </c>
+      <c r="F352" s="6">
+        <v>230.49449999999996</v>
+      </c>
+      <c r="G352" s="7">
+        <v>17</v>
+      </c>
+      <c r="H352" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="D332" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E332" s="3">
-        <v>4.97</v>
-      </c>
-      <c r="F332">
-        <v>4.97</v>
-      </c>
-      <c r="G332" s="1">
-        <v>1</v>
-      </c>
-      <c r="H332" s="2" t="s">
+      <c r="B353" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E353" s="5">
+        <v>13.558499999999997</v>
+      </c>
+      <c r="F353" s="6">
+        <v>230.49449999999996</v>
+      </c>
+      <c r="G353" s="7">
+        <v>17</v>
+      </c>
+      <c r="H353" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I332" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="J332" s="1">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C333" s="1" t="s">
+      <c r="B354" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E354" s="5">
+        <v>13.558499999999997</v>
+      </c>
+      <c r="F354" s="6">
+        <v>230.49449999999996</v>
+      </c>
+      <c r="G354" s="7">
+        <v>17</v>
+      </c>
+      <c r="H354" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D333" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E333" s="3">
-        <v>4.97</v>
-      </c>
-      <c r="F333">
-        <v>4.97</v>
-      </c>
-      <c r="G333" s="1">
-        <v>1</v>
-      </c>
-      <c r="H333" s="2" t="s">
+      <c r="B355" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E355" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F355" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G355" s="7">
+        <v>16</v>
+      </c>
+      <c r="H355" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I333" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="J333" s="1">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C334" s="1" t="s">
+      <c r="B356" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E356" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F356" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G356" s="7">
+        <v>16</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D334" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E334" s="3">
-        <v>4.97</v>
-      </c>
-      <c r="F334">
-        <v>4.97</v>
-      </c>
-      <c r="G334" s="1">
-        <v>1</v>
-      </c>
-      <c r="H334" s="2" t="s">
+      <c r="B357" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E357" s="5">
+        <v>8.8435000000000006</v>
+      </c>
+      <c r="F357" s="6">
+        <v>141.49600000000001</v>
+      </c>
+      <c r="G357" s="7">
+        <v>16</v>
+      </c>
+      <c r="H357" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I334" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="J334" s="1">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C335" s="1" t="s">
+      <c r="B358" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E358" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F358" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G358" s="7">
+        <v>16</v>
+      </c>
+      <c r="H358" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D335" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E335" s="3">
-        <v>1.98</v>
-      </c>
-      <c r="F335">
-        <v>1.98</v>
-      </c>
-      <c r="G335" s="1">
-        <v>1</v>
-      </c>
-      <c r="H335" s="2" t="s">
+      <c r="B359" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E359" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F359" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G359" s="7">
+        <v>16</v>
+      </c>
+      <c r="H359" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I335" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="J335" s="1">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C336" s="1" t="s">
+      <c r="B360" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E360" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F360" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G360" s="7">
+        <v>16</v>
+      </c>
+      <c r="H360" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D336" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E336" s="3">
-        <v>1.98</v>
-      </c>
-      <c r="F336">
-        <v>1.98</v>
-      </c>
-      <c r="G336" s="1">
-        <v>1</v>
-      </c>
-      <c r="H336" s="2" t="s">
+      <c r="B361" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E361" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F361" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G361" s="7">
+        <v>16</v>
+      </c>
+      <c r="H361" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I336" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="J336" s="1">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C337" s="1" t="s">
+      <c r="B362" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E362" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F362" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G362" s="7">
+        <v>16</v>
+      </c>
+      <c r="H362" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D337" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E337" s="3">
-        <v>1.98</v>
-      </c>
-      <c r="F337">
-        <v>1.98</v>
-      </c>
-      <c r="G337" s="1">
-        <v>1</v>
-      </c>
-      <c r="H337" s="2" t="s">
+      <c r="B363" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E363" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F363" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G363" s="7">
+        <v>16</v>
+      </c>
+      <c r="H363" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I337" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="J337" s="1">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C338" s="1" t="s">
+      <c r="B364" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E364" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F364" s="6">
+        <v>134.136</v>
+      </c>
+      <c r="G364" s="7">
+        <v>16</v>
+      </c>
+      <c r="H364" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D338" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E338" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="F338">
-        <v>3.1</v>
-      </c>
-      <c r="G338" s="1">
-        <v>1</v>
-      </c>
-      <c r="H338" s="2" t="s">
+      <c r="B365" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E365" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F365" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G365" s="7">
+        <v>17</v>
+      </c>
+      <c r="H365" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I338" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="J338" s="1">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A339" s="1" t="s">
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C339" s="1" t="s">
+      <c r="B366" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E366" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F366" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G366" s="7">
+        <v>17</v>
+      </c>
+      <c r="H366" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D339" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E339" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="F339">
-        <v>30.6</v>
-      </c>
-      <c r="G339" s="1">
-        <v>36</v>
-      </c>
-      <c r="H339" s="2" t="s">
+      <c r="B367" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E367" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F367" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G367" s="7">
+        <v>17</v>
+      </c>
+      <c r="H367" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I339" s="1">
-        <v>6.12</v>
-      </c>
-      <c r="J339" s="1">
-        <v>24.48</v>
-      </c>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A340" s="1" t="s">
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C340" s="1" t="s">
+      <c r="B368" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E368" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F368" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G368" s="7">
+        <v>17</v>
+      </c>
+      <c r="H368" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D340" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E340" s="3">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="F340">
-        <v>28.75</v>
-      </c>
-      <c r="G340" s="1">
-        <v>50</v>
-      </c>
-      <c r="H340" s="2" t="s">
+      <c r="B369" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E369" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F369" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G369" s="7">
+        <v>17</v>
+      </c>
+      <c r="H369" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I340" s="1">
-        <v>5.75</v>
-      </c>
-      <c r="J340" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A341" s="1" t="s">
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C341" s="1" t="s">
+      <c r="B370" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E370" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F370" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G370" s="7">
+        <v>17</v>
+      </c>
+      <c r="H370" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D341" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E341" s="3">
-        <v>2.48</v>
-      </c>
-      <c r="F341">
-        <v>50.15</v>
-      </c>
-      <c r="G341" s="1">
-        <v>21</v>
-      </c>
-      <c r="H341" s="2" t="s">
+      <c r="B371" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E371" s="5">
+        <v>8.3834999999999997</v>
+      </c>
+      <c r="F371" s="6">
+        <v>142.51949999999999</v>
+      </c>
+      <c r="G371" s="7">
+        <v>17</v>
+      </c>
+      <c r="H371" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I341" s="1">
-        <v>8.35</v>
-      </c>
-      <c r="J341" s="1">
-        <v>41.79</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A342" s="1" t="s">
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C342" s="1" t="s">
+      <c r="B372" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E372" s="5">
+        <v>2.4034999999999997</v>
+      </c>
+      <c r="F372" s="6">
+        <v>38.455999999999996</v>
+      </c>
+      <c r="G372" s="7">
+        <v>16</v>
+      </c>
+      <c r="H372" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D342" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E342" s="3">
-        <v>2.48</v>
-      </c>
-      <c r="F342">
-        <v>50.15</v>
-      </c>
-      <c r="G342" s="1">
-        <v>21</v>
-      </c>
-      <c r="H342" s="2" t="s">
+      <c r="B373" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E373" s="5">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="F373" s="6">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="G373" s="7">
+        <v>1</v>
+      </c>
+      <c r="H373" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I342" s="1">
-        <v>8.35</v>
-      </c>
-      <c r="J342" s="1">
-        <v>41.79</v>
-      </c>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A343" s="1" t="s">
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C343" s="1" t="s">
+      <c r="B374" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E374" s="5">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="F374" s="6">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="G374" s="7">
+        <v>1</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D343" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E343" s="3">
-        <v>2.48</v>
-      </c>
-      <c r="F343">
-        <v>50.15</v>
-      </c>
-      <c r="G343" s="1">
-        <v>21</v>
-      </c>
-      <c r="H343" s="2" t="s">
+      <c r="B375" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E375" s="5">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="F375" s="6">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="G375" s="7">
+        <v>1</v>
+      </c>
+      <c r="H375" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I343" s="1">
-        <v>8.35</v>
-      </c>
-      <c r="J343" s="1">
-        <v>41.79</v>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E376" s="5">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="F376" s="6">
+        <v>3.4384999999999999</v>
+      </c>
+      <c r="G376" s="7">
+        <v>1</v>
+      </c>
+      <c r="H376" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A377" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E377" s="5">
+        <v>9.1884999999999994</v>
+      </c>
+      <c r="F377" s="6">
+        <v>9.1884999999999994</v>
+      </c>
+      <c r="G377" s="7">
+        <v>1</v>
+      </c>
+      <c r="H377" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A378" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E378" s="5">
+        <v>9.5334999999999983</v>
+      </c>
+      <c r="F378" s="6">
+        <v>9.5334999999999983</v>
+      </c>
+      <c r="G378" s="7">
+        <v>1</v>
+      </c>
+      <c r="H378" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A379" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E379" s="5">
+        <v>8.0384999999999991</v>
+      </c>
+      <c r="F379" s="6">
+        <v>8.0384999999999991</v>
+      </c>
+      <c r="G379" s="7">
+        <v>1</v>
+      </c>
+      <c r="H379" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A380" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E380" s="5">
+        <v>20.688499999999998</v>
+      </c>
+      <c r="F380" s="6">
+        <v>20.688499999999998</v>
+      </c>
+      <c r="G380" s="7">
+        <v>1</v>
+      </c>
+      <c r="H380" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E381" s="5">
+        <v>8.2684999999999995</v>
+      </c>
+      <c r="F381" s="6">
+        <v>8.2684999999999995</v>
+      </c>
+      <c r="G381" s="7">
+        <v>1</v>
+      </c>
+      <c r="H381" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E382" s="5">
+        <v>12.638499999999999</v>
+      </c>
+      <c r="F382" s="6">
+        <v>12.638499999999999</v>
+      </c>
+      <c r="G382" s="7">
+        <v>1</v>
+      </c>
+      <c r="H382" s="4" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J305" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
+  <autoFilter ref="A1:J343" xr:uid="{298922D0-7C3D-422A-8C37-23B9AC78773C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/base_de_produtos.xlsx
+++ b/base_de_produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bsbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54B5873-E66D-48E6-AA3D-210CB5938E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338B68C6-05B4-4A6E-BCE0-63FE46483BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC546E70-3D85-46DB-8D58-E44D4DB9FE0E}"/>
   </bookViews>
@@ -14732,10 +14732,10 @@
         <v>2.4034999999999997</v>
       </c>
       <c r="F372" s="6">
-        <v>38.455999999999996</v>
+        <v>2.4</v>
       </c>
       <c r="G372" s="7">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H372" s="4" t="s">
         <v>174</v>
